--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1393594D-490F-4A1C-966C-F76E41CF2D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1E5AC3-42EB-4EC7-93A2-0E3B887233DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -31621,7 +31621,7 @@
         <v>1590</v>
       </c>
       <c r="B36" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="52" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1E5AC3-42EB-4EC7-93A2-0E3B887233DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B0D045-267C-4CF4-953D-A7D35F82092E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6549,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="48">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="48">
         <v>45</v>
@@ -31718,7 +31718,7 @@
         <v>1468</v>
       </c>
       <c r="B44" s="52">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="C44" s="52" t="s">
         <v>36</v>
@@ -31821,7 +31821,7 @@
         <v>1608</v>
       </c>
       <c r="B52" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="52" t="s">
         <v>36</v>
@@ -31961,7 +31961,7 @@
         <v>1683</v>
       </c>
       <c r="B62" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="52" t="s">
         <v>36</v>
@@ -31975,7 +31975,7 @@
         <v>1692</v>
       </c>
       <c r="B63" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="52" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B0D045-267C-4CF4-953D-A7D35F82092E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4525FE-594C-43D4-BEAA-DFABF4110976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7567" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7606" uniqueCount="1776">
   <si>
     <t>NAME</t>
   </si>
@@ -5464,6 +5464,54 @@
   </si>
   <si>
     <t>gold,403#gem,153</t>
+  </si>
+  <si>
+    <t>DMG_TYPE</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>mag</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>FIRE_RES</t>
+  </si>
+  <si>
+    <t>earth</t>
+  </si>
+  <si>
+    <t>WATER_RES</t>
+  </si>
+  <si>
+    <t>EARTH_RES</t>
+  </si>
+  <si>
+    <t>LIGHT_RES</t>
+  </si>
+  <si>
+    <t>DARK_RES</t>
+  </si>
+  <si>
+    <t>skeleton</t>
+  </si>
+  <si>
+    <t>skeleton_archer</t>
+  </si>
+  <si>
+    <t>loot_skeleton</t>
+  </si>
+  <si>
+    <t>loot_skeleton_archer</t>
   </si>
 </sst>
 </file>
@@ -6078,6 +6126,7 @@
     <col min="33" max="33" width="15.54296875" customWidth="1"/>
     <col min="34" max="34" width="10.36328125" customWidth="1"/>
     <col min="35" max="35" width="9.90625" customWidth="1"/>
+    <col min="36" max="36" width="20.26953125" customWidth="1"/>
     <col min="37" max="37" width="7.81640625" customWidth="1"/>
     <col min="38" max="38" width="8.1796875" customWidth="1"/>
     <col min="39" max="39" width="7.90625" customWidth="1"/>
@@ -6531,7 +6580,7 @@
     </row>
     <row r="4" spans="1:48" ht="12.5">
       <c r="A4" s="47" t="s">
-        <v>1407</v>
+        <v>1772</v>
       </c>
       <c r="B4" s="48">
         <v>1</v>
@@ -6549,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="48">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H4" s="48">
         <v>45</v>
@@ -6636,7 +6685,7 @@
         <v>3</v>
       </c>
       <c r="AJ4" s="46" t="s">
-        <v>1628</v>
+        <v>1774</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -6677,7 +6726,7 @@
     </row>
     <row r="5" spans="1:48" ht="12.5">
       <c r="A5" s="47" t="s">
-        <v>1408</v>
+        <v>1773</v>
       </c>
       <c r="B5" s="48">
         <v>1</v>
@@ -6695,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="48">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H5" s="48">
         <v>45</v>
@@ -6782,7 +6831,7 @@
         <v>3</v>
       </c>
       <c r="AJ5" s="46" t="s">
-        <v>1511</v>
+        <v>1775</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -44703,30 +44752,37 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:BF34"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" customWidth="1"/>
+    <col min="3" max="3" width="7.54296875" customWidth="1"/>
     <col min="4" max="4" width="8.6328125" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="5.26953125" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" customWidth="1"/>
-    <col min="9" max="9" width="17.90625" customWidth="1"/>
-    <col min="10" max="13" width="15.08984375" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="7.6328125" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" customWidth="1"/>
+    <col min="13" max="13" width="7.6328125" customWidth="1"/>
     <col min="14" max="14" width="9.7265625" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="17" width="11" customWidth="1"/>
+    <col min="15" max="15" width="7.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.90625" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="9.1796875" customWidth="1"/>
     <col min="19" max="22" width="7.90625" customWidth="1"/>
-    <col min="23" max="26" width="9.36328125" customWidth="1"/>
-    <col min="27" max="27" width="15.1796875" customWidth="1"/>
+    <col min="23" max="23" width="9.36328125" customWidth="1"/>
+    <col min="24" max="24" width="6.54296875" customWidth="1"/>
+    <col min="25" max="25" width="6.453125" customWidth="1"/>
+    <col min="26" max="26" width="9.36328125" customWidth="1"/>
+    <col min="27" max="27" width="10.26953125" customWidth="1"/>
     <col min="28" max="28" width="7.1796875" customWidth="1"/>
-    <col min="29" max="29" width="14.08984375" customWidth="1"/>
+    <col min="29" max="29" width="7.26953125" customWidth="1"/>
     <col min="30" max="30" width="13.81640625" customWidth="1"/>
-    <col min="31" max="31" width="11.81640625" customWidth="1"/>
+    <col min="31" max="31" width="9.6328125" customWidth="1"/>
     <col min="32" max="32" width="8.08984375" customWidth="1"/>
     <col min="33" max="33" width="7.26953125" customWidth="1"/>
     <col min="34" max="34" width="10.90625" customWidth="1"/>
@@ -44735,18 +44791,20 @@
     <col min="37" max="37" width="7.1796875" customWidth="1"/>
     <col min="38" max="38" width="9.54296875" customWidth="1"/>
     <col min="39" max="39" width="9.36328125" customWidth="1"/>
-    <col min="40" max="40" width="11.453125" customWidth="1"/>
-    <col min="41" max="41" width="13.453125" customWidth="1"/>
+    <col min="40" max="40" width="7.90625" customWidth="1"/>
+    <col min="41" max="41" width="6.7265625" customWidth="1"/>
     <col min="42" max="42" width="6.453125" customWidth="1"/>
-    <col min="43" max="43" width="7.6328125" customWidth="1"/>
-    <col min="44" max="44" width="6.6328125" customWidth="1"/>
-    <col min="45" max="45" width="7" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="5.90625" customWidth="1"/>
+    <col min="45" max="45" width="6.26953125" customWidth="1"/>
     <col min="46" max="46" width="7.81640625" customWidth="1"/>
     <col min="48" max="48" width="7" customWidth="1"/>
     <col min="49" max="51" width="7.08984375" customWidth="1"/>
+    <col min="53" max="53" width="8.36328125" customWidth="1"/>
+    <col min="54" max="58" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="13">
+    <row r="1" spans="1:58" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -44903,8 +44961,26 @@
       <c r="AZ1" s="43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:52">
+      <c r="BA1" s="43" t="s">
+        <v>1760</v>
+      </c>
+      <c r="BB1" s="43" t="s">
+        <v>1766</v>
+      </c>
+      <c r="BC1" s="43" t="s">
+        <v>1768</v>
+      </c>
+      <c r="BD1" s="43" t="s">
+        <v>1769</v>
+      </c>
+      <c r="BE1" s="43" t="s">
+        <v>1770</v>
+      </c>
+      <c r="BF1" s="43" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
@@ -45061,8 +45137,26 @@
       <c r="AZ2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:52">
+      <c r="BA2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
       <c r="A3" s="44" t="s">
         <v>42</v>
       </c>
@@ -45219,8 +45313,26 @@
       <c r="AZ3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:52">
+      <c r="BA3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58">
       <c r="A4" s="44" t="s">
         <v>1371</v>
       </c>
@@ -45377,8 +45489,26 @@
       <c r="AZ4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:52">
+      <c r="BA4" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58">
       <c r="A5" s="44" t="s">
         <v>1372</v>
       </c>
@@ -45535,8 +45665,26 @@
       <c r="AZ5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:52">
+      <c r="BA5" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
       <c r="A6" s="44" t="s">
         <v>1469</v>
       </c>
@@ -45693,8 +45841,26 @@
       <c r="AZ6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:52">
+      <c r="BA6" t="s">
+        <v>1767</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58">
       <c r="A7" s="44" t="s">
         <v>1483</v>
       </c>
@@ -45851,8 +46017,26 @@
       <c r="AZ7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:52">
+      <c r="BA7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:58">
       <c r="A8" s="44" t="s">
         <v>1430</v>
       </c>
@@ -46009,8 +46193,26 @@
       <c r="AZ8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:52">
+      <c r="BA8" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:58">
       <c r="A9" s="44" t="s">
         <v>1433</v>
       </c>
@@ -46167,8 +46369,26 @@
       <c r="AZ9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:52">
+      <c r="BA9" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58">
       <c r="A10" s="44" t="s">
         <v>1447</v>
       </c>
@@ -46325,8 +46545,26 @@
       <c r="AZ10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:52">
+      <c r="BA10" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
       <c r="A11" s="44" t="s">
         <v>1524</v>
       </c>
@@ -46483,8 +46721,26 @@
       <c r="AZ11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:52">
+      <c r="BA11" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
       <c r="A12" s="44" t="s">
         <v>1448</v>
       </c>
@@ -46641,8 +46897,26 @@
       <c r="AZ12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:52">
+      <c r="BA12" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
       <c r="A13" s="44" t="s">
         <v>1449</v>
       </c>
@@ -46799,8 +47073,26 @@
       <c r="AZ13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:52">
+      <c r="BA13" t="s">
+        <v>1767</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
       <c r="A14" s="44" t="s">
         <v>1485</v>
       </c>
@@ -46957,8 +47249,26 @@
       <c r="AZ14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:52">
+      <c r="BA14" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58">
       <c r="A15" s="44" t="s">
         <v>1489</v>
       </c>
@@ -47115,8 +47425,26 @@
       <c r="AZ15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:52">
+      <c r="BA15" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
       <c r="A16" s="44" t="s">
         <v>1490</v>
       </c>
@@ -47273,8 +47601,26 @@
       <c r="AZ16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:52">
+      <c r="BA16" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
       <c r="A17" s="44" t="s">
         <v>1494</v>
       </c>
@@ -47431,8 +47777,26 @@
       <c r="AZ17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:52">
+      <c r="BA17" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
       <c r="A18" s="44" t="s">
         <v>1501</v>
       </c>
@@ -47589,8 +47953,26 @@
       <c r="AZ18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:52">
+      <c r="BA18" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
       <c r="A19" s="44" t="s">
         <v>1502</v>
       </c>
@@ -47747,8 +48129,26 @@
       <c r="AZ19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:52">
+      <c r="BA19" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58">
       <c r="A20" s="44" t="s">
         <v>1431</v>
       </c>
@@ -47905,8 +48305,26 @@
       <c r="AZ20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:52">
+      <c r="BA20" t="s">
+        <v>1767</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58">
       <c r="A21" s="44" t="s">
         <v>1551</v>
       </c>
@@ -48063,8 +48481,26 @@
       <c r="AZ21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:52">
+      <c r="BA21" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58">
       <c r="A22" s="44" t="s">
         <v>1587</v>
       </c>
@@ -48221,8 +48657,26 @@
       <c r="AZ22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:52">
+      <c r="BA22" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
       <c r="A23" s="44" t="s">
         <v>935</v>
       </c>
@@ -48379,8 +48833,26 @@
       <c r="AZ23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:52">
+      <c r="BA23" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58">
       <c r="A24" s="44" t="s">
         <v>1593</v>
       </c>
@@ -48537,8 +49009,26 @@
       <c r="AZ24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:52">
+      <c r="BA24" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58">
       <c r="A25" s="44" t="s">
         <v>1602</v>
       </c>
@@ -48695,8 +49185,26 @@
       <c r="AZ25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:52">
+      <c r="BA25" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:58">
       <c r="A26" s="44" t="s">
         <v>1611</v>
       </c>
@@ -48853,8 +49361,26 @@
       <c r="AZ26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:52">
+      <c r="BA26" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58">
       <c r="A27" s="44" t="s">
         <v>1615</v>
       </c>
@@ -49011,8 +49537,26 @@
       <c r="AZ27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:52">
+      <c r="BA27" t="s">
+        <v>1767</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:58">
       <c r="A28" s="44" t="s">
         <v>1616</v>
       </c>
@@ -49169,8 +49713,26 @@
       <c r="AZ28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:52">
+      <c r="BA28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58">
       <c r="A29" s="44" t="s">
         <v>1620</v>
       </c>
@@ -49327,8 +49889,26 @@
       <c r="AZ29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:52">
+      <c r="BA29" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
       <c r="A30" s="44" t="s">
         <v>1624</v>
       </c>
@@ -49485,8 +50065,26 @@
       <c r="AZ30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:52">
+      <c r="BA30" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58">
       <c r="A31" s="44" t="s">
         <v>1647</v>
       </c>
@@ -49643,8 +50241,26 @@
       <c r="AZ31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:52">
+      <c r="BA31" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:58">
       <c r="A32" s="44" t="s">
         <v>1578</v>
       </c>
@@ -49801,8 +50417,26 @@
       <c r="AZ32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:52">
+      <c r="BA32" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58">
       <c r="A33" s="44" t="s">
         <v>1686</v>
       </c>
@@ -49959,8 +50593,26 @@
       <c r="AZ33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:52">
+      <c r="BA33" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:58">
       <c r="A34" s="44" t="s">
         <v>1728</v>
       </c>
@@ -50115,6 +50767,24 @@
         <v>0</v>
       </c>
       <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="s">
+        <v>1767</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4525FE-594C-43D4-BEAA-DFABF4110976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868800BD-852F-4D14-8821-B978A194F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7606" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="1776">
   <si>
     <t>NAME</t>
   </si>
@@ -32077,10 +32077,10 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
     <col min="3" max="3" width="10.36328125" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" customWidth="1"/>
     <col min="5" max="6" width="10.81640625" customWidth="1"/>
@@ -32980,6 +32980,98 @@
         <v>1738</v>
       </c>
       <c r="G56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>100</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>100</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>100</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>100</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G62">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868800BD-852F-4D14-8821-B978A194F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0F19EE-8FAA-4AC2-AC7D-403235E93F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="1777">
   <si>
     <t>NAME</t>
   </si>
@@ -5512,6 +5512,9 @@
   </si>
   <si>
     <t>loot_skeleton_archer</t>
+  </si>
+  <si>
+    <t>battle_endedx</t>
   </si>
 </sst>
 </file>
@@ -38117,7 +38120,7 @@
         <v>36</v>
       </c>
       <c r="P28" s="46" t="s">
-        <v>1558</v>
+        <v>1776</v>
       </c>
       <c r="Q28" s="46" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0F19EE-8FAA-4AC2-AC7D-403235E93F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FA9ED9-913E-4135-A6DD-55AD008732CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -33040,7 +33040,7 @@
         <v>0</v>
       </c>
       <c r="C61">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -33060,10 +33060,10 @@
         <v>36</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <v>1</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FA9ED9-913E-4135-A6DD-55AD008732CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90AEC87-1DC8-40C2-8603-B7557F7751A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="1777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="1784">
   <si>
     <t>NAME</t>
   </si>
@@ -5515,6 +5515,27 @@
   </si>
   <si>
     <t>battle_endedx</t>
+  </si>
+  <si>
+    <t>Take job</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>quest1</t>
+  </si>
+  <si>
+    <t>kill,Skeleton,5,&gt;=</t>
+  </si>
+  <si>
+    <t>Kill skeletons</t>
+  </si>
+  <si>
+    <t>daily_point,20#exp,100</t>
+  </si>
+  <si>
+    <t>exp</t>
   </si>
 </sst>
 </file>
@@ -29576,7 +29597,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -29815,222 +29836,254 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
         <v>1094</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>956</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>991</v>
       </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>953</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>954</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H11" t="s">
-        <v>954</v>
-      </c>
-      <c r="I11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>953</v>
       </c>
       <c r="B12" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>954</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H12" t="s">
+        <v>954</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
         <v>1094</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>956</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>958</v>
       </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>979</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>954</v>
-      </c>
-      <c r="E15" t="s">
-        <v>955</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H15" t="s">
-        <v>955</v>
-      </c>
-      <c r="I15" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>979</v>
       </c>
       <c r="B16" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>954</v>
+      </c>
+      <c r="E16" t="s">
+        <v>955</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H16" t="s">
+        <v>955</v>
+      </c>
+      <c r="I16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
         <v>1094</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>956</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>980</v>
       </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>991</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>954</v>
-      </c>
-      <c r="E18" t="s">
-        <v>955</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H18" t="s">
-        <v>955</v>
-      </c>
-      <c r="I18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>991</v>
       </c>
       <c r="B19" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>954</v>
+      </c>
+      <c r="E19" t="s">
+        <v>955</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H19" t="s">
+        <v>955</v>
+      </c>
+      <c r="I19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
         <v>1094</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>956</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>964</v>
       </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -33177,7 +33230,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
@@ -33190,10 +33243,11 @@
     <col min="8" max="8" width="14.36328125" customWidth="1"/>
     <col min="9" max="9" width="11.1796875" customWidth="1"/>
     <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="11" max="11" width="10.36328125" customWidth="1"/>
-    <col min="12" max="12" width="12.81640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6328125" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="11.90625" customWidth="1"/>
+    <col min="15" max="15" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="13">
@@ -33239,6 +33293,9 @@
       <c r="N1" s="1" t="s">
         <v>1179</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="S1" t="s">
         <v>1180</v>
       </c>
@@ -33286,6 +33343,9 @@
       <c r="N2" s="3" t="s">
         <v>1025</v>
       </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
@@ -33330,6 +33390,9 @@
       <c r="N3" s="3" t="s">
         <v>1025</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
@@ -33374,6 +33437,9 @@
       <c r="N4" s="3" t="s">
         <v>1025</v>
       </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
@@ -33418,6 +33484,9 @@
       <c r="N7" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
@@ -33462,6 +33531,9 @@
       <c r="N8" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
@@ -33506,6 +33578,9 @@
       <c r="N9" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
@@ -33550,6 +33625,9 @@
       <c r="N10" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
@@ -33594,6 +33672,9 @@
       <c r="N11" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
@@ -33638,6 +33719,9 @@
       <c r="N12" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
@@ -33682,6 +33766,9 @@
       <c r="N13" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
@@ -33726,6 +33813,9 @@
       <c r="N14" s="3" t="s">
         <v>1189</v>
       </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
@@ -33769,6 +33859,56 @@
       </c>
       <c r="N15" s="3" t="s">
         <v>1189</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -43010,7 +43150,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -43282,7 +43422,7 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="44" t="s">
-        <v>1220</v>
+        <v>1783</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -43347,7 +43487,7 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="44" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -43407,18 +43547,18 @@
         <v>11</v>
       </c>
       <c r="U6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="44" t="s">
-        <v>1613</v>
+        <v>1227</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -43454,7 +43594,7 @@
         <v>10</v>
       </c>
       <c r="O7" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -43463,21 +43603,21 @@
         <v>1</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="S7" t="s">
-        <v>1615</v>
+        <v>36</v>
       </c>
       <c r="T7">
         <v>11</v>
       </c>
       <c r="U7" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="44" t="s">
-        <v>1369</v>
+        <v>1613</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -43531,24 +43671,24 @@
         <v>38</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>1615</v>
       </c>
       <c r="T8">
         <v>11</v>
       </c>
       <c r="U8" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="44" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -43557,7 +43697,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -43584,7 +43724,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -43602,12 +43742,12 @@
         <v>11</v>
       </c>
       <c r="U9" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="44" t="s">
-        <v>1142</v>
+        <v>1370</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -43622,7 +43762,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -43658,7 +43798,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>1182</v>
+        <v>38</v>
       </c>
       <c r="S10" t="s">
         <v>36</v>
@@ -43667,12 +43807,12 @@
         <v>11</v>
       </c>
       <c r="U10" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="44" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -43732,12 +43872,12 @@
         <v>11</v>
       </c>
       <c r="U11" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="44" t="s">
-        <v>1458</v>
+        <v>1143</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -43797,12 +43937,12 @@
         <v>11</v>
       </c>
       <c r="U12" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="44" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -43862,12 +44002,12 @@
         <v>11</v>
       </c>
       <c r="U13" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="44" t="s">
-        <v>1507</v>
+        <v>1459</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -43927,12 +44067,12 @@
         <v>11</v>
       </c>
       <c r="U14" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="44" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -43992,18 +44132,18 @@
         <v>11</v>
       </c>
       <c r="U15" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="44" t="s">
-        <v>1617</v>
+        <v>1508</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -44012,7 +44152,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -44039,7 +44179,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -44048,27 +44188,27 @@
         <v>1</v>
       </c>
       <c r="R16" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="S16" t="s">
-        <v>1616</v>
+        <v>36</v>
       </c>
       <c r="T16">
         <v>11</v>
       </c>
       <c r="U16" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="44" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -44077,7 +44217,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -44104,7 +44244,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -44113,21 +44253,21 @@
         <v>1</v>
       </c>
       <c r="R17" s="44" t="s">
-        <v>1182</v>
+        <v>38</v>
       </c>
       <c r="S17" t="s">
-        <v>36</v>
+        <v>1616</v>
       </c>
       <c r="T17">
         <v>11</v>
       </c>
       <c r="U17" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="44" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -44187,12 +44327,12 @@
         <v>11</v>
       </c>
       <c r="U18" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="44" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -44252,12 +44392,12 @@
         <v>11</v>
       </c>
       <c r="U19" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="44" t="s">
-        <v>1146</v>
+        <v>1627</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -44317,12 +44457,12 @@
         <v>11</v>
       </c>
       <c r="U20" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="44" t="s">
-        <v>1719</v>
+        <v>1146</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -44387,7 +44527,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="44" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -44452,7 +44592,7 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="44" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -44517,7 +44657,7 @@
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="44" t="s">
-        <v>1728</v>
+        <v>1721</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -44582,7 +44722,7 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="44" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -44642,12 +44782,12 @@
         <v>11</v>
       </c>
       <c r="U25" t="s">
-        <v>1559</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="44" t="s">
-        <v>1740</v>
+        <v>1729</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -44707,12 +44847,12 @@
         <v>11</v>
       </c>
       <c r="U26" t="s">
-        <v>1658</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="44" t="s">
-        <v>959</v>
+        <v>1740</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -44777,7 +44917,7 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="44" t="s">
-        <v>1748</v>
+        <v>959</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -44837,6 +44977,71 @@
         <v>11</v>
       </c>
       <c r="U28" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="44" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>10</v>
+      </c>
+      <c r="O29" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S29" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29">
+        <v>11</v>
+      </c>
+      <c r="U29" t="s">
         <v>1658</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90AEC87-1DC8-40C2-8603-B7557F7751A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C70683-3A80-4D1F-9DF3-6D414E64852A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="1784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7659" uniqueCount="1787">
   <si>
     <t>NAME</t>
   </si>
@@ -5536,6 +5536,15 @@
   </si>
   <si>
     <t>exp</t>
+  </si>
+  <si>
+    <t>heal_potion</t>
+  </si>
+  <si>
+    <t>mana_potion</t>
+  </si>
+  <si>
+    <t>town_shop1</t>
   </si>
 </sst>
 </file>
@@ -32133,13 +32142,14 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
     <col min="3" max="3" width="10.36328125" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="6" width="10.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="13">
@@ -33128,6 +33138,75 @@
         <v>1146</v>
       </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>100</v>
+      </c>
+      <c r="D64">
+        <v>50</v>
+      </c>
+      <c r="E64">
+        <v>50</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>100</v>
+      </c>
+      <c r="D65">
+        <v>50</v>
+      </c>
+      <c r="E65">
+        <v>50</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>100</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G66">
         <v>0</v>
       </c>
     </row>
@@ -43150,7 +43229,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -45043,6 +45122,136 @@
       </c>
       <c r="U29" t="s">
         <v>1658</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" s="44" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>10</v>
+      </c>
+      <c r="O30" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+      <c r="R30" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S30" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30">
+        <v>11</v>
+      </c>
+      <c r="U30" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="44" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>10</v>
+      </c>
+      <c r="O31" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S31" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31">
+        <v>11</v>
+      </c>
+      <c r="U31" t="s">
+        <v>896</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C70683-3A80-4D1F-9DF3-6D414E64852A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6DE29A-C80E-4CC8-8B8B-93A568C239A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -5526,9 +5526,6 @@
     <t>quest1</t>
   </si>
   <si>
-    <t>kill,Skeleton,5,&gt;=</t>
-  </si>
-  <si>
     <t>Kill skeletons</t>
   </si>
   <si>
@@ -5545,6 +5542,9 @@
   </si>
   <si>
     <t>town_shop1</t>
+  </si>
+  <si>
+    <t>kill,skeleton,5,&gt;=</t>
   </si>
 </sst>
 </file>
@@ -33143,7 +33143,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -33158,7 +33158,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -33181,7 +33181,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -33951,22 +33951,22 @@
         <v>1182</v>
       </c>
       <c r="C19" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" t="s">
         <v>1780</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1781</v>
       </c>
       <c r="I19" t="s">
         <v>1149</v>
@@ -43501,7 +43501,7 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="44" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -45126,7 +45126,7 @@
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="44" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -45191,7 +45191,7 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="44" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B31">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCED246-CB97-46B1-A0C2-0692DB2A0609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C337452-2D4C-4078-98EC-1292688FA9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="1789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7745" uniqueCount="1792">
   <si>
     <t>NAME</t>
   </si>
@@ -5551,6 +5551,15 @@
   </si>
   <si>
     <t>USED</t>
+  </si>
+  <si>
+    <t>VULNERABLE</t>
+  </si>
+  <si>
+    <t>RESIST</t>
+  </si>
+  <si>
+    <t>IMMUNITIES</t>
   </si>
 </sst>
 </file>
@@ -6151,16 +6160,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX998"/>
+  <dimension ref="A1:BA998"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="9.26953125" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.08984375" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
-    <col min="14" max="17" width="15.90625" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.08984375" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="8.6328125" customWidth="1"/>
+    <col min="18" max="18" width="9.26953125" customWidth="1"/>
+    <col min="19" max="19" width="8.36328125" customWidth="1"/>
     <col min="20" max="20" width="19" customWidth="1"/>
     <col min="21" max="21" width="36.08984375" customWidth="1"/>
     <col min="22" max="22" width="22.453125" customWidth="1"/>
@@ -6182,9 +6198,13 @@
     <col min="47" max="47" width="8.1796875" customWidth="1"/>
     <col min="48" max="48" width="6.90625" customWidth="1"/>
     <col min="49" max="49" width="7.90625" customWidth="1"/>
+    <col min="50" max="50" width="10.6328125" customWidth="1"/>
+    <col min="51" max="51" width="20.08984375" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="38.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="15.75" customHeight="1">
+    <row r="1" spans="1:53" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6335,8 +6355,17 @@
       <c r="AX1" s="6" t="s">
         <v>1787</v>
       </c>
-    </row>
-    <row r="2" spans="1:50" ht="12.5">
+      <c r="AY1" s="6" t="s">
+        <v>1789</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>1790</v>
+      </c>
+      <c r="BA1" s="6" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" ht="12.5">
       <c r="A2" s="47" t="s">
         <v>954</v>
       </c>
@@ -6487,8 +6516,17 @@
       <c r="AX2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:50" ht="12.5">
+      <c r="AY2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" ht="12.5">
       <c r="A3" s="47" t="s">
         <v>1406</v>
       </c>
@@ -6639,8 +6677,17 @@
       <c r="AX3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:50" ht="12.5">
+      <c r="AY3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" ht="12.5">
       <c r="A4" s="47" t="s">
         <v>1772</v>
       </c>
@@ -6791,8 +6838,17 @@
       <c r="AX4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:50" ht="12.5">
+      <c r="AY4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" ht="12.5">
       <c r="A5" s="47" t="s">
         <v>1773</v>
       </c>
@@ -6943,8 +6999,17 @@
       <c r="AX5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:50" ht="12.5">
+      <c r="AY5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" ht="12.5">
       <c r="A6" s="47" t="s">
         <v>1466</v>
       </c>
@@ -7095,8 +7160,17 @@
       <c r="AX6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:50" ht="12.5">
+      <c r="AY6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="12.5">
       <c r="A7" s="47" t="s">
         <v>1467</v>
       </c>
@@ -7247,8 +7321,17 @@
       <c r="AX7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:50" ht="12.5">
+      <c r="AY7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" ht="12.5">
       <c r="A8" s="47" t="s">
         <v>43</v>
       </c>
@@ -7399,8 +7482,17 @@
       <c r="AX8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:50" ht="12.5">
+      <c r="AY8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="12.5">
       <c r="A9" s="47" t="s">
         <v>1509</v>
       </c>
@@ -7551,8 +7643,17 @@
       <c r="AX9">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:50" ht="12.5">
+      <c r="AY9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" ht="12.5">
       <c r="A10" s="47" t="s">
         <v>1510</v>
       </c>
@@ -7703,8 +7804,17 @@
       <c r="AX10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:50" ht="12.5">
+      <c r="AY10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" ht="12.5">
       <c r="A11" s="47" t="s">
         <v>1521</v>
       </c>
@@ -7855,8 +7965,17 @@
       <c r="AX11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:50" ht="12.5">
+      <c r="AY11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:53" ht="12.5">
       <c r="A12" s="47" t="s">
         <v>1522</v>
       </c>
@@ -8007,8 +8126,17 @@
       <c r="AX12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:50" ht="12.5">
+      <c r="AY12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" ht="12.5">
       <c r="A13" s="47" t="s">
         <v>1550</v>
       </c>
@@ -8159,8 +8287,17 @@
       <c r="AX13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:50" ht="12.5">
+      <c r="AY13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53" ht="12.5">
       <c r="A14" s="47" t="s">
         <v>1578</v>
       </c>
@@ -8311,8 +8448,17 @@
       <c r="AX14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:50" ht="12.5">
+      <c r="AY14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" ht="12.5">
       <c r="A15" s="47" t="s">
         <v>1601</v>
       </c>
@@ -8463,8 +8609,17 @@
       <c r="AX15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:50" ht="12.5">
+      <c r="AY15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53" ht="12.5">
       <c r="A16" s="47" t="s">
         <v>34</v>
       </c>
@@ -8615,8 +8770,17 @@
       <c r="AX16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:50" ht="12.5">
+      <c r="AY16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" ht="12.5">
       <c r="A17" s="47" t="s">
         <v>1370</v>
       </c>
@@ -8767,8 +8931,17 @@
       <c r="AX17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:50" ht="12.5">
+      <c r="AY17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:53" ht="12.5">
       <c r="A18" s="47" t="s">
         <v>1165</v>
       </c>
@@ -8919,8 +9092,17 @@
       <c r="AX18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:50" ht="12.5">
+      <c r="AY18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:53" ht="12.5">
       <c r="A19" s="47" t="s">
         <v>1619</v>
       </c>
@@ -9071,8 +9253,17 @@
       <c r="AX19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:50" ht="12.5">
+      <c r="AY19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:53" ht="12.5">
       <c r="A20" s="47" t="s">
         <v>1632</v>
       </c>
@@ -9223,8 +9414,17 @@
       <c r="AX20">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:50" ht="12.5">
+      <c r="AY20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53" ht="12.5">
       <c r="A21" s="47" t="s">
         <v>1258</v>
       </c>
@@ -9375,8 +9575,17 @@
       <c r="AX21">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:50" ht="12.5">
+      <c r="AY21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:53" ht="12.5">
       <c r="A22" s="47" t="s">
         <v>1716</v>
       </c>
@@ -9527,8 +9736,17 @@
       <c r="AX22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:50" ht="12.5">
+      <c r="AY22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:53" ht="12.5">
       <c r="A23" s="47" t="s">
         <v>1736</v>
       </c>
@@ -9679,8 +9897,17 @@
       <c r="AX23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:50" ht="12.5">
+      <c r="AY23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:53" ht="12.5">
       <c r="A24" s="47" t="s">
         <v>1737</v>
       </c>
@@ -9831,8 +10058,17 @@
       <c r="AX24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:50" ht="12.5">
+      <c r="AY24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:53" ht="12.5">
       <c r="A25" s="47" t="s">
         <v>1739</v>
       </c>
@@ -9983,8 +10219,17 @@
       <c r="AX25">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:50" ht="12.5">
+      <c r="AY25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:53" ht="12.5">
       <c r="A26" s="47" t="s">
         <v>1738</v>
       </c>
@@ -10135,8 +10380,17 @@
       <c r="AX26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:50" ht="12.5">
+      <c r="AY26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:53" ht="12.5">
       <c r="A27" s="47" t="s">
         <v>52</v>
       </c>
@@ -10287,8 +10541,17 @@
       <c r="AX27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:50" ht="12.5">
+      <c r="AY27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:53" ht="12.5">
       <c r="A28" s="47" t="s">
         <v>1728</v>
       </c>
@@ -10439,8 +10702,17 @@
       <c r="AX28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:50" ht="12.5">
+      <c r="AY28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ28" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:53" ht="12.5">
       <c r="A29" s="48"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
@@ -10475,7 +10747,7 @@
       <c r="AJ29" s="28"/>
       <c r="AK29" s="46"/>
     </row>
-    <row r="30" spans="1:50" ht="12.5">
+    <row r="30" spans="1:53" ht="12.5">
       <c r="A30" s="48"/>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
@@ -10510,7 +10782,7 @@
       <c r="AJ30" s="28"/>
       <c r="AK30" s="46"/>
     </row>
-    <row r="31" spans="1:50" ht="12.5">
+    <row r="31" spans="1:53" ht="12.5">
       <c r="A31" s="48"/>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
@@ -10544,7 +10816,7 @@
       <c r="AJ31" s="28"/>
       <c r="AK31" s="46"/>
     </row>
-    <row r="32" spans="1:50" ht="12.5">
+    <row r="32" spans="1:53" ht="12.5">
       <c r="A32" s="48"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A71E6C-8442-4491-860A-18C534D40C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EA56A4-7728-4CF4-BDDC-F1B89D8846CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7824" uniqueCount="1797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7852" uniqueCount="1799">
   <si>
     <t>NAME</t>
   </si>
@@ -5575,6 +5575,12 @@
   </si>
   <si>
     <t>EXTRAS</t>
+  </si>
+  <si>
+    <t>buff_atk1</t>
+  </si>
+  <si>
+    <t>basic_buff_atk</t>
   </si>
 </sst>
 </file>
@@ -6214,9 +6220,9 @@
     <col min="49" max="49" width="6.90625" customWidth="1"/>
     <col min="50" max="50" width="7.90625" customWidth="1"/>
     <col min="51" max="51" width="10.6328125" customWidth="1"/>
-    <col min="52" max="52" width="20.08984375" customWidth="1"/>
-    <col min="53" max="53" width="17.81640625" customWidth="1"/>
-    <col min="54" max="54" width="38.26953125" customWidth="1"/>
+    <col min="52" max="52" width="18" customWidth="1"/>
+    <col min="53" max="53" width="10.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" customHeight="1">
@@ -6734,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="48">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="I4" s="48">
         <v>45</v>
@@ -46125,12 +46131,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="4" width="7.54296875" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
     <col min="5" max="5" width="12.90625" customWidth="1"/>
     <col min="6" max="6" width="8.6328125" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" customWidth="1"/>
@@ -46152,16 +46159,16 @@
     <col min="26" max="26" width="6.54296875" customWidth="1"/>
     <col min="27" max="27" width="6.453125" customWidth="1"/>
     <col min="28" max="28" width="9.36328125" customWidth="1"/>
-    <col min="29" max="29" width="10.26953125" customWidth="1"/>
+    <col min="29" max="29" width="13.81640625" customWidth="1"/>
     <col min="30" max="30" width="7.1796875" customWidth="1"/>
-    <col min="31" max="31" width="7.26953125" customWidth="1"/>
+    <col min="31" max="31" width="11.54296875" customWidth="1"/>
     <col min="32" max="32" width="13.81640625" customWidth="1"/>
     <col min="33" max="33" width="9.6328125" customWidth="1"/>
     <col min="34" max="34" width="8.08984375" customWidth="1"/>
     <col min="35" max="35" width="7.26953125" customWidth="1"/>
     <col min="36" max="36" width="10.90625" customWidth="1"/>
     <col min="37" max="37" width="6.453125" customWidth="1"/>
-    <col min="38" max="38" width="8.7265625" customWidth="1"/>
+    <col min="38" max="38" width="12" customWidth="1"/>
     <col min="39" max="39" width="7.1796875" customWidth="1"/>
     <col min="40" max="40" width="9.54296875" customWidth="1"/>
     <col min="41" max="41" width="9.36328125" customWidth="1"/>
@@ -52129,6 +52136,346 @@
         <v>1763</v>
       </c>
       <c r="BD35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:56">
+      <c r="A36" s="44" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>3</v>
+      </c>
+      <c r="V36">
+        <v>2</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>1</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>-1</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>10</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>1797</v>
+      </c>
+      <c r="AF36" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AG36" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AH36" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AI36" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AK36" s="44">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM36" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>1</v>
+      </c>
+      <c r="AP36">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BD36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:56">
+      <c r="A37" s="44" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>1</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>5</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF37" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AG37" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AH37" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AI37" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AK37" s="44">
+        <v>1</v>
+      </c>
+      <c r="AL37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM37" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BD37" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EA56A4-7728-4CF4-BDDC-F1B89D8846CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDA45D4-FF3F-428E-A731-B9D184EEC34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -6731,7 +6731,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>30</v>
+        <v>813</v>
       </c>
       <c r="F4" s="48" t="s">
         <v>31</v>
@@ -6782,7 +6782,7 @@
         <v>33</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>36</v>
+        <v>1485</v>
       </c>
       <c r="W4" s="40" t="s">
         <v>35</v>
@@ -6895,10 +6895,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>30</v>
+        <v>813</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G5" s="48">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDA45D4-FF3F-428E-A731-B9D184EEC34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B025709C-21E4-4646-B40E-63DC05DFC0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7852" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7853" uniqueCount="1800">
   <si>
     <t>NAME</t>
   </si>
@@ -5581,6 +5581,9 @@
   </si>
   <si>
     <t>basic_buff_atk</t>
+  </si>
+  <si>
+    <t>RARITY_ROLL</t>
   </si>
 </sst>
 </file>
@@ -6740,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="48">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="I4" s="48">
         <v>45</v>
@@ -33702,7 +33705,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -33725,7 +33728,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>1146</v>
+        <v>1369</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -43819,96 +43822,100 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" customWidth="1"/>
-    <col min="5" max="5" width="11.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="21" max="21" width="10.453125" customWidth="1"/>
-    <col min="23" max="23" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" customWidth="1"/>
+    <col min="22" max="22" width="10.453125" customWidth="1"/>
+    <col min="24" max="24" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="13">
+    <row r="1" spans="1:25" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>1351</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>1788</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>1789</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>1354</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>1355</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>1356</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>1357</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>1358</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>1359</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>1360</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>815</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>1614</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>1655</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="44">
         <v>0</v>
       </c>
       <c r="C2">
@@ -43951,38 +43958,41 @@
         <v>0</v>
       </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>10</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="R2" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2">
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2">
         <v>11</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>1657</v>
       </c>
-      <c r="X2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+      <c r="Y2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="44">
         <v>0</v>
       </c>
       <c r="C3">
@@ -44025,39 +44035,42 @@
         <v>0</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>10</v>
       </c>
-      <c r="Q3" s="44" t="s">
+      <c r="R3" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3">
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3">
         <v>11</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>1658</v>
       </c>
-      <c r="X3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="Y3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" s="44">
+        <v>1</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -44069,17 +44082,17 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
       <c r="J4">
         <v>0</v>
       </c>
@@ -44099,38 +44112,41 @@
         <v>0</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="Q4" s="44" t="s">
+      <c r="R4" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
       <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4">
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4">
         <v>11</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>1659</v>
       </c>
-      <c r="X4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="Y4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="44" t="s">
         <v>1777</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="44">
         <v>0</v>
       </c>
       <c r="C5">
@@ -44173,38 +44189,41 @@
         <v>0</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>10</v>
       </c>
-      <c r="Q5" s="44" t="s">
+      <c r="R5" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
       <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U5" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5">
+      <c r="V5" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5">
         <v>11</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>1660</v>
       </c>
-      <c r="X5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="Y5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="44">
         <v>0</v>
       </c>
       <c r="C6">
@@ -44247,38 +44266,41 @@
         <v>0</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>10</v>
       </c>
-      <c r="Q6" s="44" t="s">
+      <c r="R6" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
       <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U6" t="s">
-        <v>36</v>
-      </c>
-      <c r="V6">
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6">
         <v>11</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>1660</v>
       </c>
-      <c r="X6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="Y6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="44">
         <v>0</v>
       </c>
       <c r="C7">
@@ -44321,46 +44343,49 @@
         <v>0</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>10</v>
       </c>
-      <c r="Q7" s="44" t="s">
+      <c r="R7" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
       <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U7" t="s">
-        <v>36</v>
-      </c>
-      <c r="V7">
+      <c r="V7" t="s">
+        <v>36</v>
+      </c>
+      <c r="W7">
         <v>11</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>1661</v>
       </c>
-      <c r="X7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="Y7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
-      <c r="B8">
-        <v>0</v>
+      <c r="B8" s="44">
+        <v>1</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>50</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
       <c r="E8">
         <v>0</v>
       </c>
@@ -44395,46 +44420,49 @@
         <v>0</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>10</v>
       </c>
-      <c r="Q8" s="44" t="s">
+      <c r="R8" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
       <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>1615</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>11</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>1662</v>
       </c>
-      <c r="X8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
-      <c r="B9">
-        <v>0</v>
+      <c r="B9" s="44">
+        <v>1</v>
       </c>
       <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>50</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
         <v>0</v>
       </c>
@@ -44469,38 +44497,41 @@
         <v>0</v>
       </c>
       <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>10</v>
       </c>
-      <c r="Q9" s="44" t="s">
+      <c r="R9" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
       <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="U9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V9">
+      <c r="V9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9">
         <v>11</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>1663</v>
       </c>
-      <c r="X9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="Y9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="44">
         <v>0</v>
       </c>
       <c r="C10">
@@ -44519,11 +44550,11 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
         <v>0</v>
       </c>
@@ -44543,38 +44574,41 @@
         <v>0</v>
       </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <v>10</v>
       </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
       <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="U10" t="s">
-        <v>36</v>
-      </c>
-      <c r="V10">
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10">
         <v>11</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>1664</v>
       </c>
-      <c r="X10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="44">
         <v>0</v>
       </c>
       <c r="C11">
@@ -44617,38 +44651,41 @@
         <v>0</v>
       </c>
       <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <v>10</v>
       </c>
-      <c r="Q11" s="44" t="s">
+      <c r="R11" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
       <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U11" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11">
+      <c r="V11" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11">
         <v>11</v>
       </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>1665</v>
       </c>
-      <c r="X11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="Y11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="44">
         <v>0</v>
       </c>
       <c r="C12">
@@ -44691,38 +44728,41 @@
         <v>0</v>
       </c>
       <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <v>10</v>
       </c>
-      <c r="Q12" s="44" t="s">
+      <c r="R12" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
       <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U12" t="s">
-        <v>36</v>
-      </c>
-      <c r="V12">
+      <c r="V12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12">
         <v>11</v>
       </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>1666</v>
       </c>
-      <c r="X12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="44">
         <v>0</v>
       </c>
       <c r="C13">
@@ -44765,38 +44805,41 @@
         <v>0</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <v>10</v>
       </c>
-      <c r="Q13" s="44" t="s">
+      <c r="R13" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
       <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U13" t="s">
-        <v>36</v>
-      </c>
-      <c r="V13">
+      <c r="V13" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13">
         <v>11</v>
       </c>
-      <c r="W13" t="s">
+      <c r="X13" t="s">
         <v>1667</v>
       </c>
-      <c r="X13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="Y13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="44">
         <v>0</v>
       </c>
       <c r="C14">
@@ -44839,38 +44882,41 @@
         <v>0</v>
       </c>
       <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <v>10</v>
       </c>
-      <c r="Q14" s="44" t="s">
+      <c r="R14" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
       <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U14" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14">
+      <c r="V14" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14">
         <v>11</v>
       </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>1668</v>
       </c>
-      <c r="X14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Y14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="44">
         <v>0</v>
       </c>
       <c r="C15">
@@ -44913,38 +44959,41 @@
         <v>0</v>
       </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <v>10</v>
       </c>
-      <c r="Q15" s="44" t="s">
+      <c r="R15" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
       <c r="S15">
-        <v>1</v>
-      </c>
-      <c r="T15" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U15" t="s">
-        <v>36</v>
-      </c>
-      <c r="V15">
+      <c r="V15" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15">
         <v>11</v>
       </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
         <v>1669</v>
       </c>
-      <c r="X15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="Y15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="44">
         <v>0</v>
       </c>
       <c r="C16">
@@ -44987,46 +45036,49 @@
         <v>0</v>
       </c>
       <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
         <v>10</v>
       </c>
-      <c r="Q16" s="44" t="s">
+      <c r="R16" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
       <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="V16">
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16">
         <v>11</v>
       </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>1670</v>
       </c>
-      <c r="X16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="Y16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="44">
         <v>0</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>50</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
@@ -45037,11 +45089,11 @@
         <v>0</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>5</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
       <c r="J17">
         <v>0</v>
       </c>
@@ -45061,38 +45113,41 @@
         <v>0</v>
       </c>
       <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
         <v>10</v>
       </c>
-      <c r="Q17" s="44" t="s">
+      <c r="R17" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
       <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
         <v>1616</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>11</v>
       </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>1671</v>
       </c>
-      <c r="X17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="Y17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="44">
         <v>0</v>
       </c>
       <c r="C18">
@@ -45135,38 +45190,41 @@
         <v>0</v>
       </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>10</v>
       </c>
-      <c r="Q18" s="44" t="s">
+      <c r="R18" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
       <c r="S18">
-        <v>1</v>
-      </c>
-      <c r="T18" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18">
+      <c r="V18" t="s">
+        <v>36</v>
+      </c>
+      <c r="W18">
         <v>11</v>
       </c>
-      <c r="W18" t="s">
+      <c r="X18" t="s">
         <v>1672</v>
       </c>
-      <c r="X18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24">
+      <c r="Y18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="44">
         <v>0</v>
       </c>
       <c r="C19">
@@ -45209,38 +45267,41 @@
         <v>0</v>
       </c>
       <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>10</v>
       </c>
-      <c r="Q19" s="44" t="s">
+      <c r="R19" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
       <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U19" t="s">
-        <v>36</v>
-      </c>
-      <c r="V19">
+      <c r="V19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19">
         <v>11</v>
       </c>
-      <c r="W19" t="s">
+      <c r="X19" t="s">
         <v>1673</v>
       </c>
-      <c r="X19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24">
+      <c r="Y19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="44">
         <v>0</v>
       </c>
       <c r="C20">
@@ -45283,38 +45344,41 @@
         <v>0</v>
       </c>
       <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>10</v>
       </c>
-      <c r="Q20" s="44" t="s">
+      <c r="R20" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
       <c r="S20">
-        <v>1</v>
-      </c>
-      <c r="T20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U20" t="s">
-        <v>36</v>
-      </c>
-      <c r="V20">
+      <c r="V20" t="s">
+        <v>36</v>
+      </c>
+      <c r="W20">
         <v>11</v>
       </c>
-      <c r="W20" t="s">
+      <c r="X20" t="s">
         <v>1674</v>
       </c>
-      <c r="X20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
+      <c r="Y20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="44">
         <v>0</v>
       </c>
       <c r="C21">
@@ -45357,38 +45421,41 @@
         <v>0</v>
       </c>
       <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <v>10</v>
       </c>
-      <c r="Q21" s="44" t="s">
+      <c r="R21" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
       <c r="S21">
-        <v>1</v>
-      </c>
-      <c r="T21" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U21" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21">
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21">
         <v>11</v>
       </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>1658</v>
       </c>
-      <c r="X21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24">
+      <c r="Y21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="44">
         <v>0</v>
       </c>
       <c r="C22">
@@ -45431,38 +45498,41 @@
         <v>0</v>
       </c>
       <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
         <v>10</v>
       </c>
-      <c r="Q22" s="44" t="s">
+      <c r="R22" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
       <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="T22" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22">
+      <c r="V22" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22">
         <v>11</v>
       </c>
-      <c r="W22" t="s">
+      <c r="X22" t="s">
         <v>1658</v>
       </c>
-      <c r="X22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24">
+      <c r="Y22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="44">
         <v>0</v>
       </c>
       <c r="C23">
@@ -45505,38 +45575,41 @@
         <v>0</v>
       </c>
       <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>10</v>
       </c>
-      <c r="Q23" s="44" t="s">
+      <c r="R23" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
       <c r="S23">
-        <v>1</v>
-      </c>
-      <c r="T23" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U23" t="s">
-        <v>36</v>
-      </c>
-      <c r="V23">
+      <c r="V23" t="s">
+        <v>36</v>
+      </c>
+      <c r="W23">
         <v>11</v>
       </c>
-      <c r="W23" t="s">
+      <c r="X23" t="s">
         <v>1658</v>
       </c>
-      <c r="X23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
+      <c r="Y23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="44">
         <v>0</v>
       </c>
       <c r="C24">
@@ -45579,38 +45652,41 @@
         <v>0</v>
       </c>
       <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
         <v>10</v>
       </c>
-      <c r="Q24" s="44" t="s">
+      <c r="R24" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
       <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24">
+      <c r="V24" t="s">
+        <v>36</v>
+      </c>
+      <c r="W24">
         <v>11</v>
       </c>
-      <c r="W24" t="s">
+      <c r="X24" t="s">
         <v>1658</v>
       </c>
-      <c r="X24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24">
+      <c r="Y24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="44">
         <v>0</v>
       </c>
       <c r="C25">
@@ -45653,38 +45729,41 @@
         <v>0</v>
       </c>
       <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
         <v>10</v>
       </c>
-      <c r="Q25" s="44" t="s">
+      <c r="R25" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
       <c r="S25">
-        <v>1</v>
-      </c>
-      <c r="T25" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U25" t="s">
-        <v>36</v>
-      </c>
-      <c r="V25">
+      <c r="V25" t="s">
+        <v>36</v>
+      </c>
+      <c r="W25">
         <v>11</v>
       </c>
-      <c r="W25" t="s">
+      <c r="X25" t="s">
         <v>1658</v>
       </c>
-      <c r="X25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24">
+      <c r="Y25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="44">
         <v>0</v>
       </c>
       <c r="C26">
@@ -45727,38 +45806,41 @@
         <v>0</v>
       </c>
       <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
         <v>10</v>
       </c>
-      <c r="Q26" s="44" t="s">
+      <c r="R26" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
       <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U26" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26">
+      <c r="V26" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26">
         <v>11</v>
       </c>
-      <c r="W26" t="s">
+      <c r="X26" t="s">
         <v>1559</v>
       </c>
-      <c r="X26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24">
+      <c r="Y26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="44">
         <v>0</v>
       </c>
       <c r="C27">
@@ -45801,38 +45883,41 @@
         <v>0</v>
       </c>
       <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>10</v>
       </c>
-      <c r="Q27" s="44" t="s">
+      <c r="R27" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
       <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U27" t="s">
-        <v>36</v>
-      </c>
-      <c r="V27">
+      <c r="V27" t="s">
+        <v>36</v>
+      </c>
+      <c r="W27">
         <v>11</v>
       </c>
-      <c r="W27" t="s">
+      <c r="X27" t="s">
         <v>1658</v>
       </c>
-      <c r="X27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24">
+      <c r="Y27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="44">
         <v>0</v>
       </c>
       <c r="C28">
@@ -45875,38 +45960,41 @@
         <v>0</v>
       </c>
       <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
         <v>10</v>
       </c>
-      <c r="Q28" s="44" t="s">
+      <c r="R28" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
       <c r="S28">
-        <v>1</v>
-      </c>
-      <c r="T28" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U28" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28">
+      <c r="V28" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28">
         <v>11</v>
       </c>
-      <c r="W28" t="s">
+      <c r="X28" t="s">
         <v>1658</v>
       </c>
-      <c r="X28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24">
+      <c r="Y28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="44" t="s">
         <v>1748</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="44">
         <v>0</v>
       </c>
       <c r="C29">
@@ -45949,38 +46037,41 @@
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>10</v>
       </c>
-      <c r="Q29" s="44" t="s">
+      <c r="R29" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
       <c r="S29">
-        <v>1</v>
-      </c>
-      <c r="T29" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U29" t="s">
-        <v>36</v>
-      </c>
-      <c r="V29">
+      <c r="V29" t="s">
+        <v>36</v>
+      </c>
+      <c r="W29">
         <v>11</v>
       </c>
-      <c r="W29" t="s">
+      <c r="X29" t="s">
         <v>1658</v>
       </c>
-      <c r="X29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
+      <c r="Y29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="44" t="s">
         <v>1778</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="44">
         <v>0</v>
       </c>
       <c r="C30">
@@ -46023,38 +46114,41 @@
         <v>0</v>
       </c>
       <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
         <v>10</v>
       </c>
-      <c r="Q30" s="44" t="s">
+      <c r="R30" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
       <c r="S30">
-        <v>1</v>
-      </c>
-      <c r="T30" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U30" t="s">
-        <v>36</v>
-      </c>
-      <c r="V30">
+      <c r="V30" t="s">
+        <v>36</v>
+      </c>
+      <c r="W30">
         <v>11</v>
       </c>
-      <c r="W30" t="s">
+      <c r="X30" t="s">
         <v>896</v>
       </c>
-      <c r="X30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
+      <c r="Y30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="44" t="s">
         <v>1779</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="44">
         <v>0</v>
       </c>
       <c r="C31">
@@ -46097,30 +46191,33 @@
         <v>0</v>
       </c>
       <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
         <v>10</v>
       </c>
-      <c r="Q31" s="44" t="s">
+      <c r="R31" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
       <c r="S31">
-        <v>1</v>
-      </c>
-      <c r="T31" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="U31" t="s">
-        <v>36</v>
-      </c>
-      <c r="V31">
+      <c r="V31" t="s">
+        <v>36</v>
+      </c>
+      <c r="W31">
         <v>11</v>
       </c>
-      <c r="W31" t="s">
+      <c r="X31" t="s">
         <v>896</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46177,7 +46274,7 @@
     <col min="44" max="44" width="6.453125" customWidth="1"/>
     <col min="45" max="45" width="6.54296875" customWidth="1"/>
     <col min="46" max="46" width="5.90625" customWidth="1"/>
-    <col min="47" max="47" width="6.26953125" customWidth="1"/>
+    <col min="47" max="47" width="19.08984375" customWidth="1"/>
     <col min="48" max="48" width="7.81640625" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
     <col min="51" max="53" width="7.08984375" customWidth="1"/>
@@ -49049,7 +49146,7 @@
         <v>0</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="s">
         <v>36</v>
@@ -52449,7 +52546,7 @@
         <v>0</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B025709C-21E4-4646-B40E-63DC05DFC0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C784ABA-B6EC-4350-884C-BC6A2B99ED00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7853" uniqueCount="1800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7891" uniqueCount="1802">
   <si>
     <t>NAME</t>
   </si>
@@ -5427,9 +5427,6 @@
     <t>draw_ten_itm</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1</t>
-  </si>
-  <si>
     <t>bite</t>
   </si>
   <si>
@@ -5584,6 +5581,15 @@
   </si>
   <si>
     <t>RARITY_ROLL</t>
+  </si>
+  <si>
+    <t>SUBTYPE</t>
+  </si>
+  <si>
+    <t>offhand</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1</t>
   </si>
 </sst>
 </file>
@@ -6233,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C1" s="49" t="s">
         <v>3</v>
@@ -6260,7 +6266,7 @@
         <v>10</v>
       </c>
       <c r="K1" s="49" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="L1" s="49" t="s">
         <v>1597</v>
@@ -6380,16 +6386,16 @@
         <v>1715</v>
       </c>
       <c r="AY1" s="6" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="AZ1" s="6" t="s">
+        <v>1783</v>
+      </c>
+      <c r="BA1" s="6" t="s">
         <v>1784</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>1785</v>
-      </c>
-      <c r="BB1" s="6" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="2" spans="1:54" ht="12.5">
@@ -6722,7 +6728,7 @@
     </row>
     <row r="4" spans="1:54" ht="12.5">
       <c r="A4" s="47" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B4" s="53">
         <v>1</v>
@@ -6833,7 +6839,7 @@
         <v>3</v>
       </c>
       <c r="AL4" s="46" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -6875,18 +6881,18 @@
         <v>2</v>
       </c>
       <c r="AZ4" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="BA4" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="BB4" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="5" spans="1:54" ht="12.5">
       <c r="A5" s="47" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B5" s="53">
         <v>1</v>
@@ -6997,7 +7003,7 @@
         <v>3</v>
       </c>
       <c r="AL5" s="46" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -7039,13 +7045,13 @@
         <v>3</v>
       </c>
       <c r="AZ5" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="BA5" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="BB5" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="6" spans="1:54" ht="12.5">
@@ -30438,13 +30444,13 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C9" t="s">
         <v>1772</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>1773</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1774</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -31943,7 +31949,7 @@
         <v>84</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D1" s="45" t="s">
         <v>1257</v>
@@ -32598,7 +32604,7 @@
         <v>1656</v>
       </c>
       <c r="B57" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="52" t="s">
         <v>36</v>
@@ -32707,24 +32713,24 @@
     </row>
     <row r="65" spans="1:3" ht="15.75" customHeight="1">
       <c r="A65" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B65" s="52">
+        <v>0</v>
+      </c>
+      <c r="C65" s="52" t="s">
         <v>1750</v>
-      </c>
-      <c r="B65" s="52">
-        <v>0</v>
-      </c>
-      <c r="C65" s="52" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" customHeight="1">
       <c r="A66" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B66" s="52">
+        <v>0</v>
+      </c>
+      <c r="C66" s="52" t="s">
         <v>1752</v>
-      </c>
-      <c r="B66" s="52">
-        <v>0</v>
-      </c>
-      <c r="C66" s="52" t="s">
-        <v>1753</v>
       </c>
     </row>
   </sheetData>
@@ -33644,7 +33650,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -33690,7 +33696,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -33736,7 +33742,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -33751,7 +33757,7 @@
         <v>50</v>
       </c>
       <c r="F64" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -33774,7 +33780,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -33980,7 +33986,7 @@
         <v>1182</v>
       </c>
       <c r="C2" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
@@ -34027,7 +34033,7 @@
         <v>1182</v>
       </c>
       <c r="C3" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
@@ -34074,7 +34080,7 @@
         <v>1182</v>
       </c>
       <c r="C4" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
@@ -34309,7 +34315,7 @@
         <v>1186</v>
       </c>
       <c r="C11" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
@@ -34356,7 +34362,7 @@
         <v>1186</v>
       </c>
       <c r="C12" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="D12" t="s">
         <v>36</v>
@@ -34403,7 +34409,7 @@
         <v>1186</v>
       </c>
       <c r="C13" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D13" t="s">
         <v>36</v>
@@ -34450,7 +34456,7 @@
         <v>1186</v>
       </c>
       <c r="C14" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="D14" t="s">
         <v>36</v>
@@ -34497,7 +34503,7 @@
         <v>1186</v>
       </c>
       <c r="C15" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D15" t="s">
         <v>36</v>
@@ -34538,19 +34544,19 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B19" t="s">
         <v>1182</v>
       </c>
       <c r="C19" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="F19" t="s">
         <v>36</v>
@@ -34559,7 +34565,7 @@
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="I19" t="s">
         <v>1149</v>
@@ -34595,7 +34601,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="68.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.81640625" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.81640625" customWidth="1"/>
   </cols>
@@ -34652,7 +34658,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1747</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -38932,7 +38938,7 @@
         <v>36</v>
       </c>
       <c r="P28" s="46" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="Q28" s="46" t="s">
         <v>36</v>
@@ -43822,19 +43828,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" customWidth="1"/>
-    <col min="8" max="8" width="13.1796875" customWidth="1"/>
-    <col min="22" max="22" width="10.453125" customWidth="1"/>
-    <col min="24" max="24" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" customWidth="1"/>
+    <col min="23" max="23" width="10.453125" customWidth="1"/>
+    <col min="25" max="25" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="13">
+    <row r="1" spans="1:26" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -43842,83 +43849,86 @@
         <v>1799</v>
       </c>
       <c r="C1" s="43" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>1351</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1" s="43" t="s">
         <v>1788</v>
       </c>
-      <c r="F1" s="43" t="s">
-        <v>1789</v>
-      </c>
-      <c r="G1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>1354</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>1355</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>1356</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>1357</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>1358</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>1359</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>1360</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>815</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>1614</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1655</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="Y1" s="43" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="43" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
-      <c r="B2" s="44">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C2" s="44">
         <v>0</v>
       </c>
       <c r="D2">
@@ -43961,41 +43971,44 @@
         <v>0</v>
       </c>
       <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>10</v>
       </c>
-      <c r="R2" s="44" t="s">
+      <c r="S2" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
       <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2">
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2">
         <v>11</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>1657</v>
       </c>
-      <c r="Y2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+      <c r="Z2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
-      <c r="B3" s="44">
-        <v>0</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C3" s="44">
         <v>0</v>
       </c>
       <c r="D3">
@@ -44038,42 +44051,45 @@
         <v>0</v>
       </c>
       <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>10</v>
       </c>
-      <c r="R3" s="44" t="s">
+      <c r="S3" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
       <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3">
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3">
         <v>11</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>1658</v>
       </c>
-      <c r="Y3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
-      <c r="B4" s="44">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="B4" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C4" s="44">
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -44085,17 +44101,17 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
       <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
         <v>0</v>
       </c>
@@ -44115,41 +44131,44 @@
         <v>0</v>
       </c>
       <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
         <v>10</v>
       </c>
-      <c r="R4" s="44" t="s">
+      <c r="S4" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
       <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V4" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4">
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4">
         <v>11</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>1659</v>
       </c>
-      <c r="Y4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="44" t="s">
-        <v>1777</v>
-      </c>
-      <c r="B5" s="44">
-        <v>0</v>
-      </c>
-      <c r="C5">
+        <v>1776</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C5" s="44">
         <v>0</v>
       </c>
       <c r="D5">
@@ -44192,41 +44211,44 @@
         <v>0</v>
       </c>
       <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
         <v>10</v>
       </c>
-      <c r="R5" s="44" t="s">
+      <c r="S5" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
       <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V5" t="s">
-        <v>36</v>
-      </c>
-      <c r="W5">
+      <c r="W5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5">
         <v>11</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>1660</v>
       </c>
-      <c r="Y5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
-      <c r="B6" s="44">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C6" s="44">
         <v>0</v>
       </c>
       <c r="D6">
@@ -44269,41 +44291,44 @@
         <v>0</v>
       </c>
       <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>10</v>
       </c>
-      <c r="R6" s="44" t="s">
+      <c r="S6" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
       <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V6" t="s">
-        <v>36</v>
-      </c>
-      <c r="W6">
+      <c r="W6" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6">
         <v>11</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>1660</v>
       </c>
-      <c r="Y6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
-      <c r="B7" s="44">
-        <v>0</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C7" s="44">
         <v>0</v>
       </c>
       <c r="D7">
@@ -44346,49 +44371,52 @@
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>10</v>
       </c>
-      <c r="R7" s="44" t="s">
+      <c r="S7" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
       <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V7" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7">
+      <c r="W7" t="s">
+        <v>36</v>
+      </c>
+      <c r="X7">
         <v>11</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>1661</v>
       </c>
-      <c r="Y7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
-      <c r="B8" s="44">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+      <c r="B8" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C8" s="44">
+        <v>1</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>50</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
         <v>0</v>
       </c>
@@ -44423,49 +44451,52 @@
         <v>0</v>
       </c>
       <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>10</v>
       </c>
-      <c r="R8" s="44" t="s">
+      <c r="S8" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
       <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>1615</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>11</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>1662</v>
       </c>
-      <c r="Y8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
-      <c r="B9" s="44">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
+      <c r="B9" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C9" s="44">
+        <v>1</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>50</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
       <c r="F9">
         <v>0</v>
       </c>
@@ -44500,41 +44531,44 @@
         <v>0</v>
       </c>
       <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>10</v>
       </c>
-      <c r="R9" s="44" t="s">
+      <c r="S9" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
       <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="V9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9">
+      <c r="W9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9">
         <v>11</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>1663</v>
       </c>
-      <c r="Y9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
-      <c r="B10" s="44">
-        <v>0</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C10" s="44">
         <v>0</v>
       </c>
       <c r="D10">
@@ -44553,11 +44587,11 @@
         <v>0</v>
       </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>5</v>
       </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
       <c r="K10">
         <v>0</v>
       </c>
@@ -44577,41 +44611,44 @@
         <v>0</v>
       </c>
       <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
         <v>10</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
       <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="V10" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10">
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10">
         <v>11</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
         <v>1664</v>
       </c>
-      <c r="Y10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
-      <c r="B11" s="44">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C11" s="44">
         <v>0</v>
       </c>
       <c r="D11">
@@ -44654,41 +44691,44 @@
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>10</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="S11" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
       <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V11" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11">
+      <c r="W11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11">
         <v>11</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
         <v>1665</v>
       </c>
-      <c r="Y11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
-      <c r="B12" s="44">
-        <v>0</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C12" s="44">
         <v>0</v>
       </c>
       <c r="D12">
@@ -44731,41 +44771,44 @@
         <v>0</v>
       </c>
       <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>10</v>
       </c>
-      <c r="R12" s="44" t="s">
+      <c r="S12" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
       <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V12" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12">
+      <c r="W12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12">
         <v>11</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>1666</v>
       </c>
-      <c r="Y12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+      <c r="Z12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
-      <c r="B13" s="44">
-        <v>0</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C13" s="44">
         <v>0</v>
       </c>
       <c r="D13">
@@ -44808,41 +44851,44 @@
         <v>0</v>
       </c>
       <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>10</v>
       </c>
-      <c r="R13" s="44" t="s">
+      <c r="S13" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
       <c r="T13">
-        <v>1</v>
-      </c>
-      <c r="U13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V13" t="s">
-        <v>36</v>
-      </c>
-      <c r="W13">
+      <c r="W13" t="s">
+        <v>36</v>
+      </c>
+      <c r="X13">
         <v>11</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>1667</v>
       </c>
-      <c r="Y13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+      <c r="Z13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
-      <c r="B14" s="44">
-        <v>0</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C14" s="44">
         <v>0</v>
       </c>
       <c r="D14">
@@ -44885,41 +44931,44 @@
         <v>0</v>
       </c>
       <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
         <v>10</v>
       </c>
-      <c r="R14" s="44" t="s">
+      <c r="S14" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
       <c r="T14">
-        <v>1</v>
-      </c>
-      <c r="U14" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V14" t="s">
-        <v>36</v>
-      </c>
-      <c r="W14">
+      <c r="W14" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14">
         <v>11</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>1668</v>
       </c>
-      <c r="Y14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
-      <c r="B15" s="44">
-        <v>0</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C15" s="44">
         <v>0</v>
       </c>
       <c r="D15">
@@ -44962,41 +45011,44 @@
         <v>0</v>
       </c>
       <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
         <v>10</v>
       </c>
-      <c r="R15" s="44" t="s">
+      <c r="S15" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
       <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="U15" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V15" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15">
+      <c r="W15" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15">
         <v>11</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>1669</v>
       </c>
-      <c r="Y15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
-      <c r="B16" s="44">
-        <v>0</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C16" s="44">
         <v>0</v>
       </c>
       <c r="D16">
@@ -45039,49 +45091,52 @@
         <v>0</v>
       </c>
       <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
         <v>10</v>
       </c>
-      <c r="R16" s="44" t="s">
+      <c r="S16" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
       <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V16" t="s">
-        <v>36</v>
-      </c>
-      <c r="W16">
+      <c r="W16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16">
         <v>11</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>1670</v>
       </c>
-      <c r="Y16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
-      <c r="B17" s="44">
-        <v>0</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C17" s="44">
         <v>0</v>
       </c>
       <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>50</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
       <c r="F17">
         <v>0</v>
       </c>
@@ -45092,11 +45147,11 @@
         <v>0</v>
       </c>
       <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>5</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
       <c r="K17">
         <v>0</v>
       </c>
@@ -45116,41 +45171,44 @@
         <v>0</v>
       </c>
       <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
         <v>10</v>
       </c>
-      <c r="R17" s="44" t="s">
+      <c r="S17" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
       <c r="T17">
-        <v>1</v>
-      </c>
-      <c r="U17" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
         <v>1616</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>11</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
         <v>1671</v>
       </c>
-      <c r="Y17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+      <c r="Z17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
-      <c r="B18" s="44">
-        <v>0</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C18" s="44">
         <v>0</v>
       </c>
       <c r="D18">
@@ -45193,41 +45251,44 @@
         <v>0</v>
       </c>
       <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
         <v>10</v>
       </c>
-      <c r="R18" s="44" t="s">
+      <c r="S18" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
       <c r="T18">
-        <v>1</v>
-      </c>
-      <c r="U18" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V18" t="s">
-        <v>36</v>
-      </c>
-      <c r="W18">
+      <c r="W18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X18">
         <v>11</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>1672</v>
       </c>
-      <c r="Y18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+      <c r="Z18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
-      <c r="B19" s="44">
-        <v>0</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C19" s="44">
         <v>0</v>
       </c>
       <c r="D19">
@@ -45270,41 +45331,44 @@
         <v>0</v>
       </c>
       <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
         <v>10</v>
       </c>
-      <c r="R19" s="44" t="s">
+      <c r="S19" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
       <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V19" t="s">
-        <v>36</v>
-      </c>
-      <c r="W19">
+      <c r="W19" t="s">
+        <v>36</v>
+      </c>
+      <c r="X19">
         <v>11</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
         <v>1673</v>
       </c>
-      <c r="Y19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+      <c r="Z19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
-      <c r="B20" s="44">
-        <v>0</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C20" s="44">
         <v>0</v>
       </c>
       <c r="D20">
@@ -45347,41 +45411,44 @@
         <v>0</v>
       </c>
       <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
         <v>10</v>
       </c>
-      <c r="R20" s="44" t="s">
+      <c r="S20" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
       <c r="T20">
-        <v>1</v>
-      </c>
-      <c r="U20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V20" t="s">
-        <v>36</v>
-      </c>
-      <c r="W20">
+      <c r="W20" t="s">
+        <v>36</v>
+      </c>
+      <c r="X20">
         <v>11</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
         <v>1674</v>
       </c>
-      <c r="Y20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
-      <c r="B21" s="44">
-        <v>0</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C21" s="44">
         <v>0</v>
       </c>
       <c r="D21">
@@ -45424,41 +45491,44 @@
         <v>0</v>
       </c>
       <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
         <v>10</v>
       </c>
-      <c r="R21" s="44" t="s">
+      <c r="S21" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
       <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="U21" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V21" t="s">
-        <v>36</v>
-      </c>
-      <c r="W21">
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21">
         <v>11</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
         <v>1658</v>
       </c>
-      <c r="Y21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
-      <c r="B22" s="44">
-        <v>0</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C22" s="44">
         <v>0</v>
       </c>
       <c r="D22">
@@ -45501,41 +45571,44 @@
         <v>0</v>
       </c>
       <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
         <v>10</v>
       </c>
-      <c r="R22" s="44" t="s">
+      <c r="S22" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
       <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V22" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22">
+      <c r="W22" t="s">
+        <v>36</v>
+      </c>
+      <c r="X22">
         <v>11</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>1658</v>
       </c>
-      <c r="Y22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+      <c r="Z22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
-      <c r="B23" s="44">
-        <v>0</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C23" s="44">
         <v>0</v>
       </c>
       <c r="D23">
@@ -45578,41 +45651,44 @@
         <v>0</v>
       </c>
       <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
         <v>10</v>
       </c>
-      <c r="R23" s="44" t="s">
+      <c r="S23" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
       <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V23" t="s">
-        <v>36</v>
-      </c>
-      <c r="W23">
+      <c r="W23" t="s">
+        <v>36</v>
+      </c>
+      <c r="X23">
         <v>11</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>1658</v>
       </c>
-      <c r="Y23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
-      <c r="B24" s="44">
-        <v>0</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C24" s="44">
         <v>0</v>
       </c>
       <c r="D24">
@@ -45655,41 +45731,44 @@
         <v>0</v>
       </c>
       <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
         <v>10</v>
       </c>
-      <c r="R24" s="44" t="s">
+      <c r="S24" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
       <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V24" t="s">
-        <v>36</v>
-      </c>
-      <c r="W24">
+      <c r="W24" t="s">
+        <v>36</v>
+      </c>
+      <c r="X24">
         <v>11</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>1658</v>
       </c>
-      <c r="Y24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
-      <c r="B25" s="44">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C25" s="44">
         <v>0</v>
       </c>
       <c r="D25">
@@ -45732,41 +45811,44 @@
         <v>0</v>
       </c>
       <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
         <v>10</v>
       </c>
-      <c r="R25" s="44" t="s">
+      <c r="S25" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
       <c r="T25">
-        <v>1</v>
-      </c>
-      <c r="U25" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V25" t="s">
-        <v>36</v>
-      </c>
-      <c r="W25">
+      <c r="W25" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25">
         <v>11</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>1658</v>
       </c>
-      <c r="Y25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+      <c r="Z25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
-      <c r="B26" s="44">
-        <v>0</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C26" s="44">
         <v>0</v>
       </c>
       <c r="D26">
@@ -45809,41 +45891,44 @@
         <v>0</v>
       </c>
       <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
         <v>10</v>
       </c>
-      <c r="R26" s="44" t="s">
+      <c r="S26" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
       <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V26" t="s">
-        <v>36</v>
-      </c>
-      <c r="W26">
+      <c r="W26" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26">
         <v>11</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>1559</v>
       </c>
-      <c r="Y26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+      <c r="Z26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
-      <c r="B27" s="44">
-        <v>0</v>
-      </c>
-      <c r="C27">
+      <c r="B27" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C27" s="44">
         <v>0</v>
       </c>
       <c r="D27">
@@ -45886,41 +45971,44 @@
         <v>0</v>
       </c>
       <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>10</v>
       </c>
-      <c r="R27" s="44" t="s">
+      <c r="S27" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
       <c r="T27">
-        <v>1</v>
-      </c>
-      <c r="U27" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V27" t="s">
-        <v>36</v>
-      </c>
-      <c r="W27">
+      <c r="W27" t="s">
+        <v>36</v>
+      </c>
+      <c r="X27">
         <v>11</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>1658</v>
       </c>
-      <c r="Y27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
-      <c r="B28" s="44">
-        <v>0</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C28" s="44">
         <v>0</v>
       </c>
       <c r="D28">
@@ -45963,41 +46051,44 @@
         <v>0</v>
       </c>
       <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
         <v>10</v>
       </c>
-      <c r="R28" s="44" t="s">
+      <c r="S28" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
       <c r="T28">
-        <v>1</v>
-      </c>
-      <c r="U28" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V28" t="s">
-        <v>36</v>
-      </c>
-      <c r="W28">
+      <c r="W28" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28">
         <v>11</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
         <v>1658</v>
       </c>
-      <c r="Y28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+      <c r="Z28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="44" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B29" s="44">
-        <v>0</v>
-      </c>
-      <c r="C29">
+        <v>1747</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C29" s="44">
         <v>0</v>
       </c>
       <c r="D29">
@@ -46040,184 +46131,273 @@
         <v>0</v>
       </c>
       <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
         <v>10</v>
       </c>
-      <c r="R29" s="44" t="s">
+      <c r="S29" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
       <c r="T29">
-        <v>1</v>
-      </c>
-      <c r="U29" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V29" t="s">
-        <v>36</v>
-      </c>
-      <c r="W29">
+      <c r="W29" t="s">
+        <v>36</v>
+      </c>
+      <c r="X29">
         <v>11</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
         <v>1658</v>
       </c>
-      <c r="Y29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+      <c r="Z29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="44" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C30" s="44">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>10</v>
+      </c>
+      <c r="S30" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="W30" t="s">
+        <v>36</v>
+      </c>
+      <c r="X30">
+        <v>11</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>896</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="A31" s="44" t="s">
         <v>1778</v>
       </c>
-      <c r="B30" s="44">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
+      <c r="B31" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C31" s="44">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
         <v>10</v>
       </c>
-      <c r="R30" s="44" t="s">
+      <c r="S31" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>1</v>
-      </c>
-      <c r="U30" s="44" t="s">
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V30" t="s">
-        <v>36</v>
-      </c>
-      <c r="W30">
+      <c r="W31" t="s">
+        <v>36</v>
+      </c>
+      <c r="X31">
         <v>11</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y31" t="s">
         <v>896</v>
       </c>
-      <c r="Y30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25">
-      <c r="A31" s="44" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B31" s="44">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
+      <c r="Z31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="A32" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C32" s="44">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>50</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
         <v>10</v>
       </c>
-      <c r="R31" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31" s="44" t="s">
+      <c r="S32" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="V31" t="s">
-        <v>36</v>
-      </c>
-      <c r="W31">
+      <c r="W32" t="s">
+        <v>36</v>
+      </c>
+      <c r="X32">
         <v>11</v>
       </c>
-      <c r="X31" t="s">
-        <v>896</v>
-      </c>
-      <c r="Y31" t="s">
+      <c r="Y32" t="s">
+        <v>1671</v>
+      </c>
+      <c r="Z32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46293,10 +46473,10 @@
         <v>10</v>
       </c>
       <c r="D1" s="43" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>1788</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>1789</v>
       </c>
       <c r="F1" s="43" t="s">
         <v>8</v>
@@ -46446,10 +46626,10 @@
         <v>7</v>
       </c>
       <c r="BC1" s="43" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="BD1" s="43" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="BE1" s="43"/>
       <c r="BF1" s="43"/>
@@ -46620,7 +46800,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BD2" t="s">
         <v>36</v>
@@ -46790,7 +46970,7 @@
         <v>0</v>
       </c>
       <c r="BC3" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD3" t="s">
         <v>36</v>
@@ -46960,7 +47140,7 @@
         <v>1</v>
       </c>
       <c r="BC4" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD4" t="s">
         <v>36</v>
@@ -47300,7 +47480,7 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="BD6" t="s">
         <v>36</v>
@@ -47470,7 +47650,7 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BD7" t="s">
         <v>36</v>
@@ -47640,7 +47820,7 @@
         <v>0</v>
       </c>
       <c r="BC8" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BD8" t="s">
         <v>36</v>
@@ -47810,7 +47990,7 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BD9" t="s">
         <v>36</v>
@@ -47980,7 +48160,7 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD10" t="s">
         <v>36</v>
@@ -48150,7 +48330,7 @@
         <v>0</v>
       </c>
       <c r="BC11" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD11" t="s">
         <v>36</v>
@@ -48490,7 +48670,7 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="BD13" t="s">
         <v>36</v>
@@ -48660,7 +48840,7 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BD14" t="s">
         <v>36</v>
@@ -48830,7 +49010,7 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BD15" t="s">
         <v>36</v>
@@ -49000,7 +49180,7 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BD16" t="s">
         <v>36</v>
@@ -49170,7 +49350,7 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD17" t="s">
         <v>36</v>
@@ -49340,7 +49520,7 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD18" t="s">
         <v>36</v>
@@ -49680,7 +49860,7 @@
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="BD20" t="s">
         <v>36</v>
@@ -49850,7 +50030,7 @@
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BD21" t="s">
         <v>36</v>
@@ -50020,7 +50200,7 @@
         <v>0</v>
       </c>
       <c r="BC22" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BD22" t="s">
         <v>36</v>
@@ -50190,7 +50370,7 @@
         <v>0</v>
       </c>
       <c r="BC23" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BD23" t="s">
         <v>36</v>
@@ -50360,7 +50540,7 @@
         <v>0</v>
       </c>
       <c r="BC24" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD24" t="s">
         <v>36</v>
@@ -50530,7 +50710,7 @@
         <v>0</v>
       </c>
       <c r="BC25" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD25" t="s">
         <v>36</v>
@@ -50870,7 +51050,7 @@
         <v>0</v>
       </c>
       <c r="BC27" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="BD27" t="s">
         <v>36</v>
@@ -51040,7 +51220,7 @@
         <v>0</v>
       </c>
       <c r="BC28" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BD28" t="s">
         <v>36</v>
@@ -51210,7 +51390,7 @@
         <v>0</v>
       </c>
       <c r="BC29" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BD29" t="s">
         <v>36</v>
@@ -51380,7 +51560,7 @@
         <v>0</v>
       </c>
       <c r="BC30" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BD30" t="s">
         <v>36</v>
@@ -51550,7 +51730,7 @@
         <v>0</v>
       </c>
       <c r="BC31" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD31" t="s">
         <v>36</v>
@@ -51720,7 +51900,7 @@
         <v>0</v>
       </c>
       <c r="BC32" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD32" t="s">
         <v>36</v>
@@ -52060,7 +52240,7 @@
         <v>0</v>
       </c>
       <c r="BC34" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="BD34" t="s">
         <v>36</v>
@@ -52068,7 +52248,7 @@
     </row>
     <row r="35" spans="1:56">
       <c r="A35" s="44" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -52230,7 +52410,7 @@
         <v>0</v>
       </c>
       <c r="BC35" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BD35" t="s">
         <v>36</v>
@@ -52238,7 +52418,7 @@
     </row>
     <row r="36" spans="1:56">
       <c r="A36" s="44" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -52328,7 +52508,7 @@
         <v>10</v>
       </c>
       <c r="AE36" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="AF36" s="44" t="s">
         <v>1479</v>
@@ -52400,7 +52580,7 @@
         <v>0</v>
       </c>
       <c r="BC36" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BD36" t="s">
         <v>36</v>
@@ -52408,7 +52588,7 @@
     </row>
     <row r="37" spans="1:56">
       <c r="A37" s="44" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -52570,7 +52750,7 @@
         <v>0</v>
       </c>
       <c r="BC37" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BD37" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C784ABA-B6EC-4350-884C-BC6A2B99ED00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1109B3-53EC-4C50-8A1A-7693FBACC5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7891" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="1804">
   <si>
     <t>NAME</t>
   </si>
@@ -5590,6 +5590,12 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1</t>
+  </si>
+  <si>
+    <t>book_fairy</t>
+  </si>
+  <si>
+    <t>trinket</t>
   </si>
 </sst>
 </file>
@@ -6749,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="48">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="I4" s="48">
         <v>45</v>
@@ -43828,7 +43834,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -46398,6 +46404,86 @@
         <v>1671</v>
       </c>
       <c r="Z32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26">
+      <c r="A33" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C33" s="44">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>-50</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>10</v>
+      </c>
+      <c r="S33" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="W33" t="s">
+        <v>36</v>
+      </c>
+      <c r="X33">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>1671</v>
+      </c>
+      <c r="Z33" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1109B3-53EC-4C50-8A1A-7693FBACC5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D4C6BA-3180-4A41-9E5E-49B395C2A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="1805">
   <si>
     <t>NAME</t>
   </si>
@@ -5589,13 +5589,16 @@
     <t>offhand</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1</t>
-  </si>
-  <si>
     <t>book_fairy</t>
   </si>
   <si>
     <t>trinket</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5</t>
+  </si>
+  <si>
+    <t>potion</t>
   </si>
 </sst>
 </file>
@@ -34607,7 +34610,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="84.81640625" customWidth="1"/>
+    <col min="2" max="2" width="94.26953125" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.81640625" customWidth="1"/>
   </cols>
@@ -34664,7 +34667,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -46172,7 +46175,7 @@
         <v>1777</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>1368</v>
+        <v>1804</v>
       </c>
       <c r="C30" s="44">
         <v>0</v>
@@ -46252,7 +46255,7 @@
         <v>1778</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>1368</v>
+        <v>1804</v>
       </c>
       <c r="C31" s="44">
         <v>0</v>
@@ -46409,10 +46412,10 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="44" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B33" s="44" t="s">
         <v>1802</v>
-      </c>
-      <c r="B33" s="44" t="s">
-        <v>1803</v>
       </c>
       <c r="C33" s="44">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D4C6BA-3180-4A41-9E5E-49B395C2A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F395E-34FE-4F94-9DC3-460624EF2805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7968" uniqueCount="1810">
   <si>
     <t>NAME</t>
   </si>
@@ -5595,10 +5595,25 @@
     <t>trinket</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5</t>
-  </si>
-  <si>
     <t>potion</t>
+  </si>
+  <si>
+    <t>USE_SKILL</t>
+  </si>
+  <si>
+    <t>mana_heal</t>
+  </si>
+  <si>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>cure</t>
+  </si>
+  <si>
+    <t>cure_potion</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5#cure_potion,3</t>
   </si>
 </sst>
 </file>
@@ -34610,7 +34625,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="94.26953125" customWidth="1"/>
+    <col min="2" max="2" width="105" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.81640625" customWidth="1"/>
   </cols>
@@ -34667,7 +34682,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -43837,20 +43852,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" customWidth="1"/>
-    <col min="23" max="23" width="10.453125" customWidth="1"/>
-    <col min="25" max="25" width="11.54296875" customWidth="1"/>
+    <col min="2" max="3" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" customWidth="1"/>
+    <col min="24" max="24" width="10.453125" customWidth="1"/>
+    <col min="26" max="26" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="13">
+    <row r="1" spans="1:27" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -43858,89 +43873,92 @@
         <v>1799</v>
       </c>
       <c r="C1" s="43" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>1798</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>1351</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>1787</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>1788</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>1354</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>1355</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>1356</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>1357</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>1358</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>1359</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>1360</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>815</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1614</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>1655</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Z1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>1795</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
       <c r="B2" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C2" s="44">
-        <v>0</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="44">
         <v>0</v>
       </c>
       <c r="E2">
@@ -43983,44 +44001,47 @@
         <v>0</v>
       </c>
       <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>10</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="T2" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X2">
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2">
         <v>11</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>1657</v>
       </c>
-      <c r="Z2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="AA2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
       <c r="B3" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C3" s="44">
-        <v>0</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="44">
         <v>0</v>
       </c>
       <c r="E3">
@@ -44063,45 +44084,48 @@
         <v>0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>10</v>
       </c>
-      <c r="S3" s="44" t="s">
+      <c r="T3" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3">
+      <c r="X3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3">
         <v>11</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>1658</v>
       </c>
-      <c r="Z3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="AA3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
       <c r="B4" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="C4" s="44">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="C4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="44">
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -44113,17 +44137,17 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
       <c r="L4">
         <v>0</v>
       </c>
@@ -44143,44 +44167,47 @@
         <v>0</v>
       </c>
       <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>10</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="T4" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X4">
+      <c r="X4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4">
         <v>11</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>1659</v>
       </c>
-      <c r="Z4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="44" t="s">
         <v>1776</v>
       </c>
       <c r="B5" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C5" s="44">
-        <v>0</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="44">
         <v>0</v>
       </c>
       <c r="E5">
@@ -44223,44 +44250,47 @@
         <v>0</v>
       </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>10</v>
       </c>
-      <c r="S5" s="44" t="s">
+      <c r="T5" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W5" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5">
+      <c r="X5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5">
         <v>11</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>1660</v>
       </c>
-      <c r="Z5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C6" s="44">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="44">
         <v>0</v>
       </c>
       <c r="E6">
@@ -44303,44 +44333,47 @@
         <v>0</v>
       </c>
       <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>10</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="T6" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W6" t="s">
-        <v>36</v>
-      </c>
-      <c r="X6">
+      <c r="X6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6">
         <v>11</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>1660</v>
       </c>
-      <c r="Z6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C7" s="44">
-        <v>0</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="44">
         <v>0</v>
       </c>
       <c r="E7">
@@ -44383,52 +44416,55 @@
         <v>0</v>
       </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>10</v>
       </c>
-      <c r="S7" s="44" t="s">
+      <c r="T7" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W7" t="s">
-        <v>36</v>
-      </c>
-      <c r="X7">
+      <c r="X7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7">
         <v>11</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>1661</v>
       </c>
-      <c r="Z7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="C8" s="44">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+      <c r="C8" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="44">
+        <v>1</v>
       </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>50</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -44463,52 +44499,55 @@
         <v>0</v>
       </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>10</v>
       </c>
-      <c r="S8" s="44" t="s">
+      <c r="T8" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>1615</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>11</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>1662</v>
       </c>
-      <c r="Z8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
       <c r="B9" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="C9" s="44">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+      <c r="C9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="44">
+        <v>1</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -44543,44 +44582,47 @@
         <v>0</v>
       </c>
       <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>10</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="T9" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="W9" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9">
+      <c r="X9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y9">
         <v>11</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="Z9" t="s">
         <v>1663</v>
       </c>
-      <c r="Z9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C10" s="44">
-        <v>0</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="44">
         <v>0</v>
       </c>
       <c r="E10">
@@ -44599,11 +44641,11 @@
         <v>0</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>5</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
       <c r="L10">
         <v>0</v>
       </c>
@@ -44623,44 +44665,47 @@
         <v>0</v>
       </c>
       <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>10</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="W10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10">
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10">
         <v>11</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Z10" t="s">
         <v>1664</v>
       </c>
-      <c r="Z10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
       <c r="B11" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C11" s="44">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="44">
         <v>0</v>
       </c>
       <c r="E11">
@@ -44703,44 +44748,47 @@
         <v>0</v>
       </c>
       <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>10</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="T11" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W11" t="s">
-        <v>36</v>
-      </c>
-      <c r="X11">
+      <c r="X11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11">
         <v>11</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
         <v>1665</v>
       </c>
-      <c r="Z11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C12" s="44">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="44">
         <v>0</v>
       </c>
       <c r="E12">
@@ -44783,44 +44831,47 @@
         <v>0</v>
       </c>
       <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>10</v>
       </c>
-      <c r="S12" s="44" t="s">
+      <c r="T12" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W12" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12">
+      <c r="X12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12">
         <v>11</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Z12" t="s">
         <v>1666</v>
       </c>
-      <c r="Z12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C13" s="44">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="44">
         <v>0</v>
       </c>
       <c r="E13">
@@ -44863,44 +44914,47 @@
         <v>0</v>
       </c>
       <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>10</v>
       </c>
-      <c r="S13" s="44" t="s">
+      <c r="T13" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W13" t="s">
-        <v>36</v>
-      </c>
-      <c r="X13">
+      <c r="X13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y13">
         <v>11</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
         <v>1667</v>
       </c>
-      <c r="Z13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="AA13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C14" s="44">
-        <v>0</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="44">
         <v>0</v>
       </c>
       <c r="E14">
@@ -44943,44 +44997,47 @@
         <v>0</v>
       </c>
       <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>10</v>
       </c>
-      <c r="S14" s="44" t="s">
+      <c r="T14" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W14" t="s">
-        <v>36</v>
-      </c>
-      <c r="X14">
+      <c r="X14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14">
         <v>11</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
         <v>1668</v>
       </c>
-      <c r="Z14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
       <c r="B15" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C15" s="44">
-        <v>0</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="44">
         <v>0</v>
       </c>
       <c r="E15">
@@ -45023,44 +45080,47 @@
         <v>0</v>
       </c>
       <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>10</v>
       </c>
-      <c r="S15" s="44" t="s">
+      <c r="T15" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W15" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15">
+      <c r="X15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15">
         <v>11</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Z15" t="s">
         <v>1669</v>
       </c>
-      <c r="Z15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
       <c r="B16" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C16" s="44">
-        <v>0</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="44">
         <v>0</v>
       </c>
       <c r="E16">
@@ -45103,52 +45163,55 @@
         <v>0</v>
       </c>
       <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>10</v>
       </c>
-      <c r="S16" s="44" t="s">
+      <c r="T16" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W16" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16">
+      <c r="X16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y16">
         <v>11</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Z16" t="s">
         <v>1670</v>
       </c>
-      <c r="Z16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="AA16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
       <c r="B17" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="C17" s="44">
-        <v>0</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="44">
         <v>0</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>50</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -45159,11 +45222,11 @@
         <v>0</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>5</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
       <c r="L17">
         <v>0</v>
       </c>
@@ -45183,44 +45246,47 @@
         <v>0</v>
       </c>
       <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>10</v>
       </c>
-      <c r="S17" s="44" t="s">
+      <c r="T17" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>1</v>
-      </c>
-      <c r="V17" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>1616</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>11</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Z17" t="s">
         <v>1671</v>
       </c>
-      <c r="Z17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C18" s="44">
-        <v>0</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="44">
         <v>0</v>
       </c>
       <c r="E18">
@@ -45263,44 +45329,47 @@
         <v>0</v>
       </c>
       <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>10</v>
       </c>
-      <c r="S18" s="44" t="s">
+      <c r="T18" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>1</v>
-      </c>
-      <c r="V18" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W18" t="s">
-        <v>36</v>
-      </c>
-      <c r="X18">
+      <c r="X18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y18">
         <v>11</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="Z18" t="s">
         <v>1672</v>
       </c>
-      <c r="Z18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AA18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
       <c r="B19" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C19" s="44">
-        <v>0</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="44">
         <v>0</v>
       </c>
       <c r="E19">
@@ -45343,44 +45412,47 @@
         <v>0</v>
       </c>
       <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>10</v>
       </c>
-      <c r="S19" s="44" t="s">
+      <c r="T19" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W19" t="s">
-        <v>36</v>
-      </c>
-      <c r="X19">
+      <c r="X19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y19">
         <v>11</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
         <v>1673</v>
       </c>
-      <c r="Z19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AA19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C20" s="44">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="44">
         <v>0</v>
       </c>
       <c r="E20">
@@ -45423,44 +45495,47 @@
         <v>0</v>
       </c>
       <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>10</v>
       </c>
-      <c r="S20" s="44" t="s">
+      <c r="T20" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W20" t="s">
-        <v>36</v>
-      </c>
-      <c r="X20">
+      <c r="X20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y20">
         <v>11</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Z20" t="s">
         <v>1674</v>
       </c>
-      <c r="Z20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
       <c r="B21" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C21" s="44">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="44">
         <v>0</v>
       </c>
       <c r="E21">
@@ -45503,44 +45578,47 @@
         <v>0</v>
       </c>
       <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <v>10</v>
       </c>
-      <c r="S21" s="44" t="s">
+      <c r="T21" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W21" t="s">
-        <v>36</v>
-      </c>
-      <c r="X21">
+      <c r="X21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y21">
         <v>11</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Z21" t="s">
         <v>1658</v>
       </c>
-      <c r="Z21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
       <c r="B22" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C22" s="44">
-        <v>0</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="44">
         <v>0</v>
       </c>
       <c r="E22">
@@ -45583,44 +45661,47 @@
         <v>0</v>
       </c>
       <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <v>10</v>
       </c>
-      <c r="S22" s="44" t="s">
+      <c r="T22" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W22" t="s">
-        <v>36</v>
-      </c>
-      <c r="X22">
+      <c r="X22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y22">
         <v>11</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Z22" t="s">
         <v>1658</v>
       </c>
-      <c r="Z22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
       <c r="B23" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C23" s="44">
-        <v>0</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="44">
         <v>0</v>
       </c>
       <c r="E23">
@@ -45663,44 +45744,47 @@
         <v>0</v>
       </c>
       <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>10</v>
       </c>
-      <c r="S23" s="44" t="s">
+      <c r="T23" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W23" t="s">
-        <v>36</v>
-      </c>
-      <c r="X23">
+      <c r="X23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y23">
         <v>11</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Z23" t="s">
         <v>1658</v>
       </c>
-      <c r="Z23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
       <c r="B24" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C24" s="44">
-        <v>0</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="44">
         <v>0</v>
       </c>
       <c r="E24">
@@ -45743,44 +45827,47 @@
         <v>0</v>
       </c>
       <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>10</v>
       </c>
-      <c r="S24" s="44" t="s">
+      <c r="T24" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W24" t="s">
-        <v>36</v>
-      </c>
-      <c r="X24">
+      <c r="X24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y24">
         <v>11</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Z24" t="s">
         <v>1658</v>
       </c>
-      <c r="Z24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
       <c r="B25" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C25" s="44">
-        <v>0</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="44">
         <v>0</v>
       </c>
       <c r="E25">
@@ -45823,44 +45910,47 @@
         <v>0</v>
       </c>
       <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>10</v>
       </c>
-      <c r="S25" s="44" t="s">
+      <c r="T25" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W25" t="s">
-        <v>36</v>
-      </c>
-      <c r="X25">
+      <c r="X25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y25">
         <v>11</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Z25" t="s">
         <v>1658</v>
       </c>
-      <c r="Z25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
       <c r="B26" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C26" s="44">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="44">
         <v>0</v>
       </c>
       <c r="E26">
@@ -45903,44 +45993,47 @@
         <v>0</v>
       </c>
       <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>10</v>
       </c>
-      <c r="S26" s="44" t="s">
+      <c r="T26" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W26" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26">
+      <c r="X26" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y26">
         <v>11</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>1559</v>
       </c>
-      <c r="Z26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="AA26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
       <c r="B27" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C27" s="44">
-        <v>0</v>
-      </c>
-      <c r="D27">
+      <c r="C27" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="44">
         <v>0</v>
       </c>
       <c r="E27">
@@ -45983,44 +46076,47 @@
         <v>0</v>
       </c>
       <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>10</v>
       </c>
-      <c r="S27" s="44" t="s">
+      <c r="T27" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
       <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W27" t="s">
-        <v>36</v>
-      </c>
-      <c r="X27">
+      <c r="X27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y27">
         <v>11</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>1658</v>
       </c>
-      <c r="Z27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
       <c r="B28" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C28" s="44">
-        <v>0</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="44">
         <v>0</v>
       </c>
       <c r="E28">
@@ -46063,44 +46159,47 @@
         <v>0</v>
       </c>
       <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>10</v>
       </c>
-      <c r="S28" s="44" t="s">
+      <c r="T28" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
-        <v>1</v>
-      </c>
-      <c r="V28" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W28" t="s">
-        <v>36</v>
-      </c>
-      <c r="X28">
+      <c r="X28" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y28">
         <v>11</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>1658</v>
       </c>
-      <c r="Z28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="44" t="s">
         <v>1747</v>
       </c>
       <c r="B29" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="C29" s="44">
-        <v>0</v>
-      </c>
-      <c r="D29">
+      <c r="C29" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="44">
         <v>0</v>
       </c>
       <c r="E29">
@@ -46143,44 +46242,47 @@
         <v>0</v>
       </c>
       <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>10</v>
       </c>
-      <c r="S29" s="44" t="s">
+      <c r="T29" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="V29" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W29" t="s">
-        <v>36</v>
-      </c>
-      <c r="X29">
+      <c r="X29" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y29">
         <v>11</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" t="s">
         <v>1658</v>
       </c>
-      <c r="Z29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="44" t="s">
         <v>1777</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>1804</v>
-      </c>
-      <c r="C30" s="44">
-        <v>0</v>
-      </c>
-      <c r="D30">
+        <v>1803</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D30" s="44">
         <v>0</v>
       </c>
       <c r="E30">
@@ -46223,44 +46325,47 @@
         <v>0</v>
       </c>
       <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>10</v>
       </c>
-      <c r="S30" s="44" t="s">
+      <c r="T30" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
       <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="V30" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W30" t="s">
-        <v>36</v>
-      </c>
-      <c r="X30">
+      <c r="X30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y30">
         <v>11</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>896</v>
       </c>
-      <c r="Z30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="AA30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="44" t="s">
         <v>1778</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>1804</v>
-      </c>
-      <c r="C31" s="44">
-        <v>0</v>
-      </c>
-      <c r="D31">
+        <v>1803</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D31" s="44">
         <v>0</v>
       </c>
       <c r="E31">
@@ -46303,44 +46408,47 @@
         <v>0</v>
       </c>
       <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>10</v>
       </c>
-      <c r="S31" s="44" t="s">
+      <c r="T31" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W31" t="s">
-        <v>36</v>
-      </c>
-      <c r="X31">
+      <c r="X31" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y31">
         <v>11</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>896</v>
       </c>
-      <c r="Z31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="AA31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="44" t="s">
         <v>238</v>
       </c>
       <c r="B32" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="C32" s="44">
-        <v>0</v>
-      </c>
-      <c r="D32">
+      <c r="C32" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="44">
         <v>0</v>
       </c>
       <c r="E32">
@@ -46359,11 +46467,11 @@
         <v>0</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>50</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
       <c r="L32">
         <v>0</v>
       </c>
@@ -46383,61 +46491,64 @@
         <v>0</v>
       </c>
       <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
         <v>10</v>
       </c>
-      <c r="S32" s="44" t="s">
+      <c r="T32" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
-        <v>1</v>
-      </c>
-      <c r="V32" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>1</v>
+      </c>
+      <c r="W32" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W32" t="s">
-        <v>36</v>
-      </c>
-      <c r="X32">
+      <c r="X32" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y32">
         <v>11</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Z32" t="s">
         <v>1671</v>
       </c>
-      <c r="Z32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="44" t="s">
         <v>1801</v>
       </c>
       <c r="B33" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="C33" s="44">
-        <v>0</v>
-      </c>
-      <c r="D33">
+      <c r="C33" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>50</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
         <v>-50</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
       <c r="J33">
         <v>0</v>
       </c>
@@ -46463,30 +46574,116 @@
         <v>0</v>
       </c>
       <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>10</v>
       </c>
-      <c r="S33" s="44" t="s">
+      <c r="T33" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
       <c r="U33">
-        <v>1</v>
-      </c>
-      <c r="V33" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>1</v>
+      </c>
+      <c r="W33" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="W33" t="s">
-        <v>36</v>
-      </c>
-      <c r="X33">
+      <c r="X33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y33">
         <v>11</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Z33" t="s">
         <v>1671</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
+      <c r="A34" s="44" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D34" s="44">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>10</v>
+      </c>
+      <c r="T34" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="X34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y34">
+        <v>11</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>896</v>
+      </c>
+      <c r="AA34" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46497,243 +46694,246 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BI39"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" customWidth="1"/>
-    <col min="4" max="4" width="7.54296875" customWidth="1"/>
-    <col min="5" max="5" width="12.90625" customWidth="1"/>
-    <col min="6" max="6" width="8.6328125" customWidth="1"/>
-    <col min="7" max="7" width="13.26953125" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" customWidth="1"/>
-    <col min="10" max="10" width="6.7265625" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="7.6328125" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" customWidth="1"/>
-    <col min="14" max="14" width="7.453125" customWidth="1"/>
-    <col min="15" max="15" width="7.6328125" customWidth="1"/>
-    <col min="16" max="16" width="9.7265625" customWidth="1"/>
-    <col min="17" max="17" width="7.7265625" customWidth="1"/>
-    <col min="18" max="18" width="7.90625" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="9.1796875" customWidth="1"/>
-    <col min="21" max="24" width="7.90625" customWidth="1"/>
-    <col min="25" max="25" width="9.36328125" customWidth="1"/>
-    <col min="26" max="26" width="6.54296875" customWidth="1"/>
-    <col min="27" max="27" width="6.453125" customWidth="1"/>
-    <col min="28" max="28" width="9.36328125" customWidth="1"/>
-    <col min="29" max="29" width="13.81640625" customWidth="1"/>
-    <col min="30" max="30" width="7.1796875" customWidth="1"/>
-    <col min="31" max="31" width="11.54296875" customWidth="1"/>
-    <col min="32" max="32" width="13.81640625" customWidth="1"/>
-    <col min="33" max="33" width="9.6328125" customWidth="1"/>
-    <col min="34" max="34" width="8.08984375" customWidth="1"/>
-    <col min="35" max="35" width="7.26953125" customWidth="1"/>
-    <col min="36" max="36" width="10.90625" customWidth="1"/>
-    <col min="37" max="37" width="6.453125" customWidth="1"/>
-    <col min="38" max="38" width="12" customWidth="1"/>
-    <col min="39" max="39" width="7.1796875" customWidth="1"/>
-    <col min="40" max="40" width="9.54296875" customWidth="1"/>
-    <col min="41" max="41" width="9.36328125" customWidth="1"/>
-    <col min="42" max="42" width="7.90625" customWidth="1"/>
-    <col min="43" max="43" width="6.7265625" customWidth="1"/>
-    <col min="44" max="44" width="6.453125" customWidth="1"/>
-    <col min="45" max="45" width="6.54296875" customWidth="1"/>
-    <col min="46" max="46" width="5.90625" customWidth="1"/>
-    <col min="47" max="47" width="19.08984375" customWidth="1"/>
-    <col min="48" max="48" width="7.81640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="53" width="7.08984375" customWidth="1"/>
-    <col min="55" max="55" width="11.08984375" customWidth="1"/>
-    <col min="56" max="60" width="10" customWidth="1"/>
+    <col min="2" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="5.26953125" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="12" width="8" customWidth="1"/>
+    <col min="13" max="13" width="7.6328125" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" customWidth="1"/>
+    <col min="15" max="15" width="7.453125" customWidth="1"/>
+    <col min="16" max="16" width="7.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" customWidth="1"/>
+    <col min="18" max="18" width="7.7265625" customWidth="1"/>
+    <col min="19" max="19" width="7.90625" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" customWidth="1"/>
+    <col min="22" max="25" width="7.90625" customWidth="1"/>
+    <col min="26" max="26" width="9.36328125" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" customWidth="1"/>
+    <col min="28" max="28" width="6.453125" customWidth="1"/>
+    <col min="29" max="29" width="9.36328125" customWidth="1"/>
+    <col min="30" max="30" width="13.81640625" customWidth="1"/>
+    <col min="31" max="31" width="7.1796875" customWidth="1"/>
+    <col min="32" max="32" width="11.54296875" customWidth="1"/>
+    <col min="33" max="33" width="13.81640625" customWidth="1"/>
+    <col min="34" max="34" width="9.6328125" customWidth="1"/>
+    <col min="35" max="35" width="8.08984375" customWidth="1"/>
+    <col min="36" max="36" width="7.26953125" customWidth="1"/>
+    <col min="37" max="37" width="10.90625" customWidth="1"/>
+    <col min="38" max="38" width="6.453125" customWidth="1"/>
+    <col min="39" max="39" width="12" customWidth="1"/>
+    <col min="40" max="40" width="7.1796875" customWidth="1"/>
+    <col min="41" max="41" width="9.54296875" customWidth="1"/>
+    <col min="42" max="42" width="9.36328125" customWidth="1"/>
+    <col min="43" max="43" width="7.90625" customWidth="1"/>
+    <col min="44" max="44" width="6.7265625" customWidth="1"/>
+    <col min="45" max="45" width="6.453125" customWidth="1"/>
+    <col min="46" max="46" width="6.54296875" customWidth="1"/>
+    <col min="47" max="47" width="5.90625" customWidth="1"/>
+    <col min="48" max="48" width="19.08984375" customWidth="1"/>
+    <col min="49" max="49" width="7.81640625" customWidth="1"/>
+    <col min="51" max="51" width="7" customWidth="1"/>
+    <col min="52" max="54" width="7.08984375" customWidth="1"/>
+    <col min="56" max="56" width="11.08984375" customWidth="1"/>
+    <col min="57" max="61" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="13">
+    <row r="1" spans="1:61" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>1351</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>1787</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>1788</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>1354</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>1355</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>1356</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>1528</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>1529</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>1588</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>1589</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>1357</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>1358</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>1359</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>1375</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>1484</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1525</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>1526</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Z1" s="43" t="s">
         <v>1527</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>1212</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="AB1" s="43" t="s">
         <v>1492</v>
       </c>
-      <c r="AB1" s="43" t="s">
+      <c r="AC1" s="43" t="s">
         <v>1403</v>
       </c>
-      <c r="AC1" s="43" t="s">
+      <c r="AD1" s="43" t="s">
         <v>1496</v>
       </c>
-      <c r="AD1" s="43" t="s">
+      <c r="AE1" s="43" t="s">
         <v>1360</v>
       </c>
-      <c r="AE1" s="43" t="s">
+      <c r="AF1" s="43" t="s">
         <v>1495</v>
       </c>
-      <c r="AF1" s="43" t="s">
+      <c r="AG1" s="43" t="s">
         <v>1362</v>
       </c>
-      <c r="AG1" s="43" t="s">
+      <c r="AH1" s="43" t="s">
         <v>1471</v>
       </c>
-      <c r="AH1" s="43" t="s">
+      <c r="AI1" s="43" t="s">
         <v>1472</v>
       </c>
-      <c r="AI1" s="43" t="s">
+      <c r="AJ1" s="43" t="s">
         <v>1473</v>
       </c>
-      <c r="AJ1" s="43" t="s">
+      <c r="AK1" s="43" t="s">
         <v>1476</v>
       </c>
-      <c r="AK1" s="43" t="s">
+      <c r="AL1" s="43" t="s">
         <v>1503</v>
       </c>
-      <c r="AL1" s="43" t="s">
+      <c r="AM1" s="43" t="s">
         <v>1488</v>
       </c>
-      <c r="AM1" s="43" t="s">
+      <c r="AN1" s="43" t="s">
         <v>1594</v>
       </c>
-      <c r="AN1" s="43" t="s">
+      <c r="AO1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="AO1" s="43" t="s">
+      <c r="AP1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="AP1" s="43" t="s">
+      <c r="AQ1" s="43" t="s">
         <v>1376</v>
       </c>
-      <c r="AQ1" s="43" t="s">
+      <c r="AR1" s="43" t="s">
         <v>1480</v>
       </c>
-      <c r="AR1" s="43" t="s">
+      <c r="AS1" s="43" t="s">
         <v>1612</v>
       </c>
-      <c r="AS1" s="43" t="s">
+      <c r="AT1" s="43" t="s">
         <v>1553</v>
       </c>
-      <c r="AT1" s="43" t="s">
+      <c r="AU1" s="43" t="s">
         <v>1482</v>
       </c>
-      <c r="AU1" s="43" t="s">
+      <c r="AV1" s="43" t="s">
         <v>1610</v>
       </c>
-      <c r="AV1" s="43" t="s">
+      <c r="AW1" s="43" t="s">
         <v>1618</v>
       </c>
-      <c r="AW1" s="43" t="s">
+      <c r="AX1" s="43" t="s">
         <v>1622</v>
       </c>
-      <c r="AX1" s="43" t="s">
+      <c r="AY1" s="43" t="s">
         <v>1623</v>
       </c>
-      <c r="AY1" s="43" t="s">
+      <c r="AZ1" s="43" t="s">
         <v>1685</v>
       </c>
-      <c r="AZ1" s="43" t="s">
+      <c r="BA1" s="43" t="s">
         <v>1694</v>
       </c>
-      <c r="BA1" s="43" t="s">
+      <c r="BB1" s="43" t="s">
         <v>1695</v>
       </c>
-      <c r="BB1" s="43" t="s">
+      <c r="BC1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="BC1" s="43" t="s">
+      <c r="BD1" s="43" t="s">
         <v>1759</v>
       </c>
-      <c r="BD1" s="43" t="s">
+      <c r="BE1" s="43" t="s">
         <v>1795</v>
       </c>
-      <c r="BE1" s="43"/>
       <c r="BF1" s="43"/>
       <c r="BG1" s="43"/>
       <c r="BH1" s="43"/>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1" s="43"/>
+    </row>
+    <row r="2" spans="1:61">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -46787,10 +46987,10 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -46802,73 +47002,73 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>-1</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
       <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <v>10</v>
       </c>
-      <c r="AE2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF2" s="44" t="s">
+      <c r="AF2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG2" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH2" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="44" t="s">
+      <c r="AI2" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK2" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL2" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN2">
+      <c r="AL2" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN2" s="44">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2">
         <v>1</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>36</v>
       </c>
       <c r="AU2">
         <v>0</v>
       </c>
-      <c r="AV2" t="s">
-        <v>36</v>
+      <c r="AV2">
+        <v>0</v>
       </c>
       <c r="AW2" t="s">
         <v>36</v>
@@ -46876,8 +47076,8 @@
       <c r="AX2" t="s">
         <v>36</v>
       </c>
-      <c r="AY2">
-        <v>0</v>
+      <c r="AY2" t="s">
+        <v>36</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -46888,22 +47088,25 @@
       <c r="BB2">
         <v>0</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="s">
         <v>1760</v>
       </c>
-      <c r="BD2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60">
+      <c r="BE2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
       <c r="A3" s="44" t="s">
         <v>42</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -46957,11 +47160,11 @@
         <v>0</v>
       </c>
       <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
         <v>4</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
       <c r="W3">
         <v>0</v>
       </c>
@@ -46972,73 +47175,73 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>-1</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
       <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
         <v>10</v>
       </c>
-      <c r="AE3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF3" s="44" t="s">
+      <c r="AF3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG3" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG3" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH3" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="44" t="s">
+      <c r="AI3" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK3" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL3" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN3">
+      <c r="AL3" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN3" s="44">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3">
         <v>1</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>36</v>
       </c>
       <c r="AU3">
         <v>0</v>
       </c>
-      <c r="AV3" t="s">
-        <v>36</v>
+      <c r="AV3">
+        <v>0</v>
       </c>
       <c r="AW3" t="s">
         <v>36</v>
@@ -47046,8 +47249,8 @@
       <c r="AX3" t="s">
         <v>36</v>
       </c>
-      <c r="AY3">
-        <v>0</v>
+      <c r="AY3" t="s">
+        <v>36</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -47058,14 +47261,17 @@
       <c r="BB3">
         <v>0</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="s">
         <v>1761</v>
       </c>
-      <c r="BD3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:60">
+      <c r="BE3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
       <c r="A4" s="44" t="s">
         <v>1371</v>
       </c>
@@ -47082,13 +47288,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -47127,11 +47333,11 @@
         <v>0</v>
       </c>
       <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>3</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
       <c r="W4">
         <v>0</v>
       </c>
@@ -47142,73 +47348,73 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>-1</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
       <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
         <v>10</v>
       </c>
-      <c r="AE4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF4" s="44" t="s">
+      <c r="AF4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG4" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH4" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="44" t="s">
+      <c r="AI4" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK4" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN4">
+      <c r="AL4" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="44">
         <v>0</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>36</v>
       </c>
       <c r="AU4">
         <v>0</v>
       </c>
-      <c r="AV4" t="s">
-        <v>36</v>
+      <c r="AV4">
+        <v>0</v>
       </c>
       <c r="AW4" t="s">
         <v>36</v>
@@ -47216,8 +47422,8 @@
       <c r="AX4" t="s">
         <v>36</v>
       </c>
-      <c r="AY4">
-        <v>0</v>
+      <c r="AY4" t="s">
+        <v>36</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -47226,16 +47432,19 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1</v>
-      </c>
-      <c r="BC4" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="s">
         <v>1762</v>
       </c>
-      <c r="BD4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:60">
+      <c r="BE4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
       <c r="A5" s="44" t="s">
         <v>1372</v>
       </c>
@@ -47243,11 +47452,11 @@
         <v>0</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>20</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -47297,11 +47506,11 @@
         <v>0</v>
       </c>
       <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
         <v>3</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
         <v>0</v>
       </c>
@@ -47312,73 +47521,73 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>-1</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
       <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>10</v>
       </c>
-      <c r="AE5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF5" s="44" t="s">
+      <c r="AF5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG5" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH5" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="44" t="s">
+      <c r="AI5" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK5" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN5">
+      <c r="AL5" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN5" s="44">
         <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>36</v>
       </c>
       <c r="AU5">
         <v>0</v>
       </c>
-      <c r="AV5" t="s">
-        <v>36</v>
+      <c r="AV5">
+        <v>0</v>
       </c>
       <c r="AW5" t="s">
         <v>36</v>
@@ -47386,8 +47595,8 @@
       <c r="AX5" t="s">
         <v>36</v>
       </c>
-      <c r="AY5">
-        <v>0</v>
+      <c r="AY5" t="s">
+        <v>36</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -47398,23 +47607,26 @@
       <c r="BB5">
         <v>0</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="s">
         <v>37</v>
       </c>
-      <c r="BD5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:60">
+      <c r="BE5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
       <c r="A6" s="44" t="s">
         <v>1469</v>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>-1</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6">
         <v>0</v>
       </c>
@@ -47467,11 +47679,11 @@
         <v>0</v>
       </c>
       <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
         <v>3</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
       <c r="W6">
         <v>0</v>
       </c>
@@ -47482,73 +47694,73 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <v>-1</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
       <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
         <v>10</v>
       </c>
-      <c r="AE6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF6" s="44" t="s">
+      <c r="AF6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="44" t="s">
         <v>1479</v>
       </c>
-      <c r="AG6" s="44" t="s">
+      <c r="AH6" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AH6" s="44" t="s">
+      <c r="AI6" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="AJ6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK6" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL6" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN6">
+      <c r="AL6" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN6" s="44">
         <v>0</v>
       </c>
       <c r="AO6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6">
         <v>1</v>
       </c>
-      <c r="AQ6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>36</v>
       </c>
       <c r="AU6">
         <v>0</v>
       </c>
-      <c r="AV6" t="s">
-        <v>36</v>
+      <c r="AV6">
+        <v>0</v>
       </c>
       <c r="AW6" t="s">
         <v>36</v>
@@ -47556,8 +47768,8 @@
       <c r="AX6" t="s">
         <v>36</v>
       </c>
-      <c r="AY6">
-        <v>0</v>
+      <c r="AY6" t="s">
+        <v>36</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -47568,14 +47780,17 @@
       <c r="BB6">
         <v>0</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="s">
         <v>1765</v>
       </c>
-      <c r="BD6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:60">
+      <c r="BE6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61">
       <c r="A7" s="44" t="s">
         <v>1483</v>
       </c>
@@ -47637,11 +47852,11 @@
         <v>0</v>
       </c>
       <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>3</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
       <c r="W7">
         <v>0</v>
       </c>
@@ -47652,73 +47867,73 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>-1</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
       <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
         <v>10</v>
       </c>
-      <c r="AE7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF7" s="44" t="s">
+      <c r="AF7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG7" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG7" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH7" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="44" t="s">
+      <c r="AI7" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK7" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL7" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN7">
+      <c r="AL7" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN7" s="44">
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
         <v>60</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>1481</v>
       </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>36</v>
       </c>
       <c r="AU7">
         <v>0</v>
       </c>
-      <c r="AV7" t="s">
-        <v>36</v>
+      <c r="AV7">
+        <v>0</v>
       </c>
       <c r="AW7" t="s">
         <v>36</v>
@@ -47726,8 +47941,8 @@
       <c r="AX7" t="s">
         <v>36</v>
       </c>
-      <c r="AY7">
-        <v>0</v>
+      <c r="AY7" t="s">
+        <v>36</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -47738,23 +47953,26 @@
       <c r="BB7">
         <v>0</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="s">
         <v>1763</v>
       </c>
-      <c r="BD7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:60">
+      <c r="BE7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61">
       <c r="A8" s="44" t="s">
         <v>1430</v>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>10</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
       <c r="D8">
         <v>0</v>
       </c>
@@ -47807,11 +48025,11 @@
         <v>0</v>
       </c>
       <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
         <v>3</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
         <v>0</v>
       </c>
@@ -47822,73 +48040,73 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <v>-1</v>
       </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
       <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>30</v>
       </c>
-      <c r="AE8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF8" s="44" t="s">
+      <c r="AF8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG8" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG8" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH8" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="44" t="s">
+      <c r="AI8" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK8" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL8" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN8">
+      <c r="AL8" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN8" s="44">
         <v>0</v>
       </c>
       <c r="AO8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
         <v>60</v>
       </c>
-      <c r="AQ8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
+      <c r="AR8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>36</v>
       </c>
       <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
       </c>
       <c r="AW8" t="s">
         <v>36</v>
@@ -47896,8 +48114,8 @@
       <c r="AX8" t="s">
         <v>36</v>
       </c>
-      <c r="AY8">
-        <v>0</v>
+      <c r="AY8" t="s">
+        <v>36</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -47908,22 +48126,25 @@
       <c r="BB8">
         <v>0</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="s">
         <v>1764</v>
       </c>
-      <c r="BD8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:60">
+      <c r="BE8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61">
       <c r="A9" s="44" t="s">
         <v>1433</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -47977,13 +48198,13 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>3</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -47992,73 +48213,73 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
         <v>-1</v>
       </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
       <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
         <v>30</v>
       </c>
-      <c r="AE9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF9" s="44" t="s">
+      <c r="AF9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG9" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH9" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="44" t="s">
+      <c r="AI9" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK9" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN9">
+      <c r="AL9" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN9" s="44">
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
         <v>60</v>
       </c>
-      <c r="AQ9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
+      <c r="AR9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>36</v>
       </c>
       <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
       </c>
       <c r="AW9" t="s">
         <v>36</v>
@@ -48066,8 +48287,8 @@
       <c r="AX9" t="s">
         <v>36</v>
       </c>
-      <c r="AY9">
-        <v>0</v>
+      <c r="AY9" t="s">
+        <v>36</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -48078,14 +48299,17 @@
       <c r="BB9">
         <v>0</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="s">
         <v>1760</v>
       </c>
-      <c r="BD9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:60">
+      <c r="BE9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
       <c r="A10" s="44" t="s">
         <v>1447</v>
       </c>
@@ -48093,11 +48317,11 @@
         <v>0</v>
       </c>
       <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>20</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
@@ -48147,11 +48371,11 @@
         <v>0</v>
       </c>
       <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>3</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
       <c r="W10">
         <v>0</v>
       </c>
@@ -48162,73 +48386,73 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <v>-1</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
       <c r="AD10">
         <v>0</v>
       </c>
-      <c r="AE10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF10" s="44" t="s">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG10" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG10" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH10" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="44" t="s">
+      <c r="AI10" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK10" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN10">
+      <c r="AL10" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN10" s="44">
         <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>36</v>
       </c>
       <c r="AU10">
         <v>0</v>
       </c>
-      <c r="AV10" t="s">
-        <v>36</v>
+      <c r="AV10">
+        <v>0</v>
       </c>
       <c r="AW10" t="s">
         <v>36</v>
@@ -48236,8 +48460,8 @@
       <c r="AX10" t="s">
         <v>36</v>
       </c>
-      <c r="AY10">
-        <v>0</v>
+      <c r="AY10" t="s">
+        <v>36</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -48248,14 +48472,17 @@
       <c r="BB10">
         <v>0</v>
       </c>
-      <c r="BC10" t="s">
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="s">
         <v>1761</v>
       </c>
-      <c r="BD10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:60">
+      <c r="BE10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61">
       <c r="A11" s="44" t="s">
         <v>1524</v>
       </c>
@@ -48272,13 +48499,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>40</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -48317,11 +48544,11 @@
         <v>0</v>
       </c>
       <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
         <v>3</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
       <c r="W11">
         <v>0</v>
       </c>
@@ -48332,73 +48559,73 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <v>-1</v>
       </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
       <c r="AD11">
         <v>0</v>
       </c>
-      <c r="AE11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF11" s="44" t="s">
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG11" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH11" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="44" t="s">
+      <c r="AI11" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK11" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL11" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN11">
+      <c r="AL11" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN11" s="44">
         <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>36</v>
       </c>
       <c r="AU11">
         <v>0</v>
       </c>
-      <c r="AV11" t="s">
-        <v>36</v>
+      <c r="AV11">
+        <v>0</v>
       </c>
       <c r="AW11" t="s">
         <v>36</v>
@@ -48406,8 +48633,8 @@
       <c r="AX11" t="s">
         <v>36</v>
       </c>
-      <c r="AY11">
-        <v>0</v>
+      <c r="AY11" t="s">
+        <v>36</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -48418,14 +48645,17 @@
       <c r="BB11">
         <v>0</v>
       </c>
-      <c r="BC11" t="s">
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="s">
         <v>1762</v>
       </c>
-      <c r="BD11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:60">
+      <c r="BE11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61">
       <c r="A12" s="44" t="s">
         <v>1448</v>
       </c>
@@ -48442,13 +48672,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>20</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -48487,11 +48717,11 @@
         <v>0</v>
       </c>
       <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>3</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
       <c r="W12">
         <v>0</v>
       </c>
@@ -48502,73 +48732,73 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>-1</v>
       </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
       <c r="AD12">
         <v>0</v>
       </c>
-      <c r="AE12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF12" s="44" t="s">
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG12" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG12" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="44" t="s">
+      <c r="AI12" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK12" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL12" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN12">
+      <c r="AL12" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN12" s="44">
         <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>36</v>
       </c>
       <c r="AU12">
         <v>0</v>
       </c>
-      <c r="AV12" t="s">
-        <v>36</v>
+      <c r="AV12">
+        <v>0</v>
       </c>
       <c r="AW12" t="s">
         <v>36</v>
@@ -48576,8 +48806,8 @@
       <c r="AX12" t="s">
         <v>36</v>
       </c>
-      <c r="AY12">
-        <v>0</v>
+      <c r="AY12" t="s">
+        <v>36</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -48588,14 +48818,17 @@
       <c r="BB12">
         <v>0</v>
       </c>
-      <c r="BC12" t="s">
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="s">
         <v>37</v>
       </c>
-      <c r="BD12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:60">
+      <c r="BE12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61">
       <c r="A13" s="44" t="s">
         <v>1449</v>
       </c>
@@ -48618,11 +48851,11 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>20</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
       <c r="J13">
         <v>0</v>
       </c>
@@ -48657,11 +48890,11 @@
         <v>0</v>
       </c>
       <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>3</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
       <c r="W13">
         <v>0</v>
       </c>
@@ -48672,73 +48905,73 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>-1</v>
       </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
       <c r="AD13">
         <v>0</v>
       </c>
-      <c r="AE13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF13" s="44" t="s">
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG13" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG13" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH13" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="44" t="s">
+      <c r="AI13" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK13" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN13">
+      <c r="AL13" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN13" s="44">
         <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>36</v>
       </c>
       <c r="AU13">
         <v>0</v>
       </c>
-      <c r="AV13" t="s">
-        <v>36</v>
+      <c r="AV13">
+        <v>0</v>
       </c>
       <c r="AW13" t="s">
         <v>36</v>
@@ -48746,8 +48979,8 @@
       <c r="AX13" t="s">
         <v>36</v>
       </c>
-      <c r="AY13">
-        <v>0</v>
+      <c r="AY13" t="s">
+        <v>36</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -48758,22 +48991,25 @@
       <c r="BB13">
         <v>0</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="s">
         <v>1765</v>
       </c>
-      <c r="BD13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:60">
+      <c r="BE13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61">
       <c r="A14" s="44" t="s">
         <v>1485</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -48827,14 +49063,14 @@
         <v>0</v>
       </c>
       <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>3</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>2</v>
       </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
       <c r="X14">
         <v>0</v>
       </c>
@@ -48842,73 +49078,73 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
         <v>-1</v>
       </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
       <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
         <v>10</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AF14" t="s">
         <v>1494</v>
       </c>
-      <c r="AF14" s="44" t="s">
+      <c r="AG14" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG14" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH14" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="44" t="s">
+      <c r="AI14" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK14" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN14">
+      <c r="AL14" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN14" s="44">
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
         <v>1</v>
       </c>
-      <c r="AQ14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
+      <c r="AQ14">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>36</v>
       </c>
       <c r="AU14">
         <v>0</v>
       </c>
-      <c r="AV14" t="s">
-        <v>36</v>
+      <c r="AV14">
+        <v>0</v>
       </c>
       <c r="AW14" t="s">
         <v>36</v>
@@ -48916,8 +49152,8 @@
       <c r="AX14" t="s">
         <v>36</v>
       </c>
-      <c r="AY14">
-        <v>0</v>
+      <c r="AY14" t="s">
+        <v>36</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -48928,14 +49164,17 @@
       <c r="BB14">
         <v>0</v>
       </c>
-      <c r="BC14" t="s">
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="s">
         <v>1763</v>
       </c>
-      <c r="BD14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:60">
+      <c r="BE14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61">
       <c r="A15" s="44" t="s">
         <v>1489</v>
       </c>
@@ -48943,11 +49182,11 @@
         <v>0</v>
       </c>
       <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>20</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
@@ -48997,11 +49236,11 @@
         <v>0</v>
       </c>
       <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>3</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
       <c r="W15">
         <v>0</v>
       </c>
@@ -49012,73 +49251,73 @@
         <v>0</v>
       </c>
       <c r="Z15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
         <v>-1</v>
       </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
       <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
         <v>10</v>
       </c>
-      <c r="AE15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF15" s="44" t="s">
+      <c r="AF15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG15" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG15" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH15" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="44" t="s">
+      <c r="AI15" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK15" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL15" s="44" t="s">
+      <c r="AL15" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AM15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN15">
+      <c r="AN15" s="44">
         <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>36</v>
       </c>
       <c r="AU15">
         <v>0</v>
       </c>
-      <c r="AV15" t="s">
-        <v>36</v>
+      <c r="AV15">
+        <v>0</v>
       </c>
       <c r="AW15" t="s">
         <v>36</v>
@@ -49086,8 +49325,8 @@
       <c r="AX15" t="s">
         <v>36</v>
       </c>
-      <c r="AY15">
-        <v>0</v>
+      <c r="AY15" t="s">
+        <v>36</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -49098,14 +49337,17 @@
       <c r="BB15">
         <v>0</v>
       </c>
-      <c r="BC15" t="s">
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="s">
         <v>1764</v>
       </c>
-      <c r="BD15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:60">
+      <c r="BE15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61">
       <c r="A16" s="44" t="s">
         <v>1490</v>
       </c>
@@ -49122,13 +49364,13 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>20</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -49167,11 +49409,11 @@
         <v>0</v>
       </c>
       <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
         <v>3</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
       <c r="W16">
         <v>0</v>
       </c>
@@ -49182,73 +49424,73 @@
         <v>0</v>
       </c>
       <c r="Z16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
         <v>-1</v>
       </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
       <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
         <v>10</v>
       </c>
-      <c r="AE16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF16" s="44" t="s">
+      <c r="AF16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG16" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG16" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH16" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="44" t="s">
+      <c r="AI16" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK16" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="44" t="s">
+      <c r="AL16" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AM16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN16">
+      <c r="AN16" s="44">
         <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>36</v>
       </c>
       <c r="AU16">
         <v>0</v>
       </c>
-      <c r="AV16" t="s">
-        <v>36</v>
+      <c r="AV16">
+        <v>0</v>
       </c>
       <c r="AW16" t="s">
         <v>36</v>
@@ -49256,8 +49498,8 @@
       <c r="AX16" t="s">
         <v>36</v>
       </c>
-      <c r="AY16">
-        <v>0</v>
+      <c r="AY16" t="s">
+        <v>36</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -49268,26 +49510,29 @@
       <c r="BB16">
         <v>0</v>
       </c>
-      <c r="BC16" t="s">
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="s">
         <v>1760</v>
       </c>
-      <c r="BD16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:56">
+      <c r="BE16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:57">
       <c r="A17" s="44" t="s">
         <v>1494</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>20</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
@@ -49337,11 +49582,11 @@
         <v>0</v>
       </c>
       <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
         <v>3</v>
       </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
       <c r="W17">
         <v>0</v>
       </c>
@@ -49352,73 +49597,73 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
         <v>5</v>
       </c>
-      <c r="AC17">
-        <v>1</v>
-      </c>
       <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF17" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG17" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG17" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH17" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="44" t="s">
+      <c r="AI17" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK17" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL17" s="44" t="s">
+      <c r="AL17" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AM17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN17">
+      <c r="AN17" s="44">
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
         <v>1</v>
       </c>
-      <c r="AQ17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
+      <c r="AQ17">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>36</v>
       </c>
       <c r="AU17">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>1</v>
       </c>
       <c r="AW17" t="s">
         <v>36</v>
@@ -49426,8 +49671,8 @@
       <c r="AX17" t="s">
         <v>36</v>
       </c>
-      <c r="AY17">
-        <v>0</v>
+      <c r="AY17" t="s">
+        <v>36</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -49438,14 +49683,17 @@
       <c r="BB17">
         <v>0</v>
       </c>
-      <c r="BC17" t="s">
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="s">
         <v>1761</v>
       </c>
-      <c r="BD17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:56">
+      <c r="BE17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:57">
       <c r="A18" s="44" t="s">
         <v>1501</v>
       </c>
@@ -49507,11 +49755,11 @@
         <v>0</v>
       </c>
       <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>3</v>
       </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
       <c r="W18">
         <v>0</v>
       </c>
@@ -49522,73 +49770,73 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
         <v>5</v>
       </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
       <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF18" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG18" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH18" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI18" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="44" t="s">
+      <c r="AI18" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ18" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK18" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL18" s="44" t="s">
+      <c r="AL18" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AM18" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN18">
+      <c r="AN18" s="44">
         <v>0</v>
       </c>
       <c r="AO18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18">
         <v>1</v>
       </c>
-      <c r="AQ18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
+      <c r="AQ18">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>36</v>
       </c>
       <c r="AU18">
         <v>0</v>
       </c>
-      <c r="AV18" t="s">
-        <v>36</v>
+      <c r="AV18">
+        <v>0</v>
       </c>
       <c r="AW18" t="s">
         <v>36</v>
@@ -49596,8 +49844,8 @@
       <c r="AX18" t="s">
         <v>36</v>
       </c>
-      <c r="AY18">
-        <v>0</v>
+      <c r="AY18" t="s">
+        <v>36</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -49608,14 +49856,17 @@
       <c r="BB18">
         <v>0</v>
       </c>
-      <c r="BC18" t="s">
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="s">
         <v>1762</v>
       </c>
-      <c r="BD18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:56">
+      <c r="BE18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:57">
       <c r="A19" s="44" t="s">
         <v>1502</v>
       </c>
@@ -49623,11 +49874,11 @@
         <v>0</v>
       </c>
       <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
         <v>10</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
         <v>0</v>
       </c>
@@ -49677,13 +49928,13 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19">
         <v>3</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -49692,73 +49943,73 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
         <v>-1</v>
       </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
       <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
         <v>10</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AF19" t="s">
         <v>1501</v>
       </c>
-      <c r="AF19" s="44" t="s">
+      <c r="AG19" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG19" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH19" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI19" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="44" t="s">
+      <c r="AI19" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK19" s="44">
+      <c r="AL19" s="44">
         <v>100</v>
       </c>
-      <c r="AL19" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM19" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN19">
+      <c r="AM19" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN19" s="44">
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19">
+        <v>1</v>
+      </c>
+      <c r="AQ19">
         <v>5</v>
       </c>
-      <c r="AQ19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
+      <c r="AR19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>36</v>
       </c>
       <c r="AU19">
         <v>0</v>
       </c>
-      <c r="AV19" t="s">
-        <v>36</v>
+      <c r="AV19">
+        <v>0</v>
       </c>
       <c r="AW19" t="s">
         <v>36</v>
@@ -49766,8 +50017,8 @@
       <c r="AX19" t="s">
         <v>36</v>
       </c>
-      <c r="AY19">
-        <v>0</v>
+      <c r="AY19" t="s">
+        <v>36</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -49778,23 +50029,26 @@
       <c r="BB19">
         <v>0</v>
       </c>
-      <c r="BC19" t="s">
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="s">
         <v>37</v>
       </c>
-      <c r="BD19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:56">
+      <c r="BE19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:57">
       <c r="A20" s="44" t="s">
         <v>1431</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>10</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
       <c r="D20">
         <v>0</v>
       </c>
@@ -49847,88 +50101,88 @@
         <v>0</v>
       </c>
       <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
         <v>3</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
       <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
         <v>30</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>0.2</v>
       </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
       <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
         <v>10</v>
       </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
       <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
         <v>-1</v>
       </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
       <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
         <v>30</v>
       </c>
-      <c r="AE20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF20" s="44" t="s">
+      <c r="AF20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG20" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG20" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH20" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="44" t="s">
+      <c r="AI20" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK20" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL20" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN20">
+      <c r="AL20" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN20" s="44">
         <v>0</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
         <v>60</v>
       </c>
-      <c r="AQ20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT20">
-        <v>1</v>
+      <c r="AR20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>36</v>
       </c>
       <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
       </c>
       <c r="AW20" t="s">
         <v>36</v>
@@ -49936,8 +50190,8 @@
       <c r="AX20" t="s">
         <v>36</v>
       </c>
-      <c r="AY20">
-        <v>0</v>
+      <c r="AY20" t="s">
+        <v>36</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -49948,14 +50202,17 @@
       <c r="BB20">
         <v>0</v>
       </c>
-      <c r="BC20" t="s">
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="s">
         <v>1765</v>
       </c>
-      <c r="BD20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:56">
+      <c r="BE20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:57">
       <c r="A21" s="44" t="s">
         <v>1551</v>
       </c>
@@ -50017,11 +50274,11 @@
         <v>0</v>
       </c>
       <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
         <v>3</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
       <c r="W21">
         <v>0</v>
       </c>
@@ -50032,73 +50289,73 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
         <v>-1</v>
       </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
       <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
         <v>10</v>
       </c>
-      <c r="AE21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF21" s="44" t="s">
+      <c r="AF21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG21" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG21" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH21" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI21" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="44" t="s">
+      <c r="AI21" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK21" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL21" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM21" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
+      <c r="AL21" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN21" s="44">
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
         <v>60</v>
       </c>
-      <c r="AQ21" t="s">
+      <c r="AR21" t="s">
         <v>1552</v>
       </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="s">
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="s">
         <v>1554</v>
       </c>
-      <c r="AT21">
-        <v>1</v>
-      </c>
       <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
       </c>
       <c r="AW21" t="s">
         <v>36</v>
@@ -50106,8 +50363,8 @@
       <c r="AX21" t="s">
         <v>36</v>
       </c>
-      <c r="AY21">
-        <v>0</v>
+      <c r="AY21" t="s">
+        <v>36</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -50118,14 +50375,17 @@
       <c r="BB21">
         <v>0</v>
       </c>
-      <c r="BC21" t="s">
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="s">
         <v>1763</v>
       </c>
-      <c r="BD21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:56">
+      <c r="BE21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:57">
       <c r="A22" s="44" t="s">
         <v>1587</v>
       </c>
@@ -50184,13 +50444,13 @@
         <v>0</v>
       </c>
       <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
         <v>50</v>
       </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
       <c r="V22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -50202,73 +50462,73 @@
         <v>0</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
         <v>-1</v>
       </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
       <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
         <v>10</v>
       </c>
-      <c r="AE22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF22" s="44" t="s">
+      <c r="AF22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG22" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG22" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH22" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI22" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="44" t="s">
+      <c r="AI22" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ22" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK22" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL22" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM22" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN22">
+      <c r="AL22" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN22" s="44">
         <v>0</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22">
+        <v>1</v>
+      </c>
+      <c r="AQ22">
         <v>30</v>
       </c>
-      <c r="AQ22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
+      <c r="AR22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>36</v>
       </c>
       <c r="AU22">
         <v>0</v>
       </c>
-      <c r="AV22" t="s">
-        <v>36</v>
+      <c r="AV22">
+        <v>0</v>
       </c>
       <c r="AW22" t="s">
         <v>36</v>
@@ -50276,8 +50536,8 @@
       <c r="AX22" t="s">
         <v>36</v>
       </c>
-      <c r="AY22">
-        <v>0</v>
+      <c r="AY22" t="s">
+        <v>36</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -50288,14 +50548,17 @@
       <c r="BB22">
         <v>0</v>
       </c>
-      <c r="BC22" t="s">
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="s">
         <v>1764</v>
       </c>
-      <c r="BD22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:56">
+      <c r="BE22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:57">
       <c r="A23" s="44" t="s">
         <v>935</v>
       </c>
@@ -50357,11 +50620,11 @@
         <v>0</v>
       </c>
       <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
         <v>3</v>
       </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
       <c r="W23">
         <v>0</v>
       </c>
@@ -50372,73 +50635,73 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
         <v>-1</v>
       </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
       <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
         <v>10</v>
       </c>
-      <c r="AE23" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF23" s="44" t="s">
+      <c r="AF23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG23" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG23" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH23" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI23" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="44" t="s">
+      <c r="AI23" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ23" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK23" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL23" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM23" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
+      <c r="AL23" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN23" s="44">
+        <v>1</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23">
         <v>1</v>
       </c>
-      <c r="AQ23" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
+      <c r="AQ23">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>36</v>
       </c>
       <c r="AU23">
         <v>0</v>
       </c>
-      <c r="AV23" t="s">
-        <v>36</v>
+      <c r="AV23">
+        <v>0</v>
       </c>
       <c r="AW23" t="s">
         <v>36</v>
@@ -50446,8 +50709,8 @@
       <c r="AX23" t="s">
         <v>36</v>
       </c>
-      <c r="AY23">
-        <v>0</v>
+      <c r="AY23" t="s">
+        <v>36</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -50458,14 +50721,17 @@
       <c r="BB23">
         <v>0</v>
       </c>
-      <c r="BC23" t="s">
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="s">
         <v>1760</v>
       </c>
-      <c r="BD23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:56">
+      <c r="BE23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:57">
       <c r="A24" s="44" t="s">
         <v>1593</v>
       </c>
@@ -50527,11 +50793,11 @@
         <v>0</v>
       </c>
       <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
         <v>5</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
       <c r="W24">
         <v>0</v>
       </c>
@@ -50542,73 +50808,73 @@
         <v>0</v>
       </c>
       <c r="Z24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
         <v>-1</v>
       </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
       <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
         <v>10</v>
       </c>
-      <c r="AE24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF24" s="44" t="s">
+      <c r="AF24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG24" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG24" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH24" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI24" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="44" t="s">
+      <c r="AI24" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ24" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK24" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL24" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM24" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
+      <c r="AL24" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM24" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN24" s="44">
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24">
         <v>1</v>
       </c>
-      <c r="AQ24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>36</v>
       </c>
       <c r="AU24">
         <v>0</v>
       </c>
-      <c r="AV24" t="s">
-        <v>36</v>
+      <c r="AV24">
+        <v>0</v>
       </c>
       <c r="AW24" t="s">
         <v>36</v>
@@ -50616,8 +50882,8 @@
       <c r="AX24" t="s">
         <v>36</v>
       </c>
-      <c r="AY24">
-        <v>0</v>
+      <c r="AY24" t="s">
+        <v>36</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -50628,22 +50894,25 @@
       <c r="BB24">
         <v>0</v>
       </c>
-      <c r="BC24" t="s">
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="s">
         <v>1761</v>
       </c>
-      <c r="BD24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:56">
+      <c r="BE24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:57">
       <c r="A25" s="44" t="s">
         <v>1602</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -50697,10 +50966,10 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -50712,73 +50981,73 @@
         <v>0</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
         <v>-1</v>
       </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
       <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
         <v>10</v>
       </c>
-      <c r="AE25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF25" s="44" t="s">
+      <c r="AF25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG25" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG25" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH25" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI25" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="44" t="s">
+      <c r="AI25" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ25" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK25" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL25" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM25" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN25">
+      <c r="AL25" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN25" s="44">
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25">
         <v>1</v>
       </c>
-      <c r="AQ25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>36</v>
       </c>
       <c r="AU25">
         <v>0</v>
       </c>
-      <c r="AV25" t="s">
-        <v>36</v>
+      <c r="AV25">
+        <v>0</v>
       </c>
       <c r="AW25" t="s">
         <v>36</v>
@@ -50786,8 +51055,8 @@
       <c r="AX25" t="s">
         <v>36</v>
       </c>
-      <c r="AY25">
-        <v>0</v>
+      <c r="AY25" t="s">
+        <v>36</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -50798,14 +51067,17 @@
       <c r="BB25">
         <v>0</v>
       </c>
-      <c r="BC25" t="s">
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="s">
         <v>1762</v>
       </c>
-      <c r="BD25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:56">
+      <c r="BE25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:57">
       <c r="A26" s="44" t="s">
         <v>1611</v>
       </c>
@@ -50867,11 +51139,11 @@
         <v>0</v>
       </c>
       <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
         <v>3</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
       <c r="W26">
         <v>0</v>
       </c>
@@ -50882,73 +51154,73 @@
         <v>0</v>
       </c>
       <c r="Z26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
         <v>-1</v>
       </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
       <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
         <v>10</v>
       </c>
-      <c r="AE26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF26" s="44" t="s">
+      <c r="AF26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG26" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG26" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH26" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI26" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="44" t="s">
+      <c r="AI26" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ26" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK26" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM26" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
+      <c r="AL26" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN26" s="44">
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
+        <v>1</v>
+      </c>
+      <c r="AQ26">
         <v>60</v>
       </c>
-      <c r="AQ26" t="s">
+      <c r="AR26" t="s">
         <v>1552</v>
       </c>
-      <c r="AR26">
-        <v>1</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT26">
-        <v>1</v>
+      <c r="AS26">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>36</v>
       </c>
       <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
       </c>
       <c r="AW26" t="s">
         <v>36</v>
@@ -50956,8 +51228,8 @@
       <c r="AX26" t="s">
         <v>36</v>
       </c>
-      <c r="AY26">
-        <v>0</v>
+      <c r="AY26" t="s">
+        <v>36</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -50968,22 +51240,25 @@
       <c r="BB26">
         <v>0</v>
       </c>
-      <c r="BC26" t="s">
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="s">
         <v>37</v>
       </c>
-      <c r="BD26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:56">
+      <c r="BE26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:57">
       <c r="A27" s="44" t="s">
         <v>1615</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -51037,10 +51312,10 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -51052,73 +51327,73 @@
         <v>0</v>
       </c>
       <c r="Z27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
         <v>-1</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
       <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
         <v>10</v>
       </c>
-      <c r="AE27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF27" s="44" t="s">
+      <c r="AF27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG27" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG27" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH27" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI27" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="44" t="s">
+      <c r="AI27" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ27" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK27" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL27" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM27" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN27">
+      <c r="AL27" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN27" s="44">
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27">
         <v>1</v>
       </c>
-      <c r="AQ27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
+      <c r="AQ27">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>36</v>
       </c>
       <c r="AU27">
         <v>0</v>
       </c>
-      <c r="AV27" t="s">
-        <v>36</v>
+      <c r="AV27">
+        <v>0</v>
       </c>
       <c r="AW27" t="s">
         <v>36</v>
@@ -51126,8 +51401,8 @@
       <c r="AX27" t="s">
         <v>36</v>
       </c>
-      <c r="AY27">
-        <v>0</v>
+      <c r="AY27" t="s">
+        <v>36</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -51138,22 +51413,25 @@
       <c r="BB27">
         <v>0</v>
       </c>
-      <c r="BC27" t="s">
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="s">
         <v>1765</v>
       </c>
-      <c r="BD27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:56">
+      <c r="BE27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:57">
       <c r="A28" s="44" t="s">
         <v>1616</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -51207,11 +51485,11 @@
         <v>0</v>
       </c>
       <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
         <v>3</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
       <c r="W28">
         <v>0</v>
       </c>
@@ -51222,73 +51500,73 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
         <v>-1</v>
       </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
       <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
         <v>10</v>
       </c>
-      <c r="AE28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF28" s="44" t="s">
+      <c r="AF28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG28" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG28" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH28" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI28" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="44" t="s">
+      <c r="AI28" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ28" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK28" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL28" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM28" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN28">
+      <c r="AL28" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN28" s="44">
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28">
         <v>1</v>
       </c>
-      <c r="AQ28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
+      <c r="AQ28">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>36</v>
       </c>
       <c r="AU28">
         <v>0</v>
       </c>
-      <c r="AV28" t="s">
-        <v>36</v>
+      <c r="AV28">
+        <v>0</v>
       </c>
       <c r="AW28" t="s">
         <v>36</v>
@@ -51296,8 +51574,8 @@
       <c r="AX28" t="s">
         <v>36</v>
       </c>
-      <c r="AY28">
-        <v>0</v>
+      <c r="AY28" t="s">
+        <v>36</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -51308,22 +51586,25 @@
       <c r="BB28">
         <v>0</v>
       </c>
-      <c r="BC28" t="s">
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="s">
         <v>1763</v>
       </c>
-      <c r="BD28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:56">
+      <c r="BE28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:57">
       <c r="A29" s="44" t="s">
         <v>1620</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -51377,14 +51658,14 @@
         <v>0</v>
       </c>
       <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
         <v>3</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>2</v>
       </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
       <c r="X29">
         <v>0</v>
       </c>
@@ -51392,73 +51673,73 @@
         <v>0</v>
       </c>
       <c r="Z29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
         <v>-1</v>
       </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
       <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
         <v>10</v>
       </c>
-      <c r="AE29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF29" s="44" t="s">
+      <c r="AF29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG29" s="44" t="s">
         <v>1621</v>
-      </c>
-      <c r="AG29" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH29" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI29" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="44" t="s">
+      <c r="AI29" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ29" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK29" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL29" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM29" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN29">
+      <c r="AL29" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN29" s="44">
         <v>0</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29">
         <v>1</v>
       </c>
-      <c r="AQ29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
+      <c r="AQ29">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>36</v>
       </c>
       <c r="AU29">
         <v>0</v>
       </c>
-      <c r="AV29" t="s">
-        <v>36</v>
+      <c r="AV29">
+        <v>0</v>
       </c>
       <c r="AW29" t="s">
         <v>36</v>
@@ -51466,8 +51747,8 @@
       <c r="AX29" t="s">
         <v>36</v>
       </c>
-      <c r="AY29">
-        <v>0</v>
+      <c r="AY29" t="s">
+        <v>36</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -51478,22 +51759,25 @@
       <c r="BB29">
         <v>0</v>
       </c>
-      <c r="BC29" t="s">
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="s">
         <v>1764</v>
       </c>
-      <c r="BD29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:56">
+      <c r="BE29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:57">
       <c r="A30" s="44" t="s">
         <v>1624</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -51547,11 +51831,11 @@
         <v>0</v>
       </c>
       <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
         <v>3</v>
       </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
       <c r="W30">
         <v>0</v>
       </c>
@@ -51562,83 +51846,83 @@
         <v>0</v>
       </c>
       <c r="Z30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
         <v>-1</v>
       </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
       <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
         <v>10</v>
       </c>
-      <c r="AE30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF30" s="44" t="s">
+      <c r="AF30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG30" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG30" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH30" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI30" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="44" t="s">
+      <c r="AI30" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ30" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK30" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL30" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM30" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN30">
+      <c r="AL30" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN30" s="44">
         <v>0</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP30">
         <v>1</v>
       </c>
-      <c r="AQ30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
+      <c r="AQ30">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>36</v>
       </c>
       <c r="AU30">
         <v>0</v>
       </c>
-      <c r="AV30" t="s">
-        <v>36</v>
+      <c r="AV30">
+        <v>0</v>
       </c>
       <c r="AW30" t="s">
         <v>36</v>
       </c>
       <c r="AX30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY30" t="s">
         <v>1624</v>
       </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
       <c r="AZ30">
         <v>0</v>
       </c>
@@ -51648,14 +51932,17 @@
       <c r="BB30">
         <v>0</v>
       </c>
-      <c r="BC30" t="s">
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="s">
         <v>1760</v>
       </c>
-      <c r="BD30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:56">
+      <c r="BE30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:57">
       <c r="A31" s="44" t="s">
         <v>1647</v>
       </c>
@@ -51717,10 +52004,10 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -51732,73 +52019,73 @@
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
         <v>-1</v>
       </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
       <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
         <v>10</v>
       </c>
-      <c r="AE31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF31" s="44" t="s">
+      <c r="AF31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG31" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG31" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH31" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI31" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="44" t="s">
+      <c r="AI31" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ31" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK31" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL31" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM31" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN31">
+      <c r="AL31" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM31" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN31" s="44">
         <v>0</v>
       </c>
       <c r="AO31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31">
         <v>1</v>
       </c>
-      <c r="AQ31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
+      <c r="AQ31">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>36</v>
       </c>
       <c r="AU31">
         <v>0</v>
       </c>
-      <c r="AV31" t="s">
-        <v>36</v>
+      <c r="AV31">
+        <v>0</v>
       </c>
       <c r="AW31" t="s">
         <v>36</v>
@@ -51806,8 +52093,8 @@
       <c r="AX31" t="s">
         <v>36</v>
       </c>
-      <c r="AY31">
-        <v>0</v>
+      <c r="AY31" t="s">
+        <v>36</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -51818,14 +52105,17 @@
       <c r="BB31">
         <v>0</v>
       </c>
-      <c r="BC31" t="s">
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="s">
         <v>1761</v>
       </c>
-      <c r="BD31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:56">
+      <c r="BE31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:57">
       <c r="A32" s="44" t="s">
         <v>1578</v>
       </c>
@@ -51887,11 +52177,11 @@
         <v>0</v>
       </c>
       <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
         <v>3</v>
       </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
       <c r="W32">
         <v>0</v>
       </c>
@@ -51902,73 +52192,73 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
         <v>-1</v>
       </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
       <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
         <v>10</v>
       </c>
-      <c r="AE32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF32" s="44" t="s">
+      <c r="AF32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG32" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG32" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH32" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI32" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="44" t="s">
+      <c r="AI32" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ32" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK32" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM32" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN32">
+      <c r="AL32" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN32" s="44">
         <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>36</v>
       </c>
       <c r="AU32">
         <v>0</v>
       </c>
-      <c r="AV32" t="s">
-        <v>36</v>
+      <c r="AV32">
+        <v>0</v>
       </c>
       <c r="AW32" t="s">
         <v>36</v>
@@ -51976,8 +52266,8 @@
       <c r="AX32" t="s">
         <v>36</v>
       </c>
-      <c r="AY32">
-        <v>0</v>
+      <c r="AY32" t="s">
+        <v>36</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -51988,14 +52278,17 @@
       <c r="BB32">
         <v>0</v>
       </c>
-      <c r="BC32" t="s">
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="s">
         <v>1762</v>
       </c>
-      <c r="BD32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:56">
+      <c r="BE32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:57">
       <c r="A33" s="44" t="s">
         <v>1686</v>
       </c>
@@ -52057,10 +52350,10 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -52072,73 +52365,73 @@
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
         <v>-1</v>
       </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
       <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
         <v>10</v>
       </c>
-      <c r="AE33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF33" s="44" t="s">
+      <c r="AF33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG33" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG33" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH33" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI33" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="44" t="s">
+      <c r="AI33" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ33" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK33" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM33" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN33">
-        <v>0</v>
+      <c r="AL33" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN33" s="44">
+        <v>1</v>
       </c>
       <c r="AO33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP33">
         <v>1</v>
       </c>
-      <c r="AQ33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
+      <c r="AQ33">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>36</v>
       </c>
       <c r="AU33">
         <v>0</v>
       </c>
-      <c r="AV33" t="s">
-        <v>36</v>
+      <c r="AV33">
+        <v>0</v>
       </c>
       <c r="AW33" t="s">
         <v>36</v>
@@ -52146,8 +52439,8 @@
       <c r="AX33" t="s">
         <v>36</v>
       </c>
-      <c r="AY33">
-        <v>0</v>
+      <c r="AY33" t="s">
+        <v>36</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -52158,14 +52451,17 @@
       <c r="BB33">
         <v>0</v>
       </c>
-      <c r="BC33" t="s">
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="s">
         <v>37</v>
       </c>
-      <c r="BD33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:56">
+      <c r="BE33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:57">
       <c r="A34" s="44" t="s">
         <v>1728</v>
       </c>
@@ -52227,11 +52523,11 @@
         <v>0</v>
       </c>
       <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
         <v>3</v>
       </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
       <c r="W34">
         <v>0</v>
       </c>
@@ -52242,73 +52538,73 @@
         <v>0</v>
       </c>
       <c r="Z34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
         <v>-1</v>
       </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
       <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
         <v>10</v>
       </c>
-      <c r="AE34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF34" s="44" t="s">
+      <c r="AF34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG34" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG34" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH34" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI34" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="44" t="s">
+      <c r="AI34" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ34" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK34" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM34" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN34">
+      <c r="AL34" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN34" s="44">
         <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
-      </c>
-      <c r="AQ34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>36</v>
       </c>
       <c r="AU34">
         <v>0</v>
       </c>
-      <c r="AV34" t="s">
-        <v>36</v>
+      <c r="AV34">
+        <v>0</v>
       </c>
       <c r="AW34" t="s">
         <v>36</v>
@@ -52316,8 +52612,8 @@
       <c r="AX34" t="s">
         <v>36</v>
       </c>
-      <c r="AY34">
-        <v>0</v>
+      <c r="AY34" t="s">
+        <v>36</v>
       </c>
       <c r="AZ34">
         <v>0</v>
@@ -52328,14 +52624,17 @@
       <c r="BB34">
         <v>0</v>
       </c>
-      <c r="BC34" t="s">
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="s">
         <v>1765</v>
       </c>
-      <c r="BD34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:56">
+      <c r="BE34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:57">
       <c r="A35" s="44" t="s">
         <v>1786</v>
       </c>
@@ -52349,10 +52648,10 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -52397,11 +52696,11 @@
         <v>0</v>
       </c>
       <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
         <v>4</v>
       </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
       <c r="W35">
         <v>0</v>
       </c>
@@ -52412,73 +52711,73 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
         <v>-1</v>
       </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
       <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
         <v>10</v>
       </c>
-      <c r="AE35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF35" s="44" t="s">
+      <c r="AF35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG35" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AG35" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH35" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI35" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="44" t="s">
+      <c r="AI35" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ35" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK35" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL35" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM35" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN35">
+      <c r="AL35" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM35" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN35" s="44">
         <v>0</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP35">
         <v>1</v>
       </c>
-      <c r="AQ35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
+      <c r="AQ35">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>36</v>
       </c>
       <c r="AU35">
         <v>0</v>
       </c>
-      <c r="AV35" t="s">
-        <v>36</v>
+      <c r="AV35">
+        <v>0</v>
       </c>
       <c r="AW35" t="s">
         <v>36</v>
@@ -52486,8 +52785,8 @@
       <c r="AX35" t="s">
         <v>36</v>
       </c>
-      <c r="AY35">
-        <v>0</v>
+      <c r="AY35" t="s">
+        <v>36</v>
       </c>
       <c r="AZ35">
         <v>0</v>
@@ -52498,14 +52797,17 @@
       <c r="BB35">
         <v>0</v>
       </c>
-      <c r="BC35" t="s">
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="s">
         <v>1762</v>
       </c>
-      <c r="BD35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:56">
+      <c r="BE35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:57">
       <c r="A36" s="44" t="s">
         <v>1797</v>
       </c>
@@ -52567,14 +52869,14 @@
         <v>0</v>
       </c>
       <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
         <v>3</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>2</v>
       </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
       <c r="X36">
         <v>0</v>
       </c>
@@ -52582,73 +52884,73 @@
         <v>0</v>
       </c>
       <c r="Z36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
         <v>-1</v>
       </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
       <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
         <v>10</v>
       </c>
-      <c r="AE36" t="s">
+      <c r="AF36" t="s">
         <v>1796</v>
       </c>
-      <c r="AF36" s="44" t="s">
+      <c r="AG36" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG36" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH36" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI36" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="44" t="s">
+      <c r="AI36" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ36" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK36" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL36" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM36" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN36">
+      <c r="AL36" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN36" s="44">
         <v>0</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36">
         <v>1</v>
       </c>
-      <c r="AQ36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="s">
+        <v>36</v>
       </c>
       <c r="AU36">
         <v>0</v>
       </c>
-      <c r="AV36" t="s">
-        <v>36</v>
+      <c r="AV36">
+        <v>0</v>
       </c>
       <c r="AW36" t="s">
         <v>36</v>
@@ -52656,8 +52958,8 @@
       <c r="AX36" t="s">
         <v>36</v>
       </c>
-      <c r="AY36">
-        <v>0</v>
+      <c r="AY36" t="s">
+        <v>36</v>
       </c>
       <c r="AZ36">
         <v>0</v>
@@ -52668,26 +52970,29 @@
       <c r="BB36">
         <v>0</v>
       </c>
-      <c r="BC36" t="s">
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="s">
         <v>1763</v>
       </c>
-      <c r="BD36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:56">
+      <c r="BE36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:57">
       <c r="A37" s="44" t="s">
         <v>1796</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
         <v>50</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
       <c r="E37">
         <v>0</v>
       </c>
@@ -52737,11 +53042,11 @@
         <v>0</v>
       </c>
       <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
         <v>3</v>
       </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
       <c r="W37">
         <v>0</v>
       </c>
@@ -52752,73 +53057,73 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
         <v>5</v>
       </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
       <c r="AD37">
         <v>0</v>
       </c>
-      <c r="AE37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF37" s="44" t="s">
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG37" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AG37" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AH37" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AI37" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="44" t="s">
+      <c r="AI37" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ37" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AK37" s="44">
-        <v>1</v>
-      </c>
-      <c r="AL37" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM37" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN37">
+      <c r="AL37" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN37" s="44">
         <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="s">
+        <v>36</v>
       </c>
       <c r="AU37">
-        <v>1</v>
-      </c>
-      <c r="AV37" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AV37">
+        <v>1</v>
       </c>
       <c r="AW37" t="s">
         <v>36</v>
@@ -52826,8 +53131,8 @@
       <c r="AX37" t="s">
         <v>36</v>
       </c>
-      <c r="AY37">
-        <v>0</v>
+      <c r="AY37" t="s">
+        <v>36</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -52838,10 +53143,359 @@
       <c r="BB37">
         <v>0</v>
       </c>
-      <c r="BC37" t="s">
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="s">
         <v>1761</v>
       </c>
-      <c r="BD37" t="s">
+      <c r="BE37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:57">
+      <c r="A38" s="44" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>50</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>3</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>1</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>-1</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>10</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG38" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AH38" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AI38" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ38" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AL38" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM38" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN38" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>1</v>
+      </c>
+      <c r="AQ38">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:57">
+      <c r="A39" s="44" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>3</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>1</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>-1</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>10</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG39" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AH39" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AI39" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ39" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AL39" s="44">
+        <v>1</v>
+      </c>
+      <c r="AM39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN39" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>1</v>
+      </c>
+      <c r="AQ39">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU39">
+        <v>0</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BE39" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ADB985-4784-4A6C-B3EA-AD2BB473F66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DDB9F1-D85F-4340-A470-E5DA8E06B161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -44562,10 +44562,10 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K4">
         <v>5</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DDB9F1-D85F-4340-A470-E5DA8E06B161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BBAB7F-6928-4AD0-9ED2-DCD35B415FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8026" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8029" uniqueCount="1817">
   <si>
     <t>NAME</t>
   </si>
@@ -5629,6 +5629,12 @@
   </si>
   <si>
     <t>ENCOUNTER</t>
+  </si>
+  <si>
+    <t>wait_naprig</t>
+  </si>
+  <si>
+    <t>wait in naprig</t>
   </si>
 </sst>
 </file>
@@ -32378,7 +32384,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.08984375" customWidth="1"/>
@@ -32980,7 +32986,7 @@
         <v>1608</v>
       </c>
       <c r="B52" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="52" t="s">
         <v>36</v>
@@ -32994,7 +33000,7 @@
         <v>1609</v>
       </c>
       <c r="B53" s="52">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C53" s="52" t="s">
         <v>36</v>
@@ -33005,7 +33011,7 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1">
       <c r="A54" t="s">
-        <v>1633</v>
+        <v>1815</v>
       </c>
       <c r="B54" s="52">
         <v>1</v>
@@ -33014,12 +33020,12 @@
         <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>1641</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1">
       <c r="A55" t="s">
-        <v>1645</v>
+        <v>1633</v>
       </c>
       <c r="B55" s="52">
         <v>1</v>
@@ -33028,12 +33034,12 @@
         <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1">
       <c r="A56" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="B56" s="52">
         <v>1</v>
@@ -33042,43 +33048,43 @@
         <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1">
       <c r="A57" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="B57" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>1675</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1">
       <c r="A58" t="s">
-        <v>1676</v>
+        <v>1656</v>
       </c>
       <c r="B58" s="52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C58" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1">
       <c r="A59" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B59" s="52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C59" s="52" t="s">
         <v>36</v>
@@ -33089,49 +33095,49 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1">
       <c r="A60" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B60" s="52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C60" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1">
       <c r="A61" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B61" s="52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C61" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1">
       <c r="A62" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="B62" s="52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C62" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1">
       <c r="A63" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
       <c r="B63" s="52">
         <v>0</v>
@@ -33140,42 +33146,56 @@
         <v>36</v>
       </c>
       <c r="D63" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1">
       <c r="A64" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B64" s="52">
+        <v>0</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A65" t="s">
         <v>1713</v>
       </c>
-      <c r="B64" s="52">
-        <v>0</v>
-      </c>
-      <c r="C64" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="B65" s="52">
+        <v>0</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" t="s">
         <v>1714</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A65" t="s">
+    <row r="66" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A66" t="s">
         <v>1749</v>
       </c>
-      <c r="B65" s="52">
-        <v>0</v>
-      </c>
-      <c r="C65" s="52" t="s">
+      <c r="B66" s="52">
+        <v>0</v>
+      </c>
+      <c r="C66" s="52" t="s">
         <v>1750</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A66" t="s">
+    <row r="67" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A67" t="s">
         <v>1751</v>
       </c>
-      <c r="B66" s="52">
-        <v>0</v>
-      </c>
-      <c r="C66" s="52" t="s">
+      <c r="B67" s="52">
+        <v>0</v>
+      </c>
+      <c r="C67" s="52" t="s">
         <v>1752</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BBAB7F-6928-4AD0-9ED2-DCD35B415FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D71E0F-A191-4FB4-BC12-D98D999A2CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8029" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8050" uniqueCount="1818">
   <si>
     <t>NAME</t>
   </si>
@@ -5635,6 +5635,9 @@
   </si>
   <si>
     <t>wait in naprig</t>
+  </si>
+  <si>
+    <t>beetle</t>
   </si>
 </sst>
 </file>
@@ -11211,44 +11214,180 @@
       </c>
     </row>
     <row r="29" spans="1:58" ht="12.5">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
-      <c r="AF29" s="40"/>
-      <c r="AG29" s="7"/>
-      <c r="AH29" s="7"/>
-      <c r="AL29" s="28"/>
-      <c r="AN29" s="28"/>
-      <c r="AO29" s="28"/>
-      <c r="AP29" s="46"/>
+      <c r="A29" s="47" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B29" s="53">
+        <v>1</v>
+      </c>
+      <c r="C29" s="53">
+        <v>0</v>
+      </c>
+      <c r="D29" s="53">
+        <v>1</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G29" s="48">
+        <v>1</v>
+      </c>
+      <c r="H29" s="48">
+        <v>2</v>
+      </c>
+      <c r="I29" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J29" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="48">
+        <v>0</v>
+      </c>
+      <c r="L29" s="48">
+        <v>150</v>
+      </c>
+      <c r="M29" s="48">
+        <v>45</v>
+      </c>
+      <c r="N29" s="48">
+        <v>45</v>
+      </c>
+      <c r="O29" s="48">
+        <v>45</v>
+      </c>
+      <c r="P29" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="48">
+        <v>11</v>
+      </c>
+      <c r="R29" s="48">
+        <v>1</v>
+      </c>
+      <c r="S29" s="48">
+        <v>0</v>
+      </c>
+      <c r="T29" s="48">
+        <v>0</v>
+      </c>
+      <c r="U29" s="48">
+        <v>0</v>
+      </c>
+      <c r="V29" s="48">
+        <v>0</v>
+      </c>
+      <c r="W29" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X29" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y29" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z29" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA29" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB29" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC29" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD29" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE29" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL29">
+        <v>1</v>
+      </c>
+      <c r="AM29">
+        <v>1</v>
+      </c>
+      <c r="AN29">
+        <v>6</v>
+      </c>
+      <c r="AO29">
+        <v>3</v>
+      </c>
+      <c r="AP29" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>-1</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>2</v>
+      </c>
+      <c r="BD29" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE29" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>1793</v>
+      </c>
     </row>
     <row r="30" spans="1:58" ht="12.5">
       <c r="A30" s="48"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D71E0F-A191-4FB4-BC12-D98D999A2CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC37FA7-317F-46FE-9ABF-C5D27692B7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8050" uniqueCount="1818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9079" uniqueCount="1867">
   <si>
     <t>NAME</t>
   </si>
@@ -5637,14 +5637,161 @@
     <t>wait in naprig</t>
   </si>
   <si>
-    <t>beetle</t>
+    <t>beetle_iron</t>
+  </si>
+  <si>
+    <t>animal_cat</t>
+  </si>
+  <si>
+    <t>animal_dog</t>
+  </si>
+  <si>
+    <t>animal_fox</t>
+  </si>
+  <si>
+    <t>bear_grizzly</t>
+  </si>
+  <si>
+    <t>bear_white</t>
+  </si>
+  <si>
+    <t>beetle_blood</t>
+  </si>
+  <si>
+    <t>beetle_ice</t>
+  </si>
+  <si>
+    <t>beetle_red</t>
+  </si>
+  <si>
+    <t>bird_eagle</t>
+  </si>
+  <si>
+    <t>bird_gull</t>
+  </si>
+  <si>
+    <t>bird_owl</t>
+  </si>
+  <si>
+    <t>bird_parrot</t>
+  </si>
+  <si>
+    <t>bird_red</t>
+  </si>
+  <si>
+    <t>bird_snow</t>
+  </si>
+  <si>
+    <t>bird_toucan</t>
+  </si>
+  <si>
+    <t>blowfish_angry</t>
+  </si>
+  <si>
+    <t>blowfish_beast</t>
+  </si>
+  <si>
+    <t>buffalo_disco</t>
+  </si>
+  <si>
+    <t>buffalo_wild</t>
+  </si>
+  <si>
+    <t>crab_iron</t>
+  </si>
+  <si>
+    <t>crab_rock</t>
+  </si>
+  <si>
+    <t>crab_snow</t>
+  </si>
+  <si>
+    <t>goat_angry</t>
+  </si>
+  <si>
+    <t>goat_black</t>
+  </si>
+  <si>
+    <t>goat_mushroom</t>
+  </si>
+  <si>
+    <t>goby_helmet</t>
+  </si>
+  <si>
+    <t>goby_mad</t>
+  </si>
+  <si>
+    <t>jellyfish_bouncy</t>
+  </si>
+  <si>
+    <t>jellyfish_ice</t>
+  </si>
+  <si>
+    <t>lizard_fire</t>
+  </si>
+  <si>
+    <t>lizard_horn</t>
+  </si>
+  <si>
+    <t>lizard_snail</t>
+  </si>
+  <si>
+    <t>octopus_ice</t>
+  </si>
+  <si>
+    <t>octopus_pirate</t>
+  </si>
+  <si>
+    <t>octopus_ringed</t>
+  </si>
+  <si>
+    <t>slime_green</t>
+  </si>
+  <si>
+    <t>slime_purple</t>
+  </si>
+  <si>
+    <t>snail_blue</t>
+  </si>
+  <si>
+    <t>snail_green</t>
+  </si>
+  <si>
+    <t>snail_conch</t>
+  </si>
+  <si>
+    <t>snake_bell</t>
+  </si>
+  <si>
+    <t>snake_fire</t>
+  </si>
+  <si>
+    <t>snake_green</t>
+  </si>
+  <si>
+    <t>snake_mushroom</t>
+  </si>
+  <si>
+    <t>turtle_alligator</t>
+  </si>
+  <si>
+    <t>turtle_tower</t>
+  </si>
+  <si>
+    <t>turtle_volcano</t>
+  </si>
+  <si>
+    <t>wolf_demon</t>
+  </si>
+  <si>
+    <t>wolf_gray</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5793,8 +5940,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5861,6 +6015,11 @@
         <bgColor rgb="FFB7B7B7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -5891,10 +6050,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5977,8 +6137,12 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6241,7 +6405,7 @@
   <dimension ref="A1:BF998"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
     <col min="2" max="3" width="9.26953125" customWidth="1"/>
     <col min="4" max="4" width="12.1796875" customWidth="1"/>
     <col min="5" max="5" width="11.6328125" customWidth="1"/>
@@ -11213,8 +11377,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:58" ht="12.5">
-      <c r="A29" s="47" t="s">
+    <row r="29" spans="1:58" ht="14">
+      <c r="A29" s="54" t="s">
         <v>1817</v>
       </c>
       <c r="B29" s="53">
@@ -11390,818 +11554,8636 @@
       </c>
     </row>
     <row r="30" spans="1:58" ht="12.5">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="48"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="48"/>
-      <c r="AF30" s="40"/>
-      <c r="AG30" s="7"/>
-      <c r="AH30" s="7"/>
-      <c r="AL30" s="28"/>
-      <c r="AN30" s="28"/>
-      <c r="AO30" s="28"/>
-      <c r="AP30" s="46"/>
+      <c r="A30" s="47" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B30" s="53">
+        <v>1</v>
+      </c>
+      <c r="C30" s="53">
+        <v>0</v>
+      </c>
+      <c r="D30" s="53">
+        <v>1</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G30" s="48">
+        <v>1</v>
+      </c>
+      <c r="H30" s="48">
+        <v>2</v>
+      </c>
+      <c r="I30" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J30" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="48">
+        <v>0</v>
+      </c>
+      <c r="L30" s="48">
+        <v>150</v>
+      </c>
+      <c r="M30" s="48">
+        <v>45</v>
+      </c>
+      <c r="N30" s="48">
+        <v>45</v>
+      </c>
+      <c r="O30" s="48">
+        <v>45</v>
+      </c>
+      <c r="P30" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="48">
+        <v>11</v>
+      </c>
+      <c r="R30" s="48">
+        <v>1</v>
+      </c>
+      <c r="S30" s="48">
+        <v>0</v>
+      </c>
+      <c r="T30" s="48">
+        <v>0</v>
+      </c>
+      <c r="U30" s="48">
+        <v>0</v>
+      </c>
+      <c r="V30" s="48">
+        <v>0</v>
+      </c>
+      <c r="W30" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X30" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y30" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z30" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA30" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB30" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC30" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD30" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE30" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL30">
+        <v>1</v>
+      </c>
+      <c r="AM30">
+        <v>1</v>
+      </c>
+      <c r="AN30">
+        <v>6</v>
+      </c>
+      <c r="AO30">
+        <v>3</v>
+      </c>
+      <c r="AP30" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>-1</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>2</v>
+      </c>
+      <c r="BD30" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>1793</v>
+      </c>
     </row>
     <row r="31" spans="1:58" ht="12.5">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="48"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="48"/>
-      <c r="AF31" s="40"/>
-      <c r="AG31" s="7"/>
-      <c r="AH31" s="7"/>
-      <c r="AL31" s="28"/>
-      <c r="AO31" s="28"/>
-      <c r="AP31" s="46"/>
+      <c r="A31" s="47" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B31" s="53">
+        <v>1</v>
+      </c>
+      <c r="C31" s="53">
+        <v>0</v>
+      </c>
+      <c r="D31" s="53">
+        <v>1</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G31" s="48">
+        <v>1</v>
+      </c>
+      <c r="H31" s="48">
+        <v>2</v>
+      </c>
+      <c r="I31" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J31" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="48">
+        <v>0</v>
+      </c>
+      <c r="L31" s="48">
+        <v>150</v>
+      </c>
+      <c r="M31" s="48">
+        <v>45</v>
+      </c>
+      <c r="N31" s="48">
+        <v>45</v>
+      </c>
+      <c r="O31" s="48">
+        <v>45</v>
+      </c>
+      <c r="P31" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="48">
+        <v>11</v>
+      </c>
+      <c r="R31" s="48">
+        <v>1</v>
+      </c>
+      <c r="S31" s="48">
+        <v>0</v>
+      </c>
+      <c r="T31" s="48">
+        <v>0</v>
+      </c>
+      <c r="U31" s="48">
+        <v>0</v>
+      </c>
+      <c r="V31" s="48">
+        <v>0</v>
+      </c>
+      <c r="W31" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X31" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y31" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z31" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA31" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB31" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC31" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD31" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE31" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG31" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL31">
+        <v>1</v>
+      </c>
+      <c r="AM31">
+        <v>1</v>
+      </c>
+      <c r="AN31">
+        <v>6</v>
+      </c>
+      <c r="AO31">
+        <v>3</v>
+      </c>
+      <c r="AP31" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>-1</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>2</v>
+      </c>
+      <c r="BD31" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>1793</v>
+      </c>
     </row>
     <row r="32" spans="1:58" ht="12.5">
-      <c r="A32" s="48"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="48"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
-      <c r="AF32" s="40"/>
-      <c r="AG32" s="7"/>
-      <c r="AH32" s="7"/>
-      <c r="AL32" s="28"/>
-      <c r="AN32" s="28"/>
-      <c r="AO32" s="28"/>
-      <c r="AP32" s="46"/>
-    </row>
-    <row r="33" spans="1:42" ht="12.5">
-      <c r="A33" s="48"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="48"/>
-      <c r="W33" s="48"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="48"/>
-      <c r="AF33" s="40"/>
-      <c r="AG33" s="7"/>
-      <c r="AH33" s="7"/>
-      <c r="AL33" s="28"/>
-      <c r="AN33" s="28"/>
-      <c r="AO33" s="28"/>
-      <c r="AP33" s="46"/>
-    </row>
-    <row r="34" spans="1:42" ht="12.5">
-      <c r="A34" s="48"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="48"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="48"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="48"/>
-      <c r="Y34" s="48"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="48"/>
-      <c r="AB34" s="48"/>
-      <c r="AC34" s="48"/>
-      <c r="AD34" s="48"/>
-      <c r="AE34" s="48"/>
-      <c r="AF34" s="40"/>
-      <c r="AG34" s="7"/>
-      <c r="AH34" s="7"/>
-      <c r="AL34" s="28"/>
-      <c r="AO34" s="28"/>
-      <c r="AP34" s="46"/>
-    </row>
-    <row r="35" spans="1:42" ht="12.5">
-      <c r="A35" s="48"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="48"/>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="48"/>
-      <c r="AA35" s="48"/>
-      <c r="AB35" s="48"/>
-      <c r="AC35" s="48"/>
-      <c r="AD35" s="48"/>
-      <c r="AE35" s="48"/>
-      <c r="AF35" s="40"/>
-      <c r="AG35" s="7"/>
-      <c r="AH35" s="7"/>
-      <c r="AL35" s="28"/>
-      <c r="AM35" s="28"/>
-      <c r="AO35" s="28"/>
-      <c r="AP35" s="46"/>
-    </row>
-    <row r="36" spans="1:42" ht="12.5">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="48"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="48"/>
-      <c r="V36" s="48"/>
-      <c r="W36" s="48"/>
-      <c r="X36" s="48"/>
-      <c r="Y36" s="48"/>
-      <c r="Z36" s="48"/>
-      <c r="AA36" s="48"/>
-      <c r="AB36" s="48"/>
-      <c r="AC36" s="48"/>
-      <c r="AD36" s="48"/>
-      <c r="AE36" s="48"/>
-      <c r="AF36" s="40"/>
-      <c r="AG36" s="7"/>
-      <c r="AH36" s="7"/>
-      <c r="AI36" s="28"/>
-      <c r="AL36" s="28"/>
-      <c r="AM36" s="28"/>
-      <c r="AO36" s="28"/>
-      <c r="AP36" s="46"/>
-    </row>
-    <row r="37" spans="1:42" ht="12.5">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="48"/>
-      <c r="R37" s="48"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="48"/>
-      <c r="U37" s="48"/>
-      <c r="V37" s="48"/>
-      <c r="W37" s="48"/>
-      <c r="X37" s="48"/>
-      <c r="Y37" s="48"/>
-      <c r="Z37" s="48"/>
-      <c r="AA37" s="48"/>
-      <c r="AB37" s="48"/>
-      <c r="AC37" s="48"/>
-      <c r="AD37" s="48"/>
-      <c r="AE37" s="48"/>
-      <c r="AF37" s="40"/>
-      <c r="AG37" s="7"/>
-      <c r="AH37" s="7"/>
-      <c r="AI37" s="28"/>
-      <c r="AK37" s="28"/>
-      <c r="AL37" s="28"/>
-      <c r="AM37" s="28"/>
-      <c r="AN37" s="28"/>
-      <c r="AO37" s="28"/>
-      <c r="AP37" s="46"/>
-    </row>
-    <row r="38" spans="1:42" ht="12.5">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="48"/>
-      <c r="U38" s="48"/>
-      <c r="V38" s="48"/>
-      <c r="W38" s="48"/>
-      <c r="X38" s="48"/>
-      <c r="Y38" s="48"/>
-      <c r="Z38" s="48"/>
-      <c r="AA38" s="48"/>
-      <c r="AB38" s="48"/>
-      <c r="AC38" s="48"/>
-      <c r="AD38" s="48"/>
-      <c r="AE38" s="48"/>
-      <c r="AF38" s="40"/>
-      <c r="AG38" s="7"/>
-      <c r="AH38" s="7"/>
-      <c r="AN38" s="28"/>
-      <c r="AO38" s="28"/>
-      <c r="AP38" s="46"/>
-    </row>
-    <row r="39" spans="1:42" ht="12.5">
-      <c r="A39" s="48"/>
-      <c r="B39" s="48"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="48"/>
-      <c r="R39" s="48"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="48"/>
-      <c r="V39" s="48"/>
-      <c r="W39" s="48"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="48"/>
-      <c r="Z39" s="48"/>
-      <c r="AA39" s="48"/>
-      <c r="AB39" s="48"/>
-      <c r="AC39" s="48"/>
-      <c r="AD39" s="48"/>
-      <c r="AE39" s="48"/>
-      <c r="AF39" s="40"/>
-      <c r="AG39" s="7"/>
-      <c r="AH39" s="7"/>
-      <c r="AN39" s="28"/>
-      <c r="AO39" s="28"/>
-      <c r="AP39" s="46"/>
-    </row>
-    <row r="40" spans="1:42" ht="12.5">
-      <c r="A40" s="48"/>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
-      <c r="N40" s="48"/>
-      <c r="O40" s="48"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="48"/>
-      <c r="R40" s="48"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="48"/>
-      <c r="V40" s="48"/>
-      <c r="W40" s="48"/>
-      <c r="X40" s="48"/>
-      <c r="Y40" s="48"/>
-      <c r="Z40" s="48"/>
-      <c r="AA40" s="48"/>
-      <c r="AB40" s="48"/>
-      <c r="AC40" s="48"/>
-      <c r="AD40" s="48"/>
-      <c r="AE40" s="48"/>
-      <c r="AF40" s="40"/>
-      <c r="AG40" s="7"/>
-      <c r="AH40" s="7"/>
-      <c r="AO40" s="28"/>
-      <c r="AP40" s="46"/>
-    </row>
-    <row r="41" spans="1:42" ht="12.5">
-      <c r="A41" s="48"/>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
-      <c r="L41" s="48"/>
-      <c r="M41" s="48"/>
-      <c r="N41" s="48"/>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="48"/>
-      <c r="U41" s="48"/>
-      <c r="V41" s="48"/>
-      <c r="W41" s="48"/>
-      <c r="X41" s="48"/>
-      <c r="Y41" s="48"/>
-      <c r="Z41" s="48"/>
-      <c r="AA41" s="48"/>
-      <c r="AB41" s="48"/>
-      <c r="AC41" s="48"/>
-      <c r="AD41" s="48"/>
-      <c r="AE41" s="48"/>
-      <c r="AF41" s="40"/>
-      <c r="AG41" s="7"/>
-      <c r="AH41" s="7"/>
-      <c r="AO41" s="28"/>
-      <c r="AP41" s="46"/>
-    </row>
-    <row r="42" spans="1:42" ht="12.5">
-      <c r="A42" s="48"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="48"/>
-      <c r="O42" s="48"/>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="48"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="48"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="48"/>
-      <c r="W42" s="48"/>
-      <c r="X42" s="48"/>
-      <c r="Y42" s="48"/>
-      <c r="Z42" s="48"/>
-      <c r="AA42" s="48"/>
-      <c r="AB42" s="48"/>
-      <c r="AC42" s="48"/>
-      <c r="AD42" s="48"/>
-      <c r="AE42" s="48"/>
-    </row>
-    <row r="43" spans="1:42" ht="12.5">
-      <c r="A43" s="48"/>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="48"/>
-      <c r="O43" s="48"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="48"/>
-      <c r="R43" s="48"/>
-      <c r="S43" s="48"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="48"/>
-      <c r="W43" s="48"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="48"/>
-      <c r="AA43" s="48"/>
-      <c r="AB43" s="48"/>
-      <c r="AC43" s="48"/>
-      <c r="AD43" s="48"/>
-      <c r="AE43" s="48"/>
-    </row>
-    <row r="44" spans="1:42" ht="12.5">
-      <c r="A44" s="48"/>
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="48"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="48"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="48"/>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="48"/>
-      <c r="W44" s="48"/>
-      <c r="X44" s="48"/>
-      <c r="Y44" s="48"/>
-      <c r="Z44" s="48"/>
-      <c r="AA44" s="48"/>
-      <c r="AB44" s="48"/>
-      <c r="AC44" s="48"/>
-      <c r="AD44" s="48"/>
-      <c r="AE44" s="48"/>
-    </row>
-    <row r="45" spans="1:42" ht="12.5">
-      <c r="A45" s="48"/>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="L45" s="48"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="48"/>
-      <c r="O45" s="48"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="48"/>
-      <c r="W45" s="48"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="48"/>
-      <c r="AA45" s="48"/>
-      <c r="AB45" s="48"/>
-      <c r="AC45" s="48"/>
-      <c r="AD45" s="48"/>
-      <c r="AE45" s="48"/>
-    </row>
-    <row r="46" spans="1:42" ht="12.5">
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="X46" s="41"/>
-      <c r="AE46" s="41"/>
-    </row>
-    <row r="47" spans="1:42" ht="12.5">
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="X47" s="41"/>
-      <c r="AE47" s="41"/>
-    </row>
-    <row r="48" spans="1:42" ht="12.5">
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="X48" s="41"/>
-      <c r="AE48" s="41"/>
-    </row>
-    <row r="49" spans="7:31" ht="12.5">
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="X49" s="41"/>
-      <c r="AE49" s="41"/>
-    </row>
-    <row r="50" spans="7:31" ht="12.5">
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="X50" s="41"/>
-      <c r="AE50" s="41"/>
-    </row>
-    <row r="51" spans="7:31" ht="12.5">
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
-      <c r="X51" s="41"/>
-      <c r="AE51" s="41"/>
-    </row>
-    <row r="52" spans="7:31" ht="12.5">
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="X52" s="41"/>
-      <c r="AE52" s="41"/>
-    </row>
-    <row r="53" spans="7:31" ht="12.5">
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="X53" s="41"/>
-      <c r="AE53" s="41"/>
-    </row>
-    <row r="54" spans="7:31" ht="12.5">
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="X54" s="41"/>
-      <c r="AE54" s="41"/>
-    </row>
-    <row r="55" spans="7:31" ht="12.5">
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="X55" s="41"/>
-      <c r="AE55" s="41"/>
-    </row>
-    <row r="56" spans="7:31" ht="12.5">
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="X56" s="41"/>
-      <c r="AE56" s="41"/>
-    </row>
-    <row r="57" spans="7:31" ht="12.5">
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="X57" s="41"/>
-      <c r="AE57" s="41"/>
-    </row>
-    <row r="58" spans="7:31" ht="12.5">
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="X58" s="41"/>
-      <c r="AE58" s="41"/>
-    </row>
-    <row r="59" spans="7:31" ht="12.5">
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="X59" s="41"/>
-      <c r="AE59" s="41"/>
-    </row>
-    <row r="60" spans="7:31" ht="12.5">
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="X60" s="41"/>
-      <c r="AE60" s="41"/>
-    </row>
-    <row r="61" spans="7:31" ht="12.5">
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="X61" s="41"/>
-      <c r="AE61" s="41"/>
-    </row>
-    <row r="62" spans="7:31" ht="12.5">
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="X62" s="41"/>
-      <c r="AE62" s="41"/>
-    </row>
-    <row r="63" spans="7:31" ht="12.5">
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="X63" s="41"/>
-      <c r="AE63" s="41"/>
-    </row>
-    <row r="64" spans="7:31" ht="12.5">
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="X64" s="41"/>
-      <c r="AE64" s="41"/>
-    </row>
-    <row r="65" spans="7:31" ht="12.5">
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="X65" s="41"/>
-      <c r="AE65" s="41"/>
-    </row>
-    <row r="66" spans="7:31" ht="12.5">
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="X66" s="41"/>
-      <c r="AE66" s="41"/>
-    </row>
-    <row r="67" spans="7:31" ht="12.5">
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="X67" s="41"/>
-      <c r="AE67" s="41"/>
-    </row>
-    <row r="68" spans="7:31" ht="12.5">
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="X68" s="41"/>
-      <c r="AE68" s="41"/>
-    </row>
-    <row r="69" spans="7:31" ht="12.5">
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="X69" s="41"/>
-      <c r="AE69" s="41"/>
-    </row>
-    <row r="70" spans="7:31" ht="12.5">
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="X70" s="41"/>
-      <c r="AE70" s="41"/>
-    </row>
-    <row r="71" spans="7:31" ht="12.5">
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="X71" s="41"/>
-      <c r="AE71" s="41"/>
-    </row>
-    <row r="72" spans="7:31" ht="12.5">
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="X72" s="41"/>
-      <c r="AE72" s="41"/>
-    </row>
-    <row r="73" spans="7:31" ht="12.5">
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="X73" s="41"/>
-      <c r="AE73" s="41"/>
-    </row>
-    <row r="74" spans="7:31" ht="12.5">
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="X74" s="41"/>
-      <c r="AE74" s="41"/>
-    </row>
-    <row r="75" spans="7:31" ht="12.5">
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="X75" s="41"/>
-      <c r="AE75" s="41"/>
-    </row>
-    <row r="76" spans="7:31" ht="12.5">
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="X76" s="41"/>
-      <c r="AE76" s="41"/>
-    </row>
-    <row r="77" spans="7:31" ht="12.5">
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="X77" s="41"/>
-      <c r="AE77" s="41"/>
-    </row>
-    <row r="78" spans="7:31" ht="12.5">
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="X78" s="41"/>
-      <c r="AE78" s="41"/>
-    </row>
-    <row r="79" spans="7:31" ht="12.5">
+      <c r="A32" s="47" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B32" s="53">
+        <v>1</v>
+      </c>
+      <c r="C32" s="53">
+        <v>0</v>
+      </c>
+      <c r="D32" s="53">
+        <v>1</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G32" s="48">
+        <v>1</v>
+      </c>
+      <c r="H32" s="48">
+        <v>2</v>
+      </c>
+      <c r="I32" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J32" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="48">
+        <v>0</v>
+      </c>
+      <c r="L32" s="48">
+        <v>150</v>
+      </c>
+      <c r="M32" s="48">
+        <v>45</v>
+      </c>
+      <c r="N32" s="48">
+        <v>45</v>
+      </c>
+      <c r="O32" s="48">
+        <v>45</v>
+      </c>
+      <c r="P32" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="48">
+        <v>11</v>
+      </c>
+      <c r="R32" s="48">
+        <v>1</v>
+      </c>
+      <c r="S32" s="48">
+        <v>0</v>
+      </c>
+      <c r="T32" s="48">
+        <v>0</v>
+      </c>
+      <c r="U32" s="48">
+        <v>0</v>
+      </c>
+      <c r="V32" s="48">
+        <v>0</v>
+      </c>
+      <c r="W32" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X32" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y32" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z32" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA32" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB32" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC32" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD32" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE32" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL32">
+        <v>1</v>
+      </c>
+      <c r="AM32">
+        <v>1</v>
+      </c>
+      <c r="AN32">
+        <v>6</v>
+      </c>
+      <c r="AO32">
+        <v>3</v>
+      </c>
+      <c r="AP32" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>-1</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>2</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE32" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58" ht="12.5">
+      <c r="A33" s="47" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B33" s="53">
+        <v>1</v>
+      </c>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
+      <c r="D33" s="53">
+        <v>1</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G33" s="48">
+        <v>1</v>
+      </c>
+      <c r="H33" s="48">
+        <v>2</v>
+      </c>
+      <c r="I33" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J33" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="48">
+        <v>0</v>
+      </c>
+      <c r="L33" s="48">
+        <v>150</v>
+      </c>
+      <c r="M33" s="48">
+        <v>45</v>
+      </c>
+      <c r="N33" s="48">
+        <v>45</v>
+      </c>
+      <c r="O33" s="48">
+        <v>45</v>
+      </c>
+      <c r="P33" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="48">
+        <v>11</v>
+      </c>
+      <c r="R33" s="48">
+        <v>1</v>
+      </c>
+      <c r="S33" s="48">
+        <v>0</v>
+      </c>
+      <c r="T33" s="48">
+        <v>0</v>
+      </c>
+      <c r="U33" s="48">
+        <v>0</v>
+      </c>
+      <c r="V33" s="48">
+        <v>0</v>
+      </c>
+      <c r="W33" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X33" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y33" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z33" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA33" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB33" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC33" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD33" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE33" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL33">
+        <v>1</v>
+      </c>
+      <c r="AM33">
+        <v>1</v>
+      </c>
+      <c r="AN33">
+        <v>6</v>
+      </c>
+      <c r="AO33">
+        <v>3</v>
+      </c>
+      <c r="AP33" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>-1</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>2</v>
+      </c>
+      <c r="BD33" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE33" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="34" spans="1:58" ht="12.5">
+      <c r="A34" s="47" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B34" s="53">
+        <v>1</v>
+      </c>
+      <c r="C34" s="53">
+        <v>0</v>
+      </c>
+      <c r="D34" s="53">
+        <v>1</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G34" s="48">
+        <v>1</v>
+      </c>
+      <c r="H34" s="48">
+        <v>2</v>
+      </c>
+      <c r="I34" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J34" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="48">
+        <v>0</v>
+      </c>
+      <c r="L34" s="48">
+        <v>150</v>
+      </c>
+      <c r="M34" s="48">
+        <v>45</v>
+      </c>
+      <c r="N34" s="48">
+        <v>45</v>
+      </c>
+      <c r="O34" s="48">
+        <v>45</v>
+      </c>
+      <c r="P34" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="48">
+        <v>11</v>
+      </c>
+      <c r="R34" s="48">
+        <v>1</v>
+      </c>
+      <c r="S34" s="48">
+        <v>0</v>
+      </c>
+      <c r="T34" s="48">
+        <v>0</v>
+      </c>
+      <c r="U34" s="48">
+        <v>0</v>
+      </c>
+      <c r="V34" s="48">
+        <v>0</v>
+      </c>
+      <c r="W34" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X34" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y34" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z34" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA34" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB34" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC34" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE34" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL34">
+        <v>1</v>
+      </c>
+      <c r="AM34">
+        <v>1</v>
+      </c>
+      <c r="AN34">
+        <v>6</v>
+      </c>
+      <c r="AO34">
+        <v>3</v>
+      </c>
+      <c r="AP34" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>-1</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ34" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>2</v>
+      </c>
+      <c r="BD34" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE34" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF34" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:58" ht="12.5">
+      <c r="A35" s="47" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B35" s="53">
+        <v>1</v>
+      </c>
+      <c r="C35" s="53">
+        <v>0</v>
+      </c>
+      <c r="D35" s="53">
+        <v>1</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G35" s="48">
+        <v>1</v>
+      </c>
+      <c r="H35" s="48">
+        <v>2</v>
+      </c>
+      <c r="I35" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J35" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="48">
+        <v>0</v>
+      </c>
+      <c r="L35" s="48">
+        <v>150</v>
+      </c>
+      <c r="M35" s="48">
+        <v>45</v>
+      </c>
+      <c r="N35" s="48">
+        <v>45</v>
+      </c>
+      <c r="O35" s="48">
+        <v>45</v>
+      </c>
+      <c r="P35" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="48">
+        <v>11</v>
+      </c>
+      <c r="R35" s="48">
+        <v>1</v>
+      </c>
+      <c r="S35" s="48">
+        <v>0</v>
+      </c>
+      <c r="T35" s="48">
+        <v>0</v>
+      </c>
+      <c r="U35" s="48">
+        <v>0</v>
+      </c>
+      <c r="V35" s="48">
+        <v>0</v>
+      </c>
+      <c r="W35" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X35" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y35" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z35" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA35" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB35" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC35" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD35" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE35" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL35">
+        <v>1</v>
+      </c>
+      <c r="AM35">
+        <v>1</v>
+      </c>
+      <c r="AN35">
+        <v>6</v>
+      </c>
+      <c r="AO35">
+        <v>3</v>
+      </c>
+      <c r="AP35" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>-1</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ35" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>2</v>
+      </c>
+      <c r="BD35" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE35" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF35" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:58" ht="12.5">
+      <c r="A36" s="47" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B36" s="53">
+        <v>1</v>
+      </c>
+      <c r="C36" s="53">
+        <v>0</v>
+      </c>
+      <c r="D36" s="53">
+        <v>1</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G36" s="48">
+        <v>1</v>
+      </c>
+      <c r="H36" s="48">
+        <v>2</v>
+      </c>
+      <c r="I36" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J36" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="48">
+        <v>0</v>
+      </c>
+      <c r="L36" s="48">
+        <v>150</v>
+      </c>
+      <c r="M36" s="48">
+        <v>45</v>
+      </c>
+      <c r="N36" s="48">
+        <v>45</v>
+      </c>
+      <c r="O36" s="48">
+        <v>45</v>
+      </c>
+      <c r="P36" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="48">
+        <v>11</v>
+      </c>
+      <c r="R36" s="48">
+        <v>1</v>
+      </c>
+      <c r="S36" s="48">
+        <v>0</v>
+      </c>
+      <c r="T36" s="48">
+        <v>0</v>
+      </c>
+      <c r="U36" s="48">
+        <v>0</v>
+      </c>
+      <c r="V36" s="48">
+        <v>0</v>
+      </c>
+      <c r="W36" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X36" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y36" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z36" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA36" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB36" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC36" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD36" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE36" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL36">
+        <v>1</v>
+      </c>
+      <c r="AM36">
+        <v>1</v>
+      </c>
+      <c r="AN36">
+        <v>6</v>
+      </c>
+      <c r="AO36">
+        <v>3</v>
+      </c>
+      <c r="AP36" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>-1</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ36" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>2</v>
+      </c>
+      <c r="BD36" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE36" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF36" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="37" spans="1:58" ht="12.5">
+      <c r="A37" s="47" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B37" s="53">
+        <v>1</v>
+      </c>
+      <c r="C37" s="53">
+        <v>0</v>
+      </c>
+      <c r="D37" s="53">
+        <v>1</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G37" s="48">
+        <v>1</v>
+      </c>
+      <c r="H37" s="48">
+        <v>2</v>
+      </c>
+      <c r="I37" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J37" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" s="48">
+        <v>0</v>
+      </c>
+      <c r="L37" s="48">
+        <v>150</v>
+      </c>
+      <c r="M37" s="48">
+        <v>45</v>
+      </c>
+      <c r="N37" s="48">
+        <v>45</v>
+      </c>
+      <c r="O37" s="48">
+        <v>45</v>
+      </c>
+      <c r="P37" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="48">
+        <v>11</v>
+      </c>
+      <c r="R37" s="48">
+        <v>1</v>
+      </c>
+      <c r="S37" s="48">
+        <v>0</v>
+      </c>
+      <c r="T37" s="48">
+        <v>0</v>
+      </c>
+      <c r="U37" s="48">
+        <v>0</v>
+      </c>
+      <c r="V37" s="48">
+        <v>0</v>
+      </c>
+      <c r="W37" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X37" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y37" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z37" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA37" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB37" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC37" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD37" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE37" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG37" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL37">
+        <v>1</v>
+      </c>
+      <c r="AM37">
+        <v>1</v>
+      </c>
+      <c r="AN37">
+        <v>6</v>
+      </c>
+      <c r="AO37">
+        <v>3</v>
+      </c>
+      <c r="AP37" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>-1</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ37" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>2</v>
+      </c>
+      <c r="BD37" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE37" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF37" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="38" spans="1:58" ht="12.5">
+      <c r="A38" s="47" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B38" s="53">
+        <v>1</v>
+      </c>
+      <c r="C38" s="53">
+        <v>0</v>
+      </c>
+      <c r="D38" s="53">
+        <v>1</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G38" s="48">
+        <v>1</v>
+      </c>
+      <c r="H38" s="48">
+        <v>2</v>
+      </c>
+      <c r="I38" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J38" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="48">
+        <v>0</v>
+      </c>
+      <c r="L38" s="48">
+        <v>150</v>
+      </c>
+      <c r="M38" s="48">
+        <v>45</v>
+      </c>
+      <c r="N38" s="48">
+        <v>45</v>
+      </c>
+      <c r="O38" s="48">
+        <v>45</v>
+      </c>
+      <c r="P38" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="48">
+        <v>11</v>
+      </c>
+      <c r="R38" s="48">
+        <v>1</v>
+      </c>
+      <c r="S38" s="48">
+        <v>0</v>
+      </c>
+      <c r="T38" s="48">
+        <v>0</v>
+      </c>
+      <c r="U38" s="48">
+        <v>0</v>
+      </c>
+      <c r="V38" s="48">
+        <v>0</v>
+      </c>
+      <c r="W38" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X38" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y38" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z38" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA38" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB38" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC38" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD38" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE38" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG38" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL38">
+        <v>1</v>
+      </c>
+      <c r="AM38">
+        <v>1</v>
+      </c>
+      <c r="AN38">
+        <v>6</v>
+      </c>
+      <c r="AO38">
+        <v>3</v>
+      </c>
+      <c r="AP38" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>-1</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ38" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>2</v>
+      </c>
+      <c r="BD38" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF38" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="39" spans="1:58" ht="12.5">
+      <c r="A39" s="47" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B39" s="53">
+        <v>1</v>
+      </c>
+      <c r="C39" s="53">
+        <v>0</v>
+      </c>
+      <c r="D39" s="53">
+        <v>1</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G39" s="48">
+        <v>1</v>
+      </c>
+      <c r="H39" s="48">
+        <v>2</v>
+      </c>
+      <c r="I39" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J39" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="48">
+        <v>0</v>
+      </c>
+      <c r="L39" s="48">
+        <v>150</v>
+      </c>
+      <c r="M39" s="48">
+        <v>45</v>
+      </c>
+      <c r="N39" s="48">
+        <v>45</v>
+      </c>
+      <c r="O39" s="48">
+        <v>45</v>
+      </c>
+      <c r="P39" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="48">
+        <v>11</v>
+      </c>
+      <c r="R39" s="48">
+        <v>1</v>
+      </c>
+      <c r="S39" s="48">
+        <v>0</v>
+      </c>
+      <c r="T39" s="48">
+        <v>0</v>
+      </c>
+      <c r="U39" s="48">
+        <v>0</v>
+      </c>
+      <c r="V39" s="48">
+        <v>0</v>
+      </c>
+      <c r="W39" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X39" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y39" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z39" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA39" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB39" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC39" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD39" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE39" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL39">
+        <v>1</v>
+      </c>
+      <c r="AM39">
+        <v>1</v>
+      </c>
+      <c r="AN39">
+        <v>6</v>
+      </c>
+      <c r="AO39">
+        <v>3</v>
+      </c>
+      <c r="AP39" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>-1</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ39" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>2</v>
+      </c>
+      <c r="BD39" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE39" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF39" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="40" spans="1:58" ht="12.5">
+      <c r="A40" s="47" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B40" s="53">
+        <v>1</v>
+      </c>
+      <c r="C40" s="53">
+        <v>0</v>
+      </c>
+      <c r="D40" s="53">
+        <v>1</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G40" s="48">
+        <v>1</v>
+      </c>
+      <c r="H40" s="48">
+        <v>2</v>
+      </c>
+      <c r="I40" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J40" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="48">
+        <v>0</v>
+      </c>
+      <c r="L40" s="48">
+        <v>150</v>
+      </c>
+      <c r="M40" s="48">
+        <v>45</v>
+      </c>
+      <c r="N40" s="48">
+        <v>45</v>
+      </c>
+      <c r="O40" s="48">
+        <v>45</v>
+      </c>
+      <c r="P40" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="48">
+        <v>11</v>
+      </c>
+      <c r="R40" s="48">
+        <v>1</v>
+      </c>
+      <c r="S40" s="48">
+        <v>0</v>
+      </c>
+      <c r="T40" s="48">
+        <v>0</v>
+      </c>
+      <c r="U40" s="48">
+        <v>0</v>
+      </c>
+      <c r="V40" s="48">
+        <v>0</v>
+      </c>
+      <c r="W40" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X40" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y40" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z40" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA40" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB40" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC40" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE40" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL40">
+        <v>1</v>
+      </c>
+      <c r="AM40">
+        <v>1</v>
+      </c>
+      <c r="AN40">
+        <v>6</v>
+      </c>
+      <c r="AO40">
+        <v>3</v>
+      </c>
+      <c r="AP40" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40">
+        <v>-1</v>
+      </c>
+      <c r="AV40">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ40" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA40">
+        <v>0</v>
+      </c>
+      <c r="BB40">
+        <v>0</v>
+      </c>
+      <c r="BC40">
+        <v>2</v>
+      </c>
+      <c r="BD40" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE40" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF40" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="41" spans="1:58" ht="12.5">
+      <c r="A41" s="47" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B41" s="53">
+        <v>1</v>
+      </c>
+      <c r="C41" s="53">
+        <v>0</v>
+      </c>
+      <c r="D41" s="53">
+        <v>1</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G41" s="48">
+        <v>1</v>
+      </c>
+      <c r="H41" s="48">
+        <v>2</v>
+      </c>
+      <c r="I41" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J41" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" s="48">
+        <v>0</v>
+      </c>
+      <c r="L41" s="48">
+        <v>150</v>
+      </c>
+      <c r="M41" s="48">
+        <v>45</v>
+      </c>
+      <c r="N41" s="48">
+        <v>45</v>
+      </c>
+      <c r="O41" s="48">
+        <v>45</v>
+      </c>
+      <c r="P41" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="48">
+        <v>11</v>
+      </c>
+      <c r="R41" s="48">
+        <v>1</v>
+      </c>
+      <c r="S41" s="48">
+        <v>0</v>
+      </c>
+      <c r="T41" s="48">
+        <v>0</v>
+      </c>
+      <c r="U41" s="48">
+        <v>0</v>
+      </c>
+      <c r="V41" s="48">
+        <v>0</v>
+      </c>
+      <c r="W41" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X41" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y41" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z41" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA41" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB41" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC41" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD41" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE41" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL41">
+        <v>1</v>
+      </c>
+      <c r="AM41">
+        <v>1</v>
+      </c>
+      <c r="AN41">
+        <v>6</v>
+      </c>
+      <c r="AO41">
+        <v>3</v>
+      </c>
+      <c r="AP41" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>-1</v>
+      </c>
+      <c r="AV41">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ41" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
+        <v>2</v>
+      </c>
+      <c r="BD41" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE41" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF41" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="42" spans="1:58" ht="12.5">
+      <c r="A42" s="47" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B42" s="53">
+        <v>1</v>
+      </c>
+      <c r="C42" s="53">
+        <v>0</v>
+      </c>
+      <c r="D42" s="53">
+        <v>1</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G42" s="48">
+        <v>1</v>
+      </c>
+      <c r="H42" s="48">
+        <v>2</v>
+      </c>
+      <c r="I42" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J42" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="48">
+        <v>0</v>
+      </c>
+      <c r="L42" s="48">
+        <v>150</v>
+      </c>
+      <c r="M42" s="48">
+        <v>45</v>
+      </c>
+      <c r="N42" s="48">
+        <v>45</v>
+      </c>
+      <c r="O42" s="48">
+        <v>45</v>
+      </c>
+      <c r="P42" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="48">
+        <v>11</v>
+      </c>
+      <c r="R42" s="48">
+        <v>1</v>
+      </c>
+      <c r="S42" s="48">
+        <v>0</v>
+      </c>
+      <c r="T42" s="48">
+        <v>0</v>
+      </c>
+      <c r="U42" s="48">
+        <v>0</v>
+      </c>
+      <c r="V42" s="48">
+        <v>0</v>
+      </c>
+      <c r="W42" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X42" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y42" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z42" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA42" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB42" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC42" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE42" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL42">
+        <v>1</v>
+      </c>
+      <c r="AM42">
+        <v>1</v>
+      </c>
+      <c r="AN42">
+        <v>6</v>
+      </c>
+      <c r="AO42">
+        <v>3</v>
+      </c>
+      <c r="AP42" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>-1</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ42" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
+        <v>2</v>
+      </c>
+      <c r="BD42" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE42" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF42" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="43" spans="1:58" ht="12.5">
+      <c r="A43" s="47" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B43" s="53">
+        <v>1</v>
+      </c>
+      <c r="C43" s="53">
+        <v>0</v>
+      </c>
+      <c r="D43" s="53">
+        <v>1</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F43" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G43" s="48">
+        <v>1</v>
+      </c>
+      <c r="H43" s="48">
+        <v>2</v>
+      </c>
+      <c r="I43" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J43" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="48">
+        <v>0</v>
+      </c>
+      <c r="L43" s="48">
+        <v>150</v>
+      </c>
+      <c r="M43" s="48">
+        <v>45</v>
+      </c>
+      <c r="N43" s="48">
+        <v>45</v>
+      </c>
+      <c r="O43" s="48">
+        <v>45</v>
+      </c>
+      <c r="P43" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="48">
+        <v>11</v>
+      </c>
+      <c r="R43" s="48">
+        <v>1</v>
+      </c>
+      <c r="S43" s="48">
+        <v>0</v>
+      </c>
+      <c r="T43" s="48">
+        <v>0</v>
+      </c>
+      <c r="U43" s="48">
+        <v>0</v>
+      </c>
+      <c r="V43" s="48">
+        <v>0</v>
+      </c>
+      <c r="W43" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X43" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y43" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z43" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA43" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB43" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC43" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD43" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE43" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG43" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL43">
+        <v>1</v>
+      </c>
+      <c r="AM43">
+        <v>1</v>
+      </c>
+      <c r="AN43">
+        <v>6</v>
+      </c>
+      <c r="AO43">
+        <v>3</v>
+      </c>
+      <c r="AP43" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43">
+        <v>-1</v>
+      </c>
+      <c r="AV43">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ43" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA43">
+        <v>0</v>
+      </c>
+      <c r="BB43">
+        <v>0</v>
+      </c>
+      <c r="BC43">
+        <v>2</v>
+      </c>
+      <c r="BD43" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE43" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF43" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="44" spans="1:58" ht="12.5">
+      <c r="A44" s="47" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B44" s="53">
+        <v>1</v>
+      </c>
+      <c r="C44" s="53">
+        <v>0</v>
+      </c>
+      <c r="D44" s="53">
+        <v>1</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F44" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G44" s="48">
+        <v>1</v>
+      </c>
+      <c r="H44" s="48">
+        <v>2</v>
+      </c>
+      <c r="I44" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J44" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="48">
+        <v>0</v>
+      </c>
+      <c r="L44" s="48">
+        <v>150</v>
+      </c>
+      <c r="M44" s="48">
+        <v>45</v>
+      </c>
+      <c r="N44" s="48">
+        <v>45</v>
+      </c>
+      <c r="O44" s="48">
+        <v>45</v>
+      </c>
+      <c r="P44" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="48">
+        <v>11</v>
+      </c>
+      <c r="R44" s="48">
+        <v>1</v>
+      </c>
+      <c r="S44" s="48">
+        <v>0</v>
+      </c>
+      <c r="T44" s="48">
+        <v>0</v>
+      </c>
+      <c r="U44" s="48">
+        <v>0</v>
+      </c>
+      <c r="V44" s="48">
+        <v>0</v>
+      </c>
+      <c r="W44" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X44" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y44" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z44" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA44" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB44" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC44" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD44" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE44" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF44" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG44" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL44">
+        <v>1</v>
+      </c>
+      <c r="AM44">
+        <v>1</v>
+      </c>
+      <c r="AN44">
+        <v>6</v>
+      </c>
+      <c r="AO44">
+        <v>3</v>
+      </c>
+      <c r="AP44" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44">
+        <v>-1</v>
+      </c>
+      <c r="AV44">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ44" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
+        <v>2</v>
+      </c>
+      <c r="BD44" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF44" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="45" spans="1:58" ht="12.5">
+      <c r="A45" s="47" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B45" s="53">
+        <v>1</v>
+      </c>
+      <c r="C45" s="53">
+        <v>0</v>
+      </c>
+      <c r="D45" s="53">
+        <v>1</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F45" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G45" s="48">
+        <v>1</v>
+      </c>
+      <c r="H45" s="48">
+        <v>2</v>
+      </c>
+      <c r="I45" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J45" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="48">
+        <v>0</v>
+      </c>
+      <c r="L45" s="48">
+        <v>150</v>
+      </c>
+      <c r="M45" s="48">
+        <v>45</v>
+      </c>
+      <c r="N45" s="48">
+        <v>45</v>
+      </c>
+      <c r="O45" s="48">
+        <v>45</v>
+      </c>
+      <c r="P45" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="48">
+        <v>11</v>
+      </c>
+      <c r="R45" s="48">
+        <v>1</v>
+      </c>
+      <c r="S45" s="48">
+        <v>0</v>
+      </c>
+      <c r="T45" s="48">
+        <v>0</v>
+      </c>
+      <c r="U45" s="48">
+        <v>0</v>
+      </c>
+      <c r="V45" s="48">
+        <v>0</v>
+      </c>
+      <c r="W45" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X45" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y45" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z45" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA45" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB45" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC45" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD45" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE45" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF45" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG45" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL45">
+        <v>1</v>
+      </c>
+      <c r="AM45">
+        <v>1</v>
+      </c>
+      <c r="AN45">
+        <v>6</v>
+      </c>
+      <c r="AO45">
+        <v>3</v>
+      </c>
+      <c r="AP45" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45">
+        <v>-1</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ45" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA45">
+        <v>0</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>2</v>
+      </c>
+      <c r="BD45" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE45" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF45" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="46" spans="1:58" ht="12.5">
+      <c r="A46" s="47" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B46" s="53">
+        <v>1</v>
+      </c>
+      <c r="C46" s="53">
+        <v>0</v>
+      </c>
+      <c r="D46" s="53">
+        <v>1</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F46" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G46" s="48">
+        <v>1</v>
+      </c>
+      <c r="H46" s="48">
+        <v>2</v>
+      </c>
+      <c r="I46" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J46" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="48">
+        <v>0</v>
+      </c>
+      <c r="L46" s="48">
+        <v>150</v>
+      </c>
+      <c r="M46" s="48">
+        <v>45</v>
+      </c>
+      <c r="N46" s="48">
+        <v>45</v>
+      </c>
+      <c r="O46" s="48">
+        <v>45</v>
+      </c>
+      <c r="P46" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="48">
+        <v>11</v>
+      </c>
+      <c r="R46" s="48">
+        <v>1</v>
+      </c>
+      <c r="S46" s="48">
+        <v>0</v>
+      </c>
+      <c r="T46" s="48">
+        <v>0</v>
+      </c>
+      <c r="U46" s="48">
+        <v>0</v>
+      </c>
+      <c r="V46" s="48">
+        <v>0</v>
+      </c>
+      <c r="W46" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X46" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y46" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z46" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA46" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC46" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD46" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE46" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL46">
+        <v>1</v>
+      </c>
+      <c r="AM46">
+        <v>1</v>
+      </c>
+      <c r="AN46">
+        <v>6</v>
+      </c>
+      <c r="AO46">
+        <v>3</v>
+      </c>
+      <c r="AP46" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46">
+        <v>-1</v>
+      </c>
+      <c r="AV46">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ46" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA46">
+        <v>0</v>
+      </c>
+      <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
+        <v>2</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE46" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF46" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="47" spans="1:58" ht="12.5">
+      <c r="A47" s="47" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B47" s="53">
+        <v>1</v>
+      </c>
+      <c r="C47" s="53">
+        <v>0</v>
+      </c>
+      <c r="D47" s="53">
+        <v>1</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F47" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G47" s="48">
+        <v>1</v>
+      </c>
+      <c r="H47" s="48">
+        <v>2</v>
+      </c>
+      <c r="I47" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J47" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="48">
+        <v>0</v>
+      </c>
+      <c r="L47" s="48">
+        <v>150</v>
+      </c>
+      <c r="M47" s="48">
+        <v>45</v>
+      </c>
+      <c r="N47" s="48">
+        <v>45</v>
+      </c>
+      <c r="O47" s="48">
+        <v>45</v>
+      </c>
+      <c r="P47" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="48">
+        <v>11</v>
+      </c>
+      <c r="R47" s="48">
+        <v>1</v>
+      </c>
+      <c r="S47" s="48">
+        <v>0</v>
+      </c>
+      <c r="T47" s="48">
+        <v>0</v>
+      </c>
+      <c r="U47" s="48">
+        <v>0</v>
+      </c>
+      <c r="V47" s="48">
+        <v>0</v>
+      </c>
+      <c r="W47" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X47" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y47" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z47" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA47" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB47" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC47" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD47" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE47" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL47">
+        <v>1</v>
+      </c>
+      <c r="AM47">
+        <v>1</v>
+      </c>
+      <c r="AN47">
+        <v>6</v>
+      </c>
+      <c r="AO47">
+        <v>3</v>
+      </c>
+      <c r="AP47" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47">
+        <v>-1</v>
+      </c>
+      <c r="AV47">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ47" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA47">
+        <v>0</v>
+      </c>
+      <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
+        <v>2</v>
+      </c>
+      <c r="BD47" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF47" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="48" spans="1:58" ht="12.5">
+      <c r="A48" s="47" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B48" s="53">
+        <v>1</v>
+      </c>
+      <c r="C48" s="53">
+        <v>0</v>
+      </c>
+      <c r="D48" s="53">
+        <v>1</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G48" s="48">
+        <v>1</v>
+      </c>
+      <c r="H48" s="48">
+        <v>2</v>
+      </c>
+      <c r="I48" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J48" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" s="48">
+        <v>0</v>
+      </c>
+      <c r="L48" s="48">
+        <v>150</v>
+      </c>
+      <c r="M48" s="48">
+        <v>45</v>
+      </c>
+      <c r="N48" s="48">
+        <v>45</v>
+      </c>
+      <c r="O48" s="48">
+        <v>45</v>
+      </c>
+      <c r="P48" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="48">
+        <v>11</v>
+      </c>
+      <c r="R48" s="48">
+        <v>1</v>
+      </c>
+      <c r="S48" s="48">
+        <v>0</v>
+      </c>
+      <c r="T48" s="48">
+        <v>0</v>
+      </c>
+      <c r="U48" s="48">
+        <v>0</v>
+      </c>
+      <c r="V48" s="48">
+        <v>0</v>
+      </c>
+      <c r="W48" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X48" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y48" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z48" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA48" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB48" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC48" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD48" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE48" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG48" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL48">
+        <v>1</v>
+      </c>
+      <c r="AM48">
+        <v>1</v>
+      </c>
+      <c r="AN48">
+        <v>6</v>
+      </c>
+      <c r="AO48">
+        <v>3</v>
+      </c>
+      <c r="AP48" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48">
+        <v>-1</v>
+      </c>
+      <c r="AV48">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ48" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA48">
+        <v>0</v>
+      </c>
+      <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
+        <v>2</v>
+      </c>
+      <c r="BD48" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE48" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF48" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="49" spans="1:58" ht="12.5">
+      <c r="A49" s="47" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B49" s="53">
+        <v>1</v>
+      </c>
+      <c r="C49" s="53">
+        <v>0</v>
+      </c>
+      <c r="D49" s="53">
+        <v>1</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G49" s="48">
+        <v>1</v>
+      </c>
+      <c r="H49" s="48">
+        <v>2</v>
+      </c>
+      <c r="I49" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J49" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="48">
+        <v>0</v>
+      </c>
+      <c r="L49" s="48">
+        <v>150</v>
+      </c>
+      <c r="M49" s="48">
+        <v>45</v>
+      </c>
+      <c r="N49" s="48">
+        <v>45</v>
+      </c>
+      <c r="O49" s="48">
+        <v>45</v>
+      </c>
+      <c r="P49" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="48">
+        <v>11</v>
+      </c>
+      <c r="R49" s="48">
+        <v>1</v>
+      </c>
+      <c r="S49" s="48">
+        <v>0</v>
+      </c>
+      <c r="T49" s="48">
+        <v>0</v>
+      </c>
+      <c r="U49" s="48">
+        <v>0</v>
+      </c>
+      <c r="V49" s="48">
+        <v>0</v>
+      </c>
+      <c r="W49" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X49" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y49" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z49" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA49" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB49" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC49" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD49" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE49" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF49" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG49" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL49">
+        <v>1</v>
+      </c>
+      <c r="AM49">
+        <v>1</v>
+      </c>
+      <c r="AN49">
+        <v>6</v>
+      </c>
+      <c r="AO49">
+        <v>3</v>
+      </c>
+      <c r="AP49" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49">
+        <v>-1</v>
+      </c>
+      <c r="AV49">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA49">
+        <v>0</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>2</v>
+      </c>
+      <c r="BD49" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE49" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF49" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="50" spans="1:58" ht="12.5">
+      <c r="A50" s="47" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B50" s="53">
+        <v>1</v>
+      </c>
+      <c r="C50" s="53">
+        <v>0</v>
+      </c>
+      <c r="D50" s="53">
+        <v>1</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G50" s="48">
+        <v>1</v>
+      </c>
+      <c r="H50" s="48">
+        <v>2</v>
+      </c>
+      <c r="I50" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J50" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="48">
+        <v>0</v>
+      </c>
+      <c r="L50" s="48">
+        <v>150</v>
+      </c>
+      <c r="M50" s="48">
+        <v>45</v>
+      </c>
+      <c r="N50" s="48">
+        <v>45</v>
+      </c>
+      <c r="O50" s="48">
+        <v>45</v>
+      </c>
+      <c r="P50" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="48">
+        <v>11</v>
+      </c>
+      <c r="R50" s="48">
+        <v>1</v>
+      </c>
+      <c r="S50" s="48">
+        <v>0</v>
+      </c>
+      <c r="T50" s="48">
+        <v>0</v>
+      </c>
+      <c r="U50" s="48">
+        <v>0</v>
+      </c>
+      <c r="V50" s="48">
+        <v>0</v>
+      </c>
+      <c r="W50" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X50" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y50" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z50" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA50" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB50" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC50" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD50" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE50" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG50" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL50">
+        <v>1</v>
+      </c>
+      <c r="AM50">
+        <v>1</v>
+      </c>
+      <c r="AN50">
+        <v>6</v>
+      </c>
+      <c r="AO50">
+        <v>3</v>
+      </c>
+      <c r="AP50" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50">
+        <v>-1</v>
+      </c>
+      <c r="AV50">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ50" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA50">
+        <v>0</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>2</v>
+      </c>
+      <c r="BD50" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE50" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF50" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="51" spans="1:58" ht="12.5">
+      <c r="A51" s="47" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B51" s="53">
+        <v>1</v>
+      </c>
+      <c r="C51" s="53">
+        <v>0</v>
+      </c>
+      <c r="D51" s="53">
+        <v>1</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G51" s="48">
+        <v>1</v>
+      </c>
+      <c r="H51" s="48">
+        <v>2</v>
+      </c>
+      <c r="I51" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J51" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" s="48">
+        <v>0</v>
+      </c>
+      <c r="L51" s="48">
+        <v>150</v>
+      </c>
+      <c r="M51" s="48">
+        <v>45</v>
+      </c>
+      <c r="N51" s="48">
+        <v>45</v>
+      </c>
+      <c r="O51" s="48">
+        <v>45</v>
+      </c>
+      <c r="P51" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="48">
+        <v>11</v>
+      </c>
+      <c r="R51" s="48">
+        <v>1</v>
+      </c>
+      <c r="S51" s="48">
+        <v>0</v>
+      </c>
+      <c r="T51" s="48">
+        <v>0</v>
+      </c>
+      <c r="U51" s="48">
+        <v>0</v>
+      </c>
+      <c r="V51" s="48">
+        <v>0</v>
+      </c>
+      <c r="W51" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X51" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y51" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z51" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA51" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB51" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC51" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD51" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE51" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG51" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL51">
+        <v>1</v>
+      </c>
+      <c r="AM51">
+        <v>1</v>
+      </c>
+      <c r="AN51">
+        <v>6</v>
+      </c>
+      <c r="AO51">
+        <v>3</v>
+      </c>
+      <c r="AP51" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51">
+        <v>-1</v>
+      </c>
+      <c r="AV51">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ51" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>2</v>
+      </c>
+      <c r="BD51" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE51" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF51" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="52" spans="1:58" ht="12.5">
+      <c r="A52" s="47" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B52" s="53">
+        <v>1</v>
+      </c>
+      <c r="C52" s="53">
+        <v>0</v>
+      </c>
+      <c r="D52" s="53">
+        <v>1</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G52" s="48">
+        <v>1</v>
+      </c>
+      <c r="H52" s="48">
+        <v>2</v>
+      </c>
+      <c r="I52" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J52" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="48">
+        <v>0</v>
+      </c>
+      <c r="L52" s="48">
+        <v>150</v>
+      </c>
+      <c r="M52" s="48">
+        <v>45</v>
+      </c>
+      <c r="N52" s="48">
+        <v>45</v>
+      </c>
+      <c r="O52" s="48">
+        <v>45</v>
+      </c>
+      <c r="P52" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="48">
+        <v>11</v>
+      </c>
+      <c r="R52" s="48">
+        <v>1</v>
+      </c>
+      <c r="S52" s="48">
+        <v>0</v>
+      </c>
+      <c r="T52" s="48">
+        <v>0</v>
+      </c>
+      <c r="U52" s="48">
+        <v>0</v>
+      </c>
+      <c r="V52" s="48">
+        <v>0</v>
+      </c>
+      <c r="W52" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X52" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y52" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z52" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA52" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB52" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC52" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD52" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE52" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF52" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL52">
+        <v>1</v>
+      </c>
+      <c r="AM52">
+        <v>1</v>
+      </c>
+      <c r="AN52">
+        <v>6</v>
+      </c>
+      <c r="AO52">
+        <v>3</v>
+      </c>
+      <c r="AP52" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52">
+        <v>-1</v>
+      </c>
+      <c r="AV52">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA52">
+        <v>0</v>
+      </c>
+      <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
+        <v>2</v>
+      </c>
+      <c r="BD52" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE52" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF52" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="53" spans="1:58" ht="12.5">
+      <c r="A53" s="47" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B53" s="53">
+        <v>1</v>
+      </c>
+      <c r="C53" s="53">
+        <v>0</v>
+      </c>
+      <c r="D53" s="53">
+        <v>1</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F53" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G53" s="48">
+        <v>1</v>
+      </c>
+      <c r="H53" s="48">
+        <v>2</v>
+      </c>
+      <c r="I53" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J53" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="48">
+        <v>0</v>
+      </c>
+      <c r="L53" s="48">
+        <v>150</v>
+      </c>
+      <c r="M53" s="48">
+        <v>45</v>
+      </c>
+      <c r="N53" s="48">
+        <v>45</v>
+      </c>
+      <c r="O53" s="48">
+        <v>45</v>
+      </c>
+      <c r="P53" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="48">
+        <v>11</v>
+      </c>
+      <c r="R53" s="48">
+        <v>1</v>
+      </c>
+      <c r="S53" s="48">
+        <v>0</v>
+      </c>
+      <c r="T53" s="48">
+        <v>0</v>
+      </c>
+      <c r="U53" s="48">
+        <v>0</v>
+      </c>
+      <c r="V53" s="48">
+        <v>0</v>
+      </c>
+      <c r="W53" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X53" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y53" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z53" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA53" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB53" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC53" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD53" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE53" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL53">
+        <v>1</v>
+      </c>
+      <c r="AM53">
+        <v>1</v>
+      </c>
+      <c r="AN53">
+        <v>6</v>
+      </c>
+      <c r="AO53">
+        <v>3</v>
+      </c>
+      <c r="AP53" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53">
+        <v>-1</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ53" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA53">
+        <v>0</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>2</v>
+      </c>
+      <c r="BD53" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE53" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF53" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="54" spans="1:58" ht="12.5">
+      <c r="A54" s="47" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B54" s="53">
+        <v>1</v>
+      </c>
+      <c r="C54" s="53">
+        <v>0</v>
+      </c>
+      <c r="D54" s="53">
+        <v>1</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F54" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G54" s="48">
+        <v>1</v>
+      </c>
+      <c r="H54" s="48">
+        <v>2</v>
+      </c>
+      <c r="I54" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J54" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54" s="48">
+        <v>0</v>
+      </c>
+      <c r="L54" s="48">
+        <v>150</v>
+      </c>
+      <c r="M54" s="48">
+        <v>45</v>
+      </c>
+      <c r="N54" s="48">
+        <v>45</v>
+      </c>
+      <c r="O54" s="48">
+        <v>45</v>
+      </c>
+      <c r="P54" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="48">
+        <v>11</v>
+      </c>
+      <c r="R54" s="48">
+        <v>1</v>
+      </c>
+      <c r="S54" s="48">
+        <v>0</v>
+      </c>
+      <c r="T54" s="48">
+        <v>0</v>
+      </c>
+      <c r="U54" s="48">
+        <v>0</v>
+      </c>
+      <c r="V54" s="48">
+        <v>0</v>
+      </c>
+      <c r="W54" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X54" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y54" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z54" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA54" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB54" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC54" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD54" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE54" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG54" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL54">
+        <v>1</v>
+      </c>
+      <c r="AM54">
+        <v>1</v>
+      </c>
+      <c r="AN54">
+        <v>6</v>
+      </c>
+      <c r="AO54">
+        <v>3</v>
+      </c>
+      <c r="AP54" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54">
+        <v>-1</v>
+      </c>
+      <c r="AV54">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ54" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA54">
+        <v>0</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>2</v>
+      </c>
+      <c r="BD54" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE54" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF54" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="55" spans="1:58" ht="12.5">
+      <c r="A55" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B55" s="53">
+        <v>1</v>
+      </c>
+      <c r="C55" s="53">
+        <v>0</v>
+      </c>
+      <c r="D55" s="53">
+        <v>1</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F55" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G55" s="48">
+        <v>1</v>
+      </c>
+      <c r="H55" s="48">
+        <v>2</v>
+      </c>
+      <c r="I55" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J55" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55" s="48">
+        <v>0</v>
+      </c>
+      <c r="L55" s="48">
+        <v>150</v>
+      </c>
+      <c r="M55" s="48">
+        <v>45</v>
+      </c>
+      <c r="N55" s="48">
+        <v>45</v>
+      </c>
+      <c r="O55" s="48">
+        <v>45</v>
+      </c>
+      <c r="P55" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="48">
+        <v>11</v>
+      </c>
+      <c r="R55" s="48">
+        <v>1</v>
+      </c>
+      <c r="S55" s="48">
+        <v>0</v>
+      </c>
+      <c r="T55" s="48">
+        <v>0</v>
+      </c>
+      <c r="U55" s="48">
+        <v>0</v>
+      </c>
+      <c r="V55" s="48">
+        <v>0</v>
+      </c>
+      <c r="W55" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X55" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y55" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z55" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA55" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB55" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC55" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD55" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE55" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG55" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL55">
+        <v>1</v>
+      </c>
+      <c r="AM55">
+        <v>1</v>
+      </c>
+      <c r="AN55">
+        <v>6</v>
+      </c>
+      <c r="AO55">
+        <v>3</v>
+      </c>
+      <c r="AP55" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55">
+        <v>-1</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA55">
+        <v>0</v>
+      </c>
+      <c r="BB55">
+        <v>0</v>
+      </c>
+      <c r="BC55">
+        <v>2</v>
+      </c>
+      <c r="BD55" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE55" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF55" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="56" spans="1:58" ht="12.5">
+      <c r="A56" s="47" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B56" s="53">
+        <v>1</v>
+      </c>
+      <c r="C56" s="53">
+        <v>0</v>
+      </c>
+      <c r="D56" s="53">
+        <v>1</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G56" s="48">
+        <v>1</v>
+      </c>
+      <c r="H56" s="48">
+        <v>2</v>
+      </c>
+      <c r="I56" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J56" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56" s="48">
+        <v>0</v>
+      </c>
+      <c r="L56" s="48">
+        <v>150</v>
+      </c>
+      <c r="M56" s="48">
+        <v>45</v>
+      </c>
+      <c r="N56" s="48">
+        <v>45</v>
+      </c>
+      <c r="O56" s="48">
+        <v>45</v>
+      </c>
+      <c r="P56" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="48">
+        <v>11</v>
+      </c>
+      <c r="R56" s="48">
+        <v>1</v>
+      </c>
+      <c r="S56" s="48">
+        <v>0</v>
+      </c>
+      <c r="T56" s="48">
+        <v>0</v>
+      </c>
+      <c r="U56" s="48">
+        <v>0</v>
+      </c>
+      <c r="V56" s="48">
+        <v>0</v>
+      </c>
+      <c r="W56" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X56" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y56" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z56" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA56" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB56" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC56" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD56" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE56" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG56" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL56">
+        <v>1</v>
+      </c>
+      <c r="AM56">
+        <v>1</v>
+      </c>
+      <c r="AN56">
+        <v>6</v>
+      </c>
+      <c r="AO56">
+        <v>3</v>
+      </c>
+      <c r="AP56" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56">
+        <v>-1</v>
+      </c>
+      <c r="AV56">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA56">
+        <v>0</v>
+      </c>
+      <c r="BB56">
+        <v>0</v>
+      </c>
+      <c r="BC56">
+        <v>2</v>
+      </c>
+      <c r="BD56" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE56" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF56" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="57" spans="1:58" ht="12.5">
+      <c r="A57" s="47" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B57" s="53">
+        <v>1</v>
+      </c>
+      <c r="C57" s="53">
+        <v>0</v>
+      </c>
+      <c r="D57" s="53">
+        <v>1</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G57" s="48">
+        <v>1</v>
+      </c>
+      <c r="H57" s="48">
+        <v>2</v>
+      </c>
+      <c r="I57" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J57" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57" s="48">
+        <v>0</v>
+      </c>
+      <c r="L57" s="48">
+        <v>150</v>
+      </c>
+      <c r="M57" s="48">
+        <v>45</v>
+      </c>
+      <c r="N57" s="48">
+        <v>45</v>
+      </c>
+      <c r="O57" s="48">
+        <v>45</v>
+      </c>
+      <c r="P57" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="48">
+        <v>11</v>
+      </c>
+      <c r="R57" s="48">
+        <v>1</v>
+      </c>
+      <c r="S57" s="48">
+        <v>0</v>
+      </c>
+      <c r="T57" s="48">
+        <v>0</v>
+      </c>
+      <c r="U57" s="48">
+        <v>0</v>
+      </c>
+      <c r="V57" s="48">
+        <v>0</v>
+      </c>
+      <c r="W57" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X57" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y57" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z57" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA57" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB57" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC57" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD57" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE57" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG57" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL57">
+        <v>1</v>
+      </c>
+      <c r="AM57">
+        <v>1</v>
+      </c>
+      <c r="AN57">
+        <v>6</v>
+      </c>
+      <c r="AO57">
+        <v>3</v>
+      </c>
+      <c r="AP57" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57">
+        <v>-1</v>
+      </c>
+      <c r="AV57">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA57">
+        <v>0</v>
+      </c>
+      <c r="BB57">
+        <v>0</v>
+      </c>
+      <c r="BC57">
+        <v>2</v>
+      </c>
+      <c r="BD57" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE57" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF57" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="58" spans="1:58" ht="12.5">
+      <c r="A58" s="47" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B58" s="53">
+        <v>1</v>
+      </c>
+      <c r="C58" s="53">
+        <v>0</v>
+      </c>
+      <c r="D58" s="53">
+        <v>1</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F58" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G58" s="48">
+        <v>1</v>
+      </c>
+      <c r="H58" s="48">
+        <v>2</v>
+      </c>
+      <c r="I58" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J58" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58" s="48">
+        <v>0</v>
+      </c>
+      <c r="L58" s="48">
+        <v>150</v>
+      </c>
+      <c r="M58" s="48">
+        <v>45</v>
+      </c>
+      <c r="N58" s="48">
+        <v>45</v>
+      </c>
+      <c r="O58" s="48">
+        <v>45</v>
+      </c>
+      <c r="P58" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="48">
+        <v>11</v>
+      </c>
+      <c r="R58" s="48">
+        <v>1</v>
+      </c>
+      <c r="S58" s="48">
+        <v>0</v>
+      </c>
+      <c r="T58" s="48">
+        <v>0</v>
+      </c>
+      <c r="U58" s="48">
+        <v>0</v>
+      </c>
+      <c r="V58" s="48">
+        <v>0</v>
+      </c>
+      <c r="W58" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X58" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y58" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z58" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA58" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB58" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC58" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD58" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE58" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG58" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL58">
+        <v>1</v>
+      </c>
+      <c r="AM58">
+        <v>1</v>
+      </c>
+      <c r="AN58">
+        <v>6</v>
+      </c>
+      <c r="AO58">
+        <v>3</v>
+      </c>
+      <c r="AP58" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58">
+        <v>-1</v>
+      </c>
+      <c r="AV58">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA58">
+        <v>0</v>
+      </c>
+      <c r="BB58">
+        <v>0</v>
+      </c>
+      <c r="BC58">
+        <v>2</v>
+      </c>
+      <c r="BD58" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE58" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF58" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="59" spans="1:58" ht="12.5">
+      <c r="A59" s="47" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B59" s="53">
+        <v>1</v>
+      </c>
+      <c r="C59" s="53">
+        <v>0</v>
+      </c>
+      <c r="D59" s="53">
+        <v>1</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G59" s="48">
+        <v>1</v>
+      </c>
+      <c r="H59" s="48">
+        <v>2</v>
+      </c>
+      <c r="I59" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J59" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59" s="48">
+        <v>0</v>
+      </c>
+      <c r="L59" s="48">
+        <v>150</v>
+      </c>
+      <c r="M59" s="48">
+        <v>45</v>
+      </c>
+      <c r="N59" s="48">
+        <v>45</v>
+      </c>
+      <c r="O59" s="48">
+        <v>45</v>
+      </c>
+      <c r="P59" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="48">
+        <v>11</v>
+      </c>
+      <c r="R59" s="48">
+        <v>1</v>
+      </c>
+      <c r="S59" s="48">
+        <v>0</v>
+      </c>
+      <c r="T59" s="48">
+        <v>0</v>
+      </c>
+      <c r="U59" s="48">
+        <v>0</v>
+      </c>
+      <c r="V59" s="48">
+        <v>0</v>
+      </c>
+      <c r="W59" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X59" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y59" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z59" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA59" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB59" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC59" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD59" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE59" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG59" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL59">
+        <v>1</v>
+      </c>
+      <c r="AM59">
+        <v>1</v>
+      </c>
+      <c r="AN59">
+        <v>6</v>
+      </c>
+      <c r="AO59">
+        <v>3</v>
+      </c>
+      <c r="AP59" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59">
+        <v>-1</v>
+      </c>
+      <c r="AV59">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ59" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA59">
+        <v>0</v>
+      </c>
+      <c r="BB59">
+        <v>0</v>
+      </c>
+      <c r="BC59">
+        <v>2</v>
+      </c>
+      <c r="BD59" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE59" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF59" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="60" spans="1:58" ht="12.5">
+      <c r="A60" s="47" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B60" s="53">
+        <v>1</v>
+      </c>
+      <c r="C60" s="53">
+        <v>0</v>
+      </c>
+      <c r="D60" s="53">
+        <v>1</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F60" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G60" s="48">
+        <v>1</v>
+      </c>
+      <c r="H60" s="48">
+        <v>2</v>
+      </c>
+      <c r="I60" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J60" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K60" s="48">
+        <v>0</v>
+      </c>
+      <c r="L60" s="48">
+        <v>150</v>
+      </c>
+      <c r="M60" s="48">
+        <v>45</v>
+      </c>
+      <c r="N60" s="48">
+        <v>45</v>
+      </c>
+      <c r="O60" s="48">
+        <v>45</v>
+      </c>
+      <c r="P60" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="48">
+        <v>11</v>
+      </c>
+      <c r="R60" s="48">
+        <v>1</v>
+      </c>
+      <c r="S60" s="48">
+        <v>0</v>
+      </c>
+      <c r="T60" s="48">
+        <v>0</v>
+      </c>
+      <c r="U60" s="48">
+        <v>0</v>
+      </c>
+      <c r="V60" s="48">
+        <v>0</v>
+      </c>
+      <c r="W60" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X60" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y60" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z60" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA60" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB60" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC60" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD60" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE60" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG60" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL60">
+        <v>1</v>
+      </c>
+      <c r="AM60">
+        <v>1</v>
+      </c>
+      <c r="AN60">
+        <v>6</v>
+      </c>
+      <c r="AO60">
+        <v>3</v>
+      </c>
+      <c r="AP60" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60">
+        <v>-1</v>
+      </c>
+      <c r="AV60">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ60" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA60">
+        <v>0</v>
+      </c>
+      <c r="BB60">
+        <v>0</v>
+      </c>
+      <c r="BC60">
+        <v>2</v>
+      </c>
+      <c r="BD60" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE60" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF60" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="61" spans="1:58" ht="12.5">
+      <c r="A61" s="47" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B61" s="53">
+        <v>1</v>
+      </c>
+      <c r="C61" s="53">
+        <v>0</v>
+      </c>
+      <c r="D61" s="53">
+        <v>1</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G61" s="48">
+        <v>1</v>
+      </c>
+      <c r="H61" s="48">
+        <v>2</v>
+      </c>
+      <c r="I61" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J61" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61" s="48">
+        <v>0</v>
+      </c>
+      <c r="L61" s="48">
+        <v>150</v>
+      </c>
+      <c r="M61" s="48">
+        <v>45</v>
+      </c>
+      <c r="N61" s="48">
+        <v>45</v>
+      </c>
+      <c r="O61" s="48">
+        <v>45</v>
+      </c>
+      <c r="P61" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="48">
+        <v>11</v>
+      </c>
+      <c r="R61" s="48">
+        <v>1</v>
+      </c>
+      <c r="S61" s="48">
+        <v>0</v>
+      </c>
+      <c r="T61" s="48">
+        <v>0</v>
+      </c>
+      <c r="U61" s="48">
+        <v>0</v>
+      </c>
+      <c r="V61" s="48">
+        <v>0</v>
+      </c>
+      <c r="W61" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X61" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y61" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z61" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA61" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB61" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC61" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD61" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE61" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF61" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG61" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL61">
+        <v>1</v>
+      </c>
+      <c r="AM61">
+        <v>1</v>
+      </c>
+      <c r="AN61">
+        <v>6</v>
+      </c>
+      <c r="AO61">
+        <v>3</v>
+      </c>
+      <c r="AP61" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61">
+        <v>-1</v>
+      </c>
+      <c r="AV61">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ61" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA61">
+        <v>0</v>
+      </c>
+      <c r="BB61">
+        <v>0</v>
+      </c>
+      <c r="BC61">
+        <v>2</v>
+      </c>
+      <c r="BD61" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE61" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF61" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="62" spans="1:58" ht="12.5">
+      <c r="A62" s="47" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B62" s="53">
+        <v>1</v>
+      </c>
+      <c r="C62" s="53">
+        <v>0</v>
+      </c>
+      <c r="D62" s="53">
+        <v>1</v>
+      </c>
+      <c r="E62" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G62" s="48">
+        <v>1</v>
+      </c>
+      <c r="H62" s="48">
+        <v>2</v>
+      </c>
+      <c r="I62" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J62" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K62" s="48">
+        <v>0</v>
+      </c>
+      <c r="L62" s="48">
+        <v>150</v>
+      </c>
+      <c r="M62" s="48">
+        <v>45</v>
+      </c>
+      <c r="N62" s="48">
+        <v>45</v>
+      </c>
+      <c r="O62" s="48">
+        <v>45</v>
+      </c>
+      <c r="P62" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="48">
+        <v>11</v>
+      </c>
+      <c r="R62" s="48">
+        <v>1</v>
+      </c>
+      <c r="S62" s="48">
+        <v>0</v>
+      </c>
+      <c r="T62" s="48">
+        <v>0</v>
+      </c>
+      <c r="U62" s="48">
+        <v>0</v>
+      </c>
+      <c r="V62" s="48">
+        <v>0</v>
+      </c>
+      <c r="W62" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X62" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y62" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z62" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA62" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB62" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC62" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD62" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE62" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG62" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL62">
+        <v>1</v>
+      </c>
+      <c r="AM62">
+        <v>1</v>
+      </c>
+      <c r="AN62">
+        <v>6</v>
+      </c>
+      <c r="AO62">
+        <v>3</v>
+      </c>
+      <c r="AP62" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62">
+        <v>-1</v>
+      </c>
+      <c r="AV62">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA62">
+        <v>0</v>
+      </c>
+      <c r="BB62">
+        <v>0</v>
+      </c>
+      <c r="BC62">
+        <v>2</v>
+      </c>
+      <c r="BD62" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE62" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="63" spans="1:58" ht="12.5">
+      <c r="A63" s="47" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B63" s="53">
+        <v>1</v>
+      </c>
+      <c r="C63" s="53">
+        <v>0</v>
+      </c>
+      <c r="D63" s="53">
+        <v>1</v>
+      </c>
+      <c r="E63" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F63" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G63" s="48">
+        <v>1</v>
+      </c>
+      <c r="H63" s="48">
+        <v>2</v>
+      </c>
+      <c r="I63" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J63" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" s="48">
+        <v>0</v>
+      </c>
+      <c r="L63" s="48">
+        <v>150</v>
+      </c>
+      <c r="M63" s="48">
+        <v>45</v>
+      </c>
+      <c r="N63" s="48">
+        <v>45</v>
+      </c>
+      <c r="O63" s="48">
+        <v>45</v>
+      </c>
+      <c r="P63" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="48">
+        <v>11</v>
+      </c>
+      <c r="R63" s="48">
+        <v>1</v>
+      </c>
+      <c r="S63" s="48">
+        <v>0</v>
+      </c>
+      <c r="T63" s="48">
+        <v>0</v>
+      </c>
+      <c r="U63" s="48">
+        <v>0</v>
+      </c>
+      <c r="V63" s="48">
+        <v>0</v>
+      </c>
+      <c r="W63" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X63" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y63" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z63" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA63" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB63" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC63" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD63" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE63" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG63" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL63">
+        <v>1</v>
+      </c>
+      <c r="AM63">
+        <v>1</v>
+      </c>
+      <c r="AN63">
+        <v>6</v>
+      </c>
+      <c r="AO63">
+        <v>3</v>
+      </c>
+      <c r="AP63" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63">
+        <v>-1</v>
+      </c>
+      <c r="AV63">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ63" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA63">
+        <v>0</v>
+      </c>
+      <c r="BB63">
+        <v>0</v>
+      </c>
+      <c r="BC63">
+        <v>2</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE63" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="64" spans="1:58" ht="12.5">
+      <c r="A64" s="47" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B64" s="53">
+        <v>1</v>
+      </c>
+      <c r="C64" s="53">
+        <v>0</v>
+      </c>
+      <c r="D64" s="53">
+        <v>1</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G64" s="48">
+        <v>1</v>
+      </c>
+      <c r="H64" s="48">
+        <v>2</v>
+      </c>
+      <c r="I64" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J64" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" s="48">
+        <v>0</v>
+      </c>
+      <c r="L64" s="48">
+        <v>150</v>
+      </c>
+      <c r="M64" s="48">
+        <v>45</v>
+      </c>
+      <c r="N64" s="48">
+        <v>45</v>
+      </c>
+      <c r="O64" s="48">
+        <v>45</v>
+      </c>
+      <c r="P64" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="48">
+        <v>11</v>
+      </c>
+      <c r="R64" s="48">
+        <v>1</v>
+      </c>
+      <c r="S64" s="48">
+        <v>0</v>
+      </c>
+      <c r="T64" s="48">
+        <v>0</v>
+      </c>
+      <c r="U64" s="48">
+        <v>0</v>
+      </c>
+      <c r="V64" s="48">
+        <v>0</v>
+      </c>
+      <c r="W64" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X64" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y64" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z64" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA64" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB64" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC64" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD64" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE64" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG64" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK64" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL64">
+        <v>1</v>
+      </c>
+      <c r="AM64">
+        <v>1</v>
+      </c>
+      <c r="AN64">
+        <v>6</v>
+      </c>
+      <c r="AO64">
+        <v>3</v>
+      </c>
+      <c r="AP64" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64">
+        <v>-1</v>
+      </c>
+      <c r="AV64">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA64">
+        <v>0</v>
+      </c>
+      <c r="BB64">
+        <v>0</v>
+      </c>
+      <c r="BC64">
+        <v>2</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE64" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF64" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="65" spans="1:58" ht="12.5">
+      <c r="A65" s="47" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B65" s="53">
+        <v>1</v>
+      </c>
+      <c r="C65" s="53">
+        <v>0</v>
+      </c>
+      <c r="D65" s="53">
+        <v>1</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F65" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G65" s="48">
+        <v>1</v>
+      </c>
+      <c r="H65" s="48">
+        <v>2</v>
+      </c>
+      <c r="I65" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J65" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65" s="48">
+        <v>0</v>
+      </c>
+      <c r="L65" s="48">
+        <v>150</v>
+      </c>
+      <c r="M65" s="48">
+        <v>45</v>
+      </c>
+      <c r="N65" s="48">
+        <v>45</v>
+      </c>
+      <c r="O65" s="48">
+        <v>45</v>
+      </c>
+      <c r="P65" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="48">
+        <v>11</v>
+      </c>
+      <c r="R65" s="48">
+        <v>1</v>
+      </c>
+      <c r="S65" s="48">
+        <v>0</v>
+      </c>
+      <c r="T65" s="48">
+        <v>0</v>
+      </c>
+      <c r="U65" s="48">
+        <v>0</v>
+      </c>
+      <c r="V65" s="48">
+        <v>0</v>
+      </c>
+      <c r="W65" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X65" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y65" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z65" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA65" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB65" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC65" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD65" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE65" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG65" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL65">
+        <v>1</v>
+      </c>
+      <c r="AM65">
+        <v>1</v>
+      </c>
+      <c r="AN65">
+        <v>6</v>
+      </c>
+      <c r="AO65">
+        <v>3</v>
+      </c>
+      <c r="AP65" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65">
+        <v>-1</v>
+      </c>
+      <c r="AV65">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ65" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA65">
+        <v>0</v>
+      </c>
+      <c r="BB65">
+        <v>0</v>
+      </c>
+      <c r="BC65">
+        <v>2</v>
+      </c>
+      <c r="BD65" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE65" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF65" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="66" spans="1:58" ht="12.5">
+      <c r="A66" s="47" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B66" s="53">
+        <v>1</v>
+      </c>
+      <c r="C66" s="53">
+        <v>0</v>
+      </c>
+      <c r="D66" s="53">
+        <v>1</v>
+      </c>
+      <c r="E66" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F66" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G66" s="48">
+        <v>1</v>
+      </c>
+      <c r="H66" s="48">
+        <v>2</v>
+      </c>
+      <c r="I66" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J66" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66" s="48">
+        <v>0</v>
+      </c>
+      <c r="L66" s="48">
+        <v>150</v>
+      </c>
+      <c r="M66" s="48">
+        <v>45</v>
+      </c>
+      <c r="N66" s="48">
+        <v>45</v>
+      </c>
+      <c r="O66" s="48">
+        <v>45</v>
+      </c>
+      <c r="P66" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="48">
+        <v>11</v>
+      </c>
+      <c r="R66" s="48">
+        <v>1</v>
+      </c>
+      <c r="S66" s="48">
+        <v>0</v>
+      </c>
+      <c r="T66" s="48">
+        <v>0</v>
+      </c>
+      <c r="U66" s="48">
+        <v>0</v>
+      </c>
+      <c r="V66" s="48">
+        <v>0</v>
+      </c>
+      <c r="W66" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X66" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y66" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z66" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA66" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB66" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC66" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD66" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE66" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG66" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL66">
+        <v>1</v>
+      </c>
+      <c r="AM66">
+        <v>1</v>
+      </c>
+      <c r="AN66">
+        <v>6</v>
+      </c>
+      <c r="AO66">
+        <v>3</v>
+      </c>
+      <c r="AP66" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66">
+        <v>-1</v>
+      </c>
+      <c r="AV66">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA66">
+        <v>0</v>
+      </c>
+      <c r="BB66">
+        <v>0</v>
+      </c>
+      <c r="BC66">
+        <v>2</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE66" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF66" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="67" spans="1:58" ht="12.5">
+      <c r="A67" s="47" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B67" s="53">
+        <v>1</v>
+      </c>
+      <c r="C67" s="53">
+        <v>0</v>
+      </c>
+      <c r="D67" s="53">
+        <v>1</v>
+      </c>
+      <c r="E67" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F67" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G67" s="48">
+        <v>1</v>
+      </c>
+      <c r="H67" s="48">
+        <v>2</v>
+      </c>
+      <c r="I67" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J67" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67" s="48">
+        <v>0</v>
+      </c>
+      <c r="L67" s="48">
+        <v>150</v>
+      </c>
+      <c r="M67" s="48">
+        <v>45</v>
+      </c>
+      <c r="N67" s="48">
+        <v>45</v>
+      </c>
+      <c r="O67" s="48">
+        <v>45</v>
+      </c>
+      <c r="P67" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="48">
+        <v>11</v>
+      </c>
+      <c r="R67" s="48">
+        <v>1</v>
+      </c>
+      <c r="S67" s="48">
+        <v>0</v>
+      </c>
+      <c r="T67" s="48">
+        <v>0</v>
+      </c>
+      <c r="U67" s="48">
+        <v>0</v>
+      </c>
+      <c r="V67" s="48">
+        <v>0</v>
+      </c>
+      <c r="W67" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X67" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y67" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z67" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA67" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB67" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC67" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD67" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE67" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG67" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL67">
+        <v>1</v>
+      </c>
+      <c r="AM67">
+        <v>1</v>
+      </c>
+      <c r="AN67">
+        <v>6</v>
+      </c>
+      <c r="AO67">
+        <v>3</v>
+      </c>
+      <c r="AP67" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67">
+        <v>-1</v>
+      </c>
+      <c r="AV67">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA67">
+        <v>0</v>
+      </c>
+      <c r="BB67">
+        <v>0</v>
+      </c>
+      <c r="BC67">
+        <v>2</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE67" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="68" spans="1:58" ht="12.5">
+      <c r="A68" s="47" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B68" s="53">
+        <v>1</v>
+      </c>
+      <c r="C68" s="53">
+        <v>0</v>
+      </c>
+      <c r="D68" s="53">
+        <v>1</v>
+      </c>
+      <c r="E68" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F68" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G68" s="48">
+        <v>1</v>
+      </c>
+      <c r="H68" s="48">
+        <v>2</v>
+      </c>
+      <c r="I68" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J68" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68" s="48">
+        <v>0</v>
+      </c>
+      <c r="L68" s="48">
+        <v>150</v>
+      </c>
+      <c r="M68" s="48">
+        <v>45</v>
+      </c>
+      <c r="N68" s="48">
+        <v>45</v>
+      </c>
+      <c r="O68" s="48">
+        <v>45</v>
+      </c>
+      <c r="P68" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="48">
+        <v>11</v>
+      </c>
+      <c r="R68" s="48">
+        <v>1</v>
+      </c>
+      <c r="S68" s="48">
+        <v>0</v>
+      </c>
+      <c r="T68" s="48">
+        <v>0</v>
+      </c>
+      <c r="U68" s="48">
+        <v>0</v>
+      </c>
+      <c r="V68" s="48">
+        <v>0</v>
+      </c>
+      <c r="W68" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X68" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y68" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z68" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA68" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB68" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC68" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD68" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE68" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG68" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL68">
+        <v>1</v>
+      </c>
+      <c r="AM68">
+        <v>1</v>
+      </c>
+      <c r="AN68">
+        <v>6</v>
+      </c>
+      <c r="AO68">
+        <v>3</v>
+      </c>
+      <c r="AP68" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68">
+        <v>-1</v>
+      </c>
+      <c r="AV68">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ68" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA68">
+        <v>0</v>
+      </c>
+      <c r="BB68">
+        <v>0</v>
+      </c>
+      <c r="BC68">
+        <v>2</v>
+      </c>
+      <c r="BD68" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE68" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF68" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="69" spans="1:58" ht="12.5">
+      <c r="A69" s="47" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B69" s="53">
+        <v>1</v>
+      </c>
+      <c r="C69" s="53">
+        <v>0</v>
+      </c>
+      <c r="D69" s="53">
+        <v>1</v>
+      </c>
+      <c r="E69" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F69" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G69" s="48">
+        <v>1</v>
+      </c>
+      <c r="H69" s="48">
+        <v>2</v>
+      </c>
+      <c r="I69" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J69" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69" s="48">
+        <v>0</v>
+      </c>
+      <c r="L69" s="48">
+        <v>150</v>
+      </c>
+      <c r="M69" s="48">
+        <v>45</v>
+      </c>
+      <c r="N69" s="48">
+        <v>45</v>
+      </c>
+      <c r="O69" s="48">
+        <v>45</v>
+      </c>
+      <c r="P69" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="48">
+        <v>11</v>
+      </c>
+      <c r="R69" s="48">
+        <v>1</v>
+      </c>
+      <c r="S69" s="48">
+        <v>0</v>
+      </c>
+      <c r="T69" s="48">
+        <v>0</v>
+      </c>
+      <c r="U69" s="48">
+        <v>0</v>
+      </c>
+      <c r="V69" s="48">
+        <v>0</v>
+      </c>
+      <c r="W69" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X69" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y69" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z69" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA69" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB69" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC69" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD69" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE69" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG69" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK69" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL69">
+        <v>1</v>
+      </c>
+      <c r="AM69">
+        <v>1</v>
+      </c>
+      <c r="AN69">
+        <v>6</v>
+      </c>
+      <c r="AO69">
+        <v>3</v>
+      </c>
+      <c r="AP69" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69">
+        <v>-1</v>
+      </c>
+      <c r="AV69">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ69" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA69">
+        <v>0</v>
+      </c>
+      <c r="BB69">
+        <v>0</v>
+      </c>
+      <c r="BC69">
+        <v>2</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE69" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="70" spans="1:58" ht="12.5">
+      <c r="A70" s="47" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B70" s="53">
+        <v>1</v>
+      </c>
+      <c r="C70" s="53">
+        <v>0</v>
+      </c>
+      <c r="D70" s="53">
+        <v>1</v>
+      </c>
+      <c r="E70" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F70" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G70" s="48">
+        <v>1</v>
+      </c>
+      <c r="H70" s="48">
+        <v>2</v>
+      </c>
+      <c r="I70" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J70" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="48">
+        <v>0</v>
+      </c>
+      <c r="L70" s="48">
+        <v>150</v>
+      </c>
+      <c r="M70" s="48">
+        <v>45</v>
+      </c>
+      <c r="N70" s="48">
+        <v>45</v>
+      </c>
+      <c r="O70" s="48">
+        <v>45</v>
+      </c>
+      <c r="P70" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="48">
+        <v>11</v>
+      </c>
+      <c r="R70" s="48">
+        <v>1</v>
+      </c>
+      <c r="S70" s="48">
+        <v>0</v>
+      </c>
+      <c r="T70" s="48">
+        <v>0</v>
+      </c>
+      <c r="U70" s="48">
+        <v>0</v>
+      </c>
+      <c r="V70" s="48">
+        <v>0</v>
+      </c>
+      <c r="W70" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X70" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y70" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z70" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA70" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB70" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC70" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD70" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE70" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG70" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL70">
+        <v>1</v>
+      </c>
+      <c r="AM70">
+        <v>1</v>
+      </c>
+      <c r="AN70">
+        <v>6</v>
+      </c>
+      <c r="AO70">
+        <v>3</v>
+      </c>
+      <c r="AP70" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70">
+        <v>-1</v>
+      </c>
+      <c r="AV70">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ70" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA70">
+        <v>0</v>
+      </c>
+      <c r="BB70">
+        <v>0</v>
+      </c>
+      <c r="BC70">
+        <v>2</v>
+      </c>
+      <c r="BD70" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE70" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="71" spans="1:58" ht="12.5">
+      <c r="A71" s="47" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B71" s="53">
+        <v>1</v>
+      </c>
+      <c r="C71" s="53">
+        <v>0</v>
+      </c>
+      <c r="D71" s="53">
+        <v>1</v>
+      </c>
+      <c r="E71" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F71" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G71" s="48">
+        <v>1</v>
+      </c>
+      <c r="H71" s="48">
+        <v>2</v>
+      </c>
+      <c r="I71" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J71" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71" s="48">
+        <v>0</v>
+      </c>
+      <c r="L71" s="48">
+        <v>150</v>
+      </c>
+      <c r="M71" s="48">
+        <v>45</v>
+      </c>
+      <c r="N71" s="48">
+        <v>45</v>
+      </c>
+      <c r="O71" s="48">
+        <v>45</v>
+      </c>
+      <c r="P71" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="48">
+        <v>11</v>
+      </c>
+      <c r="R71" s="48">
+        <v>1</v>
+      </c>
+      <c r="S71" s="48">
+        <v>0</v>
+      </c>
+      <c r="T71" s="48">
+        <v>0</v>
+      </c>
+      <c r="U71" s="48">
+        <v>0</v>
+      </c>
+      <c r="V71" s="48">
+        <v>0</v>
+      </c>
+      <c r="W71" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X71" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y71" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z71" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA71" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB71" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC71" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD71" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE71" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK71" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL71">
+        <v>1</v>
+      </c>
+      <c r="AM71">
+        <v>1</v>
+      </c>
+      <c r="AN71">
+        <v>6</v>
+      </c>
+      <c r="AO71">
+        <v>3</v>
+      </c>
+      <c r="AP71" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71">
+        <v>-1</v>
+      </c>
+      <c r="AV71">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ71" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA71">
+        <v>0</v>
+      </c>
+      <c r="BB71">
+        <v>0</v>
+      </c>
+      <c r="BC71">
+        <v>2</v>
+      </c>
+      <c r="BD71" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE71" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="72" spans="1:58" ht="12.5">
+      <c r="A72" s="47" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B72" s="53">
+        <v>1</v>
+      </c>
+      <c r="C72" s="53">
+        <v>0</v>
+      </c>
+      <c r="D72" s="53">
+        <v>1</v>
+      </c>
+      <c r="E72" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F72" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G72" s="48">
+        <v>1</v>
+      </c>
+      <c r="H72" s="48">
+        <v>2</v>
+      </c>
+      <c r="I72" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J72" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" s="48">
+        <v>0</v>
+      </c>
+      <c r="L72" s="48">
+        <v>150</v>
+      </c>
+      <c r="M72" s="48">
+        <v>45</v>
+      </c>
+      <c r="N72" s="48">
+        <v>45</v>
+      </c>
+      <c r="O72" s="48">
+        <v>45</v>
+      </c>
+      <c r="P72" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="48">
+        <v>11</v>
+      </c>
+      <c r="R72" s="48">
+        <v>1</v>
+      </c>
+      <c r="S72" s="48">
+        <v>0</v>
+      </c>
+      <c r="T72" s="48">
+        <v>0</v>
+      </c>
+      <c r="U72" s="48">
+        <v>0</v>
+      </c>
+      <c r="V72" s="48">
+        <v>0</v>
+      </c>
+      <c r="W72" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X72" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y72" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z72" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA72" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB72" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC72" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD72" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE72" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF72" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG72" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ72" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK72" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL72">
+        <v>1</v>
+      </c>
+      <c r="AM72">
+        <v>1</v>
+      </c>
+      <c r="AN72">
+        <v>6</v>
+      </c>
+      <c r="AO72">
+        <v>3</v>
+      </c>
+      <c r="AP72" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72">
+        <v>-1</v>
+      </c>
+      <c r="AV72">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA72">
+        <v>0</v>
+      </c>
+      <c r="BB72">
+        <v>0</v>
+      </c>
+      <c r="BC72">
+        <v>2</v>
+      </c>
+      <c r="BD72" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE72" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="73" spans="1:58" ht="12.5">
+      <c r="A73" s="47" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B73" s="53">
+        <v>1</v>
+      </c>
+      <c r="C73" s="53">
+        <v>0</v>
+      </c>
+      <c r="D73" s="53">
+        <v>1</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F73" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G73" s="48">
+        <v>1</v>
+      </c>
+      <c r="H73" s="48">
+        <v>2</v>
+      </c>
+      <c r="I73" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J73" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" s="48">
+        <v>0</v>
+      </c>
+      <c r="L73" s="48">
+        <v>150</v>
+      </c>
+      <c r="M73" s="48">
+        <v>45</v>
+      </c>
+      <c r="N73" s="48">
+        <v>45</v>
+      </c>
+      <c r="O73" s="48">
+        <v>45</v>
+      </c>
+      <c r="P73" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="48">
+        <v>11</v>
+      </c>
+      <c r="R73" s="48">
+        <v>1</v>
+      </c>
+      <c r="S73" s="48">
+        <v>0</v>
+      </c>
+      <c r="T73" s="48">
+        <v>0</v>
+      </c>
+      <c r="U73" s="48">
+        <v>0</v>
+      </c>
+      <c r="V73" s="48">
+        <v>0</v>
+      </c>
+      <c r="W73" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X73" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y73" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z73" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA73" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB73" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC73" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD73" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE73" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG73" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK73" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL73">
+        <v>1</v>
+      </c>
+      <c r="AM73">
+        <v>1</v>
+      </c>
+      <c r="AN73">
+        <v>6</v>
+      </c>
+      <c r="AO73">
+        <v>3</v>
+      </c>
+      <c r="AP73" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73">
+        <v>-1</v>
+      </c>
+      <c r="AV73">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ73" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA73">
+        <v>0</v>
+      </c>
+      <c r="BB73">
+        <v>0</v>
+      </c>
+      <c r="BC73">
+        <v>2</v>
+      </c>
+      <c r="BD73" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE73" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="74" spans="1:58" ht="12.5">
+      <c r="A74" s="47" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B74" s="53">
+        <v>1</v>
+      </c>
+      <c r="C74" s="53">
+        <v>0</v>
+      </c>
+      <c r="D74" s="53">
+        <v>1</v>
+      </c>
+      <c r="E74" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F74" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G74" s="48">
+        <v>1</v>
+      </c>
+      <c r="H74" s="48">
+        <v>2</v>
+      </c>
+      <c r="I74" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J74" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74" s="48">
+        <v>0</v>
+      </c>
+      <c r="L74" s="48">
+        <v>150</v>
+      </c>
+      <c r="M74" s="48">
+        <v>45</v>
+      </c>
+      <c r="N74" s="48">
+        <v>45</v>
+      </c>
+      <c r="O74" s="48">
+        <v>45</v>
+      </c>
+      <c r="P74" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="48">
+        <v>11</v>
+      </c>
+      <c r="R74" s="48">
+        <v>1</v>
+      </c>
+      <c r="S74" s="48">
+        <v>0</v>
+      </c>
+      <c r="T74" s="48">
+        <v>0</v>
+      </c>
+      <c r="U74" s="48">
+        <v>0</v>
+      </c>
+      <c r="V74" s="48">
+        <v>0</v>
+      </c>
+      <c r="W74" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X74" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y74" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z74" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA74" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB74" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC74" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD74" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE74" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF74" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG74" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ74" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK74" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL74">
+        <v>1</v>
+      </c>
+      <c r="AM74">
+        <v>1</v>
+      </c>
+      <c r="AN74">
+        <v>6</v>
+      </c>
+      <c r="AO74">
+        <v>3</v>
+      </c>
+      <c r="AP74" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>0</v>
+      </c>
+      <c r="AT74">
+        <v>0</v>
+      </c>
+      <c r="AU74">
+        <v>-1</v>
+      </c>
+      <c r="AV74">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ74" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA74">
+        <v>0</v>
+      </c>
+      <c r="BB74">
+        <v>0</v>
+      </c>
+      <c r="BC74">
+        <v>2</v>
+      </c>
+      <c r="BD74" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE74" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="75" spans="1:58" ht="12.5">
+      <c r="A75" s="47" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B75" s="53">
+        <v>1</v>
+      </c>
+      <c r="C75" s="53">
+        <v>0</v>
+      </c>
+      <c r="D75" s="53">
+        <v>1</v>
+      </c>
+      <c r="E75" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F75" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G75" s="48">
+        <v>1</v>
+      </c>
+      <c r="H75" s="48">
+        <v>2</v>
+      </c>
+      <c r="I75" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J75" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" s="48">
+        <v>0</v>
+      </c>
+      <c r="L75" s="48">
+        <v>150</v>
+      </c>
+      <c r="M75" s="48">
+        <v>45</v>
+      </c>
+      <c r="N75" s="48">
+        <v>45</v>
+      </c>
+      <c r="O75" s="48">
+        <v>45</v>
+      </c>
+      <c r="P75" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="48">
+        <v>11</v>
+      </c>
+      <c r="R75" s="48">
+        <v>1</v>
+      </c>
+      <c r="S75" s="48">
+        <v>0</v>
+      </c>
+      <c r="T75" s="48">
+        <v>0</v>
+      </c>
+      <c r="U75" s="48">
+        <v>0</v>
+      </c>
+      <c r="V75" s="48">
+        <v>0</v>
+      </c>
+      <c r="W75" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X75" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y75" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z75" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA75" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB75" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC75" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD75" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE75" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG75" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK75" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL75">
+        <v>1</v>
+      </c>
+      <c r="AM75">
+        <v>1</v>
+      </c>
+      <c r="AN75">
+        <v>6</v>
+      </c>
+      <c r="AO75">
+        <v>3</v>
+      </c>
+      <c r="AP75" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75">
+        <v>-1</v>
+      </c>
+      <c r="AV75">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ75" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA75">
+        <v>0</v>
+      </c>
+      <c r="BB75">
+        <v>0</v>
+      </c>
+      <c r="BC75">
+        <v>2</v>
+      </c>
+      <c r="BD75" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE75" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF75" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="76" spans="1:58" ht="12.5">
+      <c r="A76" s="47" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B76" s="53">
+        <v>1</v>
+      </c>
+      <c r="C76" s="53">
+        <v>0</v>
+      </c>
+      <c r="D76" s="53">
+        <v>1</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F76" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G76" s="48">
+        <v>1</v>
+      </c>
+      <c r="H76" s="48">
+        <v>2</v>
+      </c>
+      <c r="I76" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J76" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" s="48">
+        <v>0</v>
+      </c>
+      <c r="L76" s="48">
+        <v>150</v>
+      </c>
+      <c r="M76" s="48">
+        <v>45</v>
+      </c>
+      <c r="N76" s="48">
+        <v>45</v>
+      </c>
+      <c r="O76" s="48">
+        <v>45</v>
+      </c>
+      <c r="P76" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="48">
+        <v>11</v>
+      </c>
+      <c r="R76" s="48">
+        <v>1</v>
+      </c>
+      <c r="S76" s="48">
+        <v>0</v>
+      </c>
+      <c r="T76" s="48">
+        <v>0</v>
+      </c>
+      <c r="U76" s="48">
+        <v>0</v>
+      </c>
+      <c r="V76" s="48">
+        <v>0</v>
+      </c>
+      <c r="W76" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X76" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y76" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z76" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA76" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB76" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC76" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD76" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE76" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK76" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL76">
+        <v>1</v>
+      </c>
+      <c r="AM76">
+        <v>1</v>
+      </c>
+      <c r="AN76">
+        <v>6</v>
+      </c>
+      <c r="AO76">
+        <v>3</v>
+      </c>
+      <c r="AP76" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76">
+        <v>0</v>
+      </c>
+      <c r="AS76">
+        <v>0</v>
+      </c>
+      <c r="AT76">
+        <v>0</v>
+      </c>
+      <c r="AU76">
+        <v>-1</v>
+      </c>
+      <c r="AV76">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ76" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA76">
+        <v>0</v>
+      </c>
+      <c r="BB76">
+        <v>0</v>
+      </c>
+      <c r="BC76">
+        <v>2</v>
+      </c>
+      <c r="BD76" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE76" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF76" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="77" spans="1:58" ht="12.5">
+      <c r="A77" s="47" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B77" s="53">
+        <v>1</v>
+      </c>
+      <c r="C77" s="53">
+        <v>0</v>
+      </c>
+      <c r="D77" s="53">
+        <v>1</v>
+      </c>
+      <c r="E77" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F77" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G77" s="48">
+        <v>1</v>
+      </c>
+      <c r="H77" s="48">
+        <v>2</v>
+      </c>
+      <c r="I77" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J77" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" s="48">
+        <v>0</v>
+      </c>
+      <c r="L77" s="48">
+        <v>150</v>
+      </c>
+      <c r="M77" s="48">
+        <v>45</v>
+      </c>
+      <c r="N77" s="48">
+        <v>45</v>
+      </c>
+      <c r="O77" s="48">
+        <v>45</v>
+      </c>
+      <c r="P77" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="48">
+        <v>11</v>
+      </c>
+      <c r="R77" s="48">
+        <v>1</v>
+      </c>
+      <c r="S77" s="48">
+        <v>0</v>
+      </c>
+      <c r="T77" s="48">
+        <v>0</v>
+      </c>
+      <c r="U77" s="48">
+        <v>0</v>
+      </c>
+      <c r="V77" s="48">
+        <v>0</v>
+      </c>
+      <c r="W77" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X77" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y77" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z77" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA77" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB77" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC77" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD77" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE77" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK77" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL77">
+        <v>1</v>
+      </c>
+      <c r="AM77">
+        <v>1</v>
+      </c>
+      <c r="AN77">
+        <v>6</v>
+      </c>
+      <c r="AO77">
+        <v>3</v>
+      </c>
+      <c r="AP77" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77">
+        <v>0</v>
+      </c>
+      <c r="AS77">
+        <v>0</v>
+      </c>
+      <c r="AT77">
+        <v>0</v>
+      </c>
+      <c r="AU77">
+        <v>-1</v>
+      </c>
+      <c r="AV77">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ77" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA77">
+        <v>0</v>
+      </c>
+      <c r="BB77">
+        <v>0</v>
+      </c>
+      <c r="BC77">
+        <v>2</v>
+      </c>
+      <c r="BD77" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE77" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF77" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="78" spans="1:58" ht="12.5">
+      <c r="A78" s="47" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B78" s="53">
+        <v>1</v>
+      </c>
+      <c r="C78" s="53">
+        <v>0</v>
+      </c>
+      <c r="D78" s="53">
+        <v>1</v>
+      </c>
+      <c r="E78" s="53" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F78" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G78" s="48">
+        <v>1</v>
+      </c>
+      <c r="H78" s="48">
+        <v>2</v>
+      </c>
+      <c r="I78" s="48" t="s">
+        <v>813</v>
+      </c>
+      <c r="J78" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" s="48">
+        <v>0</v>
+      </c>
+      <c r="L78" s="48">
+        <v>150</v>
+      </c>
+      <c r="M78" s="48">
+        <v>45</v>
+      </c>
+      <c r="N78" s="48">
+        <v>45</v>
+      </c>
+      <c r="O78" s="48">
+        <v>45</v>
+      </c>
+      <c r="P78" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="48">
+        <v>11</v>
+      </c>
+      <c r="R78" s="48">
+        <v>1</v>
+      </c>
+      <c r="S78" s="48">
+        <v>0</v>
+      </c>
+      <c r="T78" s="48">
+        <v>0</v>
+      </c>
+      <c r="U78" s="48">
+        <v>0</v>
+      </c>
+      <c r="V78" s="48">
+        <v>0</v>
+      </c>
+      <c r="W78" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X78" s="48">
+        <v>30</v>
+      </c>
+      <c r="Y78" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z78" s="40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AA78" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB78" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC78" s="40">
+        <v>40</v>
+      </c>
+      <c r="AD78" s="7">
+        <v>80</v>
+      </c>
+      <c r="AE78" s="42">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="40">
+        <v>45</v>
+      </c>
+      <c r="AG78" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK78" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL78">
+        <v>1</v>
+      </c>
+      <c r="AM78">
+        <v>1</v>
+      </c>
+      <c r="AN78">
+        <v>6</v>
+      </c>
+      <c r="AO78">
+        <v>3</v>
+      </c>
+      <c r="AP78" s="46" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78">
+        <v>0</v>
+      </c>
+      <c r="AS78">
+        <v>0</v>
+      </c>
+      <c r="AT78">
+        <v>0</v>
+      </c>
+      <c r="AU78">
+        <v>-1</v>
+      </c>
+      <c r="AV78">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ78" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA78">
+        <v>0</v>
+      </c>
+      <c r="BB78">
+        <v>0</v>
+      </c>
+      <c r="BC78">
+        <v>2</v>
+      </c>
+      <c r="BD78" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BE78" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BF78" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="79" spans="1:58" ht="12.5">
       <c r="G79" s="38"/>
       <c r="H79" s="38"/>
       <c r="X79" s="41"/>
       <c r="AE79" s="41"/>
     </row>
-    <row r="80" spans="7:31" ht="12.5">
+    <row r="80" spans="1:58" ht="12.5">
       <c r="G80" s="38"/>
       <c r="H80" s="38"/>
       <c r="X80" s="41"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0343173F-53B3-4628-B9B8-4CA971CF56EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28254772-FD19-4BCC-A6CB-D60791066686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="48">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="O4" s="48">
         <v>45</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28254772-FD19-4BCC-A6CB-D60791066686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EE69E3-7F0A-4102-8BF4-FB632F971A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7092,7 +7092,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>1869</v>
+        <v>36</v>
       </c>
       <c r="AC4" s="40" t="s">
         <v>35</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EE69E3-7F0A-4102-8BF4-FB632F971A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C0C3D4-5401-495B-B06D-2AA9C4FF0C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7092,7 +7092,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>36</v>
+        <v>1587</v>
       </c>
       <c r="AC4" s="40" t="s">
         <v>35</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C0C3D4-5401-495B-B06D-2AA9C4FF0C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EAB3FA-905D-4A0A-892F-E4B9D813699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="8" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -6692,7 +6692,7 @@
         <v>45</v>
       </c>
       <c r="P2" s="48">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q2" s="48">
         <v>100</v>
@@ -42738,7 +42738,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>1142</v>
+        <v>1366</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -42761,7 +42761,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>1143</v>
+        <v>1369</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -56353,7 +56353,7 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EAB3FA-905D-4A0A-892F-E4B9D813699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DAD45D-8EB7-480B-9823-C9058099D4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="8" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -52906,7 +52906,7 @@
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
     <col min="2" max="3" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
     <col min="6" max="6" width="11.36328125" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" customWidth="1"/>
@@ -59733,7 +59733,7 @@
         <v>1</v>
       </c>
       <c r="AR22">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AS22" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DAD45D-8EB7-480B-9823-C9058099D4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3DA795-55A1-4C6C-A775-E7617F2DD151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -7092,7 +7092,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>1587</v>
+        <v>1485</v>
       </c>
       <c r="AC4" s="40" t="s">
         <v>35</v>
@@ -7101,10 +7101,10 @@
         <v>36</v>
       </c>
       <c r="AE4" s="40">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="AF4" s="7">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="AG4" s="42">
         <v>1</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3DA795-55A1-4C6C-A775-E7617F2DD151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB7F33A-E41F-47A7-886E-7B337FBCE577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9111" uniqueCount="1871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9139" uniqueCount="1873">
   <si>
     <t>NAME</t>
   </si>
@@ -5797,6 +5797,12 @@
   </si>
   <si>
     <t>blind</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>buff_def1</t>
   </si>
 </sst>
 </file>
@@ -7050,13 +7056,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="48">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="O4" s="48">
         <v>45</v>
       </c>
       <c r="P4" s="48">
-        <v>45</v>
+        <v>4500</v>
       </c>
       <c r="Q4" s="48">
         <v>45</v>
@@ -55846,7 +55852,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BJ41"/>
+  <dimension ref="A1:BJ43"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -63122,6 +63128,358 @@
         <v>36</v>
       </c>
     </row>
+    <row r="42" spans="1:58">
+      <c r="A42" s="44" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>3</v>
+      </c>
+      <c r="X42">
+        <v>2</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>1</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>-1</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>10</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>1872</v>
+      </c>
+      <c r="AH42" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AI42" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ42" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK42" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM42" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO42" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>1</v>
+      </c>
+      <c r="AR42">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ42" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
+        <v>0</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BF42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:58">
+      <c r="A43" s="44" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>50</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>3</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>1</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>5</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH43" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AI43" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ43" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK43" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM43" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN43" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO43" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>0</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>1</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV43">
+        <v>0</v>
+      </c>
+      <c r="AW43">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ43" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA43">
+        <v>0</v>
+      </c>
+      <c r="BB43">
+        <v>0</v>
+      </c>
+      <c r="BC43">
+        <v>0</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BF43" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB7F33A-E41F-47A7-886E-7B337FBCE577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C98744-44A1-4EFB-B01B-29301010DFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -56156,7 +56156,7 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X2">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C98744-44A1-4EFB-B01B-29301010DFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0140378-2D1C-4135-BABF-A38D60E7DD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7062,7 +7062,7 @@
         <v>45</v>
       </c>
       <c r="P4" s="48">
-        <v>4500</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="48">
         <v>45</v>
@@ -56219,7 +56219,7 @@
         <v>1</v>
       </c>
       <c r="AR2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="s">
         <v>36</v>
@@ -56395,7 +56395,7 @@
         <v>1</v>
       </c>
       <c r="AR3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0140378-2D1C-4135-BABF-A38D60E7DD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24F2E56-7FD9-42EF-BDAE-AE0646A77071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -53543,7 +53543,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -53594,7 +53594,7 @@
         <v>1</v>
       </c>
       <c r="X8" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="Y8" t="s">
         <v>1615</v>
@@ -53629,7 +53629,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -53680,7 +53680,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="Y9" t="s">
         <v>36</v>
@@ -53766,7 +53766,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="Y10" t="s">
         <v>36</v>
@@ -54368,7 +54368,7 @@
         <v>1</v>
       </c>
       <c r="X17" s="44" t="s">
-        <v>38</v>
+        <v>1182</v>
       </c>
       <c r="Y17" t="s">
         <v>1616</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24F2E56-7FD9-42EF-BDAE-AE0646A77071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF5D889-BE28-41DC-A4A9-5DB447E1CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -5613,9 +5613,6 @@
     <t>cure_potion</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5#cure_potion,3</t>
-  </si>
-  <si>
     <t>IS_BOSS</t>
   </si>
   <si>
@@ -5803,6 +5800,9 @@
   </si>
   <si>
     <t>buff_def1</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5#cure_potion,3#wood,100</t>
   </si>
 </sst>
 </file>
@@ -6474,25 +6474,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>1812</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>1868</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>1811</v>
-      </c>
       <c r="H1" s="6" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="I1" s="49" t="s">
         <v>3</v>
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H4" s="53" t="s">
         <v>1182</v>
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H5" s="53" t="s">
         <v>1182</v>
@@ -11221,7 +11221,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H27" s="53" t="s">
         <v>1182</v>
@@ -11567,7 +11567,7 @@
     </row>
     <row r="29" spans="1:60" ht="14">
       <c r="A29" s="54" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B29" s="53">
         <v>1</v>
@@ -11585,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H29" s="53" t="s">
         <v>1182</v>
@@ -11749,7 +11749,7 @@
     </row>
     <row r="30" spans="1:60" ht="12.5">
       <c r="A30" s="47" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B30" s="53">
         <v>2</v>
@@ -11767,7 +11767,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H30" s="53" t="s">
         <v>1182</v>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="31" spans="1:60" ht="12.5">
       <c r="A31" s="47" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B31" s="53">
         <v>3</v>
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H31" s="53" t="s">
         <v>1182</v>
@@ -12113,7 +12113,7 @@
     </row>
     <row r="32" spans="1:60" ht="12.5">
       <c r="A32" s="47" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B32" s="53">
         <v>4</v>
@@ -12131,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H32" s="53" t="s">
         <v>1182</v>
@@ -12295,7 +12295,7 @@
     </row>
     <row r="33" spans="1:60" ht="12.5">
       <c r="A33" s="47" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B33" s="53">
         <v>5</v>
@@ -12313,7 +12313,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H33" s="53" t="s">
         <v>1182</v>
@@ -12477,7 +12477,7 @@
     </row>
     <row r="34" spans="1:60" ht="12.5">
       <c r="A34" s="47" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B34" s="53">
         <v>6</v>
@@ -12495,7 +12495,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H34" s="53" t="s">
         <v>1182</v>
@@ -12659,7 +12659,7 @@
     </row>
     <row r="35" spans="1:60" ht="12.5">
       <c r="A35" s="47" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B35" s="53">
         <v>7</v>
@@ -12677,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H35" s="53" t="s">
         <v>1182</v>
@@ -12841,7 +12841,7 @@
     </row>
     <row r="36" spans="1:60" ht="12.5">
       <c r="A36" s="47" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B36" s="53">
         <v>8</v>
@@ -12859,7 +12859,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H36" s="53" t="s">
         <v>1182</v>
@@ -13023,7 +13023,7 @@
     </row>
     <row r="37" spans="1:60" ht="12.5">
       <c r="A37" s="47" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="B37" s="53">
         <v>9</v>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H37" s="53" t="s">
         <v>1182</v>
@@ -13205,7 +13205,7 @@
     </row>
     <row r="38" spans="1:60" ht="12.5">
       <c r="A38" s="47" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B38" s="53">
         <v>1</v>
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H38" s="53" t="s">
         <v>1182</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="39" spans="1:60" ht="12.5">
       <c r="A39" s="47" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B39" s="53">
         <v>2</v>
@@ -13405,7 +13405,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H39" s="53" t="s">
         <v>1182</v>
@@ -13569,7 +13569,7 @@
     </row>
     <row r="40" spans="1:60" ht="12.5">
       <c r="A40" s="47" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B40" s="53">
         <v>3</v>
@@ -13587,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H40" s="53" t="s">
         <v>1182</v>
@@ -13751,7 +13751,7 @@
     </row>
     <row r="41" spans="1:60" ht="12.5">
       <c r="A41" s="47" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B41" s="53">
         <v>4</v>
@@ -13769,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H41" s="53" t="s">
         <v>1182</v>
@@ -13933,7 +13933,7 @@
     </row>
     <row r="42" spans="1:60" ht="12.5">
       <c r="A42" s="47" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B42" s="53">
         <v>5</v>
@@ -13951,7 +13951,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H42" s="53" t="s">
         <v>1182</v>
@@ -14115,7 +14115,7 @@
     </row>
     <row r="43" spans="1:60" ht="12.5">
       <c r="A43" s="47" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B43" s="53">
         <v>6</v>
@@ -14133,7 +14133,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H43" s="53" t="s">
         <v>1182</v>
@@ -14297,7 +14297,7 @@
     </row>
     <row r="44" spans="1:60" ht="12.5">
       <c r="A44" s="47" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B44" s="53">
         <v>7</v>
@@ -14315,7 +14315,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H44" s="53" t="s">
         <v>1182</v>
@@ -14479,7 +14479,7 @@
     </row>
     <row r="45" spans="1:60" ht="12.5">
       <c r="A45" s="47" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B45" s="53">
         <v>8</v>
@@ -14497,7 +14497,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H45" s="53" t="s">
         <v>1182</v>
@@ -14661,7 +14661,7 @@
     </row>
     <row r="46" spans="1:60" ht="12.5">
       <c r="A46" s="47" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B46" s="53">
         <v>9</v>
@@ -14679,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H46" s="53" t="s">
         <v>1182</v>
@@ -14843,7 +14843,7 @@
     </row>
     <row r="47" spans="1:60" ht="12.5">
       <c r="A47" s="47" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B47" s="53">
         <v>1</v>
@@ -14861,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H47" s="53" t="s">
         <v>1182</v>
@@ -15025,7 +15025,7 @@
     </row>
     <row r="48" spans="1:60" ht="12.5">
       <c r="A48" s="47" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B48" s="53">
         <v>2</v>
@@ -15043,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H48" s="53" t="s">
         <v>1182</v>
@@ -15207,7 +15207,7 @@
     </row>
     <row r="49" spans="1:60" ht="12.5">
       <c r="A49" s="47" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B49" s="53">
         <v>3</v>
@@ -15225,7 +15225,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H49" s="53" t="s">
         <v>1182</v>
@@ -15389,7 +15389,7 @@
     </row>
     <row r="50" spans="1:60" ht="12.5">
       <c r="A50" s="47" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B50" s="53">
         <v>4</v>
@@ -15407,7 +15407,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H50" s="53" t="s">
         <v>1182</v>
@@ -15571,7 +15571,7 @@
     </row>
     <row r="51" spans="1:60" ht="12.5">
       <c r="A51" s="47" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B51" s="53">
         <v>5</v>
@@ -15589,7 +15589,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H51" s="53" t="s">
         <v>1182</v>
@@ -15753,7 +15753,7 @@
     </row>
     <row r="52" spans="1:60" ht="12.5">
       <c r="A52" s="47" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B52" s="53">
         <v>6</v>
@@ -15771,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H52" s="53" t="s">
         <v>1182</v>
@@ -15935,7 +15935,7 @@
     </row>
     <row r="53" spans="1:60" ht="12.5">
       <c r="A53" s="47" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B53" s="53">
         <v>7</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H53" s="53" t="s">
         <v>1182</v>
@@ -16117,7 +16117,7 @@
     </row>
     <row r="54" spans="1:60" ht="12.5">
       <c r="A54" s="47" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B54" s="53">
         <v>8</v>
@@ -16135,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H54" s="53" t="s">
         <v>1182</v>
@@ -16299,7 +16299,7 @@
     </row>
     <row r="55" spans="1:60" ht="12.5">
       <c r="A55" s="47" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B55" s="53">
         <v>9</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H55" s="53" t="s">
         <v>1182</v>
@@ -16481,7 +16481,7 @@
     </row>
     <row r="56" spans="1:60" ht="12.5">
       <c r="A56" s="47" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B56" s="53">
         <v>1</v>
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H56" s="53" t="s">
         <v>1182</v>
@@ -16663,7 +16663,7 @@
     </row>
     <row r="57" spans="1:60" ht="12.5">
       <c r="A57" s="47" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="B57" s="53">
         <v>2</v>
@@ -16681,7 +16681,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H57" s="53" t="s">
         <v>1182</v>
@@ -16845,7 +16845,7 @@
     </row>
     <row r="58" spans="1:60" ht="12.5">
       <c r="A58" s="47" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B58" s="53">
         <v>3</v>
@@ -16863,7 +16863,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H58" s="53" t="s">
         <v>1182</v>
@@ -17027,7 +17027,7 @@
     </row>
     <row r="59" spans="1:60" ht="12.5">
       <c r="A59" s="47" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B59" s="53">
         <v>4</v>
@@ -17045,7 +17045,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H59" s="53" t="s">
         <v>1182</v>
@@ -17209,7 +17209,7 @@
     </row>
     <row r="60" spans="1:60" ht="12.5">
       <c r="A60" s="47" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B60" s="53">
         <v>5</v>
@@ -17227,7 +17227,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H60" s="53" t="s">
         <v>1182</v>
@@ -17391,7 +17391,7 @@
     </row>
     <row r="61" spans="1:60" ht="12.5">
       <c r="A61" s="47" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B61" s="53">
         <v>6</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H61" s="53" t="s">
         <v>1182</v>
@@ -17573,7 +17573,7 @@
     </row>
     <row r="62" spans="1:60" ht="12.5">
       <c r="A62" s="47" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B62" s="53">
         <v>7</v>
@@ -17591,7 +17591,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H62" s="53" t="s">
         <v>1182</v>
@@ -17755,7 +17755,7 @@
     </row>
     <row r="63" spans="1:60" ht="12.5">
       <c r="A63" s="47" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B63" s="53">
         <v>8</v>
@@ -17773,7 +17773,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H63" s="53" t="s">
         <v>1182</v>
@@ -17937,7 +17937,7 @@
     </row>
     <row r="64" spans="1:60" ht="12.5">
       <c r="A64" s="47" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B64" s="53">
         <v>9</v>
@@ -17955,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H64" s="53" t="s">
         <v>1182</v>
@@ -18119,7 +18119,7 @@
     </row>
     <row r="65" spans="1:60" ht="12.5">
       <c r="A65" s="47" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B65" s="53">
         <v>1</v>
@@ -18137,7 +18137,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H65" s="53" t="s">
         <v>1182</v>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="66" spans="1:60" ht="12.5">
       <c r="A66" s="47" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="B66" s="53">
         <v>2</v>
@@ -18319,7 +18319,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H66" s="53" t="s">
         <v>1182</v>
@@ -18483,7 +18483,7 @@
     </row>
     <row r="67" spans="1:60" ht="12.5">
       <c r="A67" s="47" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B67" s="53">
         <v>3</v>
@@ -18501,7 +18501,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H67" s="53" t="s">
         <v>1182</v>
@@ -18665,7 +18665,7 @@
     </row>
     <row r="68" spans="1:60" ht="12.5">
       <c r="A68" s="47" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B68" s="53">
         <v>4</v>
@@ -18683,7 +18683,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H68" s="53" t="s">
         <v>1182</v>
@@ -18847,7 +18847,7 @@
     </row>
     <row r="69" spans="1:60" ht="12.5">
       <c r="A69" s="47" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B69" s="53">
         <v>5</v>
@@ -18865,7 +18865,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H69" s="53" t="s">
         <v>1182</v>
@@ -19029,7 +19029,7 @@
     </row>
     <row r="70" spans="1:60" ht="12.5">
       <c r="A70" s="47" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B70" s="53">
         <v>6</v>
@@ -19047,7 +19047,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H70" s="53" t="s">
         <v>1182</v>
@@ -19211,7 +19211,7 @@
     </row>
     <row r="71" spans="1:60" ht="12.5">
       <c r="A71" s="47" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B71" s="53">
         <v>7</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H71" s="53" t="s">
         <v>1182</v>
@@ -19393,7 +19393,7 @@
     </row>
     <row r="72" spans="1:60" ht="12.5">
       <c r="A72" s="47" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B72" s="53">
         <v>8</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H72" s="53" t="s">
         <v>1182</v>
@@ -19575,7 +19575,7 @@
     </row>
     <row r="73" spans="1:60" ht="12.5">
       <c r="A73" s="47" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B73" s="53">
         <v>9</v>
@@ -19593,7 +19593,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H73" s="53" t="s">
         <v>1182</v>
@@ -19757,7 +19757,7 @@
     </row>
     <row r="74" spans="1:60" ht="12.5">
       <c r="A74" s="47" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B74" s="53">
         <v>1</v>
@@ -19775,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H74" s="53" t="s">
         <v>1182</v>
@@ -19939,7 +19939,7 @@
     </row>
     <row r="75" spans="1:60" ht="12.5">
       <c r="A75" s="47" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B75" s="53">
         <v>2</v>
@@ -19957,7 +19957,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H75" s="53" t="s">
         <v>1182</v>
@@ -20121,7 +20121,7 @@
     </row>
     <row r="76" spans="1:60" ht="12.5">
       <c r="A76" s="47" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B76" s="53">
         <v>3</v>
@@ -20139,7 +20139,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H76" s="53" t="s">
         <v>1182</v>
@@ -20303,7 +20303,7 @@
     </row>
     <row r="77" spans="1:60" ht="12.5">
       <c r="A77" s="47" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B77" s="53">
         <v>4</v>
@@ -20321,7 +20321,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H77" s="53" t="s">
         <v>1182</v>
@@ -20485,7 +20485,7 @@
     </row>
     <row r="78" spans="1:60" ht="12.5">
       <c r="A78" s="47" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B78" s="53">
         <v>5</v>
@@ -20503,7 +20503,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="53" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H78" s="53" t="s">
         <v>1182</v>
@@ -41624,16 +41624,16 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1">
       <c r="A54" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B54" s="52">
+        <v>1</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
         <v>1815</v>
-      </c>
-      <c r="B54" s="52">
-        <v>1</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1">
@@ -43680,7 +43680,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="105" customWidth="1"/>
+    <col min="2" max="2" width="111.36328125" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="15.81640625" customWidth="1"/>
   </cols>
@@ -43737,7 +43737,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1809</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -52938,7 +52938,7 @@
         <v>1351</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="G1" s="43" t="s">
         <v>10</v>
@@ -55919,7 +55919,7 @@
         <v>1351</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="E1" s="43" t="s">
         <v>10</v>
@@ -62778,7 +62778,7 @@
     </row>
     <row r="40" spans="1:58">
       <c r="A40" s="44" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -62874,7 +62874,7 @@
         <v>10</v>
       </c>
       <c r="AG40" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="AH40" s="44" t="s">
         <v>1363</v>
@@ -62954,7 +62954,7 @@
     </row>
     <row r="41" spans="1:58">
       <c r="A41" s="44" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B41">
         <v>-1</v>
@@ -63130,7 +63130,7 @@
     </row>
     <row r="42" spans="1:58">
       <c r="A42" s="44" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -63226,7 +63226,7 @@
         <v>10</v>
       </c>
       <c r="AG42" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="AH42" s="44" t="s">
         <v>1479</v>
@@ -63306,7 +63306,7 @@
     </row>
     <row r="43" spans="1:58">
       <c r="A43" s="44" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B43">
         <v>1</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF5D889-BE28-41DC-A4A9-5DB447E1CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01621FFB-433F-411B-B04A-894544C59943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9139" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9217" uniqueCount="1874">
   <si>
     <t>NAME</t>
   </si>
@@ -5803,6 +5803,9 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5#cure_potion,3#wood,100</t>
+  </si>
+  <si>
+    <t>CODEX_REWARD</t>
   </si>
 </sst>
 </file>
@@ -6420,7 +6423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BH998"/>
+  <dimension ref="A1:BI998"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.453125" customWidth="1"/>
@@ -6466,10 +6469,11 @@
     <col min="57" max="57" width="10.6328125" customWidth="1"/>
     <col min="58" max="58" width="18" customWidth="1"/>
     <col min="59" max="59" width="10.453125" customWidth="1"/>
-    <col min="60" max="60" width="17.90625" customWidth="1"/>
+    <col min="60" max="60" width="15.08984375" customWidth="1"/>
+    <col min="61" max="61" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="15.75" customHeight="1">
+    <row r="1" spans="1:61" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6650,8 +6654,11 @@
       <c r="BH1" s="6" t="s">
         <v>1785</v>
       </c>
-    </row>
-    <row r="2" spans="1:60" ht="12.5">
+      <c r="BI1" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61" ht="12.5">
       <c r="A2" s="47" t="s">
         <v>954</v>
       </c>
@@ -6832,8 +6839,11 @@
       <c r="BH2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:60" ht="12.5">
+      <c r="BI2" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61" ht="12.5">
       <c r="A3" s="47" t="s">
         <v>1406</v>
       </c>
@@ -7014,8 +7024,11 @@
       <c r="BH3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:60" ht="12.5">
+      <c r="BI3" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61" ht="12.5">
       <c r="A4" s="47" t="s">
         <v>1766</v>
       </c>
@@ -7196,8 +7209,11 @@
       <c r="BH4" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="5" spans="1:60" ht="12.5">
+      <c r="BI4" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61" ht="12.5">
       <c r="A5" s="47" t="s">
         <v>1767</v>
       </c>
@@ -7378,8 +7394,11 @@
       <c r="BH5" t="s">
         <v>1794</v>
       </c>
-    </row>
-    <row r="6" spans="1:60" ht="12.5">
+      <c r="BI5" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61" ht="12.5">
       <c r="A6" s="47" t="s">
         <v>1466</v>
       </c>
@@ -7560,8 +7579,11 @@
       <c r="BH6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:60" ht="12.5">
+      <c r="BI6" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61" ht="12.5">
       <c r="A7" s="47" t="s">
         <v>1467</v>
       </c>
@@ -7742,8 +7764,11 @@
       <c r="BH7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:60" ht="12.5">
+      <c r="BI7" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61" ht="12.5">
       <c r="A8" s="47" t="s">
         <v>43</v>
       </c>
@@ -7924,8 +7949,11 @@
       <c r="BH8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:60" ht="12.5">
+      <c r="BI8" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61" ht="12.5">
       <c r="A9" s="47" t="s">
         <v>1509</v>
       </c>
@@ -8106,8 +8134,11 @@
       <c r="BH9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:60" ht="12.5">
+      <c r="BI9" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61" ht="12.5">
       <c r="A10" s="47" t="s">
         <v>1510</v>
       </c>
@@ -8288,8 +8319,11 @@
       <c r="BH10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:60" ht="12.5">
+      <c r="BI10" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61" ht="12.5">
       <c r="A11" s="47" t="s">
         <v>1521</v>
       </c>
@@ -8470,8 +8504,11 @@
       <c r="BH11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:60" ht="12.5">
+      <c r="BI11" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61" ht="12.5">
       <c r="A12" s="47" t="s">
         <v>1522</v>
       </c>
@@ -8652,8 +8689,11 @@
       <c r="BH12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:60" ht="12.5">
+      <c r="BI12" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61" ht="12.5">
       <c r="A13" s="47" t="s">
         <v>1550</v>
       </c>
@@ -8834,8 +8874,11 @@
       <c r="BH13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:60" ht="12.5">
+      <c r="BI13" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61" ht="12.5">
       <c r="A14" s="47" t="s">
         <v>1578</v>
       </c>
@@ -9016,8 +9059,11 @@
       <c r="BH14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:60" ht="12.5">
+      <c r="BI14" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61" ht="12.5">
       <c r="A15" s="47" t="s">
         <v>1601</v>
       </c>
@@ -9198,8 +9244,11 @@
       <c r="BH15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:60" ht="12.5">
+      <c r="BI15" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61" ht="12.5">
       <c r="A16" s="47" t="s">
         <v>34</v>
       </c>
@@ -9380,8 +9429,11 @@
       <c r="BH16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:60" ht="12.5">
+      <c r="BI16" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" ht="12.5">
       <c r="A17" s="47" t="s">
         <v>1370</v>
       </c>
@@ -9562,8 +9614,11 @@
       <c r="BH17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:60" ht="12.5">
+      <c r="BI17" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" ht="12.5">
       <c r="A18" s="47" t="s">
         <v>1165</v>
       </c>
@@ -9744,8 +9799,11 @@
       <c r="BH18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:60" ht="12.5">
+      <c r="BI18" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61" ht="12.5">
       <c r="A19" s="47" t="s">
         <v>1619</v>
       </c>
@@ -9926,8 +9984,11 @@
       <c r="BH19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:60" ht="12.5">
+      <c r="BI19" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" ht="12.5">
       <c r="A20" s="47" t="s">
         <v>1632</v>
       </c>
@@ -10108,8 +10169,11 @@
       <c r="BH20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:60" ht="12.5">
+      <c r="BI20" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" ht="12.5">
       <c r="A21" s="47" t="s">
         <v>1258</v>
       </c>
@@ -10290,8 +10354,11 @@
       <c r="BH21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:60" ht="12.5">
+      <c r="BI21" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" ht="12.5">
       <c r="A22" s="47" t="s">
         <v>1716</v>
       </c>
@@ -10472,8 +10539,11 @@
       <c r="BH22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:60" ht="12.5">
+      <c r="BI22" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" ht="12.5">
       <c r="A23" s="47" t="s">
         <v>1736</v>
       </c>
@@ -10654,8 +10724,11 @@
       <c r="BH23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:60" ht="12.5">
+      <c r="BI23" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61" ht="12.5">
       <c r="A24" s="47" t="s">
         <v>1737</v>
       </c>
@@ -10836,8 +10909,11 @@
       <c r="BH24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:60" ht="12.5">
+      <c r="BI24" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="25" spans="1:61" ht="12.5">
       <c r="A25" s="47" t="s">
         <v>1739</v>
       </c>
@@ -11018,8 +11094,11 @@
       <c r="BH25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:60" ht="12.5">
+      <c r="BI25" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61" ht="12.5">
       <c r="A26" s="47" t="s">
         <v>1738</v>
       </c>
@@ -11200,8 +11279,11 @@
       <c r="BH26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:60" ht="12.5">
+      <c r="BI26" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="27" spans="1:61" ht="12.5">
       <c r="A27" s="47" t="s">
         <v>52</v>
       </c>
@@ -11382,8 +11464,11 @@
       <c r="BH27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:60" ht="12.5">
+      <c r="BI27" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" ht="12.5">
       <c r="A28" s="47" t="s">
         <v>1728</v>
       </c>
@@ -11564,8 +11649,11 @@
       <c r="BH28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:60" ht="14">
+      <c r="BI28" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61" ht="14">
       <c r="A29" s="54" t="s">
         <v>1816</v>
       </c>
@@ -11746,8 +11834,11 @@
       <c r="BH29" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="30" spans="1:60" ht="12.5">
+      <c r="BI29" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61" ht="12.5">
       <c r="A30" s="47" t="s">
         <v>1817</v>
       </c>
@@ -11928,8 +12019,11 @@
       <c r="BH30" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="31" spans="1:60" ht="12.5">
+      <c r="BI30" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61" ht="12.5">
       <c r="A31" s="47" t="s">
         <v>1818</v>
       </c>
@@ -12110,8 +12204,11 @@
       <c r="BH31" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="32" spans="1:60" ht="12.5">
+      <c r="BI31" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61" ht="12.5">
       <c r="A32" s="47" t="s">
         <v>1819</v>
       </c>
@@ -12292,8 +12389,11 @@
       <c r="BH32" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="33" spans="1:60" ht="12.5">
+      <c r="BI32" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:61" ht="12.5">
       <c r="A33" s="47" t="s">
         <v>1820</v>
       </c>
@@ -12474,8 +12574,11 @@
       <c r="BH33" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="34" spans="1:60" ht="12.5">
+      <c r="BI33" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:61" ht="12.5">
       <c r="A34" s="47" t="s">
         <v>1821</v>
       </c>
@@ -12656,8 +12759,11 @@
       <c r="BH34" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="35" spans="1:60" ht="12.5">
+      <c r="BI34" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:61" ht="12.5">
       <c r="A35" s="47" t="s">
         <v>1822</v>
       </c>
@@ -12838,8 +12944,11 @@
       <c r="BH35" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="36" spans="1:60" ht="12.5">
+      <c r="BI35" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:61" ht="12.5">
       <c r="A36" s="47" t="s">
         <v>1823</v>
       </c>
@@ -13020,8 +13129,11 @@
       <c r="BH36" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="37" spans="1:60" ht="12.5">
+      <c r="BI36" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="37" spans="1:61" ht="12.5">
       <c r="A37" s="47" t="s">
         <v>1824</v>
       </c>
@@ -13202,8 +13314,11 @@
       <c r="BH37" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="38" spans="1:60" ht="12.5">
+      <c r="BI37" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:61" ht="12.5">
       <c r="A38" s="47" t="s">
         <v>1825</v>
       </c>
@@ -13384,8 +13499,11 @@
       <c r="BH38" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="39" spans="1:60" ht="12.5">
+      <c r="BI38" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="39" spans="1:61" ht="12.5">
       <c r="A39" s="47" t="s">
         <v>1826</v>
       </c>
@@ -13566,8 +13684,11 @@
       <c r="BH39" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="40" spans="1:60" ht="12.5">
+      <c r="BI39" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:61" ht="12.5">
       <c r="A40" s="47" t="s">
         <v>1827</v>
       </c>
@@ -13748,8 +13869,11 @@
       <c r="BH40" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="41" spans="1:60" ht="12.5">
+      <c r="BI40" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="41" spans="1:61" ht="12.5">
       <c r="A41" s="47" t="s">
         <v>1828</v>
       </c>
@@ -13930,8 +14054,11 @@
       <c r="BH41" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="42" spans="1:60" ht="12.5">
+      <c r="BI41" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="42" spans="1:61" ht="12.5">
       <c r="A42" s="47" t="s">
         <v>1829</v>
       </c>
@@ -14112,8 +14239,11 @@
       <c r="BH42" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="43" spans="1:60" ht="12.5">
+      <c r="BI42" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="43" spans="1:61" ht="12.5">
       <c r="A43" s="47" t="s">
         <v>1830</v>
       </c>
@@ -14294,8 +14424,11 @@
       <c r="BH43" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="44" spans="1:60" ht="12.5">
+      <c r="BI43" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:61" ht="12.5">
       <c r="A44" s="47" t="s">
         <v>1831</v>
       </c>
@@ -14476,8 +14609,11 @@
       <c r="BH44" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="45" spans="1:60" ht="12.5">
+      <c r="BI44" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:61" ht="12.5">
       <c r="A45" s="47" t="s">
         <v>1832</v>
       </c>
@@ -14658,8 +14794,11 @@
       <c r="BH45" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="46" spans="1:60" ht="12.5">
+      <c r="BI45" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="46" spans="1:61" ht="12.5">
       <c r="A46" s="47" t="s">
         <v>1833</v>
       </c>
@@ -14840,8 +14979,11 @@
       <c r="BH46" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="47" spans="1:60" ht="12.5">
+      <c r="BI46" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="47" spans="1:61" ht="12.5">
       <c r="A47" s="47" t="s">
         <v>1834</v>
       </c>
@@ -15022,8 +15164,11 @@
       <c r="BH47" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="48" spans="1:60" ht="12.5">
+      <c r="BI47" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:61" ht="12.5">
       <c r="A48" s="47" t="s">
         <v>1835</v>
       </c>
@@ -15204,8 +15349,11 @@
       <c r="BH48" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="49" spans="1:60" ht="12.5">
+      <c r="BI48" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="49" spans="1:61" ht="12.5">
       <c r="A49" s="47" t="s">
         <v>1836</v>
       </c>
@@ -15386,8 +15534,11 @@
       <c r="BH49" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="50" spans="1:60" ht="12.5">
+      <c r="BI49" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="50" spans="1:61" ht="12.5">
       <c r="A50" s="47" t="s">
         <v>1837</v>
       </c>
@@ -15568,8 +15719,11 @@
       <c r="BH50" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="51" spans="1:60" ht="12.5">
+      <c r="BI50" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="51" spans="1:61" ht="12.5">
       <c r="A51" s="47" t="s">
         <v>1838</v>
       </c>
@@ -15750,8 +15904,11 @@
       <c r="BH51" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="52" spans="1:60" ht="12.5">
+      <c r="BI51" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="52" spans="1:61" ht="12.5">
       <c r="A52" s="47" t="s">
         <v>1839</v>
       </c>
@@ -15932,8 +16089,11 @@
       <c r="BH52" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="53" spans="1:60" ht="12.5">
+      <c r="BI52" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="53" spans="1:61" ht="12.5">
       <c r="A53" s="47" t="s">
         <v>1840</v>
       </c>
@@ -16114,8 +16274,11 @@
       <c r="BH53" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="54" spans="1:60" ht="12.5">
+      <c r="BI53" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="54" spans="1:61" ht="12.5">
       <c r="A54" s="47" t="s">
         <v>1841</v>
       </c>
@@ -16296,8 +16459,11 @@
       <c r="BH54" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="55" spans="1:60" ht="12.5">
+      <c r="BI54" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="55" spans="1:61" ht="12.5">
       <c r="A55" s="47" t="s">
         <v>1842</v>
       </c>
@@ -16478,8 +16644,11 @@
       <c r="BH55" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="56" spans="1:60" ht="12.5">
+      <c r="BI55" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="56" spans="1:61" ht="12.5">
       <c r="A56" s="47" t="s">
         <v>1843</v>
       </c>
@@ -16660,8 +16829,11 @@
       <c r="BH56" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="57" spans="1:60" ht="12.5">
+      <c r="BI56" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="57" spans="1:61" ht="12.5">
       <c r="A57" s="47" t="s">
         <v>1844</v>
       </c>
@@ -16842,8 +17014,11 @@
       <c r="BH57" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="58" spans="1:60" ht="12.5">
+      <c r="BI57" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="58" spans="1:61" ht="12.5">
       <c r="A58" s="47" t="s">
         <v>1845</v>
       </c>
@@ -17024,8 +17199,11 @@
       <c r="BH58" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="59" spans="1:60" ht="12.5">
+      <c r="BI58" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="59" spans="1:61" ht="12.5">
       <c r="A59" s="47" t="s">
         <v>1846</v>
       </c>
@@ -17206,8 +17384,11 @@
       <c r="BH59" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="60" spans="1:60" ht="12.5">
+      <c r="BI59" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="60" spans="1:61" ht="12.5">
       <c r="A60" s="47" t="s">
         <v>1847</v>
       </c>
@@ -17388,8 +17569,11 @@
       <c r="BH60" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="61" spans="1:60" ht="12.5">
+      <c r="BI60" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="61" spans="1:61" ht="12.5">
       <c r="A61" s="47" t="s">
         <v>1848</v>
       </c>
@@ -17570,8 +17754,11 @@
       <c r="BH61" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="62" spans="1:60" ht="12.5">
+      <c r="BI61" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="62" spans="1:61" ht="12.5">
       <c r="A62" s="47" t="s">
         <v>1849</v>
       </c>
@@ -17752,8 +17939,11 @@
       <c r="BH62" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="63" spans="1:60" ht="12.5">
+      <c r="BI62" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="63" spans="1:61" ht="12.5">
       <c r="A63" s="47" t="s">
         <v>1850</v>
       </c>
@@ -17934,8 +18124,11 @@
       <c r="BH63" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="64" spans="1:60" ht="12.5">
+      <c r="BI63" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="64" spans="1:61" ht="12.5">
       <c r="A64" s="47" t="s">
         <v>1851</v>
       </c>
@@ -18116,8 +18309,11 @@
       <c r="BH64" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="65" spans="1:60" ht="12.5">
+      <c r="BI64" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="65" spans="1:61" ht="12.5">
       <c r="A65" s="47" t="s">
         <v>1852</v>
       </c>
@@ -18298,8 +18494,11 @@
       <c r="BH65" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="66" spans="1:60" ht="12.5">
+      <c r="BI65" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="66" spans="1:61" ht="12.5">
       <c r="A66" s="47" t="s">
         <v>1853</v>
       </c>
@@ -18480,8 +18679,11 @@
       <c r="BH66" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="67" spans="1:60" ht="12.5">
+      <c r="BI66" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:61" ht="12.5">
       <c r="A67" s="47" t="s">
         <v>1854</v>
       </c>
@@ -18662,8 +18864,11 @@
       <c r="BH67" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="68" spans="1:60" ht="12.5">
+      <c r="BI67" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:61" ht="12.5">
       <c r="A68" s="47" t="s">
         <v>1855</v>
       </c>
@@ -18844,8 +19049,11 @@
       <c r="BH68" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="69" spans="1:60" ht="12.5">
+      <c r="BI68" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="69" spans="1:61" ht="12.5">
       <c r="A69" s="47" t="s">
         <v>1856</v>
       </c>
@@ -19026,8 +19234,11 @@
       <c r="BH69" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="70" spans="1:60" ht="12.5">
+      <c r="BI69" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="70" spans="1:61" ht="12.5">
       <c r="A70" s="47" t="s">
         <v>1857</v>
       </c>
@@ -19208,8 +19419,11 @@
       <c r="BH70" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="71" spans="1:60" ht="12.5">
+      <c r="BI70" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="71" spans="1:61" ht="12.5">
       <c r="A71" s="47" t="s">
         <v>1858</v>
       </c>
@@ -19390,8 +19604,11 @@
       <c r="BH71" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="72" spans="1:60" ht="12.5">
+      <c r="BI71" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:61" ht="12.5">
       <c r="A72" s="47" t="s">
         <v>1859</v>
       </c>
@@ -19572,8 +19789,11 @@
       <c r="BH72" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="73" spans="1:60" ht="12.5">
+      <c r="BI72" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:61" ht="12.5">
       <c r="A73" s="47" t="s">
         <v>1860</v>
       </c>
@@ -19754,8 +19974,11 @@
       <c r="BH73" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="74" spans="1:60" ht="12.5">
+      <c r="BI73" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="74" spans="1:61" ht="12.5">
       <c r="A74" s="47" t="s">
         <v>1861</v>
       </c>
@@ -19936,8 +20159,11 @@
       <c r="BH74" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="75" spans="1:60" ht="12.5">
+      <c r="BI74" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="75" spans="1:61" ht="12.5">
       <c r="A75" s="47" t="s">
         <v>1862</v>
       </c>
@@ -20118,8 +20344,11 @@
       <c r="BH75" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="76" spans="1:60" ht="12.5">
+      <c r="BI75" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="76" spans="1:61" ht="12.5">
       <c r="A76" s="47" t="s">
         <v>1863</v>
       </c>
@@ -20300,8 +20529,11 @@
       <c r="BH76" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="77" spans="1:60" ht="12.5">
+      <c r="BI76" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="77" spans="1:61" ht="12.5">
       <c r="A77" s="47" t="s">
         <v>1864</v>
       </c>
@@ -20482,8 +20714,11 @@
       <c r="BH77" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="78" spans="1:60" ht="12.5">
+      <c r="BI77" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:61" ht="12.5">
       <c r="A78" s="47" t="s">
         <v>1865</v>
       </c>
@@ -20664,15 +20899,18 @@
       <c r="BH78" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="79" spans="1:60" ht="12.5">
+      <c r="BI78" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="79" spans="1:61" ht="12.5">
       <c r="B79" s="53"/>
       <c r="I79" s="38"/>
       <c r="J79" s="38"/>
       <c r="Z79" s="41"/>
       <c r="AG79" s="41"/>
     </row>
-    <row r="80" spans="1:60" ht="12.5">
+    <row r="80" spans="1:61" ht="12.5">
       <c r="B80" s="53"/>
       <c r="I80" s="38"/>
       <c r="J80" s="38"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01621FFB-433F-411B-B04A-894544C59943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F8D96C-A6C0-4539-B28B-24B8EA71FF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9217" uniqueCount="1874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9217" uniqueCount="1875">
   <si>
     <t>NAME</t>
   </si>
@@ -5806,6 +5806,9 @@
   </si>
   <si>
     <t>CODEX_REWARD</t>
+  </si>
+  <si>
+    <t>fire,-50</t>
   </si>
 </sst>
 </file>
@@ -14416,13 +14419,13 @@
         <v>2</v>
       </c>
       <c r="BF43" t="s">
-        <v>1789</v>
+        <v>1874</v>
       </c>
       <c r="BG43" t="s">
-        <v>1791</v>
+        <v>36</v>
       </c>
       <c r="BH43" t="s">
-        <v>1793</v>
+        <v>36</v>
       </c>
       <c r="BI43" t="s">
         <v>1369</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F8D96C-A6C0-4539-B28B-24B8EA71FF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16F41CF-369F-4D51-8E89-0AE64C9E40F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9217" uniqueCount="1875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9250" uniqueCount="1881">
   <si>
     <t>NAME</t>
   </si>
@@ -5802,13 +5802,31 @@
     <t>buff_def1</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1#heal_potion,5#mana_potion,5#cure_potion,3#wood,100</t>
-  </si>
-  <si>
     <t>CODEX_REWARD</t>
   </si>
   <si>
     <t>fire,-50</t>
+  </si>
+  <si>
+    <t>ADORN_CNT</t>
+  </si>
+  <si>
+    <t>adorn_atk</t>
+  </si>
+  <si>
+    <t>adorn</t>
+  </si>
+  <si>
+    <t>adorn_def</t>
+  </si>
+  <si>
+    <t>adorn_hp</t>
+  </si>
+  <si>
+    <t>adorn_magic</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1</t>
   </si>
 </sst>
 </file>
@@ -6658,7 +6676,7 @@
         <v>1785</v>
       </c>
       <c r="BI1" s="6" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="12.5">
@@ -14419,7 +14437,7 @@
         <v>2</v>
       </c>
       <c r="BF43" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="BG43" t="s">
         <v>36</v>
@@ -43978,7 +43996,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1872</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -53148,7 +53166,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -53157,12 +53175,13 @@
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
     <col min="6" max="6" width="11.36328125" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" customWidth="1"/>
+    <col min="11" max="11" width="12.90625" customWidth="1"/>
     <col min="25" max="25" width="10.453125" customWidth="1"/>
     <col min="27" max="27" width="11.54296875" customWidth="1"/>
+    <col min="29" max="29" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="13">
+    <row r="1" spans="1:29" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -53247,8 +53266,11 @@
       <c r="AB1" s="43" t="s">
         <v>1795</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" s="43" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
@@ -53333,8 +53355,11 @@
       <c r="AB2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="AC2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
@@ -53419,8 +53444,11 @@
       <c r="AB3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:28">
+      <c r="AC3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
@@ -53505,8 +53533,11 @@
       <c r="AB4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:28">
+      <c r="AC4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="44" t="s">
         <v>1776</v>
       </c>
@@ -53591,8 +53622,11 @@
       <c r="AB5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:28">
+      <c r="AC5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
@@ -53677,8 +53711,11 @@
       <c r="AB6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:28">
+      <c r="AC6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
@@ -53763,8 +53800,11 @@
       <c r="AB7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:28">
+      <c r="AC7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
@@ -53849,8 +53889,11 @@
       <c r="AB8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:28">
+      <c r="AC8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
@@ -53935,8 +53978,11 @@
       <c r="AB9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:28">
+      <c r="AC9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
@@ -54021,8 +54067,11 @@
       <c r="AB10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:28">
+      <c r="AC10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
@@ -54107,8 +54156,11 @@
       <c r="AB11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:28">
+      <c r="AC11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
@@ -54193,8 +54245,11 @@
       <c r="AB12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:28">
+      <c r="AC12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
@@ -54279,8 +54334,11 @@
       <c r="AB13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:28">
+      <c r="AC13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
@@ -54365,8 +54423,11 @@
       <c r="AB14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:28">
+      <c r="AC14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
@@ -54451,8 +54512,11 @@
       <c r="AB15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:28">
+      <c r="AC15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
@@ -54537,8 +54601,11 @@
       <c r="AB16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:28">
+      <c r="AC16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
@@ -54623,8 +54690,11 @@
       <c r="AB17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:28">
+      <c r="AC17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
@@ -54709,8 +54779,11 @@
       <c r="AB18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:28">
+      <c r="AC18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
@@ -54795,8 +54868,11 @@
       <c r="AB19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:28">
+      <c r="AC19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
@@ -54881,8 +54957,11 @@
       <c r="AB20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:28">
+      <c r="AC20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
@@ -54967,8 +55046,11 @@
       <c r="AB21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:28">
+      <c r="AC21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
@@ -55053,8 +55135,11 @@
       <c r="AB22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:28">
+      <c r="AC22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
@@ -55139,8 +55224,11 @@
       <c r="AB23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:28">
+      <c r="AC23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
@@ -55225,8 +55313,11 @@
       <c r="AB24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:28">
+      <c r="AC24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
@@ -55311,8 +55402,11 @@
       <c r="AB25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:28">
+      <c r="AC25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
@@ -55397,8 +55491,11 @@
       <c r="AB26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:28">
+      <c r="AC26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
@@ -55483,8 +55580,11 @@
       <c r="AB27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:28">
+      <c r="AC27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
@@ -55569,8 +55669,11 @@
       <c r="AB28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:28">
+      <c r="AC28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="44" t="s">
         <v>1747</v>
       </c>
@@ -55655,8 +55758,11 @@
       <c r="AB29" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:28">
+      <c r="AC29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="44" t="s">
         <v>1777</v>
       </c>
@@ -55741,8 +55847,11 @@
       <c r="AB30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:28">
+      <c r="AC30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="44" t="s">
         <v>1778</v>
       </c>
@@ -55827,8 +55936,11 @@
       <c r="AB31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:28">
+      <c r="AC31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="44" t="s">
         <v>238</v>
       </c>
@@ -55913,8 +56025,11 @@
       <c r="AB32" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:28">
+      <c r="AC32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="44" t="s">
         <v>1801</v>
       </c>
@@ -55999,8 +56114,11 @@
       <c r="AB33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:28">
+      <c r="AC33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="44" t="s">
         <v>1808</v>
       </c>
@@ -56084,6 +56202,365 @@
       </c>
       <c r="AB34" t="s">
         <v>36</v>
+      </c>
+      <c r="AC34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
+      <c r="A35" s="44" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="44">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>10</v>
+      </c>
+      <c r="U35" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z35">
+        <v>11</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
+      <c r="A36" s="44" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="44">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>50</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>10</v>
+      </c>
+      <c r="U36" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>1</v>
+      </c>
+      <c r="X36" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z36">
+        <v>11</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
+      <c r="A37" s="44" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="44">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>10</v>
+      </c>
+      <c r="U37" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>1</v>
+      </c>
+      <c r="X37" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z37">
+        <v>11</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
+      <c r="A38" s="44" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="44">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>20</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>10</v>
+      </c>
+      <c r="U38" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>1</v>
+      </c>
+      <c r="X38" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z38">
+        <v>11</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC38">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3AA556-D04F-434E-8F42-89D7502F5FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D679158F-F824-40F4-9842-A7A736D206B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9251" uniqueCount="1882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9345" uniqueCount="1886">
   <si>
     <t>NAME</t>
   </si>
@@ -5830,6 +5830,18 @@
   </si>
   <si>
     <t>MAX_STACK</t>
+  </si>
+  <si>
+    <t>town_spells1</t>
+  </si>
+  <si>
+    <t>ice_arrow</t>
+  </si>
+  <si>
+    <t>earth_arrow</t>
+  </si>
+  <si>
+    <t>dark_arrow</t>
   </si>
 </sst>
 </file>
@@ -42318,7 +42330,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
@@ -43383,6 +43395,75 @@
         <v>1366</v>
       </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>100</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>36</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>100</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>100</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1885</v>
+      </c>
+      <c r="G70">
         <v>0</v>
       </c>
     </row>
@@ -56809,7 +56890,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BJ43"/>
+  <dimension ref="A1:BJ46"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -56862,7 +56943,9 @@
     <col min="53" max="53" width="12.7265625" customWidth="1"/>
     <col min="54" max="55" width="7.08984375" customWidth="1"/>
     <col min="57" max="57" width="11.08984375" customWidth="1"/>
-    <col min="58" max="62" width="10" customWidth="1"/>
+    <col min="58" max="58" width="10" customWidth="1"/>
+    <col min="59" max="59" width="11.54296875" customWidth="1"/>
+    <col min="60" max="62" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="13">
@@ -57040,7 +57123,9 @@
       <c r="BF1" s="43" t="s">
         <v>1795</v>
       </c>
-      <c r="BG1" s="43"/>
+      <c r="BG1" s="43" t="s">
+        <v>1101</v>
+      </c>
       <c r="BH1" s="43"/>
       <c r="BI1" s="43"/>
       <c r="BJ1" s="43"/>
@@ -57220,6 +57305,9 @@
       <c r="BF2" t="s">
         <v>36</v>
       </c>
+      <c r="BG2" t="s">
+        <v>1657</v>
+      </c>
     </row>
     <row r="3" spans="1:62">
       <c r="A3" s="44" t="s">
@@ -57396,6 +57484,9 @@
       <c r="BF3" t="s">
         <v>36</v>
       </c>
+      <c r="BG3" t="s">
+        <v>1658</v>
+      </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="44" t="s">
@@ -57572,6 +57663,9 @@
       <c r="BF4" t="s">
         <v>36</v>
       </c>
+      <c r="BG4" t="s">
+        <v>1659</v>
+      </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="44" t="s">
@@ -57748,6 +57842,9 @@
       <c r="BF5" t="s">
         <v>36</v>
       </c>
+      <c r="BG5" t="s">
+        <v>1660</v>
+      </c>
     </row>
     <row r="6" spans="1:62">
       <c r="A6" s="44" t="s">
@@ -57924,6 +58021,9 @@
       <c r="BF6" t="s">
         <v>36</v>
       </c>
+      <c r="BG6" t="s">
+        <v>1660</v>
+      </c>
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="44" t="s">
@@ -58100,6 +58200,9 @@
       <c r="BF7" t="s">
         <v>36</v>
       </c>
+      <c r="BG7" t="s">
+        <v>1661</v>
+      </c>
     </row>
     <row r="8" spans="1:62">
       <c r="A8" s="44" t="s">
@@ -58276,6 +58379,9 @@
       <c r="BF8" t="s">
         <v>36</v>
       </c>
+      <c r="BG8" t="s">
+        <v>1662</v>
+      </c>
     </row>
     <row r="9" spans="1:62">
       <c r="A9" s="44" t="s">
@@ -58452,6 +58558,9 @@
       <c r="BF9" t="s">
         <v>36</v>
       </c>
+      <c r="BG9" t="s">
+        <v>1663</v>
+      </c>
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="44" t="s">
@@ -58628,6 +58737,9 @@
       <c r="BF10" t="s">
         <v>36</v>
       </c>
+      <c r="BG10" t="s">
+        <v>1664</v>
+      </c>
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="44" t="s">
@@ -58804,6 +58916,9 @@
       <c r="BF11" t="s">
         <v>36</v>
       </c>
+      <c r="BG11" t="s">
+        <v>1665</v>
+      </c>
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="44" t="s">
@@ -58980,6 +59095,9 @@
       <c r="BF12" t="s">
         <v>36</v>
       </c>
+      <c r="BG12" t="s">
+        <v>1666</v>
+      </c>
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="44" t="s">
@@ -59156,6 +59274,9 @@
       <c r="BF13" t="s">
         <v>36</v>
       </c>
+      <c r="BG13" t="s">
+        <v>1667</v>
+      </c>
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="44" t="s">
@@ -59332,6 +59453,9 @@
       <c r="BF14" t="s">
         <v>36</v>
       </c>
+      <c r="BG14" t="s">
+        <v>1668</v>
+      </c>
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="44" t="s">
@@ -59508,6 +59632,9 @@
       <c r="BF15" t="s">
         <v>36</v>
       </c>
+      <c r="BG15" t="s">
+        <v>1669</v>
+      </c>
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="44" t="s">
@@ -59684,8 +59811,11 @@
       <c r="BF16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:58">
+      <c r="BG16" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="17" spans="1:59">
       <c r="A17" s="44" t="s">
         <v>1494</v>
       </c>
@@ -59860,8 +59990,11 @@
       <c r="BF17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:58">
+      <c r="BG17" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:59">
       <c r="A18" s="44" t="s">
         <v>1501</v>
       </c>
@@ -60036,8 +60169,11 @@
       <c r="BF18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:58">
+      <c r="BG18" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:59">
       <c r="A19" s="44" t="s">
         <v>1502</v>
       </c>
@@ -60212,8 +60348,11 @@
       <c r="BF19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:58">
+      <c r="BG19" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="20" spans="1:59">
       <c r="A20" s="44" t="s">
         <v>1431</v>
       </c>
@@ -60388,8 +60527,11 @@
       <c r="BF20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:58">
+      <c r="BG20" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="21" spans="1:59">
       <c r="A21" s="44" t="s">
         <v>1551</v>
       </c>
@@ -60564,8 +60706,11 @@
       <c r="BF21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:58">
+      <c r="BG21" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:59">
       <c r="A22" s="44" t="s">
         <v>1587</v>
       </c>
@@ -60740,8 +60885,11 @@
       <c r="BF22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:58">
+      <c r="BG22" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="23" spans="1:59">
       <c r="A23" s="44" t="s">
         <v>935</v>
       </c>
@@ -60916,8 +61064,11 @@
       <c r="BF23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:58">
+      <c r="BG23" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="24" spans="1:59">
       <c r="A24" s="44" t="s">
         <v>1593</v>
       </c>
@@ -61092,8 +61243,11 @@
       <c r="BF24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:58">
+      <c r="BG24" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="25" spans="1:59">
       <c r="A25" s="44" t="s">
         <v>1602</v>
       </c>
@@ -61268,8 +61422,11 @@
       <c r="BF25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:58">
+      <c r="BG25" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59">
       <c r="A26" s="44" t="s">
         <v>1611</v>
       </c>
@@ -61444,8 +61601,11 @@
       <c r="BF26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:58">
+      <c r="BG26" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="27" spans="1:59">
       <c r="A27" s="44" t="s">
         <v>1615</v>
       </c>
@@ -61620,8 +61780,11 @@
       <c r="BF27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:58">
+      <c r="BG27" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="28" spans="1:59">
       <c r="A28" s="44" t="s">
         <v>1616</v>
       </c>
@@ -61796,8 +61959,11 @@
       <c r="BF28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:58">
+      <c r="BG28" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="29" spans="1:59">
       <c r="A29" s="44" t="s">
         <v>1620</v>
       </c>
@@ -61972,8 +62138,11 @@
       <c r="BF29" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:58">
+      <c r="BG29" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="30" spans="1:59">
       <c r="A30" s="44" t="s">
         <v>1624</v>
       </c>
@@ -62148,8 +62317,11 @@
       <c r="BF30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:58">
+      <c r="BG30" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="31" spans="1:59">
       <c r="A31" s="44" t="s">
         <v>1647</v>
       </c>
@@ -62324,8 +62496,11 @@
       <c r="BF31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:58">
+      <c r="BG31" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="32" spans="1:59">
       <c r="A32" s="44" t="s">
         <v>1578</v>
       </c>
@@ -62500,8 +62675,11 @@
       <c r="BF32" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:58">
+      <c r="BG32" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:59">
       <c r="A33" s="44" t="s">
         <v>1686</v>
       </c>
@@ -62676,8 +62854,11 @@
       <c r="BF33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:58">
+      <c r="BG33" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="34" spans="1:59">
       <c r="A34" s="44" t="s">
         <v>1728</v>
       </c>
@@ -62852,8 +63033,11 @@
       <c r="BF34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:58">
+      <c r="BG34" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="35" spans="1:59">
       <c r="A35" s="44" t="s">
         <v>1786</v>
       </c>
@@ -63028,8 +63212,11 @@
       <c r="BF35" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:58">
+      <c r="BG35" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:59">
       <c r="A36" s="44" t="s">
         <v>1797</v>
       </c>
@@ -63204,8 +63391,11 @@
       <c r="BF36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:58">
+      <c r="BG36" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:59">
       <c r="A37" s="44" t="s">
         <v>1796</v>
       </c>
@@ -63380,8 +63570,11 @@
       <c r="BF37" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:58">
+      <c r="BG37" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:59">
       <c r="A38" s="44" t="s">
         <v>1805</v>
       </c>
@@ -63556,8 +63749,11 @@
       <c r="BF38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:58">
+      <c r="BG38" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:59">
       <c r="A39" s="44" t="s">
         <v>1807</v>
       </c>
@@ -63732,8 +63928,11 @@
       <c r="BF39" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:58">
+      <c r="BG39" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:59">
       <c r="A40" s="44" t="s">
         <v>1868</v>
       </c>
@@ -63908,8 +64107,11 @@
       <c r="BF40" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:58">
+      <c r="BG40" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="41" spans="1:59">
       <c r="A41" s="44" t="s">
         <v>1869</v>
       </c>
@@ -64084,8 +64286,11 @@
       <c r="BF41" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:58">
+      <c r="BG41" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="42" spans="1:59">
       <c r="A42" s="44" t="s">
         <v>1870</v>
       </c>
@@ -64260,8 +64465,11 @@
       <c r="BF42" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:58">
+      <c r="BG42" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:59">
       <c r="A43" s="44" t="s">
         <v>1871</v>
       </c>
@@ -64435,6 +64643,546 @@
       </c>
       <c r="BF43" t="s">
         <v>36</v>
+      </c>
+      <c r="BG43" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="44" spans="1:59">
+      <c r="A44" s="44" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>4</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>1</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>-1</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>10</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH44" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI44" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ44" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK44" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM44" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN44" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO44" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>0</v>
+      </c>
+      <c r="AQ44">
+        <v>1</v>
+      </c>
+      <c r="AR44">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV44">
+        <v>0</v>
+      </c>
+      <c r="AW44">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ44" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
+        <v>0</v>
+      </c>
+      <c r="BD44">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>37</v>
+      </c>
+      <c r="BF44" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG44" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="45" spans="1:59">
+      <c r="A45" s="44" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>4</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>1</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>-1</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>10</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH45" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI45" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ45" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK45" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM45" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN45" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO45" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>0</v>
+      </c>
+      <c r="AQ45">
+        <v>1</v>
+      </c>
+      <c r="AR45">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ45" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA45">
+        <v>0</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BF45" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG45" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="46" spans="1:59">
+      <c r="A46" s="44" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>4</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>1</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>-1</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>10</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH46" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI46" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ46" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK46" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM46" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN46" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO46" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP46">
+        <v>0</v>
+      </c>
+      <c r="AQ46">
+        <v>1</v>
+      </c>
+      <c r="AR46">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV46">
+        <v>0</v>
+      </c>
+      <c r="AW46">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ46" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA46">
+        <v>0</v>
+      </c>
+      <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
+        <v>0</v>
+      </c>
+      <c r="BD46">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BF46" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG46" t="s">
+        <v>1663</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D679158F-F824-40F4-9842-A7A736D206B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48E5153-D240-4773-839A-CB78A31C8880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9345" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9393" uniqueCount="1893">
   <si>
     <t>NAME</t>
   </si>
@@ -5842,6 +5842,27 @@
   </si>
   <si>
     <t>dark_arrow</t>
+  </si>
+  <si>
+    <t>avidity1,life_siphon1</t>
+  </si>
+  <si>
+    <t>--------------------------------------PASSIVES---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>avidity1</t>
+  </si>
+  <si>
+    <t>life_siphon1</t>
+  </si>
+  <si>
+    <t>basic_harm</t>
+  </si>
+  <si>
+    <t>--------------------------------------HERO CLASSES---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>EXTRA_TURN</t>
   </si>
 </sst>
 </file>
@@ -6111,7 +6132,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6197,6 +6218,12 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="21" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -6485,6 +6512,7 @@
     <col min="28" max="28" width="19" customWidth="1"/>
     <col min="29" max="29" width="36.08984375" customWidth="1"/>
     <col min="30" max="30" width="22.453125" customWidth="1"/>
+    <col min="31" max="31" width="18.26953125" customWidth="1"/>
     <col min="37" max="37" width="15" customWidth="1"/>
     <col min="40" max="40" width="8.453125" customWidth="1"/>
     <col min="41" max="41" width="8.08984375" customWidth="1"/>
@@ -6790,7 +6818,7 @@
         <v>42</v>
       </c>
       <c r="AE2" s="40" t="s">
-        <v>36</v>
+        <v>1886</v>
       </c>
       <c r="AF2" s="40">
         <v>40</v>
@@ -21174,11 +21202,23 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="79" spans="1:62" ht="12.5">
-      <c r="B79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
+    <row r="79" spans="1:62" ht="14">
+      <c r="A79" s="55" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B79" s="56"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="58"/>
+      <c r="K79" s="58"/>
+      <c r="L79" s="57"/>
+      <c r="M79" s="57"/>
+      <c r="N79" s="57"/>
       <c r="AA79" s="41"/>
       <c r="AH79" s="41"/>
     </row>
@@ -56890,7 +56930,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BJ46"/>
+  <dimension ref="A1:BJ83"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -56945,7 +56985,8 @@
     <col min="57" max="57" width="11.08984375" customWidth="1"/>
     <col min="58" max="58" width="10" customWidth="1"/>
     <col min="59" max="59" width="11.54296875" customWidth="1"/>
-    <col min="60" max="62" width="10" customWidth="1"/>
+    <col min="60" max="60" width="15.36328125" customWidth="1"/>
+    <col min="61" max="62" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="13">
@@ -57126,7 +57167,9 @@
       <c r="BG1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="BH1" s="43"/>
+      <c r="BH1" s="43" t="s">
+        <v>1892</v>
+      </c>
       <c r="BI1" s="43"/>
       <c r="BJ1" s="43"/>
     </row>
@@ -57308,6 +57351,9 @@
       <c r="BG2" t="s">
         <v>1657</v>
       </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:62">
       <c r="A3" s="44" t="s">
@@ -57487,6 +57533,9 @@
       <c r="BG3" t="s">
         <v>1658</v>
       </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="44" t="s">
@@ -57666,6 +57715,9 @@
       <c r="BG4" t="s">
         <v>1659</v>
       </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="44" t="s">
@@ -57845,16 +57897,19 @@
       <c r="BG5" t="s">
         <v>1660</v>
       </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:62">
       <c r="A6" s="44" t="s">
-        <v>1469</v>
+        <v>1890</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -58024,16 +58079,19 @@
       <c r="BG6" t="s">
         <v>1660</v>
       </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="44" t="s">
-        <v>1483</v>
+        <v>1469</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -58129,7 +58187,7 @@
         <v>1479</v>
       </c>
       <c r="AI7" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AJ7" s="44" t="s">
         <v>1470</v>
@@ -58156,10 +58214,10 @@
         <v>1</v>
       </c>
       <c r="AR7">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="s">
-        <v>1481</v>
+        <v>36</v>
       </c>
       <c r="AT7">
         <v>0</v>
@@ -58195,24 +58253,27 @@
         <v>0</v>
       </c>
       <c r="BE7" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF7" t="s">
         <v>36</v>
       </c>
       <c r="BG7" t="s">
-        <v>1661</v>
+        <v>1660</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:62">
       <c r="A8" s="44" t="s">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -58299,13 +58360,13 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="s">
         <v>36</v>
       </c>
       <c r="AH8" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI8" s="44" t="s">
         <v>1470</v>
@@ -58338,7 +58399,7 @@
         <v>60</v>
       </c>
       <c r="AS8" t="s">
-        <v>36</v>
+        <v>1481</v>
       </c>
       <c r="AT8">
         <v>0</v>
@@ -58347,7 +58408,7 @@
         <v>36</v>
       </c>
       <c r="AV8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8">
         <v>0</v>
@@ -58374,24 +58435,27 @@
         <v>0</v>
       </c>
       <c r="BE8" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF8" t="s">
         <v>36</v>
       </c>
       <c r="BG8" t="s">
-        <v>1662</v>
+        <v>1661</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:62">
       <c r="A9" s="44" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -58454,7 +58518,7 @@
         <v>3</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -58469,7 +58533,7 @@
         <v>1</v>
       </c>
       <c r="AC9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>-1</v>
@@ -58553,30 +58617,33 @@
         <v>0</v>
       </c>
       <c r="BE9" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF9" t="s">
         <v>36</v>
       </c>
       <c r="BG9" t="s">
-        <v>1663</v>
+        <v>1662</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="44" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -58633,7 +58700,7 @@
         <v>3</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -58648,7 +58715,7 @@
         <v>1</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
         <v>-1</v>
@@ -58657,7 +58724,7 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="s">
         <v>36</v>
@@ -58690,10 +58757,10 @@
         <v>0</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS10" t="s">
         <v>36</v>
@@ -58705,7 +58772,7 @@
         <v>36</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10">
         <v>0</v>
@@ -58732,18 +58799,21 @@
         <v>0</v>
       </c>
       <c r="BE10" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF10" t="s">
         <v>36</v>
       </c>
       <c r="BG10" t="s">
-        <v>1664</v>
+        <v>1663</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="44" t="s">
-        <v>1524</v>
+        <v>1447</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -58755,7 +58825,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -58764,10 +58834,10 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -58911,18 +58981,21 @@
         <v>0</v>
       </c>
       <c r="BE11" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF11" t="s">
         <v>36</v>
       </c>
       <c r="BG11" t="s">
-        <v>1665</v>
+        <v>1664</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="44" t="s">
-        <v>1448</v>
+        <v>1524</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -58943,10 +59016,10 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -59090,18 +59163,21 @@
         <v>0</v>
       </c>
       <c r="BE12" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF12" t="s">
         <v>36</v>
       </c>
       <c r="BG12" t="s">
-        <v>1666</v>
+        <v>1665</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="44" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -59122,13 +59198,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -59269,24 +59345,27 @@
         <v>0</v>
       </c>
       <c r="BE13" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF13" t="s">
         <v>36</v>
       </c>
       <c r="BG13" t="s">
-        <v>1667</v>
+        <v>1666</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="44" t="s">
-        <v>1485</v>
+        <v>1449</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -59307,7 +59386,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -59346,10 +59425,10 @@
         <v>0</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y14">
         <v>0</v>
@@ -59373,10 +59452,10 @@
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="s">
-        <v>1494</v>
+        <v>36</v>
       </c>
       <c r="AH14" s="44" t="s">
         <v>1363</v>
@@ -59406,7 +59485,7 @@
         <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR14">
         <v>1</v>
@@ -59436,7 +59515,7 @@
         <v>36</v>
       </c>
       <c r="BA14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB14">
         <v>0</v>
@@ -59448,30 +59527,33 @@
         <v>0</v>
       </c>
       <c r="BE14" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF14" t="s">
         <v>36</v>
       </c>
       <c r="BG14" t="s">
-        <v>1668</v>
+        <v>1667</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="44" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -59525,10 +59607,10 @@
         <v>0</v>
       </c>
       <c r="W15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>0</v>
@@ -59555,7 +59637,7 @@
         <v>10</v>
       </c>
       <c r="AG15" t="s">
-        <v>36</v>
+        <v>1494</v>
       </c>
       <c r="AH15" s="44" t="s">
         <v>1363</v>
@@ -59576,7 +59658,7 @@
         <v>1</v>
       </c>
       <c r="AN15" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AO15" s="44">
         <v>0</v>
@@ -59585,7 +59667,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>1</v>
@@ -59615,7 +59697,7 @@
         <v>36</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB15">
         <v>0</v>
@@ -59627,18 +59709,21 @@
         <v>0</v>
       </c>
       <c r="BE15" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF15" t="s">
         <v>36</v>
       </c>
       <c r="BG15" t="s">
-        <v>1669</v>
+        <v>1668</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="44" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -59650,7 +59735,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -59659,10 +59744,10 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -59806,21 +59891,24 @@
         <v>0</v>
       </c>
       <c r="BE16" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF16" t="s">
         <v>36</v>
       </c>
       <c r="BG16" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="17" spans="1:59">
+        <v>1669</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60">
       <c r="A17" s="44" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -59829,19 +59917,19 @@
         <v>0</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>20</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -59904,13 +59992,13 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG17" t="s">
         <v>36</v>
@@ -59943,7 +60031,7 @@
         <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17">
         <v>1</v>
@@ -59961,7 +60049,7 @@
         <v>0</v>
       </c>
       <c r="AW17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="s">
         <v>36</v>
@@ -59985,21 +60073,24 @@
         <v>0</v>
       </c>
       <c r="BE17" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF17" t="s">
         <v>36</v>
       </c>
       <c r="BG17" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="18" spans="1:59">
+        <v>1670</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60">
       <c r="A18" s="44" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -60008,7 +60099,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -60140,7 +60231,7 @@
         <v>0</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="s">
         <v>36</v>
@@ -60164,18 +60255,21 @@
         <v>0</v>
       </c>
       <c r="BE18" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF18" t="s">
         <v>36</v>
       </c>
       <c r="BG18" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="19" spans="1:59">
+        <v>1671</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60">
       <c r="A19" s="44" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -60187,7 +60281,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -60244,7 +60338,7 @@
         <v>3</v>
       </c>
       <c r="X19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -60262,16 +60356,16 @@
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>1501</v>
+        <v>36</v>
       </c>
       <c r="AH19" s="44" t="s">
         <v>1363</v>
@@ -60289,10 +60383,10 @@
         <v>1474</v>
       </c>
       <c r="AM19" s="44">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AN19" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AO19" s="44">
         <v>0</v>
@@ -60304,7 +60398,7 @@
         <v>1</v>
       </c>
       <c r="AR19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="s">
         <v>36</v>
@@ -60343,30 +60437,33 @@
         <v>0</v>
       </c>
       <c r="BE19" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF19" t="s">
         <v>36</v>
       </c>
       <c r="BG19" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="20" spans="1:59">
+        <v>1672</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60">
       <c r="A20" s="44" t="s">
-        <v>1431</v>
+        <v>1502</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>10</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -60423,19 +60520,19 @@
         <v>3</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -60447,10 +60544,10 @@
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="s">
-        <v>36</v>
+        <v>1501</v>
       </c>
       <c r="AH20" s="44" t="s">
         <v>1363</v>
@@ -60468,7 +60565,7 @@
         <v>1474</v>
       </c>
       <c r="AM20" s="44">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AN20" s="44" t="s">
         <v>36</v>
@@ -60483,7 +60580,7 @@
         <v>1</v>
       </c>
       <c r="AR20">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="s">
         <v>36</v>
@@ -60495,7 +60592,7 @@
         <v>36</v>
       </c>
       <c r="AV20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW20">
         <v>0</v>
@@ -60522,24 +60619,27 @@
         <v>0</v>
       </c>
       <c r="BE20" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF20" t="s">
         <v>36</v>
       </c>
       <c r="BG20" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="21" spans="1:59">
+        <v>1673</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60">
       <c r="A21" s="44" t="s">
-        <v>1551</v>
+        <v>1431</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -60605,16 +60705,16 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -60626,13 +60726,13 @@
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="s">
         <v>36</v>
       </c>
       <c r="AH21" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI21" s="44" t="s">
         <v>1470</v>
@@ -60653,7 +60753,7 @@
         <v>36</v>
       </c>
       <c r="AO21" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21">
         <v>0</v>
@@ -60665,13 +60765,13 @@
         <v>60</v>
       </c>
       <c r="AS21" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AT21">
         <v>0</v>
       </c>
       <c r="AU21" t="s">
-        <v>1554</v>
+        <v>36</v>
       </c>
       <c r="AV21">
         <v>1</v>
@@ -60701,18 +60801,21 @@
         <v>0</v>
       </c>
       <c r="BE21" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF21" t="s">
         <v>36</v>
       </c>
       <c r="BG21" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="22" spans="1:59">
+        <v>1674</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60">
       <c r="A22" s="44" t="s">
-        <v>1587</v>
+        <v>1551</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -60775,10 +60878,10 @@
         <v>0</v>
       </c>
       <c r="V22">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -60832,7 +60935,7 @@
         <v>36</v>
       </c>
       <c r="AO22" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP22">
         <v>0</v>
@@ -60841,19 +60944,19 @@
         <v>1</v>
       </c>
       <c r="AR22">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS22" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AT22">
         <v>0</v>
       </c>
       <c r="AU22" t="s">
-        <v>36</v>
+        <v>1554</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW22">
         <v>0</v>
@@ -60880,7 +60983,7 @@
         <v>0</v>
       </c>
       <c r="BE22" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF22" t="s">
         <v>36</v>
@@ -60888,10 +60991,13 @@
       <c r="BG22" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="23" spans="1:59">
+      <c r="BH22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60">
       <c r="A23" s="44" t="s">
-        <v>935</v>
+        <v>1587</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -60954,10 +61060,10 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -61011,7 +61117,7 @@
         <v>36</v>
       </c>
       <c r="AO23" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23">
         <v>0</v>
@@ -61059,7 +61165,7 @@
         <v>0</v>
       </c>
       <c r="BE23" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF23" t="s">
         <v>36</v>
@@ -61067,10 +61173,13 @@
       <c r="BG23" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="24" spans="1:59">
+      <c r="BH23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60">
       <c r="A24" s="44" t="s">
-        <v>1593</v>
+        <v>935</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -61136,7 +61245,7 @@
         <v>0</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -61238,7 +61347,7 @@
         <v>0</v>
       </c>
       <c r="BE24" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF24" t="s">
         <v>36</v>
@@ -61246,16 +61355,19 @@
       <c r="BG24" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="25" spans="1:59">
+      <c r="BH24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60">
       <c r="A25" s="44" t="s">
-        <v>1602</v>
+        <v>1593</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -61315,7 +61427,7 @@
         <v>0</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -61348,7 +61460,7 @@
         <v>36</v>
       </c>
       <c r="AH25" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI25" s="44" t="s">
         <v>1470</v>
@@ -61369,7 +61481,7 @@
         <v>36</v>
       </c>
       <c r="AO25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25">
         <v>0</v>
@@ -61417,7 +61529,7 @@
         <v>0</v>
       </c>
       <c r="BE25" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF25" t="s">
         <v>36</v>
@@ -61425,16 +61537,19 @@
       <c r="BG25" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="26" spans="1:59">
+      <c r="BH25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60">
       <c r="A26" s="44" t="s">
-        <v>1611</v>
+        <v>1602</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -61494,7 +61609,7 @@
         <v>0</v>
       </c>
       <c r="W26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -61527,7 +61642,7 @@
         <v>36</v>
       </c>
       <c r="AH26" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI26" s="44" t="s">
         <v>1470</v>
@@ -61548,7 +61663,7 @@
         <v>36</v>
       </c>
       <c r="AO26" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26">
         <v>0</v>
@@ -61557,19 +61672,19 @@
         <v>1</v>
       </c>
       <c r="AR26">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AS26" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AT26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="s">
         <v>36</v>
       </c>
       <c r="AV26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW26">
         <v>0</v>
@@ -61596,24 +61711,27 @@
         <v>0</v>
       </c>
       <c r="BE26" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF26" t="s">
         <v>36</v>
       </c>
       <c r="BG26" t="s">
-        <v>1559</v>
-      </c>
-    </row>
-    <row r="27" spans="1:59">
+        <v>1658</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60">
       <c r="A27" s="44" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -61673,7 +61791,7 @@
         <v>0</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -61706,7 +61824,7 @@
         <v>36</v>
       </c>
       <c r="AH27" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI27" s="44" t="s">
         <v>1470</v>
@@ -61727,7 +61845,7 @@
         <v>36</v>
       </c>
       <c r="AO27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27">
         <v>0</v>
@@ -61736,19 +61854,19 @@
         <v>1</v>
       </c>
       <c r="AR27">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS27" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="s">
         <v>36</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW27">
         <v>0</v>
@@ -61775,18 +61893,21 @@
         <v>0</v>
       </c>
       <c r="BE27" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF27" t="s">
         <v>36</v>
       </c>
       <c r="BG27" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="28" spans="1:59">
+        <v>1559</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60">
       <c r="A28" s="44" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -61852,7 +61973,7 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -61954,7 +62075,7 @@
         <v>0</v>
       </c>
       <c r="BE28" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF28" t="s">
         <v>36</v>
@@ -61962,10 +62083,13 @@
       <c r="BG28" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="29" spans="1:59">
+      <c r="BH28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60">
       <c r="A29" s="44" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -62034,7 +62158,7 @@
         <v>3</v>
       </c>
       <c r="X29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y29">
         <v>0</v>
@@ -62064,7 +62188,7 @@
         <v>36</v>
       </c>
       <c r="AH29" s="44" t="s">
-        <v>1621</v>
+        <v>1363</v>
       </c>
       <c r="AI29" s="44" t="s">
         <v>1470</v>
@@ -62133,7 +62257,7 @@
         <v>0</v>
       </c>
       <c r="BE29" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF29" t="s">
         <v>36</v>
@@ -62141,10 +62265,13 @@
       <c r="BG29" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="30" spans="1:59">
+      <c r="BH29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60">
       <c r="A30" s="44" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -62213,7 +62340,7 @@
         <v>3</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y30">
         <v>0</v>
@@ -62243,7 +62370,7 @@
         <v>36</v>
       </c>
       <c r="AH30" s="44" t="s">
-        <v>1363</v>
+        <v>1621</v>
       </c>
       <c r="AI30" s="44" t="s">
         <v>1470</v>
@@ -62297,39 +62424,42 @@
         <v>36</v>
       </c>
       <c r="AZ30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG30" t="s">
+        <v>1658</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60">
+      <c r="A31" s="44" t="s">
         <v>1624</v>
       </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>0</v>
-      </c>
-      <c r="BC30">
-        <v>0</v>
-      </c>
-      <c r="BD30">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>1760</v>
-      </c>
-      <c r="BF30" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG30" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="31" spans="1:59">
-      <c r="A31" s="44" t="s">
-        <v>1647</v>
-      </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -62389,7 +62519,7 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X31">
         <v>0</v>
@@ -62476,7 +62606,7 @@
         <v>36</v>
       </c>
       <c r="AZ31" t="s">
-        <v>36</v>
+        <v>1624</v>
       </c>
       <c r="BA31">
         <v>0</v>
@@ -62491,7 +62621,7 @@
         <v>0</v>
       </c>
       <c r="BE31" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF31" t="s">
         <v>36</v>
@@ -62499,10 +62629,13 @@
       <c r="BG31" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="32" spans="1:59">
+      <c r="BH31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60">
       <c r="A32" s="44" t="s">
-        <v>1578</v>
+        <v>1647</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -62568,7 +62701,7 @@
         <v>0</v>
       </c>
       <c r="W32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -62628,7 +62761,7 @@
         <v>0</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1</v>
@@ -62670,18 +62803,21 @@
         <v>0</v>
       </c>
       <c r="BE32" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF32" t="s">
         <v>36</v>
       </c>
       <c r="BG32" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="33" spans="1:59">
+        <v>896</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60">
       <c r="A33" s="44" t="s">
-        <v>1686</v>
+        <v>1578</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -62747,7 +62883,7 @@
         <v>0</v>
       </c>
       <c r="W33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -62780,7 +62916,7 @@
         <v>36</v>
       </c>
       <c r="AH33" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI33" s="44" t="s">
         <v>1470</v>
@@ -62801,13 +62937,13 @@
         <v>36</v>
       </c>
       <c r="AO33" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP33">
         <v>0</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR33">
         <v>1</v>
@@ -62849,7 +62985,7 @@
         <v>0</v>
       </c>
       <c r="BE33" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF33" t="s">
         <v>36</v>
@@ -62857,10 +62993,13 @@
       <c r="BG33" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="34" spans="1:59">
+      <c r="BH33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60">
       <c r="A34" s="44" t="s">
-        <v>1728</v>
+        <v>1686</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -62926,7 +63065,7 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -62959,7 +63098,7 @@
         <v>36</v>
       </c>
       <c r="AH34" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI34" s="44" t="s">
         <v>1470</v>
@@ -62980,13 +63119,13 @@
         <v>36</v>
       </c>
       <c r="AO34" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP34">
         <v>0</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1</v>
@@ -63028,18 +63167,21 @@
         <v>0</v>
       </c>
       <c r="BE34" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF34" t="s">
         <v>36</v>
       </c>
       <c r="BG34" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="35" spans="1:59">
+        <v>1671</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60">
       <c r="A35" s="44" t="s">
-        <v>1786</v>
+        <v>1728</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -63057,7 +63199,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -63105,7 +63247,7 @@
         <v>0</v>
       </c>
       <c r="W35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -63165,7 +63307,7 @@
         <v>0</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR35">
         <v>1</v>
@@ -63207,18 +63349,21 @@
         <v>0</v>
       </c>
       <c r="BE35" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="BF35" t="s">
         <v>36</v>
       </c>
       <c r="BG35" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="36" spans="1:59">
+        <v>896</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60">
       <c r="A36" s="44" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -63236,7 +63381,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -63284,10 +63429,10 @@
         <v>0</v>
       </c>
       <c r="W36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -63314,10 +63459,10 @@
         <v>10</v>
       </c>
       <c r="AG36" t="s">
-        <v>1796</v>
+        <v>36</v>
       </c>
       <c r="AH36" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI36" s="44" t="s">
         <v>1470</v>
@@ -63386,7 +63531,7 @@
         <v>0</v>
       </c>
       <c r="BE36" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BF36" t="s">
         <v>36</v>
@@ -63394,13 +63539,16 @@
       <c r="BG36" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="37" spans="1:59">
+      <c r="BH36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60">
       <c r="A37" s="44" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -63409,7 +63557,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -63466,7 +63614,7 @@
         <v>3</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -63484,16 +63632,16 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG37" t="s">
-        <v>36</v>
+        <v>1796</v>
       </c>
       <c r="AH37" s="44" t="s">
         <v>1479</v>
@@ -63523,7 +63671,7 @@
         <v>0</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1</v>
@@ -63541,7 +63689,7 @@
         <v>0</v>
       </c>
       <c r="AW37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="s">
         <v>36</v>
@@ -63565,7 +63713,7 @@
         <v>0</v>
       </c>
       <c r="BE37" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF37" t="s">
         <v>36</v>
@@ -63573,13 +63721,16 @@
       <c r="BG37" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="38" spans="1:59">
+      <c r="BH37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60">
       <c r="A38" s="44" t="s">
-        <v>1805</v>
+        <v>1796</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -63588,7 +63739,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -63633,7 +63784,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -63663,13 +63814,13 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="s">
         <v>36</v>
@@ -63678,7 +63829,7 @@
         <v>1479</v>
       </c>
       <c r="AI38" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AJ38" s="44" t="s">
         <v>1470</v>
@@ -63702,7 +63853,7 @@
         <v>0</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR38">
         <v>1</v>
@@ -63720,7 +63871,7 @@
         <v>0</v>
       </c>
       <c r="AW38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX38" t="s">
         <v>36</v>
@@ -63744,7 +63895,7 @@
         <v>0</v>
       </c>
       <c r="BE38" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BF38" t="s">
         <v>36</v>
@@ -63752,10 +63903,13 @@
       <c r="BG38" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="39" spans="1:59">
+      <c r="BH38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:60">
       <c r="A39" s="44" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -63812,7 +63966,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -63929,12 +64083,15 @@
         <v>36</v>
       </c>
       <c r="BG39" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="40" spans="1:59">
+        <v>1663</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:60">
       <c r="A40" s="44" t="s">
-        <v>1868</v>
+        <v>1807</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -63946,7 +64103,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -64003,7 +64160,7 @@
         <v>3</v>
       </c>
       <c r="X40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40">
         <v>0</v>
@@ -64030,13 +64187,13 @@
         <v>10</v>
       </c>
       <c r="AG40" t="s">
-        <v>1869</v>
+        <v>36</v>
       </c>
       <c r="AH40" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI40" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AJ40" s="44" t="s">
         <v>1470</v>
@@ -64102,7 +64259,7 @@
         <v>0</v>
       </c>
       <c r="BE40" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF40" t="s">
         <v>36</v>
@@ -64110,22 +64267,25 @@
       <c r="BG40" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="41" spans="1:59">
+      <c r="BH40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:60">
       <c r="A41" s="44" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -64182,7 +64342,7 @@
         <v>3</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -64200,16 +64360,16 @@
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG41" t="s">
-        <v>36</v>
+        <v>1869</v>
       </c>
       <c r="AH41" s="44" t="s">
         <v>1363</v>
@@ -64239,7 +64399,7 @@
         <v>0</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -64257,7 +64417,7 @@
         <v>0</v>
       </c>
       <c r="AW41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="s">
         <v>36</v>
@@ -64281,27 +64441,30 @@
         <v>0</v>
       </c>
       <c r="BE41" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF41" t="s">
         <v>36</v>
       </c>
       <c r="BG41" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="42" spans="1:59">
+        <v>1671</v>
+      </c>
+      <c r="BH41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:60">
       <c r="A42" s="44" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -64361,7 +64524,7 @@
         <v>3</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -64379,19 +64542,19 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="s">
-        <v>1871</v>
+        <v>36</v>
       </c>
       <c r="AH42" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI42" s="44" t="s">
         <v>1470</v>
@@ -64418,7 +64581,7 @@
         <v>0</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR42">
         <v>1</v>
@@ -64436,7 +64599,7 @@
         <v>0</v>
       </c>
       <c r="AW42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX42" t="s">
         <v>36</v>
@@ -64460,21 +64623,24 @@
         <v>0</v>
       </c>
       <c r="BE42" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="BF42" t="s">
         <v>36</v>
       </c>
       <c r="BG42" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="43" spans="1:59">
+        <v>896</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:60">
       <c r="A43" s="44" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -64498,7 +64664,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -64540,7 +64706,7 @@
         <v>3</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -64558,16 +64724,16 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG43" t="s">
-        <v>36</v>
+        <v>1871</v>
       </c>
       <c r="AH43" s="44" t="s">
         <v>1479</v>
@@ -64597,7 +64763,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1</v>
@@ -64615,7 +64781,7 @@
         <v>0</v>
       </c>
       <c r="AW43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="s">
         <v>36</v>
@@ -64639,7 +64805,7 @@
         <v>0</v>
       </c>
       <c r="BE43" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF43" t="s">
         <v>36</v>
@@ -64647,13 +64813,16 @@
       <c r="BG43" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="44" spans="1:59">
+      <c r="BH43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:60">
       <c r="A44" s="44" t="s">
-        <v>1883</v>
+        <v>1871</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -64668,7 +64837,7 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -64677,7 +64846,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -64716,7 +64885,7 @@
         <v>0</v>
       </c>
       <c r="W44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -64737,19 +64906,19 @@
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="s">
         <v>36</v>
       </c>
       <c r="AH44" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI44" s="44" t="s">
         <v>1470</v>
@@ -64776,7 +64945,7 @@
         <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR44">
         <v>1</v>
@@ -64794,7 +64963,7 @@
         <v>0</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" t="s">
         <v>36</v>
@@ -64818,7 +64987,7 @@
         <v>0</v>
       </c>
       <c r="BE44" t="s">
-        <v>37</v>
+        <v>1761</v>
       </c>
       <c r="BF44" t="s">
         <v>36</v>
@@ -64826,10 +64995,13 @@
       <c r="BG44" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="45" spans="1:59">
+      <c r="BH44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:60">
       <c r="A45" s="44" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -64997,7 +65169,7 @@
         <v>0</v>
       </c>
       <c r="BE45" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF45" t="s">
         <v>36</v>
@@ -65005,10 +65177,13 @@
       <c r="BG45" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="46" spans="1:59">
+      <c r="BH45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:60">
       <c r="A46" s="44" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -65176,7 +65351,7 @@
         <v>0</v>
       </c>
       <c r="BE46" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="BF46" t="s">
         <v>36</v>
@@ -65184,6 +65359,1308 @@
       <c r="BG46" t="s">
         <v>1663</v>
       </c>
+      <c r="BH46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:60">
+      <c r="A47" s="44" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>4</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>1</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>-1</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>10</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH47" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI47" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ47" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK47" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM47" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN47" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO47" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>0</v>
+      </c>
+      <c r="AQ47">
+        <v>1</v>
+      </c>
+      <c r="AR47">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV47">
+        <v>0</v>
+      </c>
+      <c r="AW47">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ47" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA47">
+        <v>0</v>
+      </c>
+      <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
+        <v>0</v>
+      </c>
+      <c r="BD47">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BF47" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG47" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BH47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:60" ht="14">
+      <c r="A48" s="55" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B48" s="55"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="BH48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:60">
+      <c r="A49" s="44" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>200</v>
+      </c>
+      <c r="I49">
+        <v>200</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>3</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>1</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>-1</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>10</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH49" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI49" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ49" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK49" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM49" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN49" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO49" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>0</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV49">
+        <v>0</v>
+      </c>
+      <c r="AW49">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA49">
+        <v>0</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>0</v>
+      </c>
+      <c r="BD49">
+        <v>1</v>
+      </c>
+      <c r="BE49" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BF49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG49" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BH49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:60">
+      <c r="A50" s="44" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>10</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>3</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>1</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>-1</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>10</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH50" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI50" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ50" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK50" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM50" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN50" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO50" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP50">
+        <v>0</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>1</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV50">
+        <v>0</v>
+      </c>
+      <c r="AW50">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ50" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA50">
+        <v>0</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>0</v>
+      </c>
+      <c r="BD50">
+        <v>1</v>
+      </c>
+      <c r="BE50" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BF50" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG50" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BH50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:60">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" spans="1:60">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" spans="1:60">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="1:60">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" spans="1:60">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="1:60">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="1:60">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" spans="1:60">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" spans="1:60">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="1:60">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="1:60">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+    </row>
+    <row r="62" spans="1:60">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+    </row>
+    <row r="63" spans="1:60">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+    </row>
+    <row r="64" spans="1:60">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+    </row>
+    <row r="81" spans="1:20">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="1:20">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48E5153-D240-4773-839A-CB78A31C8880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C646B02-F24B-4EDB-B1BE-0FC2997C0B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9393" uniqueCount="1893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9503" uniqueCount="1898">
   <si>
     <t>NAME</t>
   </si>
@@ -5863,6 +5863,21 @@
   </si>
   <si>
     <t>EXTRA_TURN</t>
+  </si>
+  <si>
+    <t>hero_warrior</t>
+  </si>
+  <si>
+    <t>hero_thief</t>
+  </si>
+  <si>
+    <t>hero_mage</t>
+  </si>
+  <si>
+    <t>hero_sorcerer</t>
+  </si>
+  <si>
+    <t>hero_archmage</t>
   </si>
 </sst>
 </file>
@@ -21223,105 +21238,1012 @@
       <c r="AH79" s="41"/>
     </row>
     <row r="80" spans="1:62" ht="12.5">
-      <c r="B80" s="53"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
-      <c r="AA80" s="41"/>
-      <c r="AH80" s="41"/>
-    </row>
-    <row r="81" spans="2:34" ht="12.5">
-      <c r="B81" s="53"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
-      <c r="AA81" s="41"/>
-      <c r="AH81" s="41"/>
-    </row>
-    <row r="82" spans="2:34" ht="12.5">
-      <c r="B82" s="53"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
-      <c r="AA82" s="41"/>
-      <c r="AH82" s="41"/>
-    </row>
-    <row r="83" spans="2:34" ht="12.5">
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
-      <c r="AA83" s="41"/>
-      <c r="AH83" s="41"/>
-    </row>
-    <row r="84" spans="2:34" ht="12.5">
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
-      <c r="AA84" s="41"/>
-      <c r="AH84" s="41"/>
-    </row>
-    <row r="85" spans="2:34" ht="12.5">
+      <c r="A80" s="47" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B80" s="53">
+        <v>1</v>
+      </c>
+      <c r="C80" s="53">
+        <v>0</v>
+      </c>
+      <c r="D80" s="53">
+        <v>0</v>
+      </c>
+      <c r="E80" s="53">
+        <v>1</v>
+      </c>
+      <c r="F80" s="53">
+        <v>0</v>
+      </c>
+      <c r="G80" s="53">
+        <v>0</v>
+      </c>
+      <c r="H80" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J80" s="48">
+        <v>1</v>
+      </c>
+      <c r="K80" s="48">
+        <v>2</v>
+      </c>
+      <c r="L80" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N80" s="48">
+        <v>0</v>
+      </c>
+      <c r="O80" s="48">
+        <v>1000</v>
+      </c>
+      <c r="P80" s="48">
+        <v>45</v>
+      </c>
+      <c r="Q80" s="48">
+        <v>200</v>
+      </c>
+      <c r="R80" s="48">
+        <v>100</v>
+      </c>
+      <c r="S80" s="48">
+        <v>0</v>
+      </c>
+      <c r="T80" s="48">
+        <v>11</v>
+      </c>
+      <c r="U80" s="48">
+        <v>1</v>
+      </c>
+      <c r="V80" s="48">
+        <v>0</v>
+      </c>
+      <c r="W80" s="48">
+        <v>0</v>
+      </c>
+      <c r="X80" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA80" s="48">
+        <v>30</v>
+      </c>
+      <c r="AB80" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC80" s="40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AD80" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE80" s="40" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AF80" s="40">
+        <v>40</v>
+      </c>
+      <c r="AG80" s="7">
+        <v>80</v>
+      </c>
+      <c r="AH80" s="42">
+        <v>1</v>
+      </c>
+      <c r="AI80" s="40">
+        <v>45</v>
+      </c>
+      <c r="AJ80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM80" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO80">
+        <v>1</v>
+      </c>
+      <c r="AP80">
+        <v>1</v>
+      </c>
+      <c r="AQ80">
+        <v>6</v>
+      </c>
+      <c r="AR80">
+        <v>3</v>
+      </c>
+      <c r="AS80" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AT80">
+        <v>0</v>
+      </c>
+      <c r="AU80">
+        <v>0</v>
+      </c>
+      <c r="AV80">
+        <v>0</v>
+      </c>
+      <c r="AW80">
+        <v>0</v>
+      </c>
+      <c r="AX80">
+        <v>-1</v>
+      </c>
+      <c r="AY80">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD80">
+        <v>0</v>
+      </c>
+      <c r="BE80">
+        <v>0</v>
+      </c>
+      <c r="BF80">
+        <v>0</v>
+      </c>
+      <c r="BG80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ80" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="81" spans="1:62" ht="12.5">
+      <c r="A81" s="47" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B81" s="53">
+        <v>1</v>
+      </c>
+      <c r="C81" s="53">
+        <v>0</v>
+      </c>
+      <c r="D81" s="53">
+        <v>0</v>
+      </c>
+      <c r="E81" s="53">
+        <v>1</v>
+      </c>
+      <c r="F81" s="53">
+        <v>0</v>
+      </c>
+      <c r="G81" s="53">
+        <v>0</v>
+      </c>
+      <c r="H81" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I81" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J81" s="48">
+        <v>1</v>
+      </c>
+      <c r="K81" s="48">
+        <v>2</v>
+      </c>
+      <c r="L81" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N81" s="48">
+        <v>0</v>
+      </c>
+      <c r="O81" s="48">
+        <v>1000</v>
+      </c>
+      <c r="P81" s="48">
+        <v>45</v>
+      </c>
+      <c r="Q81" s="48">
+        <v>200</v>
+      </c>
+      <c r="R81" s="48">
+        <v>100</v>
+      </c>
+      <c r="S81" s="48">
+        <v>0</v>
+      </c>
+      <c r="T81" s="48">
+        <v>11</v>
+      </c>
+      <c r="U81" s="48">
+        <v>1</v>
+      </c>
+      <c r="V81" s="48">
+        <v>0</v>
+      </c>
+      <c r="W81" s="48">
+        <v>0</v>
+      </c>
+      <c r="X81" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA81" s="48">
+        <v>30</v>
+      </c>
+      <c r="AB81" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC81" s="40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AD81" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE81" s="40" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AF81" s="40">
+        <v>40</v>
+      </c>
+      <c r="AG81" s="7">
+        <v>80</v>
+      </c>
+      <c r="AH81" s="42">
+        <v>1</v>
+      </c>
+      <c r="AI81" s="40">
+        <v>45</v>
+      </c>
+      <c r="AJ81" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM81" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO81">
+        <v>1</v>
+      </c>
+      <c r="AP81">
+        <v>1</v>
+      </c>
+      <c r="AQ81">
+        <v>6</v>
+      </c>
+      <c r="AR81">
+        <v>3</v>
+      </c>
+      <c r="AS81" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AT81">
+        <v>0</v>
+      </c>
+      <c r="AU81">
+        <v>0</v>
+      </c>
+      <c r="AV81">
+        <v>0</v>
+      </c>
+      <c r="AW81">
+        <v>0</v>
+      </c>
+      <c r="AX81">
+        <v>-1</v>
+      </c>
+      <c r="AY81">
+        <v>0</v>
+      </c>
+      <c r="AZ81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD81">
+        <v>0</v>
+      </c>
+      <c r="BE81">
+        <v>0</v>
+      </c>
+      <c r="BF81">
+        <v>0</v>
+      </c>
+      <c r="BG81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="82" spans="1:62" ht="12.5">
+      <c r="A82" s="47" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B82" s="53">
+        <v>1</v>
+      </c>
+      <c r="C82" s="53">
+        <v>0</v>
+      </c>
+      <c r="D82" s="53">
+        <v>0</v>
+      </c>
+      <c r="E82" s="53">
+        <v>1</v>
+      </c>
+      <c r="F82" s="53">
+        <v>0</v>
+      </c>
+      <c r="G82" s="53">
+        <v>0</v>
+      </c>
+      <c r="H82" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I82" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J82" s="48">
+        <v>1</v>
+      </c>
+      <c r="K82" s="48">
+        <v>2</v>
+      </c>
+      <c r="L82" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N82" s="48">
+        <v>0</v>
+      </c>
+      <c r="O82" s="48">
+        <v>1000</v>
+      </c>
+      <c r="P82" s="48">
+        <v>45</v>
+      </c>
+      <c r="Q82" s="48">
+        <v>200</v>
+      </c>
+      <c r="R82" s="48">
+        <v>100</v>
+      </c>
+      <c r="S82" s="48">
+        <v>0</v>
+      </c>
+      <c r="T82" s="48">
+        <v>11</v>
+      </c>
+      <c r="U82" s="48">
+        <v>1</v>
+      </c>
+      <c r="V82" s="48">
+        <v>0</v>
+      </c>
+      <c r="W82" s="48">
+        <v>0</v>
+      </c>
+      <c r="X82" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA82" s="48">
+        <v>30</v>
+      </c>
+      <c r="AB82" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC82" s="40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AD82" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE82" s="40" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AF82" s="40">
+        <v>40</v>
+      </c>
+      <c r="AG82" s="7">
+        <v>80</v>
+      </c>
+      <c r="AH82" s="42">
+        <v>1</v>
+      </c>
+      <c r="AI82" s="40">
+        <v>45</v>
+      </c>
+      <c r="AJ82" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM82" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO82">
+        <v>1</v>
+      </c>
+      <c r="AP82">
+        <v>1</v>
+      </c>
+      <c r="AQ82">
+        <v>6</v>
+      </c>
+      <c r="AR82">
+        <v>3</v>
+      </c>
+      <c r="AS82" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AT82">
+        <v>0</v>
+      </c>
+      <c r="AU82">
+        <v>0</v>
+      </c>
+      <c r="AV82">
+        <v>0</v>
+      </c>
+      <c r="AW82">
+        <v>0</v>
+      </c>
+      <c r="AX82">
+        <v>-1</v>
+      </c>
+      <c r="AY82">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD82">
+        <v>0</v>
+      </c>
+      <c r="BE82">
+        <v>0</v>
+      </c>
+      <c r="BF82">
+        <v>0</v>
+      </c>
+      <c r="BG82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI82" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="83" spans="1:62" ht="12.5">
+      <c r="A83" s="47" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B83" s="53">
+        <v>1</v>
+      </c>
+      <c r="C83" s="53">
+        <v>0</v>
+      </c>
+      <c r="D83" s="53">
+        <v>0</v>
+      </c>
+      <c r="E83" s="53">
+        <v>1</v>
+      </c>
+      <c r="F83" s="53">
+        <v>0</v>
+      </c>
+      <c r="G83" s="53">
+        <v>0</v>
+      </c>
+      <c r="H83" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I83" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J83" s="48">
+        <v>1</v>
+      </c>
+      <c r="K83" s="48">
+        <v>2</v>
+      </c>
+      <c r="L83" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M83" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N83" s="48">
+        <v>0</v>
+      </c>
+      <c r="O83" s="48">
+        <v>1000</v>
+      </c>
+      <c r="P83" s="48">
+        <v>45</v>
+      </c>
+      <c r="Q83" s="48">
+        <v>200</v>
+      </c>
+      <c r="R83" s="48">
+        <v>100</v>
+      </c>
+      <c r="S83" s="48">
+        <v>0</v>
+      </c>
+      <c r="T83" s="48">
+        <v>11</v>
+      </c>
+      <c r="U83" s="48">
+        <v>1</v>
+      </c>
+      <c r="V83" s="48">
+        <v>0</v>
+      </c>
+      <c r="W83" s="48">
+        <v>0</v>
+      </c>
+      <c r="X83" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA83" s="48">
+        <v>30</v>
+      </c>
+      <c r="AB83" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC83" s="40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AD83" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE83" s="40" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AF83" s="40">
+        <v>40</v>
+      </c>
+      <c r="AG83" s="7">
+        <v>80</v>
+      </c>
+      <c r="AH83" s="42">
+        <v>1</v>
+      </c>
+      <c r="AI83" s="40">
+        <v>45</v>
+      </c>
+      <c r="AJ83" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM83" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO83">
+        <v>1</v>
+      </c>
+      <c r="AP83">
+        <v>1</v>
+      </c>
+      <c r="AQ83">
+        <v>6</v>
+      </c>
+      <c r="AR83">
+        <v>3</v>
+      </c>
+      <c r="AS83" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AT83">
+        <v>0</v>
+      </c>
+      <c r="AU83">
+        <v>0</v>
+      </c>
+      <c r="AV83">
+        <v>0</v>
+      </c>
+      <c r="AW83">
+        <v>0</v>
+      </c>
+      <c r="AX83">
+        <v>-1</v>
+      </c>
+      <c r="AY83">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD83">
+        <v>0</v>
+      </c>
+      <c r="BE83">
+        <v>0</v>
+      </c>
+      <c r="BF83">
+        <v>0</v>
+      </c>
+      <c r="BG83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="84" spans="1:62" ht="12.5">
+      <c r="A84" s="47" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B84" s="53">
+        <v>1</v>
+      </c>
+      <c r="C84" s="53">
+        <v>0</v>
+      </c>
+      <c r="D84" s="53">
+        <v>0</v>
+      </c>
+      <c r="E84" s="53">
+        <v>1</v>
+      </c>
+      <c r="F84" s="53">
+        <v>0</v>
+      </c>
+      <c r="G84" s="53">
+        <v>0</v>
+      </c>
+      <c r="H84" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I84" s="53" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J84" s="48">
+        <v>1</v>
+      </c>
+      <c r="K84" s="48">
+        <v>2</v>
+      </c>
+      <c r="L84" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N84" s="48">
+        <v>0</v>
+      </c>
+      <c r="O84" s="48">
+        <v>1000</v>
+      </c>
+      <c r="P84" s="48">
+        <v>45</v>
+      </c>
+      <c r="Q84" s="48">
+        <v>200</v>
+      </c>
+      <c r="R84" s="48">
+        <v>100</v>
+      </c>
+      <c r="S84" s="48">
+        <v>0</v>
+      </c>
+      <c r="T84" s="48">
+        <v>11</v>
+      </c>
+      <c r="U84" s="48">
+        <v>1</v>
+      </c>
+      <c r="V84" s="48">
+        <v>0</v>
+      </c>
+      <c r="W84" s="48">
+        <v>0</v>
+      </c>
+      <c r="X84" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA84" s="48">
+        <v>30</v>
+      </c>
+      <c r="AB84" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC84" s="40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AD84" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE84" s="40" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AF84" s="40">
+        <v>40</v>
+      </c>
+      <c r="AG84" s="7">
+        <v>80</v>
+      </c>
+      <c r="AH84" s="42">
+        <v>1</v>
+      </c>
+      <c r="AI84" s="40">
+        <v>45</v>
+      </c>
+      <c r="AJ84" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM84" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO84">
+        <v>1</v>
+      </c>
+      <c r="AP84">
+        <v>1</v>
+      </c>
+      <c r="AQ84">
+        <v>6</v>
+      </c>
+      <c r="AR84">
+        <v>3</v>
+      </c>
+      <c r="AS84" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AT84">
+        <v>0</v>
+      </c>
+      <c r="AU84">
+        <v>0</v>
+      </c>
+      <c r="AV84">
+        <v>0</v>
+      </c>
+      <c r="AW84">
+        <v>0</v>
+      </c>
+      <c r="AX84">
+        <v>-1</v>
+      </c>
+      <c r="AY84">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD84">
+        <v>0</v>
+      </c>
+      <c r="BE84">
+        <v>0</v>
+      </c>
+      <c r="BF84">
+        <v>0</v>
+      </c>
+      <c r="BG84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI84" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="85" spans="1:62" ht="12.5">
       <c r="J85" s="38"/>
       <c r="K85" s="38"/>
       <c r="AA85" s="41"/>
       <c r="AH85" s="41"/>
     </row>
-    <row r="86" spans="2:34" ht="12.5">
+    <row r="86" spans="1:62" ht="12.5">
       <c r="J86" s="38"/>
       <c r="K86" s="38"/>
       <c r="AA86" s="41"/>
       <c r="AH86" s="41"/>
     </row>
-    <row r="87" spans="2:34" ht="12.5">
+    <row r="87" spans="1:62" ht="12.5">
       <c r="J87" s="38"/>
       <c r="K87" s="38"/>
       <c r="AA87" s="41"/>
       <c r="AH87" s="41"/>
     </row>
-    <row r="88" spans="2:34" ht="12.5">
+    <row r="88" spans="1:62" ht="12.5">
       <c r="J88" s="38"/>
       <c r="K88" s="38"/>
       <c r="AA88" s="41"/>
       <c r="AH88" s="41"/>
     </row>
-    <row r="89" spans="2:34" ht="12.5">
+    <row r="89" spans="1:62" ht="12.5">
       <c r="J89" s="38"/>
       <c r="K89" s="38"/>
       <c r="AA89" s="41"/>
       <c r="AH89" s="41"/>
     </row>
-    <row r="90" spans="2:34" ht="12.5">
+    <row r="90" spans="1:62" ht="12.5">
       <c r="J90" s="38"/>
       <c r="K90" s="38"/>
       <c r="AA90" s="41"/>
       <c r="AH90" s="41"/>
     </row>
-    <row r="91" spans="2:34" ht="12.5">
+    <row r="91" spans="1:62" ht="12.5">
       <c r="J91" s="38"/>
       <c r="K91" s="38"/>
       <c r="AA91" s="41"/>
       <c r="AH91" s="41"/>
     </row>
-    <row r="92" spans="2:34" ht="12.5">
+    <row r="92" spans="1:62" ht="12.5">
       <c r="J92" s="38"/>
       <c r="K92" s="38"/>
       <c r="AA92" s="41"/>
       <c r="AH92" s="41"/>
     </row>
-    <row r="93" spans="2:34" ht="12.5">
+    <row r="93" spans="1:62" ht="12.5">
       <c r="J93" s="38"/>
       <c r="K93" s="38"/>
       <c r="AA93" s="41"/>
       <c r="AH93" s="41"/>
     </row>
-    <row r="94" spans="2:34" ht="12.5">
+    <row r="94" spans="1:62" ht="12.5">
       <c r="J94" s="38"/>
       <c r="K94" s="38"/>
       <c r="AA94" s="41"/>
       <c r="AH94" s="41"/>
     </row>
-    <row r="95" spans="2:34" ht="12.5">
+    <row r="95" spans="1:62" ht="12.5">
       <c r="J95" s="38"/>
       <c r="K95" s="38"/>
       <c r="AA95" s="41"/>
       <c r="AH95" s="41"/>
     </row>
-    <row r="96" spans="2:34" ht="12.5">
+    <row r="96" spans="1:62" ht="12.5">
       <c r="J96" s="38"/>
       <c r="K96" s="38"/>
       <c r="AA96" s="41"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C646B02-F24B-4EDB-B1BE-0FC2997C0B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F147E7-A14C-4275-AD3A-4E6C62B4179D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9503" uniqueCount="1898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9585" uniqueCount="1902">
   <si>
     <t>NAME</t>
   </si>
@@ -5878,13 +5878,25 @@
   </si>
   <si>
     <t>hero_archmage</t>
+  </si>
+  <si>
+    <t>col_damage1</t>
+  </si>
+  <si>
+    <t>EXTRA_PARS</t>
+  </si>
+  <si>
+    <t>col_strike</t>
+  </si>
+  <si>
+    <t>col_chance,100#col_damage,50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -6040,6 +6052,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212529"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -6147,7 +6166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6239,6 +6258,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -6507,7 +6529,7 @@
     <col min="1" max="1" width="16.453125" customWidth="1"/>
     <col min="2" max="2" width="9.36328125" customWidth="1"/>
     <col min="3" max="4" width="9.26953125" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" customWidth="1"/>
     <col min="6" max="6" width="8.90625" customWidth="1"/>
     <col min="7" max="7" width="10.08984375" customWidth="1"/>
     <col min="8" max="8" width="11.6328125" customWidth="1"/>
@@ -21328,8 +21350,8 @@
       <c r="AD80" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AE80" s="40" t="s">
-        <v>1886</v>
+      <c r="AE80" s="59" t="s">
+        <v>1898</v>
       </c>
       <c r="AF80" s="40">
         <v>40</v>
@@ -57852,7 +57874,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BJ83"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -57895,7 +57917,7 @@
     <col min="42" max="42" width="9.54296875" customWidth="1"/>
     <col min="43" max="43" width="9.36328125" customWidth="1"/>
     <col min="44" max="44" width="7.90625" customWidth="1"/>
-    <col min="45" max="45" width="6.7265625" customWidth="1"/>
+    <col min="45" max="45" width="13.6328125" customWidth="1"/>
     <col min="46" max="46" width="6.453125" customWidth="1"/>
     <col min="47" max="47" width="6.54296875" customWidth="1"/>
     <col min="48" max="48" width="5.90625" customWidth="1"/>
@@ -57907,8 +57929,9 @@
     <col min="57" max="57" width="11.08984375" customWidth="1"/>
     <col min="58" max="58" width="10" customWidth="1"/>
     <col min="59" max="59" width="11.54296875" customWidth="1"/>
-    <col min="60" max="60" width="15.36328125" customWidth="1"/>
-    <col min="61" max="62" width="10" customWidth="1"/>
+    <col min="60" max="60" width="13.26953125" customWidth="1"/>
+    <col min="61" max="61" width="26.26953125" customWidth="1"/>
+    <col min="62" max="62" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="13">
@@ -58092,7 +58115,9 @@
       <c r="BH1" s="43" t="s">
         <v>1892</v>
       </c>
-      <c r="BI1" s="43"/>
+      <c r="BI1" s="43" t="s">
+        <v>1899</v>
+      </c>
       <c r="BJ1" s="43"/>
     </row>
     <row r="2" spans="1:62">
@@ -58276,16 +58301,19 @@
       <c r="BH2">
         <v>0</v>
       </c>
+      <c r="BI2" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="3" spans="1:62">
       <c r="A3" s="44" t="s">
-        <v>42</v>
+        <v>1900</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -58345,7 +58373,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -58372,7 +58400,7 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="s">
         <v>36</v>
@@ -58447,27 +58475,30 @@
         <v>0</v>
       </c>
       <c r="BE3" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF3" t="s">
         <v>36</v>
       </c>
       <c r="BG3" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="BH3">
         <v>0</v>
+      </c>
+      <c r="BI3" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="44" t="s">
-        <v>1371</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -58482,10 +58513,10 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -58527,7 +58558,7 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -58554,7 +58585,7 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="s">
         <v>36</v>
@@ -58587,10 +58618,10 @@
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="s">
         <v>36</v>
@@ -58626,24 +58657,27 @@
         <v>0</v>
       </c>
       <c r="BD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF4" t="s">
         <v>36</v>
       </c>
       <c r="BG4" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="BH4">
         <v>0</v>
+      </c>
+      <c r="BI4" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="44" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -58655,19 +58689,19 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -58808,36 +58842,39 @@
         <v>0</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF5" t="s">
         <v>36</v>
       </c>
       <c r="BG5" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="BH5">
         <v>0</v>
+      </c>
+      <c r="BI5" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:62">
       <c r="A6" s="44" t="s">
-        <v>1890</v>
+        <v>1372</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -58924,10 +58961,10 @@
         <v>36</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI6" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AJ6" s="44" t="s">
         <v>1470</v>
@@ -58951,7 +58988,7 @@
         <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR6">
         <v>1</v>
@@ -58993,7 +59030,7 @@
         <v>0</v>
       </c>
       <c r="BE6" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF6" t="s">
         <v>36</v>
@@ -59004,16 +59041,19 @@
       <c r="BH6">
         <v>0</v>
       </c>
+      <c r="BI6" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="44" t="s">
-        <v>1469</v>
+        <v>1890</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -59186,16 +59226,19 @@
       <c r="BH7">
         <v>0</v>
       </c>
+      <c r="BI7" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:62">
       <c r="A8" s="44" t="s">
-        <v>1483</v>
+        <v>1469</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -59291,7 +59334,7 @@
         <v>1479</v>
       </c>
       <c r="AI8" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AJ8" s="44" t="s">
         <v>1470</v>
@@ -59318,10 +59361,10 @@
         <v>1</v>
       </c>
       <c r="AR8">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="s">
-        <v>1481</v>
+        <v>36</v>
       </c>
       <c r="AT8">
         <v>0</v>
@@ -59357,27 +59400,30 @@
         <v>0</v>
       </c>
       <c r="BE8" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF8" t="s">
         <v>36</v>
       </c>
       <c r="BG8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="BH8">
         <v>0</v>
+      </c>
+      <c r="BI8" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:62">
       <c r="A9" s="44" t="s">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -59464,13 +59510,13 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="s">
         <v>36</v>
       </c>
       <c r="AH9" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI9" s="44" t="s">
         <v>1470</v>
@@ -59503,7 +59549,7 @@
         <v>60</v>
       </c>
       <c r="AS9" t="s">
-        <v>36</v>
+        <v>1481</v>
       </c>
       <c r="AT9">
         <v>0</v>
@@ -59512,7 +59558,7 @@
         <v>36</v>
       </c>
       <c r="AV9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9">
         <v>0</v>
@@ -59539,27 +59585,30 @@
         <v>0</v>
       </c>
       <c r="BE9" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF9" t="s">
         <v>36</v>
       </c>
       <c r="BG9" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="BH9">
         <v>0</v>
+      </c>
+      <c r="BI9" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="44" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -59622,7 +59671,7 @@
         <v>3</v>
       </c>
       <c r="X10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -59637,7 +59686,7 @@
         <v>1</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>-1</v>
@@ -59721,33 +59770,36 @@
         <v>0</v>
       </c>
       <c r="BE10" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF10" t="s">
         <v>36</v>
       </c>
       <c r="BG10" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="BH10">
         <v>0</v>
+      </c>
+      <c r="BI10" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="44" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -59804,7 +59856,7 @@
         <v>3</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y11">
         <v>0</v>
@@ -59819,7 +59871,7 @@
         <v>1</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11">
         <v>-1</v>
@@ -59828,7 +59880,7 @@
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="s">
         <v>36</v>
@@ -59861,10 +59913,10 @@
         <v>0</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS11" t="s">
         <v>36</v>
@@ -59876,7 +59928,7 @@
         <v>36</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11">
         <v>0</v>
@@ -59903,21 +59955,24 @@
         <v>0</v>
       </c>
       <c r="BE11" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF11" t="s">
         <v>36</v>
       </c>
       <c r="BG11" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="BH11">
         <v>0</v>
+      </c>
+      <c r="BI11" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="44" t="s">
-        <v>1524</v>
+        <v>1447</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -59929,7 +59984,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -59938,10 +59993,10 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -60085,21 +60140,24 @@
         <v>0</v>
       </c>
       <c r="BE12" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF12" t="s">
         <v>36</v>
       </c>
       <c r="BG12" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="BH12">
         <v>0</v>
+      </c>
+      <c r="BI12" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="44" t="s">
-        <v>1448</v>
+        <v>1524</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -60120,10 +60178,10 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -60267,21 +60325,24 @@
         <v>0</v>
       </c>
       <c r="BE13" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF13" t="s">
         <v>36</v>
       </c>
       <c r="BG13" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="BH13">
         <v>0</v>
+      </c>
+      <c r="BI13" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="44" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -60302,13 +60363,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -60449,27 +60510,30 @@
         <v>0</v>
       </c>
       <c r="BE14" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF14" t="s">
         <v>36</v>
       </c>
       <c r="BG14" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="BH14">
         <v>0</v>
+      </c>
+      <c r="BI14" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="44" t="s">
-        <v>1485</v>
+        <v>1449</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -60490,7 +60554,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -60529,10 +60593,10 @@
         <v>0</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y15">
         <v>0</v>
@@ -60556,10 +60620,10 @@
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="s">
-        <v>1494</v>
+        <v>36</v>
       </c>
       <c r="AH15" s="44" t="s">
         <v>1363</v>
@@ -60589,7 +60653,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR15">
         <v>1</v>
@@ -60619,7 +60683,7 @@
         <v>36</v>
       </c>
       <c r="BA15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB15">
         <v>0</v>
@@ -60631,33 +60695,36 @@
         <v>0</v>
       </c>
       <c r="BE15" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF15" t="s">
         <v>36</v>
       </c>
       <c r="BG15" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="BH15">
         <v>0</v>
+      </c>
+      <c r="BI15" s="46" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="44" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -60711,10 +60778,10 @@
         <v>0</v>
       </c>
       <c r="W16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -60741,7 +60808,7 @@
         <v>10</v>
       </c>
       <c r="AG16" t="s">
-        <v>36</v>
+        <v>1494</v>
       </c>
       <c r="AH16" s="44" t="s">
         <v>1363</v>
@@ -60762,7 +60829,7 @@
         <v>1</v>
       </c>
       <c r="AN16" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AO16" s="44">
         <v>0</v>
@@ -60771,7 +60838,7 @@
         <v>0</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1</v>
@@ -60801,7 +60868,7 @@
         <v>36</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB16">
         <v>0</v>
@@ -60813,21 +60880,24 @@
         <v>0</v>
       </c>
       <c r="BE16" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF16" t="s">
         <v>36</v>
       </c>
       <c r="BG16" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="BH16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:60">
+      <c r="BI16" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61">
       <c r="A17" s="44" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -60839,7 +60909,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -60848,10 +60918,10 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -60995,24 +61065,27 @@
         <v>0</v>
       </c>
       <c r="BE17" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF17" t="s">
         <v>36</v>
       </c>
       <c r="BG17" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="BH17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:60">
+      <c r="BI17" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61">
       <c r="A18" s="44" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -61021,19 +61094,19 @@
         <v>0</v>
       </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>20</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -61096,13 +61169,13 @@
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG18" t="s">
         <v>36</v>
@@ -61135,7 +61208,7 @@
         <v>0</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR18">
         <v>1</v>
@@ -61153,7 +61226,7 @@
         <v>0</v>
       </c>
       <c r="AW18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="s">
         <v>36</v>
@@ -61177,24 +61250,27 @@
         <v>0</v>
       </c>
       <c r="BE18" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF18" t="s">
         <v>36</v>
       </c>
       <c r="BG18" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="BH18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:60">
+      <c r="BI18" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61">
       <c r="A19" s="44" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -61203,7 +61279,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -61335,7 +61411,7 @@
         <v>0</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="s">
         <v>36</v>
@@ -61359,21 +61435,24 @@
         <v>0</v>
       </c>
       <c r="BE19" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF19" t="s">
         <v>36</v>
       </c>
       <c r="BG19" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="BH19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:60">
+      <c r="BI19" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61">
       <c r="A20" s="44" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -61385,7 +61464,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -61442,7 +61521,7 @@
         <v>3</v>
       </c>
       <c r="X20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20">
         <v>0</v>
@@ -61460,16 +61539,16 @@
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="s">
-        <v>1501</v>
+        <v>36</v>
       </c>
       <c r="AH20" s="44" t="s">
         <v>1363</v>
@@ -61487,10 +61566,10 @@
         <v>1474</v>
       </c>
       <c r="AM20" s="44">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AN20" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AO20" s="44">
         <v>0</v>
@@ -61502,7 +61581,7 @@
         <v>1</v>
       </c>
       <c r="AR20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS20" t="s">
         <v>36</v>
@@ -61541,33 +61620,36 @@
         <v>0</v>
       </c>
       <c r="BE20" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF20" t="s">
         <v>36</v>
       </c>
       <c r="BG20" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="BH20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:60">
+      <c r="BI20" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61">
       <c r="A21" s="44" t="s">
-        <v>1431</v>
+        <v>1502</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>10</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -61624,19 +61706,19 @@
         <v>3</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -61648,10 +61730,10 @@
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="s">
-        <v>36</v>
+        <v>1501</v>
       </c>
       <c r="AH21" s="44" t="s">
         <v>1363</v>
@@ -61669,7 +61751,7 @@
         <v>1474</v>
       </c>
       <c r="AM21" s="44">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AN21" s="44" t="s">
         <v>36</v>
@@ -61684,7 +61766,7 @@
         <v>1</v>
       </c>
       <c r="AR21">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="s">
         <v>36</v>
@@ -61696,7 +61778,7 @@
         <v>36</v>
       </c>
       <c r="AV21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW21">
         <v>0</v>
@@ -61723,27 +61805,30 @@
         <v>0</v>
       </c>
       <c r="BE21" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF21" t="s">
         <v>36</v>
       </c>
       <c r="BG21" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="BH21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:60">
+      <c r="BI21" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61">
       <c r="A22" s="44" t="s">
-        <v>1551</v>
+        <v>1431</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -61809,16 +61894,16 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -61830,13 +61915,13 @@
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG22" t="s">
         <v>36</v>
       </c>
       <c r="AH22" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI22" s="44" t="s">
         <v>1470</v>
@@ -61857,7 +61942,7 @@
         <v>36</v>
       </c>
       <c r="AO22" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22">
         <v>0</v>
@@ -61869,13 +61954,13 @@
         <v>60</v>
       </c>
       <c r="AS22" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AT22">
         <v>0</v>
       </c>
       <c r="AU22" t="s">
-        <v>1554</v>
+        <v>36</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -61905,21 +61990,24 @@
         <v>0</v>
       </c>
       <c r="BE22" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF22" t="s">
         <v>36</v>
       </c>
       <c r="BG22" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
       <c r="BH22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:60">
+      <c r="BI22" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61">
       <c r="A23" s="44" t="s">
-        <v>1587</v>
+        <v>1551</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -61982,10 +62070,10 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -62039,7 +62127,7 @@
         <v>36</v>
       </c>
       <c r="AO23" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP23">
         <v>0</v>
@@ -62048,19 +62136,19 @@
         <v>1</v>
       </c>
       <c r="AR23">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS23" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AT23">
         <v>0</v>
       </c>
       <c r="AU23" t="s">
-        <v>36</v>
+        <v>1554</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW23">
         <v>0</v>
@@ -62087,7 +62175,7 @@
         <v>0</v>
       </c>
       <c r="BE23" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF23" t="s">
         <v>36</v>
@@ -62098,10 +62186,13 @@
       <c r="BH23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:60">
+      <c r="BI23" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61">
       <c r="A24" s="44" t="s">
-        <v>935</v>
+        <v>1587</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -62164,10 +62255,10 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -62221,7 +62312,7 @@
         <v>36</v>
       </c>
       <c r="AO24" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24">
         <v>0</v>
@@ -62269,7 +62360,7 @@
         <v>0</v>
       </c>
       <c r="BE24" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BF24" t="s">
         <v>36</v>
@@ -62280,10 +62371,13 @@
       <c r="BH24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:60">
+      <c r="BI24" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:61">
       <c r="A25" s="44" t="s">
-        <v>1593</v>
+        <v>935</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -62349,7 +62443,7 @@
         <v>0</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -62451,7 +62545,7 @@
         <v>0</v>
       </c>
       <c r="BE25" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF25" t="s">
         <v>36</v>
@@ -62462,16 +62556,19 @@
       <c r="BH25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:60">
+      <c r="BI25" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61">
       <c r="A26" s="44" t="s">
-        <v>1602</v>
+        <v>1593</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -62531,7 +62628,7 @@
         <v>0</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -62564,7 +62661,7 @@
         <v>36</v>
       </c>
       <c r="AH26" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI26" s="44" t="s">
         <v>1470</v>
@@ -62585,7 +62682,7 @@
         <v>36</v>
       </c>
       <c r="AO26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26">
         <v>0</v>
@@ -62633,7 +62730,7 @@
         <v>0</v>
       </c>
       <c r="BE26" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF26" t="s">
         <v>36</v>
@@ -62644,16 +62741,19 @@
       <c r="BH26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:60">
+      <c r="BI26" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:61">
       <c r="A27" s="44" t="s">
-        <v>1611</v>
+        <v>1602</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -62713,7 +62813,7 @@
         <v>0</v>
       </c>
       <c r="W27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -62746,7 +62846,7 @@
         <v>36</v>
       </c>
       <c r="AH27" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI27" s="44" t="s">
         <v>1470</v>
@@ -62767,7 +62867,7 @@
         <v>36</v>
       </c>
       <c r="AO27" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27">
         <v>0</v>
@@ -62776,19 +62876,19 @@
         <v>1</v>
       </c>
       <c r="AR27">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AT27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="s">
         <v>36</v>
       </c>
       <c r="AV27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW27">
         <v>0</v>
@@ -62815,27 +62915,30 @@
         <v>0</v>
       </c>
       <c r="BE27" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF27" t="s">
         <v>36</v>
       </c>
       <c r="BG27" t="s">
-        <v>1559</v>
+        <v>1658</v>
       </c>
       <c r="BH27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:60">
+      <c r="BI27" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61">
       <c r="A28" s="44" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -62895,7 +62998,7 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -62928,7 +63031,7 @@
         <v>36</v>
       </c>
       <c r="AH28" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI28" s="44" t="s">
         <v>1470</v>
@@ -62949,7 +63052,7 @@
         <v>36</v>
       </c>
       <c r="AO28" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28">
         <v>0</v>
@@ -62958,19 +63061,19 @@
         <v>1</v>
       </c>
       <c r="AR28">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AS28" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="s">
         <v>36</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW28">
         <v>0</v>
@@ -62997,21 +63100,24 @@
         <v>0</v>
       </c>
       <c r="BE28" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF28" t="s">
         <v>36</v>
       </c>
       <c r="BG28" t="s">
-        <v>1658</v>
+        <v>1559</v>
       </c>
       <c r="BH28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:60">
+      <c r="BI28" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61">
       <c r="A29" s="44" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -63077,7 +63183,7 @@
         <v>0</v>
       </c>
       <c r="W29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X29">
         <v>0</v>
@@ -63179,7 +63285,7 @@
         <v>0</v>
       </c>
       <c r="BE29" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF29" t="s">
         <v>36</v>
@@ -63190,10 +63296,13 @@
       <c r="BH29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:60">
+      <c r="BI29" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61">
       <c r="A30" s="44" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -63262,7 +63371,7 @@
         <v>3</v>
       </c>
       <c r="X30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y30">
         <v>0</v>
@@ -63292,7 +63401,7 @@
         <v>36</v>
       </c>
       <c r="AH30" s="44" t="s">
-        <v>1621</v>
+        <v>1363</v>
       </c>
       <c r="AI30" s="44" t="s">
         <v>1470</v>
@@ -63361,7 +63470,7 @@
         <v>0</v>
       </c>
       <c r="BE30" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BF30" t="s">
         <v>36</v>
@@ -63372,10 +63481,13 @@
       <c r="BH30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:60">
+      <c r="BI30" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61">
       <c r="A31" s="44" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -63444,7 +63556,7 @@
         <v>3</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -63474,7 +63586,7 @@
         <v>36</v>
       </c>
       <c r="AH31" s="44" t="s">
-        <v>1363</v>
+        <v>1621</v>
       </c>
       <c r="AI31" s="44" t="s">
         <v>1470</v>
@@ -63528,42 +63640,45 @@
         <v>36</v>
       </c>
       <c r="AZ31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG31" t="s">
+        <v>1658</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61">
+      <c r="A32" s="44" t="s">
         <v>1624</v>
       </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>0</v>
-      </c>
-      <c r="BC31">
-        <v>0</v>
-      </c>
-      <c r="BD31">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="s">
-        <v>1760</v>
-      </c>
-      <c r="BF31" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG31" t="s">
-        <v>896</v>
-      </c>
-      <c r="BH31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:60">
-      <c r="A32" s="44" t="s">
-        <v>1647</v>
-      </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -63623,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="W32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -63710,7 +63825,7 @@
         <v>36</v>
       </c>
       <c r="AZ32" t="s">
-        <v>36</v>
+        <v>1624</v>
       </c>
       <c r="BA32">
         <v>0</v>
@@ -63725,7 +63840,7 @@
         <v>0</v>
       </c>
       <c r="BE32" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BF32" t="s">
         <v>36</v>
@@ -63736,10 +63851,13 @@
       <c r="BH32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:60">
+      <c r="BI32" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:61">
       <c r="A33" s="44" t="s">
-        <v>1578</v>
+        <v>1647</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -63805,7 +63923,7 @@
         <v>0</v>
       </c>
       <c r="W33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -63865,7 +63983,7 @@
         <v>0</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1</v>
@@ -63907,21 +64025,24 @@
         <v>0</v>
       </c>
       <c r="BE33" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BF33" t="s">
         <v>36</v>
       </c>
       <c r="BG33" t="s">
-        <v>1671</v>
+        <v>896</v>
       </c>
       <c r="BH33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:60">
+      <c r="BI33" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:61">
       <c r="A34" s="44" t="s">
-        <v>1686</v>
+        <v>1578</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -63987,7 +64108,7 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -64020,7 +64141,7 @@
         <v>36</v>
       </c>
       <c r="AH34" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI34" s="44" t="s">
         <v>1470</v>
@@ -64041,13 +64162,13 @@
         <v>36</v>
       </c>
       <c r="AO34" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34">
         <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34">
         <v>1</v>
@@ -64089,7 +64210,7 @@
         <v>0</v>
       </c>
       <c r="BE34" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BF34" t="s">
         <v>36</v>
@@ -64100,10 +64221,13 @@
       <c r="BH34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:60">
+      <c r="BI34" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:61">
       <c r="A35" s="44" t="s">
-        <v>1728</v>
+        <v>1686</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -64169,7 +64293,7 @@
         <v>0</v>
       </c>
       <c r="W35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -64202,7 +64326,7 @@
         <v>36</v>
       </c>
       <c r="AH35" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI35" s="44" t="s">
         <v>1470</v>
@@ -64223,13 +64347,13 @@
         <v>36</v>
       </c>
       <c r="AO35" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP35">
         <v>0</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1</v>
@@ -64271,21 +64395,24 @@
         <v>0</v>
       </c>
       <c r="BE35" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF35" t="s">
         <v>36</v>
       </c>
       <c r="BG35" t="s">
-        <v>896</v>
+        <v>1671</v>
       </c>
       <c r="BH35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:60">
+      <c r="BI35" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:61">
       <c r="A36" s="44" t="s">
-        <v>1786</v>
+        <v>1728</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -64303,7 +64430,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -64351,7 +64478,7 @@
         <v>0</v>
       </c>
       <c r="W36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -64411,7 +64538,7 @@
         <v>0</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR36">
         <v>1</v>
@@ -64453,21 +64580,24 @@
         <v>0</v>
       </c>
       <c r="BE36" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="BF36" t="s">
         <v>36</v>
       </c>
       <c r="BG36" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BH36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:60">
+      <c r="BI36" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:61">
       <c r="A37" s="44" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -64485,7 +64615,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -64533,10 +64663,10 @@
         <v>0</v>
       </c>
       <c r="W37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -64563,10 +64693,10 @@
         <v>10</v>
       </c>
       <c r="AG37" t="s">
-        <v>1796</v>
+        <v>36</v>
       </c>
       <c r="AH37" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI37" s="44" t="s">
         <v>1470</v>
@@ -64635,7 +64765,7 @@
         <v>0</v>
       </c>
       <c r="BE37" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BF37" t="s">
         <v>36</v>
@@ -64646,13 +64776,16 @@
       <c r="BH37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:60">
+      <c r="BI37" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:61">
       <c r="A38" s="44" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -64661,7 +64794,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -64718,7 +64851,7 @@
         <v>3</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -64736,16 +64869,16 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG38" t="s">
-        <v>36</v>
+        <v>1796</v>
       </c>
       <c r="AH38" s="44" t="s">
         <v>1479</v>
@@ -64775,7 +64908,7 @@
         <v>0</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1</v>
@@ -64793,7 +64926,7 @@
         <v>0</v>
       </c>
       <c r="AW38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="s">
         <v>36</v>
@@ -64817,7 +64950,7 @@
         <v>0</v>
       </c>
       <c r="BE38" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF38" t="s">
         <v>36</v>
@@ -64828,13 +64961,16 @@
       <c r="BH38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:60">
+      <c r="BI38" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:61">
       <c r="A39" s="44" t="s">
-        <v>1805</v>
+        <v>1796</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -64843,7 +64979,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -64888,7 +65024,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -64918,13 +65054,13 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="s">
         <v>36</v>
@@ -64933,7 +65069,7 @@
         <v>1479</v>
       </c>
       <c r="AI39" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AJ39" s="44" t="s">
         <v>1470</v>
@@ -64957,7 +65093,7 @@
         <v>0</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR39">
         <v>1</v>
@@ -64975,7 +65111,7 @@
         <v>0</v>
       </c>
       <c r="AW39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="s">
         <v>36</v>
@@ -64999,7 +65135,7 @@
         <v>0</v>
       </c>
       <c r="BE39" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BF39" t="s">
         <v>36</v>
@@ -65010,10 +65146,13 @@
       <c r="BH39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:60">
+      <c r="BI39" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:61">
       <c r="A40" s="44" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -65070,7 +65209,7 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -65187,15 +65326,18 @@
         <v>36</v>
       </c>
       <c r="BG40" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BH40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:60">
+      <c r="BI40" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:61">
       <c r="A41" s="44" t="s">
-        <v>1868</v>
+        <v>1807</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -65207,7 +65349,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -65264,7 +65406,7 @@
         <v>3</v>
       </c>
       <c r="X41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -65291,13 +65433,13 @@
         <v>10</v>
       </c>
       <c r="AG41" t="s">
-        <v>1869</v>
+        <v>36</v>
       </c>
       <c r="AH41" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI41" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AJ41" s="44" t="s">
         <v>1470</v>
@@ -65363,7 +65505,7 @@
         <v>0</v>
       </c>
       <c r="BE41" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BF41" t="s">
         <v>36</v>
@@ -65374,22 +65516,25 @@
       <c r="BH41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:60">
+      <c r="BI41" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:61">
       <c r="A42" s="44" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -65446,7 +65591,7 @@
         <v>3</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -65464,16 +65609,16 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG42" t="s">
-        <v>36</v>
+        <v>1869</v>
       </c>
       <c r="AH42" s="44" t="s">
         <v>1363</v>
@@ -65503,7 +65648,7 @@
         <v>0</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1</v>
@@ -65521,7 +65666,7 @@
         <v>0</v>
       </c>
       <c r="AW42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="s">
         <v>36</v>
@@ -65545,30 +65690,33 @@
         <v>0</v>
       </c>
       <c r="BE42" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF42" t="s">
         <v>36</v>
       </c>
       <c r="BG42" t="s">
-        <v>896</v>
+        <v>1671</v>
       </c>
       <c r="BH42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:60">
+      <c r="BI42" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:61">
       <c r="A43" s="44" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -65628,7 +65776,7 @@
         <v>3</v>
       </c>
       <c r="X43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -65646,19 +65794,19 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="s">
-        <v>1871</v>
+        <v>36</v>
       </c>
       <c r="AH43" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AI43" s="44" t="s">
         <v>1470</v>
@@ -65685,7 +65833,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR43">
         <v>1</v>
@@ -65703,7 +65851,7 @@
         <v>0</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="s">
         <v>36</v>
@@ -65727,24 +65875,27 @@
         <v>0</v>
       </c>
       <c r="BE43" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="BF43" t="s">
         <v>36</v>
       </c>
       <c r="BG43" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BH43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:60">
+      <c r="BI43" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:61">
       <c r="A44" s="44" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -65768,7 +65919,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -65810,7 +65961,7 @@
         <v>3</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y44">
         <v>0</v>
@@ -65828,16 +65979,16 @@
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="s">
-        <v>36</v>
+        <v>1871</v>
       </c>
       <c r="AH44" s="44" t="s">
         <v>1479</v>
@@ -65867,7 +66018,7 @@
         <v>0</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1</v>
@@ -65885,7 +66036,7 @@
         <v>0</v>
       </c>
       <c r="AW44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="s">
         <v>36</v>
@@ -65909,7 +66060,7 @@
         <v>0</v>
       </c>
       <c r="BE44" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BF44" t="s">
         <v>36</v>
@@ -65920,13 +66071,16 @@
       <c r="BH44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:60">
+      <c r="BI44" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:61">
       <c r="A45" s="44" t="s">
-        <v>1883</v>
+        <v>1871</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -65941,7 +66095,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -65950,7 +66104,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -65989,7 +66143,7 @@
         <v>0</v>
       </c>
       <c r="W45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X45">
         <v>0</v>
@@ -66010,19 +66164,19 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="s">
         <v>36</v>
       </c>
       <c r="AH45" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AI45" s="44" t="s">
         <v>1470</v>
@@ -66049,7 +66203,7 @@
         <v>0</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -66067,7 +66221,7 @@
         <v>0</v>
       </c>
       <c r="AW45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX45" t="s">
         <v>36</v>
@@ -66091,7 +66245,7 @@
         <v>0</v>
       </c>
       <c r="BE45" t="s">
-        <v>37</v>
+        <v>1761</v>
       </c>
       <c r="BF45" t="s">
         <v>36</v>
@@ -66102,10 +66256,13 @@
       <c r="BH45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:60">
+      <c r="BI45" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:61">
       <c r="A46" s="44" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -66273,7 +66430,7 @@
         <v>0</v>
       </c>
       <c r="BE46" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BF46" t="s">
         <v>36</v>
@@ -66284,10 +66441,13 @@
       <c r="BH46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:60">
+      <c r="BI46" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:61">
       <c r="A47" s="44" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -66455,7 +66615,7 @@
         <v>0</v>
       </c>
       <c r="BE47" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="BF47" t="s">
         <v>36</v>
@@ -66466,244 +66626,253 @@
       <c r="BH47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:60" ht="14">
-      <c r="A48" s="55" t="s">
+      <c r="BI47" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:61">
+      <c r="A48" s="44" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>4</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>1</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>-1</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>10</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH48" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI48" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ48" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK48" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM48" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN48" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO48" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>0</v>
+      </c>
+      <c r="AQ48">
+        <v>1</v>
+      </c>
+      <c r="AR48">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV48">
+        <v>0</v>
+      </c>
+      <c r="AW48">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ48" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA48">
+        <v>0</v>
+      </c>
+      <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
+        <v>0</v>
+      </c>
+      <c r="BD48">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BF48" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG48" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BH48">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:61" ht="14">
+      <c r="A49" s="55" t="s">
         <v>1887</v>
       </c>
-      <c r="B48" s="55"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="BH48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:60">
-      <c r="A49" s="44" t="s">
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="BH49">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:61">
+      <c r="A50" s="44" t="s">
         <v>1888</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>200</v>
       </c>
-      <c r="I49">
+      <c r="I50">
         <v>200</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>3</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>1</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>-1</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>10</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH49" s="44" t="s">
-        <v>1363</v>
-      </c>
-      <c r="AI49" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AJ49" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK49" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL49" s="44" t="s">
-        <v>1474</v>
-      </c>
-      <c r="AM49" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN49" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO49" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP49">
-        <v>0</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>1</v>
-      </c>
-      <c r="AS49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV49">
-        <v>0</v>
-      </c>
-      <c r="AW49">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AY49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ49" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA49">
-        <v>0</v>
-      </c>
-      <c r="BB49">
-        <v>0</v>
-      </c>
-      <c r="BC49">
-        <v>0</v>
-      </c>
-      <c r="BD49">
-        <v>1</v>
-      </c>
-      <c r="BE49" t="s">
-        <v>1762</v>
-      </c>
-      <c r="BF49" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG49" t="s">
-        <v>1659</v>
-      </c>
-      <c r="BH49">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:60">
-      <c r="A50" s="44" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
       <c r="J50">
         <v>0</v>
       </c>
@@ -66723,7 +66892,7 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -66855,54 +67024,383 @@
         <v>1659</v>
       </c>
       <c r="BH50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:60">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-    </row>
-    <row r="52" spans="1:60">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-    </row>
-    <row r="53" spans="1:60">
+        <v>10</v>
+      </c>
+      <c r="BI50" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:61">
+      <c r="A51" s="44" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>10</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>3</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>1</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>-1</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>10</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH51" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI51" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ51" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK51" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM51" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN51" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO51" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>0</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>1</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV51">
+        <v>0</v>
+      </c>
+      <c r="AW51">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ51" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>0</v>
+      </c>
+      <c r="BD51">
+        <v>1</v>
+      </c>
+      <c r="BE51" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BF51" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG51" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BH51">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:61">
+      <c r="A52" s="44" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>3</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>1</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>-1</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>10</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH52" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI52" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ52" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK52" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM52" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN52" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO52" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP52">
+        <v>0</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>1</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV52">
+        <v>0</v>
+      </c>
+      <c r="AW52">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA52">
+        <v>0</v>
+      </c>
+      <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
+        <v>0</v>
+      </c>
+      <c r="BD52">
+        <v>1</v>
+      </c>
+      <c r="BE52" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BF52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG52" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BH52">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="46" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="53" spans="1:61">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -66923,8 +67421,9 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
-    </row>
-    <row r="54" spans="1:60">
+      <c r="BI53" s="46"/>
+    </row>
+    <row r="54" spans="1:61">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -66945,8 +67444,9 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
-    </row>
-    <row r="55" spans="1:60">
+      <c r="BI54" s="46"/>
+    </row>
+    <row r="55" spans="1:61">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -66967,8 +67467,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="1:60">
+      <c r="BI55" s="46"/>
+    </row>
+    <row r="56" spans="1:61">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -66990,7 +67491,7 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
     </row>
-    <row r="57" spans="1:60">
+    <row r="57" spans="1:61">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -67012,7 +67513,7 @@
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
     </row>
-    <row r="58" spans="1:60">
+    <row r="58" spans="1:61">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -67034,7 +67535,7 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
     </row>
-    <row r="59" spans="1:60">
+    <row r="59" spans="1:61">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -67056,7 +67557,7 @@
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
     </row>
-    <row r="60" spans="1:60">
+    <row r="60" spans="1:61">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -67078,7 +67579,7 @@
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
     </row>
-    <row r="61" spans="1:60">
+    <row r="61" spans="1:61">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -67100,7 +67601,7 @@
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
     </row>
-    <row r="62" spans="1:60">
+    <row r="62" spans="1:61">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -67122,7 +67623,7 @@
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
     </row>
-    <row r="63" spans="1:60">
+    <row r="63" spans="1:61">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -67144,7 +67645,7 @@
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
     </row>
-    <row r="64" spans="1:60">
+    <row r="64" spans="1:61">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -67583,6 +68084,28 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="1:20">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F147E7-A14C-4275-AD3A-4E6C62B4179D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE822E-2F28-495E-9E54-838D91E8FFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE822E-2F28-495E-9E54-838D91E8FFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD413B8-35DC-405F-BE66-D1A8949AAD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9585" uniqueCount="1902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9601" uniqueCount="1904">
   <si>
     <t>NAME</t>
   </si>
@@ -5889,7 +5889,13 @@
     <t>col_strike</t>
   </si>
   <si>
-    <t>col_chance,100#col_damage,50</t>
+    <t>col_chance,10#col_damage,15</t>
+  </si>
+  <si>
+    <t>mana_siphon1</t>
+  </si>
+  <si>
+    <t>mana_siphon,100</t>
   </si>
 </sst>
 </file>
@@ -21679,16 +21685,16 @@
         <v>0</v>
       </c>
       <c r="O82" s="48">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="P82" s="48">
         <v>45</v>
       </c>
       <c r="Q82" s="48">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R82" s="48">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S82" s="48">
         <v>0</v>
@@ -21726,8 +21732,8 @@
       <c r="AD82" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AE82" s="40" t="s">
-        <v>1886</v>
+      <c r="AE82" s="59" t="s">
+        <v>1902</v>
       </c>
       <c r="AF82" s="40">
         <v>40</v>
@@ -67401,27 +67407,189 @@
       </c>
     </row>
     <row r="53" spans="1:61">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="BI53" s="46"/>
+      <c r="A53" s="44" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>3</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>1</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>-1</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>10</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH53" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AI53" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AJ53" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK53" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AM53" s="44">
+        <v>1</v>
+      </c>
+      <c r="AN53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO53" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP53">
+        <v>0</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>1</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ53" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA53">
+        <v>0</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>0</v>
+      </c>
+      <c r="BD53">
+        <v>1</v>
+      </c>
+      <c r="BE53" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BF53" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG53" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="46" t="s">
+        <v>1903</v>
+      </c>
     </row>
     <row r="54" spans="1:61">
       <c r="A54" s="3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD413B8-35DC-405F-BE66-D1A8949AAD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AABDF2-B90A-44F4-8CB4-21EFDFBBBFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9601" uniqueCount="1904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9705" uniqueCount="1908">
   <si>
     <t>NAME</t>
   </si>
@@ -5896,6 +5896,18 @@
   </si>
   <si>
     <t>mana_siphon,100</t>
+  </si>
+  <si>
+    <t>ALSO_CAST</t>
+  </si>
+  <si>
+    <t>crit_strike</t>
+  </si>
+  <si>
+    <t>buff_crit</t>
+  </si>
+  <si>
+    <t>do_strike</t>
   </si>
 </sst>
 </file>
@@ -21497,16 +21509,16 @@
         <v>0</v>
       </c>
       <c r="O81" s="48">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="P81" s="48">
         <v>45</v>
       </c>
       <c r="Q81" s="48">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="R81" s="48">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="S81" s="48">
         <v>0</v>
@@ -21545,7 +21557,7 @@
         <v>42</v>
       </c>
       <c r="AE81" s="40" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="AF81" s="40">
         <v>40</v>
@@ -57880,7 +57892,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BJ84"/>
+  <dimension ref="A1:BK87"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -57911,36 +57923,37 @@
     <col min="30" max="30" width="9.36328125" customWidth="1"/>
     <col min="31" max="31" width="13.81640625" customWidth="1"/>
     <col min="32" max="32" width="7.1796875" customWidth="1"/>
-    <col min="33" max="33" width="11.54296875" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" customWidth="1"/>
-    <col min="35" max="35" width="9.6328125" customWidth="1"/>
-    <col min="36" max="36" width="8.08984375" customWidth="1"/>
-    <col min="37" max="37" width="7.26953125" customWidth="1"/>
-    <col min="38" max="38" width="10.90625" customWidth="1"/>
-    <col min="39" max="39" width="11.36328125" customWidth="1"/>
-    <col min="40" max="40" width="12" customWidth="1"/>
-    <col min="41" max="41" width="7.1796875" customWidth="1"/>
-    <col min="42" max="42" width="9.54296875" customWidth="1"/>
-    <col min="43" max="43" width="9.36328125" customWidth="1"/>
-    <col min="44" max="44" width="7.90625" customWidth="1"/>
-    <col min="45" max="45" width="13.6328125" customWidth="1"/>
-    <col min="46" max="46" width="6.453125" customWidth="1"/>
-    <col min="47" max="47" width="6.54296875" customWidth="1"/>
-    <col min="48" max="48" width="5.90625" customWidth="1"/>
-    <col min="49" max="49" width="19.08984375" customWidth="1"/>
-    <col min="50" max="50" width="7.81640625" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="12.7265625" customWidth="1"/>
-    <col min="54" max="55" width="7.08984375" customWidth="1"/>
-    <col min="57" max="57" width="11.08984375" customWidth="1"/>
-    <col min="58" max="58" width="10" customWidth="1"/>
-    <col min="59" max="59" width="11.54296875" customWidth="1"/>
-    <col min="60" max="60" width="13.26953125" customWidth="1"/>
-    <col min="61" max="61" width="26.26953125" customWidth="1"/>
-    <col min="62" max="62" width="10" customWidth="1"/>
+    <col min="33" max="33" width="13.08984375" customWidth="1"/>
+    <col min="34" max="34" width="11.54296875" customWidth="1"/>
+    <col min="35" max="35" width="13.81640625" customWidth="1"/>
+    <col min="36" max="36" width="9.6328125" customWidth="1"/>
+    <col min="37" max="37" width="8.08984375" customWidth="1"/>
+    <col min="38" max="38" width="7.26953125" customWidth="1"/>
+    <col min="39" max="39" width="10.90625" customWidth="1"/>
+    <col min="40" max="40" width="11.36328125" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="7.1796875" customWidth="1"/>
+    <col min="43" max="43" width="9.54296875" customWidth="1"/>
+    <col min="44" max="44" width="9.36328125" customWidth="1"/>
+    <col min="45" max="45" width="7.90625" customWidth="1"/>
+    <col min="46" max="46" width="13.6328125" customWidth="1"/>
+    <col min="47" max="47" width="6.453125" customWidth="1"/>
+    <col min="48" max="48" width="6.54296875" customWidth="1"/>
+    <col min="49" max="49" width="5.90625" customWidth="1"/>
+    <col min="50" max="50" width="19.08984375" customWidth="1"/>
+    <col min="51" max="51" width="7.81640625" customWidth="1"/>
+    <col min="53" max="53" width="7" customWidth="1"/>
+    <col min="54" max="54" width="12.7265625" customWidth="1"/>
+    <col min="55" max="56" width="7.08984375" customWidth="1"/>
+    <col min="58" max="58" width="11.08984375" customWidth="1"/>
+    <col min="59" max="59" width="10" customWidth="1"/>
+    <col min="60" max="60" width="11.54296875" customWidth="1"/>
+    <col min="61" max="61" width="13.26953125" customWidth="1"/>
+    <col min="62" max="62" width="26.26953125" customWidth="1"/>
+    <col min="63" max="63" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="13">
+    <row r="1" spans="1:63" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -58038,95 +58051,98 @@
         <v>1360</v>
       </c>
       <c r="AG1" s="43" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AH1" s="43" t="s">
         <v>1495</v>
       </c>
-      <c r="AH1" s="43" t="s">
+      <c r="AI1" s="43" t="s">
         <v>1362</v>
       </c>
-      <c r="AI1" s="43" t="s">
+      <c r="AJ1" s="43" t="s">
         <v>1471</v>
       </c>
-      <c r="AJ1" s="43" t="s">
+      <c r="AK1" s="43" t="s">
         <v>1472</v>
       </c>
-      <c r="AK1" s="43" t="s">
+      <c r="AL1" s="43" t="s">
         <v>1473</v>
       </c>
-      <c r="AL1" s="43" t="s">
+      <c r="AM1" s="43" t="s">
         <v>1476</v>
       </c>
-      <c r="AM1" s="43" t="s">
+      <c r="AN1" s="43" t="s">
         <v>1503</v>
       </c>
-      <c r="AN1" s="43" t="s">
+      <c r="AO1" s="43" t="s">
         <v>1488</v>
       </c>
-      <c r="AO1" s="43" t="s">
+      <c r="AP1" s="43" t="s">
         <v>1594</v>
       </c>
-      <c r="AP1" s="43" t="s">
+      <c r="AQ1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="AQ1" s="43" t="s">
+      <c r="AR1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="AR1" s="43" t="s">
+      <c r="AS1" s="43" t="s">
         <v>1376</v>
       </c>
-      <c r="AS1" s="43" t="s">
+      <c r="AT1" s="43" t="s">
         <v>1480</v>
       </c>
-      <c r="AT1" s="43" t="s">
+      <c r="AU1" s="43" t="s">
         <v>1612</v>
       </c>
-      <c r="AU1" s="43" t="s">
+      <c r="AV1" s="43" t="s">
         <v>1553</v>
       </c>
-      <c r="AV1" s="43" t="s">
+      <c r="AW1" s="43" t="s">
         <v>1482</v>
       </c>
-      <c r="AW1" s="43" t="s">
+      <c r="AX1" s="43" t="s">
         <v>1610</v>
       </c>
-      <c r="AX1" s="43" t="s">
+      <c r="AY1" s="43" t="s">
         <v>1618</v>
       </c>
-      <c r="AY1" s="43" t="s">
+      <c r="AZ1" s="43" t="s">
         <v>1622</v>
       </c>
-      <c r="AZ1" s="43" t="s">
+      <c r="BA1" s="43" t="s">
         <v>1623</v>
       </c>
-      <c r="BA1" s="43" t="s">
+      <c r="BB1" s="43" t="s">
         <v>1685</v>
       </c>
-      <c r="BB1" s="43" t="s">
+      <c r="BC1" s="43" t="s">
         <v>1694</v>
       </c>
-      <c r="BC1" s="43" t="s">
+      <c r="BD1" s="43" t="s">
         <v>1695</v>
       </c>
-      <c r="BD1" s="43" t="s">
+      <c r="BE1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="BE1" s="43" t="s">
+      <c r="BF1" s="43" t="s">
         <v>1759</v>
       </c>
-      <c r="BF1" s="43" t="s">
+      <c r="BG1" s="43" t="s">
         <v>1795</v>
       </c>
-      <c r="BG1" s="43" t="s">
+      <c r="BH1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="BH1" s="43" t="s">
+      <c r="BI1" s="43" t="s">
         <v>1892</v>
       </c>
-      <c r="BI1" s="43" t="s">
+      <c r="BJ1" s="43" t="s">
         <v>1899</v>
       </c>
-      <c r="BJ1" s="43"/>
-    </row>
-    <row r="2" spans="1:62">
+      <c r="BK1" s="43"/>
+    </row>
+    <row r="2" spans="1:63">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
@@ -58226,56 +58242,56 @@
       <c r="AG2" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="44" t="s">
+      <c r="AH2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI2" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI2" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ2" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="44" t="s">
+      <c r="AK2" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM2" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP2">
+      <c r="AN2" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP2" s="44">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>36</v>
       </c>
       <c r="AW2">
         <v>0</v>
       </c>
-      <c r="AX2" t="s">
-        <v>36</v>
+      <c r="AX2">
+        <v>0</v>
       </c>
       <c r="AY2" t="s">
         <v>36</v>
@@ -58283,8 +58299,8 @@
       <c r="AZ2" t="s">
         <v>36</v>
       </c>
-      <c r="BA2">
-        <v>0</v>
+      <c r="BA2" t="s">
+        <v>36</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -58295,23 +58311,26 @@
       <c r="BD2">
         <v>0</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="s">
         <v>1760</v>
       </c>
-      <c r="BF2" t="s">
-        <v>36</v>
-      </c>
       <c r="BG2" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH2" t="s">
         <v>1657</v>
       </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:62">
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63">
       <c r="A3" s="44" t="s">
         <v>1900</v>
       </c>
@@ -58411,56 +58430,56 @@
       <c r="AG3" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="44" t="s">
+      <c r="AH3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI3" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI3" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ3" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="44" t="s">
+      <c r="AK3" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM3" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP3">
+      <c r="AN3" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP3" s="44">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>36</v>
       </c>
       <c r="AW3">
         <v>0</v>
       </c>
-      <c r="AX3" t="s">
-        <v>36</v>
+      <c r="AX3">
+        <v>0</v>
       </c>
       <c r="AY3" t="s">
         <v>36</v>
@@ -58468,8 +58487,8 @@
       <c r="AZ3" t="s">
         <v>36</v>
       </c>
-      <c r="BA3">
-        <v>0</v>
+      <c r="BA3" t="s">
+        <v>36</v>
       </c>
       <c r="BB3">
         <v>0</v>
@@ -58480,23 +58499,26 @@
       <c r="BD3">
         <v>0</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="s">
         <v>1760</v>
       </c>
-      <c r="BF3" t="s">
-        <v>36</v>
-      </c>
       <c r="BG3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH3" t="s">
         <v>1657</v>
       </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:62">
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63">
       <c r="A4" s="44" t="s">
         <v>42</v>
       </c>
@@ -58596,56 +58618,56 @@
       <c r="AG4" t="s">
         <v>36</v>
       </c>
-      <c r="AH4" s="44" t="s">
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI4" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ4" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="44" t="s">
+      <c r="AK4" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM4" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN4" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP4">
+      <c r="AN4" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP4" s="44">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>36</v>
       </c>
       <c r="AW4">
         <v>0</v>
       </c>
-      <c r="AX4" t="s">
-        <v>36</v>
+      <c r="AX4">
+        <v>0</v>
       </c>
       <c r="AY4" t="s">
         <v>36</v>
@@ -58653,8 +58675,8 @@
       <c r="AZ4" t="s">
         <v>36</v>
       </c>
-      <c r="BA4">
-        <v>0</v>
+      <c r="BA4" t="s">
+        <v>36</v>
       </c>
       <c r="BB4">
         <v>0</v>
@@ -58665,23 +58687,26 @@
       <c r="BD4">
         <v>0</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="s">
         <v>1761</v>
       </c>
-      <c r="BF4" t="s">
-        <v>36</v>
-      </c>
       <c r="BG4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH4" t="s">
         <v>1658</v>
       </c>
-      <c r="BH4">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:62">
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63">
       <c r="A5" s="44" t="s">
         <v>1371</v>
       </c>
@@ -58781,56 +58806,56 @@
       <c r="AG5" t="s">
         <v>36</v>
       </c>
-      <c r="AH5" s="44" t="s">
+      <c r="AH5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI5" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI5" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ5" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="44" t="s">
+      <c r="AK5" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM5" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP5">
+      <c r="AN5" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP5" s="44">
         <v>0</v>
       </c>
       <c r="AQ5">
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>36</v>
       </c>
       <c r="AW5">
         <v>0</v>
       </c>
-      <c r="AX5" t="s">
-        <v>36</v>
+      <c r="AX5">
+        <v>0</v>
       </c>
       <c r="AY5" t="s">
         <v>36</v>
@@ -58838,8 +58863,8 @@
       <c r="AZ5" t="s">
         <v>36</v>
       </c>
-      <c r="BA5">
-        <v>0</v>
+      <c r="BA5" t="s">
+        <v>36</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -58848,25 +58873,28 @@
         <v>0</v>
       </c>
       <c r="BD5">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>1</v>
+      </c>
+      <c r="BF5" t="s">
         <v>1762</v>
       </c>
-      <c r="BF5" t="s">
-        <v>36</v>
-      </c>
       <c r="BG5" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH5" t="s">
         <v>1659</v>
       </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:62">
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:63">
       <c r="A6" s="44" t="s">
         <v>1372</v>
       </c>
@@ -58966,56 +58994,56 @@
       <c r="AG6" t="s">
         <v>36</v>
       </c>
-      <c r="AH6" s="44" t="s">
+      <c r="AH6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI6" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI6" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ6" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AK6" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM6" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP6">
+      <c r="AN6" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP6" s="44">
         <v>0</v>
       </c>
       <c r="AQ6">
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>36</v>
       </c>
       <c r="AW6">
         <v>0</v>
       </c>
-      <c r="AX6" t="s">
-        <v>36</v>
+      <c r="AX6">
+        <v>0</v>
       </c>
       <c r="AY6" t="s">
         <v>36</v>
@@ -59023,8 +59051,8 @@
       <c r="AZ6" t="s">
         <v>36</v>
       </c>
-      <c r="BA6">
-        <v>0</v>
+      <c r="BA6" t="s">
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -59035,23 +59063,26 @@
       <c r="BD6">
         <v>0</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="s">
         <v>37</v>
       </c>
-      <c r="BF6" t="s">
-        <v>36</v>
-      </c>
       <c r="BG6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH6" t="s">
         <v>1660</v>
       </c>
-      <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:62">
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63">
       <c r="A7" s="44" t="s">
         <v>1890</v>
       </c>
@@ -59151,56 +59182,56 @@
       <c r="AG7" t="s">
         <v>36</v>
       </c>
-      <c r="AH7" s="44" t="s">
+      <c r="AH7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI7" s="44" t="s">
         <v>1479</v>
       </c>
-      <c r="AI7" s="44" t="s">
+      <c r="AJ7" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AJ7" s="44" t="s">
+      <c r="AK7" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="44" t="s">
+      <c r="AL7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM7" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP7">
+      <c r="AN7" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP7" s="44">
         <v>0</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR7">
         <v>1</v>
       </c>
-      <c r="AS7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>36</v>
       </c>
       <c r="AW7">
         <v>0</v>
       </c>
-      <c r="AX7" t="s">
-        <v>36</v>
+      <c r="AX7">
+        <v>0</v>
       </c>
       <c r="AY7" t="s">
         <v>36</v>
@@ -59208,8 +59239,8 @@
       <c r="AZ7" t="s">
         <v>36</v>
       </c>
-      <c r="BA7">
-        <v>0</v>
+      <c r="BA7" t="s">
+        <v>36</v>
       </c>
       <c r="BB7">
         <v>0</v>
@@ -59220,23 +59251,26 @@
       <c r="BD7">
         <v>0</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="s">
         <v>1765</v>
       </c>
-      <c r="BF7" t="s">
-        <v>36</v>
-      </c>
       <c r="BG7" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH7" t="s">
         <v>1660</v>
       </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:62">
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63">
       <c r="A8" s="44" t="s">
         <v>1469</v>
       </c>
@@ -59336,56 +59370,56 @@
       <c r="AG8" t="s">
         <v>36</v>
       </c>
-      <c r="AH8" s="44" t="s">
+      <c r="AH8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI8" s="44" t="s">
         <v>1479</v>
       </c>
-      <c r="AI8" s="44" t="s">
+      <c r="AJ8" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AJ8" s="44" t="s">
+      <c r="AK8" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="44" t="s">
+      <c r="AL8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM8" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN8" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP8">
+      <c r="AN8" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP8" s="44">
         <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8">
         <v>1</v>
       </c>
-      <c r="AS8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>36</v>
       </c>
       <c r="AW8">
         <v>0</v>
       </c>
-      <c r="AX8" t="s">
-        <v>36</v>
+      <c r="AX8">
+        <v>0</v>
       </c>
       <c r="AY8" t="s">
         <v>36</v>
@@ -59393,8 +59427,8 @@
       <c r="AZ8" t="s">
         <v>36</v>
       </c>
-      <c r="BA8">
-        <v>0</v>
+      <c r="BA8" t="s">
+        <v>36</v>
       </c>
       <c r="BB8">
         <v>0</v>
@@ -59405,23 +59439,26 @@
       <c r="BD8">
         <v>0</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="s">
         <v>1765</v>
       </c>
-      <c r="BF8" t="s">
-        <v>36</v>
-      </c>
       <c r="BG8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH8" t="s">
         <v>1660</v>
       </c>
-      <c r="BH8">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:62">
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63">
       <c r="A9" s="44" t="s">
         <v>1483</v>
       </c>
@@ -59521,56 +59558,56 @@
       <c r="AG9" t="s">
         <v>36</v>
       </c>
-      <c r="AH9" s="44" t="s">
+      <c r="AH9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI9" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI9" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ9" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="44" t="s">
+      <c r="AK9" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM9" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP9">
+      <c r="AN9" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP9" s="44">
         <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
         <v>60</v>
       </c>
-      <c r="AS9" t="s">
+      <c r="AT9" t="s">
         <v>1481</v>
       </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>36</v>
       </c>
       <c r="AW9">
         <v>0</v>
       </c>
-      <c r="AX9" t="s">
-        <v>36</v>
+      <c r="AX9">
+        <v>0</v>
       </c>
       <c r="AY9" t="s">
         <v>36</v>
@@ -59578,8 +59615,8 @@
       <c r="AZ9" t="s">
         <v>36</v>
       </c>
-      <c r="BA9">
-        <v>0</v>
+      <c r="BA9" t="s">
+        <v>36</v>
       </c>
       <c r="BB9">
         <v>0</v>
@@ -59590,23 +59627,26 @@
       <c r="BD9">
         <v>0</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="s">
         <v>1763</v>
       </c>
-      <c r="BF9" t="s">
-        <v>36</v>
-      </c>
       <c r="BG9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH9" t="s">
         <v>1661</v>
       </c>
-      <c r="BH9">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:62">
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:63">
       <c r="A10" s="44" t="s">
         <v>1430</v>
       </c>
@@ -59706,56 +59746,56 @@
       <c r="AG10" t="s">
         <v>36</v>
       </c>
-      <c r="AH10" s="44" t="s">
+      <c r="AH10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI10" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI10" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ10" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="44" t="s">
+      <c r="AK10" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM10" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP10">
+      <c r="AN10" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP10" s="44">
         <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AS10">
         <v>60</v>
       </c>
-      <c r="AS10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV10">
-        <v>1</v>
+      <c r="AT10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>36</v>
       </c>
       <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
       </c>
       <c r="AY10" t="s">
         <v>36</v>
@@ -59763,8 +59803,8 @@
       <c r="AZ10" t="s">
         <v>36</v>
       </c>
-      <c r="BA10">
-        <v>0</v>
+      <c r="BA10" t="s">
+        <v>36</v>
       </c>
       <c r="BB10">
         <v>0</v>
@@ -59775,23 +59815,26 @@
       <c r="BD10">
         <v>0</v>
       </c>
-      <c r="BE10" t="s">
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="s">
         <v>1764</v>
       </c>
-      <c r="BF10" t="s">
-        <v>36</v>
-      </c>
       <c r="BG10" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH10" t="s">
         <v>1662</v>
       </c>
-      <c r="BH10">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:62">
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:63">
       <c r="A11" s="44" t="s">
         <v>1433</v>
       </c>
@@ -59891,56 +59934,56 @@
       <c r="AG11" t="s">
         <v>36</v>
       </c>
-      <c r="AH11" s="44" t="s">
+      <c r="AH11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI11" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI11" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ11" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="44" t="s">
+      <c r="AK11" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM11" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN11" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP11">
+      <c r="AN11" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP11" s="44">
         <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
         <v>60</v>
       </c>
-      <c r="AS11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV11">
-        <v>1</v>
+      <c r="AT11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>36</v>
       </c>
       <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
       </c>
       <c r="AY11" t="s">
         <v>36</v>
@@ -59948,8 +59991,8 @@
       <c r="AZ11" t="s">
         <v>36</v>
       </c>
-      <c r="BA11">
-        <v>0</v>
+      <c r="BA11" t="s">
+        <v>36</v>
       </c>
       <c r="BB11">
         <v>0</v>
@@ -59960,23 +60003,26 @@
       <c r="BD11">
         <v>0</v>
       </c>
-      <c r="BE11" t="s">
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="s">
         <v>1760</v>
       </c>
-      <c r="BF11" t="s">
-        <v>36</v>
-      </c>
       <c r="BG11" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH11" t="s">
         <v>1663</v>
       </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:62">
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:63">
       <c r="A12" s="44" t="s">
         <v>1447</v>
       </c>
@@ -60076,56 +60122,56 @@
       <c r="AG12" t="s">
         <v>36</v>
       </c>
-      <c r="AH12" s="44" t="s">
+      <c r="AH12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI12" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI12" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ12" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="44" t="s">
+      <c r="AK12" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM12" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN12" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP12">
+      <c r="AN12" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP12" s="44">
         <v>0</v>
       </c>
       <c r="AQ12">
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>1</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>36</v>
       </c>
       <c r="AW12">
         <v>0</v>
       </c>
-      <c r="AX12" t="s">
-        <v>36</v>
+      <c r="AX12">
+        <v>0</v>
       </c>
       <c r="AY12" t="s">
         <v>36</v>
@@ -60133,8 +60179,8 @@
       <c r="AZ12" t="s">
         <v>36</v>
       </c>
-      <c r="BA12">
-        <v>0</v>
+      <c r="BA12" t="s">
+        <v>36</v>
       </c>
       <c r="BB12">
         <v>0</v>
@@ -60145,23 +60191,26 @@
       <c r="BD12">
         <v>0</v>
       </c>
-      <c r="BE12" t="s">
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="s">
         <v>1761</v>
       </c>
-      <c r="BF12" t="s">
-        <v>36</v>
-      </c>
       <c r="BG12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH12" t="s">
         <v>1664</v>
       </c>
-      <c r="BH12">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:62">
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:63">
       <c r="A13" s="44" t="s">
         <v>1524</v>
       </c>
@@ -60261,56 +60310,56 @@
       <c r="AG13" t="s">
         <v>36</v>
       </c>
-      <c r="AH13" s="44" t="s">
+      <c r="AH13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI13" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI13" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ13" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="44" t="s">
+      <c r="AK13" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM13" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN13" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP13">
+      <c r="AN13" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP13" s="44">
         <v>0</v>
       </c>
       <c r="AQ13">
         <v>0</v>
       </c>
       <c r="AR13">
-        <v>1</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>36</v>
       </c>
       <c r="AW13">
         <v>0</v>
       </c>
-      <c r="AX13" t="s">
-        <v>36</v>
+      <c r="AX13">
+        <v>0</v>
       </c>
       <c r="AY13" t="s">
         <v>36</v>
@@ -60318,8 +60367,8 @@
       <c r="AZ13" t="s">
         <v>36</v>
       </c>
-      <c r="BA13">
-        <v>0</v>
+      <c r="BA13" t="s">
+        <v>36</v>
       </c>
       <c r="BB13">
         <v>0</v>
@@ -60330,23 +60379,26 @@
       <c r="BD13">
         <v>0</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="s">
         <v>1762</v>
       </c>
-      <c r="BF13" t="s">
-        <v>36</v>
-      </c>
       <c r="BG13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH13" t="s">
         <v>1665</v>
       </c>
-      <c r="BH13">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:62">
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:63">
       <c r="A14" s="44" t="s">
         <v>1448</v>
       </c>
@@ -60446,56 +60498,56 @@
       <c r="AG14" t="s">
         <v>36</v>
       </c>
-      <c r="AH14" s="44" t="s">
+      <c r="AH14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI14" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI14" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ14" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="44" t="s">
+      <c r="AK14" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM14" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN14" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP14">
+      <c r="AN14" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP14" s="44">
         <v>0</v>
       </c>
       <c r="AQ14">
         <v>0</v>
       </c>
       <c r="AR14">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>36</v>
       </c>
       <c r="AW14">
         <v>0</v>
       </c>
-      <c r="AX14" t="s">
-        <v>36</v>
+      <c r="AX14">
+        <v>0</v>
       </c>
       <c r="AY14" t="s">
         <v>36</v>
@@ -60503,8 +60555,8 @@
       <c r="AZ14" t="s">
         <v>36</v>
       </c>
-      <c r="BA14">
-        <v>0</v>
+      <c r="BA14" t="s">
+        <v>36</v>
       </c>
       <c r="BB14">
         <v>0</v>
@@ -60515,23 +60567,26 @@
       <c r="BD14">
         <v>0</v>
       </c>
-      <c r="BE14" t="s">
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="s">
         <v>37</v>
       </c>
-      <c r="BF14" t="s">
-        <v>36</v>
-      </c>
       <c r="BG14" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH14" t="s">
         <v>1666</v>
       </c>
-      <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:62">
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:63">
       <c r="A15" s="44" t="s">
         <v>1449</v>
       </c>
@@ -60631,56 +60686,56 @@
       <c r="AG15" t="s">
         <v>36</v>
       </c>
-      <c r="AH15" s="44" t="s">
+      <c r="AH15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI15" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI15" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ15" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="44" t="s">
+      <c r="AK15" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM15" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP15">
+      <c r="AN15" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP15" s="44">
         <v>0</v>
       </c>
       <c r="AQ15">
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>1</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>1</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>36</v>
       </c>
       <c r="AW15">
         <v>0</v>
       </c>
-      <c r="AX15" t="s">
-        <v>36</v>
+      <c r="AX15">
+        <v>0</v>
       </c>
       <c r="AY15" t="s">
         <v>36</v>
@@ -60688,8 +60743,8 @@
       <c r="AZ15" t="s">
         <v>36</v>
       </c>
-      <c r="BA15">
-        <v>0</v>
+      <c r="BA15" t="s">
+        <v>36</v>
       </c>
       <c r="BB15">
         <v>0</v>
@@ -60700,23 +60755,26 @@
       <c r="BD15">
         <v>0</v>
       </c>
-      <c r="BE15" t="s">
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="s">
         <v>1765</v>
       </c>
-      <c r="BF15" t="s">
-        <v>36</v>
-      </c>
       <c r="BG15" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH15" t="s">
         <v>1667</v>
       </c>
-      <c r="BH15">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:62">
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:63">
       <c r="A16" s="44" t="s">
         <v>1485</v>
       </c>
@@ -60814,58 +60872,58 @@
         <v>10</v>
       </c>
       <c r="AG16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH16" t="s">
         <v>1494</v>
       </c>
-      <c r="AH16" s="44" t="s">
+      <c r="AI16" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI16" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ16" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="44" t="s">
+      <c r="AK16" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM16" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP16">
+      <c r="AN16" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP16" s="44">
         <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR16">
         <v>1</v>
       </c>
-      <c r="AS16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
+      <c r="AS16">
+        <v>1</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>36</v>
       </c>
       <c r="AW16">
         <v>0</v>
       </c>
-      <c r="AX16" t="s">
-        <v>36</v>
+      <c r="AX16">
+        <v>0</v>
       </c>
       <c r="AY16" t="s">
         <v>36</v>
@@ -60873,35 +60931,38 @@
       <c r="AZ16" t="s">
         <v>36</v>
       </c>
-      <c r="BA16">
+      <c r="BA16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB16">
         <v>50</v>
       </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
       <c r="BC16">
         <v>0</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
-      <c r="BE16" t="s">
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="s">
         <v>1763</v>
       </c>
-      <c r="BF16" t="s">
-        <v>36</v>
-      </c>
       <c r="BG16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH16" t="s">
         <v>1668</v>
       </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:61">
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:62">
       <c r="A17" s="44" t="s">
         <v>1489</v>
       </c>
@@ -61001,56 +61062,56 @@
       <c r="AG17" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="44" t="s">
+      <c r="AH17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI17" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI17" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ17" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="44" t="s">
+      <c r="AK17" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM17" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN17" s="44" t="s">
+      <c r="AN17" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AO17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP17">
+      <c r="AP17" s="44">
         <v>0</v>
       </c>
       <c r="AQ17">
         <v>0</v>
       </c>
       <c r="AR17">
-        <v>1</v>
-      </c>
-      <c r="AS17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>36</v>
       </c>
       <c r="AW17">
         <v>0</v>
       </c>
-      <c r="AX17" t="s">
-        <v>36</v>
+      <c r="AX17">
+        <v>0</v>
       </c>
       <c r="AY17" t="s">
         <v>36</v>
@@ -61058,8 +61119,8 @@
       <c r="AZ17" t="s">
         <v>36</v>
       </c>
-      <c r="BA17">
-        <v>0</v>
+      <c r="BA17" t="s">
+        <v>36</v>
       </c>
       <c r="BB17">
         <v>0</v>
@@ -61070,23 +61131,26 @@
       <c r="BD17">
         <v>0</v>
       </c>
-      <c r="BE17" t="s">
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="s">
         <v>1764</v>
       </c>
-      <c r="BF17" t="s">
-        <v>36</v>
-      </c>
       <c r="BG17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH17" t="s">
         <v>1669</v>
       </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:61">
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:62">
       <c r="A18" s="44" t="s">
         <v>1490</v>
       </c>
@@ -61186,56 +61250,56 @@
       <c r="AG18" t="s">
         <v>36</v>
       </c>
-      <c r="AH18" s="44" t="s">
+      <c r="AH18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI18" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI18" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ18" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK18" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="44" t="s">
+      <c r="AK18" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL18" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM18" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN18" s="44" t="s">
+      <c r="AN18" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AO18" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP18">
+      <c r="AP18" s="44">
         <v>0</v>
       </c>
       <c r="AQ18">
         <v>0</v>
       </c>
       <c r="AR18">
-        <v>1</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>36</v>
       </c>
       <c r="AW18">
         <v>0</v>
       </c>
-      <c r="AX18" t="s">
-        <v>36</v>
+      <c r="AX18">
+        <v>0</v>
       </c>
       <c r="AY18" t="s">
         <v>36</v>
@@ -61243,8 +61307,8 @@
       <c r="AZ18" t="s">
         <v>36</v>
       </c>
-      <c r="BA18">
-        <v>0</v>
+      <c r="BA18" t="s">
+        <v>36</v>
       </c>
       <c r="BB18">
         <v>0</v>
@@ -61255,23 +61319,26 @@
       <c r="BD18">
         <v>0</v>
       </c>
-      <c r="BE18" t="s">
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="s">
         <v>1760</v>
       </c>
-      <c r="BF18" t="s">
-        <v>36</v>
-      </c>
       <c r="BG18" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH18" t="s">
         <v>1670</v>
       </c>
-      <c r="BH18">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:61">
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:62">
       <c r="A19" s="44" t="s">
         <v>1494</v>
       </c>
@@ -61371,56 +61438,56 @@
       <c r="AG19" t="s">
         <v>36</v>
       </c>
-      <c r="AH19" s="44" t="s">
+      <c r="AH19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI19" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI19" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ19" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK19" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="44" t="s">
+      <c r="AK19" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM19" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN19" s="44" t="s">
+      <c r="AN19" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AO19" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP19">
+      <c r="AP19" s="44">
         <v>0</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR19">
         <v>1</v>
       </c>
-      <c r="AS19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
+      <c r="AS19">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>36</v>
       </c>
       <c r="AW19">
-        <v>1</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
       </c>
       <c r="AY19" t="s">
         <v>36</v>
@@ -61428,8 +61495,8 @@
       <c r="AZ19" t="s">
         <v>36</v>
       </c>
-      <c r="BA19">
-        <v>0</v>
+      <c r="BA19" t="s">
+        <v>36</v>
       </c>
       <c r="BB19">
         <v>0</v>
@@ -61440,23 +61507,26 @@
       <c r="BD19">
         <v>0</v>
       </c>
-      <c r="BE19" t="s">
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="s">
         <v>1761</v>
       </c>
-      <c r="BF19" t="s">
-        <v>36</v>
-      </c>
       <c r="BG19" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH19" t="s">
         <v>1671</v>
       </c>
-      <c r="BH19">
-        <v>0</v>
-      </c>
-      <c r="BI19" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:61">
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:62">
       <c r="A20" s="44" t="s">
         <v>1501</v>
       </c>
@@ -61556,56 +61626,56 @@
       <c r="AG20" t="s">
         <v>36</v>
       </c>
-      <c r="AH20" s="44" t="s">
+      <c r="AH20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI20" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI20" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ20" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="44" t="s">
+      <c r="AK20" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM20" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN20" s="44" t="s">
+      <c r="AN20" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="AO20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP20">
+      <c r="AP20" s="44">
         <v>0</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR20">
         <v>1</v>
       </c>
-      <c r="AS20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
+      <c r="AS20">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>36</v>
       </c>
       <c r="AW20">
         <v>0</v>
       </c>
-      <c r="AX20" t="s">
-        <v>36</v>
+      <c r="AX20">
+        <v>0</v>
       </c>
       <c r="AY20" t="s">
         <v>36</v>
@@ -61613,8 +61683,8 @@
       <c r="AZ20" t="s">
         <v>36</v>
       </c>
-      <c r="BA20">
-        <v>0</v>
+      <c r="BA20" t="s">
+        <v>36</v>
       </c>
       <c r="BB20">
         <v>0</v>
@@ -61625,23 +61695,26 @@
       <c r="BD20">
         <v>0</v>
       </c>
-      <c r="BE20" t="s">
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="s">
         <v>1762</v>
       </c>
-      <c r="BF20" t="s">
-        <v>36</v>
-      </c>
       <c r="BG20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH20" t="s">
         <v>1672</v>
       </c>
-      <c r="BH20">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:61">
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:62">
       <c r="A21" s="44" t="s">
         <v>1502</v>
       </c>
@@ -61739,58 +61812,58 @@
         <v>10</v>
       </c>
       <c r="AG21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH21" t="s">
         <v>1501</v>
       </c>
-      <c r="AH21" s="44" t="s">
+      <c r="AI21" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI21" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ21" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK21" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="44" t="s">
+      <c r="AK21" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM21" s="44">
+      <c r="AN21" s="44">
         <v>100</v>
       </c>
-      <c r="AN21" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO21" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP21">
+      <c r="AO21" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP21" s="44">
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR21">
+        <v>1</v>
+      </c>
+      <c r="AS21">
         <v>5</v>
       </c>
-      <c r="AS21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
+      <c r="AT21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>36</v>
       </c>
       <c r="AW21">
         <v>0</v>
       </c>
-      <c r="AX21" t="s">
-        <v>36</v>
+      <c r="AX21">
+        <v>0</v>
       </c>
       <c r="AY21" t="s">
         <v>36</v>
@@ -61798,8 +61871,8 @@
       <c r="AZ21" t="s">
         <v>36</v>
       </c>
-      <c r="BA21">
-        <v>0</v>
+      <c r="BA21" t="s">
+        <v>36</v>
       </c>
       <c r="BB21">
         <v>0</v>
@@ -61810,23 +61883,26 @@
       <c r="BD21">
         <v>0</v>
       </c>
-      <c r="BE21" t="s">
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="s">
         <v>37</v>
       </c>
-      <c r="BF21" t="s">
-        <v>36</v>
-      </c>
       <c r="BG21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH21" t="s">
         <v>1673</v>
       </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:61">
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:62">
       <c r="A22" s="44" t="s">
         <v>1431</v>
       </c>
@@ -61926,56 +62002,56 @@
       <c r="AG22" t="s">
         <v>36</v>
       </c>
-      <c r="AH22" s="44" t="s">
+      <c r="AH22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI22" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI22" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ22" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK22" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="44" t="s">
+      <c r="AK22" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL22" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM22" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN22" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO22" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP22">
+      <c r="AN22" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP22" s="44">
         <v>0</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR22">
+        <v>1</v>
+      </c>
+      <c r="AS22">
         <v>60</v>
       </c>
-      <c r="AS22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV22">
-        <v>1</v>
+      <c r="AT22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>36</v>
       </c>
       <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
       </c>
       <c r="AY22" t="s">
         <v>36</v>
@@ -61983,8 +62059,8 @@
       <c r="AZ22" t="s">
         <v>36</v>
       </c>
-      <c r="BA22">
-        <v>0</v>
+      <c r="BA22" t="s">
+        <v>36</v>
       </c>
       <c r="BB22">
         <v>0</v>
@@ -61995,23 +62071,26 @@
       <c r="BD22">
         <v>0</v>
       </c>
-      <c r="BE22" t="s">
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="s">
         <v>1765</v>
       </c>
-      <c r="BF22" t="s">
-        <v>36</v>
-      </c>
       <c r="BG22" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH22" t="s">
         <v>1674</v>
       </c>
-      <c r="BH22">
-        <v>0</v>
-      </c>
-      <c r="BI22" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:61">
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:62">
       <c r="A23" s="44" t="s">
         <v>1551</v>
       </c>
@@ -62111,56 +62190,56 @@
       <c r="AG23" t="s">
         <v>36</v>
       </c>
-      <c r="AH23" s="44" t="s">
+      <c r="AH23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI23" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI23" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ23" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK23" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="44" t="s">
+      <c r="AK23" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL23" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM23" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN23" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO23" s="44">
-        <v>1</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
+      <c r="AN23" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP23" s="44">
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR23">
+        <v>1</v>
+      </c>
+      <c r="AS23">
         <v>60</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AT23" t="s">
         <v>1552</v>
       </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="s">
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="s">
         <v>1554</v>
       </c>
-      <c r="AV23">
-        <v>1</v>
-      </c>
       <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
       </c>
       <c r="AY23" t="s">
         <v>36</v>
@@ -62168,8 +62247,8 @@
       <c r="AZ23" t="s">
         <v>36</v>
       </c>
-      <c r="BA23">
-        <v>0</v>
+      <c r="BA23" t="s">
+        <v>36</v>
       </c>
       <c r="BB23">
         <v>0</v>
@@ -62180,23 +62259,26 @@
       <c r="BD23">
         <v>0</v>
       </c>
-      <c r="BE23" t="s">
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="s">
         <v>1763</v>
       </c>
-      <c r="BF23" t="s">
-        <v>36</v>
-      </c>
       <c r="BG23" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH23" t="s">
         <v>1658</v>
       </c>
-      <c r="BH23">
-        <v>0</v>
-      </c>
-      <c r="BI23" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:61">
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:62">
       <c r="A24" s="44" t="s">
         <v>1587</v>
       </c>
@@ -62296,56 +62378,56 @@
       <c r="AG24" t="s">
         <v>36</v>
       </c>
-      <c r="AH24" s="44" t="s">
+      <c r="AH24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI24" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI24" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ24" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK24" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="44" t="s">
+      <c r="AK24" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL24" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM24" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN24" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO24" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP24">
+      <c r="AN24" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO24" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP24" s="44">
         <v>0</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR24">
         <v>1</v>
       </c>
-      <c r="AS24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>36</v>
       </c>
       <c r="AW24">
         <v>0</v>
       </c>
-      <c r="AX24" t="s">
-        <v>36</v>
+      <c r="AX24">
+        <v>0</v>
       </c>
       <c r="AY24" t="s">
         <v>36</v>
@@ -62353,8 +62435,8 @@
       <c r="AZ24" t="s">
         <v>36</v>
       </c>
-      <c r="BA24">
-        <v>0</v>
+      <c r="BA24" t="s">
+        <v>36</v>
       </c>
       <c r="BB24">
         <v>0</v>
@@ -62365,23 +62447,26 @@
       <c r="BD24">
         <v>0</v>
       </c>
-      <c r="BE24" t="s">
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="s">
         <v>1764</v>
       </c>
-      <c r="BF24" t="s">
-        <v>36</v>
-      </c>
       <c r="BG24" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH24" t="s">
         <v>1658</v>
       </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:61">
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:62">
       <c r="A25" s="44" t="s">
         <v>935</v>
       </c>
@@ -62481,56 +62566,56 @@
       <c r="AG25" t="s">
         <v>36</v>
       </c>
-      <c r="AH25" s="44" t="s">
+      <c r="AH25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI25" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI25" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ25" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK25" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="44" t="s">
+      <c r="AK25" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL25" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM25" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN25" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO25" s="44">
-        <v>1</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
+      <c r="AN25" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP25" s="44">
+        <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR25">
         <v>1</v>
       </c>
-      <c r="AS25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
+      <c r="AS25">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>36</v>
       </c>
       <c r="AW25">
         <v>0</v>
       </c>
-      <c r="AX25" t="s">
-        <v>36</v>
+      <c r="AX25">
+        <v>0</v>
       </c>
       <c r="AY25" t="s">
         <v>36</v>
@@ -62538,8 +62623,8 @@
       <c r="AZ25" t="s">
         <v>36</v>
       </c>
-      <c r="BA25">
-        <v>0</v>
+      <c r="BA25" t="s">
+        <v>36</v>
       </c>
       <c r="BB25">
         <v>0</v>
@@ -62550,23 +62635,26 @@
       <c r="BD25">
         <v>0</v>
       </c>
-      <c r="BE25" t="s">
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="s">
         <v>1760</v>
       </c>
-      <c r="BF25" t="s">
-        <v>36</v>
-      </c>
       <c r="BG25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH25" t="s">
         <v>1658</v>
       </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:61">
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:62">
       <c r="A26" s="44" t="s">
         <v>1593</v>
       </c>
@@ -62666,56 +62754,56 @@
       <c r="AG26" t="s">
         <v>36</v>
       </c>
-      <c r="AH26" s="44" t="s">
+      <c r="AH26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI26" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI26" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ26" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK26" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="44" t="s">
+      <c r="AK26" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL26" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM26" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO26" s="44">
-        <v>1</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
+      <c r="AN26" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP26" s="44">
+        <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR26">
         <v>1</v>
       </c>
-      <c r="AS26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
+      <c r="AS26">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>36</v>
       </c>
       <c r="AW26">
         <v>0</v>
       </c>
-      <c r="AX26" t="s">
-        <v>36</v>
+      <c r="AX26">
+        <v>0</v>
       </c>
       <c r="AY26" t="s">
         <v>36</v>
@@ -62723,8 +62811,8 @@
       <c r="AZ26" t="s">
         <v>36</v>
       </c>
-      <c r="BA26">
-        <v>0</v>
+      <c r="BA26" t="s">
+        <v>36</v>
       </c>
       <c r="BB26">
         <v>0</v>
@@ -62735,23 +62823,26 @@
       <c r="BD26">
         <v>0</v>
       </c>
-      <c r="BE26" t="s">
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="s">
         <v>1761</v>
       </c>
-      <c r="BF26" t="s">
-        <v>36</v>
-      </c>
       <c r="BG26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH26" t="s">
         <v>1658</v>
       </c>
-      <c r="BH26">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:61">
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:62">
       <c r="A27" s="44" t="s">
         <v>1602</v>
       </c>
@@ -62851,56 +62942,56 @@
       <c r="AG27" t="s">
         <v>36</v>
       </c>
-      <c r="AH27" s="44" t="s">
+      <c r="AH27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI27" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI27" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ27" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK27" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="44" t="s">
+      <c r="AK27" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL27" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM27" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN27" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO27" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP27">
+      <c r="AN27" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP27" s="44">
         <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR27">
         <v>1</v>
       </c>
-      <c r="AS27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
+      <c r="AS27">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>36</v>
       </c>
       <c r="AW27">
         <v>0</v>
       </c>
-      <c r="AX27" t="s">
-        <v>36</v>
+      <c r="AX27">
+        <v>0</v>
       </c>
       <c r="AY27" t="s">
         <v>36</v>
@@ -62908,8 +62999,8 @@
       <c r="AZ27" t="s">
         <v>36</v>
       </c>
-      <c r="BA27">
-        <v>0</v>
+      <c r="BA27" t="s">
+        <v>36</v>
       </c>
       <c r="BB27">
         <v>0</v>
@@ -62920,23 +63011,26 @@
       <c r="BD27">
         <v>0</v>
       </c>
-      <c r="BE27" t="s">
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="s">
         <v>1762</v>
       </c>
-      <c r="BF27" t="s">
-        <v>36</v>
-      </c>
       <c r="BG27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH27" t="s">
         <v>1658</v>
       </c>
-      <c r="BH27">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:61">
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:62">
       <c r="A28" s="44" t="s">
         <v>1611</v>
       </c>
@@ -63036,56 +63130,56 @@
       <c r="AG28" t="s">
         <v>36</v>
       </c>
-      <c r="AH28" s="44" t="s">
+      <c r="AH28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI28" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI28" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ28" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK28" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="44" t="s">
+      <c r="AK28" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL28" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM28" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN28" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO28" s="44">
-        <v>1</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
+      <c r="AN28" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP28" s="44">
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR28">
+        <v>1</v>
+      </c>
+      <c r="AS28">
         <v>60</v>
       </c>
-      <c r="AS28" t="s">
+      <c r="AT28" t="s">
         <v>1552</v>
       </c>
-      <c r="AT28">
-        <v>1</v>
-      </c>
-      <c r="AU28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV28">
-        <v>1</v>
+      <c r="AU28">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>36</v>
       </c>
       <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
       </c>
       <c r="AY28" t="s">
         <v>36</v>
@@ -63093,8 +63187,8 @@
       <c r="AZ28" t="s">
         <v>36</v>
       </c>
-      <c r="BA28">
-        <v>0</v>
+      <c r="BA28" t="s">
+        <v>36</v>
       </c>
       <c r="BB28">
         <v>0</v>
@@ -63105,23 +63199,26 @@
       <c r="BD28">
         <v>0</v>
       </c>
-      <c r="BE28" t="s">
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="s">
         <v>37</v>
       </c>
-      <c r="BF28" t="s">
-        <v>36</v>
-      </c>
       <c r="BG28" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH28" t="s">
         <v>1559</v>
       </c>
-      <c r="BH28">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:61">
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:62">
       <c r="A29" s="44" t="s">
         <v>1615</v>
       </c>
@@ -63221,56 +63318,56 @@
       <c r="AG29" t="s">
         <v>36</v>
       </c>
-      <c r="AH29" s="44" t="s">
+      <c r="AH29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI29" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI29" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ29" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK29" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="44" t="s">
+      <c r="AK29" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL29" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM29" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN29" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO29" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP29">
+      <c r="AN29" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP29" s="44">
         <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR29">
         <v>1</v>
       </c>
-      <c r="AS29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV29">
-        <v>0</v>
+      <c r="AS29">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>36</v>
       </c>
       <c r="AW29">
         <v>0</v>
       </c>
-      <c r="AX29" t="s">
-        <v>36</v>
+      <c r="AX29">
+        <v>0</v>
       </c>
       <c r="AY29" t="s">
         <v>36</v>
@@ -63278,8 +63375,8 @@
       <c r="AZ29" t="s">
         <v>36</v>
       </c>
-      <c r="BA29">
-        <v>0</v>
+      <c r="BA29" t="s">
+        <v>36</v>
       </c>
       <c r="BB29">
         <v>0</v>
@@ -63290,23 +63387,26 @@
       <c r="BD29">
         <v>0</v>
       </c>
-      <c r="BE29" t="s">
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="s">
         <v>1765</v>
       </c>
-      <c r="BF29" t="s">
-        <v>36</v>
-      </c>
       <c r="BG29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH29" t="s">
         <v>1658</v>
       </c>
-      <c r="BH29">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:61">
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:62">
       <c r="A30" s="44" t="s">
         <v>1616</v>
       </c>
@@ -63406,56 +63506,56 @@
       <c r="AG30" t="s">
         <v>36</v>
       </c>
-      <c r="AH30" s="44" t="s">
+      <c r="AH30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI30" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI30" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ30" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK30" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="44" t="s">
+      <c r="AK30" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL30" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM30" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO30" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP30">
+      <c r="AN30" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP30" s="44">
         <v>0</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR30">
         <v>1</v>
       </c>
-      <c r="AS30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
+      <c r="AS30">
+        <v>1</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>36</v>
       </c>
       <c r="AW30">
         <v>0</v>
       </c>
-      <c r="AX30" t="s">
-        <v>36</v>
+      <c r="AX30">
+        <v>0</v>
       </c>
       <c r="AY30" t="s">
         <v>36</v>
@@ -63463,8 +63563,8 @@
       <c r="AZ30" t="s">
         <v>36</v>
       </c>
-      <c r="BA30">
-        <v>0</v>
+      <c r="BA30" t="s">
+        <v>36</v>
       </c>
       <c r="BB30">
         <v>0</v>
@@ -63475,23 +63575,26 @@
       <c r="BD30">
         <v>0</v>
       </c>
-      <c r="BE30" t="s">
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="s">
         <v>1763</v>
       </c>
-      <c r="BF30" t="s">
-        <v>36</v>
-      </c>
       <c r="BG30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH30" t="s">
         <v>1658</v>
       </c>
-      <c r="BH30">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:61">
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:62">
       <c r="A31" s="44" t="s">
         <v>1620</v>
       </c>
@@ -63591,56 +63694,56 @@
       <c r="AG31" t="s">
         <v>36</v>
       </c>
-      <c r="AH31" s="44" t="s">
+      <c r="AH31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI31" s="44" t="s">
         <v>1621</v>
-      </c>
-      <c r="AI31" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ31" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK31" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="44" t="s">
+      <c r="AK31" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL31" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM31" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN31" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO31" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP31">
+      <c r="AN31" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP31" s="44">
         <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR31">
         <v>1</v>
       </c>
-      <c r="AS31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
+      <c r="AS31">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>36</v>
       </c>
       <c r="AW31">
         <v>0</v>
       </c>
-      <c r="AX31" t="s">
-        <v>36</v>
+      <c r="AX31">
+        <v>0</v>
       </c>
       <c r="AY31" t="s">
         <v>36</v>
@@ -63648,8 +63751,8 @@
       <c r="AZ31" t="s">
         <v>36</v>
       </c>
-      <c r="BA31">
-        <v>0</v>
+      <c r="BA31" t="s">
+        <v>36</v>
       </c>
       <c r="BB31">
         <v>0</v>
@@ -63660,23 +63763,26 @@
       <c r="BD31">
         <v>0</v>
       </c>
-      <c r="BE31" t="s">
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="s">
         <v>1764</v>
       </c>
-      <c r="BF31" t="s">
-        <v>36</v>
-      </c>
       <c r="BG31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH31" t="s">
         <v>1658</v>
       </c>
-      <c r="BH31">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:61">
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:62">
       <c r="A32" s="44" t="s">
         <v>1624</v>
       </c>
@@ -63776,66 +63882,66 @@
       <c r="AG32" t="s">
         <v>36</v>
       </c>
-      <c r="AH32" s="44" t="s">
+      <c r="AH32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI32" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI32" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ32" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK32" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="44" t="s">
+      <c r="AK32" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL32" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM32" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN32" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO32" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP32">
+      <c r="AN32" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO32" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP32" s="44">
         <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR32">
         <v>1</v>
       </c>
-      <c r="AS32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
+      <c r="AS32">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>36</v>
       </c>
       <c r="AW32">
         <v>0</v>
       </c>
-      <c r="AX32" t="s">
-        <v>36</v>
+      <c r="AX32">
+        <v>0</v>
       </c>
       <c r="AY32" t="s">
         <v>36</v>
       </c>
       <c r="AZ32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA32" t="s">
         <v>1624</v>
       </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
       <c r="BB32">
         <v>0</v>
       </c>
@@ -63845,23 +63951,26 @@
       <c r="BD32">
         <v>0</v>
       </c>
-      <c r="BE32" t="s">
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="s">
         <v>1760</v>
       </c>
-      <c r="BF32" t="s">
-        <v>36</v>
-      </c>
       <c r="BG32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH32" t="s">
         <v>896</v>
       </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:61">
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:62">
       <c r="A33" s="44" t="s">
         <v>1647</v>
       </c>
@@ -63961,56 +64070,56 @@
       <c r="AG33" t="s">
         <v>36</v>
       </c>
-      <c r="AH33" s="44" t="s">
+      <c r="AH33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI33" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI33" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ33" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK33" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="44" t="s">
+      <c r="AK33" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL33" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM33" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO33" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP33">
+      <c r="AN33" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP33" s="44">
         <v>0</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR33">
         <v>1</v>
       </c>
-      <c r="AS33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV33">
-        <v>0</v>
+      <c r="AS33">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>36</v>
       </c>
       <c r="AW33">
         <v>0</v>
       </c>
-      <c r="AX33" t="s">
-        <v>36</v>
+      <c r="AX33">
+        <v>0</v>
       </c>
       <c r="AY33" t="s">
         <v>36</v>
@@ -64018,8 +64127,8 @@
       <c r="AZ33" t="s">
         <v>36</v>
       </c>
-      <c r="BA33">
-        <v>0</v>
+      <c r="BA33" t="s">
+        <v>36</v>
       </c>
       <c r="BB33">
         <v>0</v>
@@ -64030,23 +64139,26 @@
       <c r="BD33">
         <v>0</v>
       </c>
-      <c r="BE33" t="s">
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="s">
         <v>1761</v>
       </c>
-      <c r="BF33" t="s">
-        <v>36</v>
-      </c>
       <c r="BG33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH33" t="s">
         <v>896</v>
       </c>
-      <c r="BH33">
-        <v>0</v>
-      </c>
-      <c r="BI33" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:61">
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:62">
       <c r="A34" s="44" t="s">
         <v>1578</v>
       </c>
@@ -64146,56 +64258,56 @@
       <c r="AG34" t="s">
         <v>36</v>
       </c>
-      <c r="AH34" s="44" t="s">
+      <c r="AH34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI34" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI34" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ34" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK34" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="44" t="s">
+      <c r="AK34" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL34" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM34" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO34" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP34">
+      <c r="AN34" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP34" s="44">
         <v>0</v>
       </c>
       <c r="AQ34">
         <v>0</v>
       </c>
       <c r="AR34">
-        <v>1</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>1</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>36</v>
       </c>
       <c r="AW34">
         <v>0</v>
       </c>
-      <c r="AX34" t="s">
-        <v>36</v>
+      <c r="AX34">
+        <v>0</v>
       </c>
       <c r="AY34" t="s">
         <v>36</v>
@@ -64203,8 +64315,8 @@
       <c r="AZ34" t="s">
         <v>36</v>
       </c>
-      <c r="BA34">
-        <v>0</v>
+      <c r="BA34" t="s">
+        <v>36</v>
       </c>
       <c r="BB34">
         <v>0</v>
@@ -64215,23 +64327,26 @@
       <c r="BD34">
         <v>0</v>
       </c>
-      <c r="BE34" t="s">
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="s">
         <v>1762</v>
       </c>
-      <c r="BF34" t="s">
-        <v>36</v>
-      </c>
       <c r="BG34" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH34" t="s">
         <v>1671</v>
       </c>
-      <c r="BH34">
-        <v>0</v>
-      </c>
-      <c r="BI34" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:61">
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:62">
       <c r="A35" s="44" t="s">
         <v>1686</v>
       </c>
@@ -64331,56 +64446,56 @@
       <c r="AG35" t="s">
         <v>36</v>
       </c>
-      <c r="AH35" s="44" t="s">
+      <c r="AH35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI35" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI35" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ35" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK35" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="44" t="s">
+      <c r="AK35" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL35" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM35" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN35" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO35" s="44">
-        <v>1</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
+      <c r="AN35" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO35" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP35" s="44">
+        <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR35">
         <v>1</v>
       </c>
-      <c r="AS35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
+      <c r="AS35">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>36</v>
       </c>
       <c r="AW35">
         <v>0</v>
       </c>
-      <c r="AX35" t="s">
-        <v>36</v>
+      <c r="AX35">
+        <v>0</v>
       </c>
       <c r="AY35" t="s">
         <v>36</v>
@@ -64388,8 +64503,8 @@
       <c r="AZ35" t="s">
         <v>36</v>
       </c>
-      <c r="BA35">
-        <v>0</v>
+      <c r="BA35" t="s">
+        <v>36</v>
       </c>
       <c r="BB35">
         <v>0</v>
@@ -64400,23 +64515,26 @@
       <c r="BD35">
         <v>0</v>
       </c>
-      <c r="BE35" t="s">
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="s">
         <v>37</v>
       </c>
-      <c r="BF35" t="s">
-        <v>36</v>
-      </c>
       <c r="BG35" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH35" t="s">
         <v>1671</v>
       </c>
-      <c r="BH35">
-        <v>0</v>
-      </c>
-      <c r="BI35" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:61">
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:62">
       <c r="A36" s="44" t="s">
         <v>1728</v>
       </c>
@@ -64516,56 +64634,56 @@
       <c r="AG36" t="s">
         <v>36</v>
       </c>
-      <c r="AH36" s="44" t="s">
+      <c r="AH36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI36" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI36" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ36" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK36" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="44" t="s">
+      <c r="AK36" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL36" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM36" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN36" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO36" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP36">
+      <c r="AN36" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP36" s="44">
         <v>0</v>
       </c>
       <c r="AQ36">
         <v>0</v>
       </c>
       <c r="AR36">
-        <v>1</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>1</v>
+      </c>
+      <c r="AT36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>36</v>
       </c>
       <c r="AW36">
         <v>0</v>
       </c>
-      <c r="AX36" t="s">
-        <v>36</v>
+      <c r="AX36">
+        <v>0</v>
       </c>
       <c r="AY36" t="s">
         <v>36</v>
@@ -64573,8 +64691,8 @@
       <c r="AZ36" t="s">
         <v>36</v>
       </c>
-      <c r="BA36">
-        <v>0</v>
+      <c r="BA36" t="s">
+        <v>36</v>
       </c>
       <c r="BB36">
         <v>0</v>
@@ -64585,23 +64703,26 @@
       <c r="BD36">
         <v>0</v>
       </c>
-      <c r="BE36" t="s">
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="s">
         <v>1765</v>
       </c>
-      <c r="BF36" t="s">
-        <v>36</v>
-      </c>
       <c r="BG36" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH36" t="s">
         <v>896</v>
       </c>
-      <c r="BH36">
-        <v>0</v>
-      </c>
-      <c r="BI36" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:61">
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:62">
       <c r="A37" s="44" t="s">
         <v>1786</v>
       </c>
@@ -64701,56 +64822,56 @@
       <c r="AG37" t="s">
         <v>36</v>
       </c>
-      <c r="AH37" s="44" t="s">
+      <c r="AH37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI37" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI37" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ37" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK37" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="44" t="s">
+      <c r="AK37" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL37" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM37" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN37" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO37" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP37">
+      <c r="AN37" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP37" s="44">
         <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR37">
         <v>1</v>
       </c>
-      <c r="AS37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV37">
-        <v>0</v>
+      <c r="AS37">
+        <v>1</v>
+      </c>
+      <c r="AT37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="s">
+        <v>36</v>
       </c>
       <c r="AW37">
         <v>0</v>
       </c>
-      <c r="AX37" t="s">
-        <v>36</v>
+      <c r="AX37">
+        <v>0</v>
       </c>
       <c r="AY37" t="s">
         <v>36</v>
@@ -64758,8 +64879,8 @@
       <c r="AZ37" t="s">
         <v>36</v>
       </c>
-      <c r="BA37">
-        <v>0</v>
+      <c r="BA37" t="s">
+        <v>36</v>
       </c>
       <c r="BB37">
         <v>0</v>
@@ -64770,25 +64891,28 @@
       <c r="BD37">
         <v>0</v>
       </c>
-      <c r="BE37" t="s">
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="s">
         <v>1762</v>
       </c>
-      <c r="BF37" t="s">
-        <v>36</v>
-      </c>
       <c r="BG37" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH37" t="s">
         <v>1663</v>
       </c>
-      <c r="BH37">
-        <v>0</v>
-      </c>
-      <c r="BI37" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:61">
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:62">
       <c r="A38" s="44" t="s">
-        <v>1797</v>
+        <v>1905</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -64884,58 +65008,58 @@
         <v>10</v>
       </c>
       <c r="AG38" t="s">
-        <v>1796</v>
-      </c>
-      <c r="AH38" s="44" t="s">
+        <v>1907</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>1906</v>
+      </c>
+      <c r="AI38" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI38" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ38" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK38" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="44" t="s">
+      <c r="AK38" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL38" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM38" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN38" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO38" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP38">
+      <c r="AN38" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO38" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP38" s="44">
         <v>0</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR38">
         <v>1</v>
       </c>
-      <c r="AS38" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV38">
-        <v>0</v>
+      <c r="AS38">
+        <v>1</v>
+      </c>
+      <c r="AT38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>36</v>
       </c>
       <c r="AW38">
         <v>0</v>
       </c>
-      <c r="AX38" t="s">
-        <v>36</v>
+      <c r="AX38">
+        <v>0</v>
       </c>
       <c r="AY38" t="s">
         <v>36</v>
@@ -64943,8 +65067,8 @@
       <c r="AZ38" t="s">
         <v>36</v>
       </c>
-      <c r="BA38">
-        <v>0</v>
+      <c r="BA38" t="s">
+        <v>36</v>
       </c>
       <c r="BB38">
         <v>0</v>
@@ -64955,25 +65079,28 @@
       <c r="BD38">
         <v>0</v>
       </c>
-      <c r="BE38" t="s">
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="s">
         <v>1763</v>
       </c>
-      <c r="BF38" t="s">
-        <v>36</v>
-      </c>
       <c r="BG38" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH38" t="s">
         <v>1663</v>
       </c>
-      <c r="BH38">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:61">
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:62">
       <c r="A39" s="44" t="s">
-        <v>1796</v>
+        <v>1906</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -64985,7 +65112,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -65012,7 +65139,7 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -65060,7 +65187,7 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -65071,56 +65198,56 @@
       <c r="AG39" t="s">
         <v>36</v>
       </c>
-      <c r="AH39" s="44" t="s">
+      <c r="AH39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI39" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI39" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ39" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK39" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="44" t="s">
+      <c r="AK39" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL39" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM39" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN39" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO39" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP39">
+      <c r="AN39" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP39" s="44">
         <v>0</v>
       </c>
       <c r="AQ39">
         <v>0</v>
       </c>
       <c r="AR39">
-        <v>1</v>
-      </c>
-      <c r="AS39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>1</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU39">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="s">
+        <v>36</v>
       </c>
       <c r="AW39">
-        <v>1</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AX39">
+        <v>1</v>
       </c>
       <c r="AY39" t="s">
         <v>36</v>
@@ -65128,8 +65255,8 @@
       <c r="AZ39" t="s">
         <v>36</v>
       </c>
-      <c r="BA39">
-        <v>0</v>
+      <c r="BA39" t="s">
+        <v>36</v>
       </c>
       <c r="BB39">
         <v>0</v>
@@ -65140,31 +65267,34 @@
       <c r="BD39">
         <v>0</v>
       </c>
-      <c r="BE39" t="s">
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="s">
         <v>1761</v>
       </c>
-      <c r="BF39" t="s">
-        <v>36</v>
-      </c>
       <c r="BG39" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH39" t="s">
         <v>1663</v>
       </c>
-      <c r="BH39">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:61">
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:62">
       <c r="A40" s="44" t="s">
-        <v>1805</v>
+        <v>1907</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -65215,7 +65345,7 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -65224,7 +65354,7 @@
         <v>0</v>
       </c>
       <c r="W40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -65256,56 +65386,56 @@
       <c r="AG40" t="s">
         <v>36</v>
       </c>
-      <c r="AH40" s="44" t="s">
-        <v>1479</v>
+      <c r="AH40" t="s">
+        <v>36</v>
       </c>
       <c r="AI40" s="44" t="s">
-        <v>1474</v>
+        <v>1363</v>
       </c>
       <c r="AJ40" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK40" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL40" s="44" t="s">
+      <c r="AK40" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL40" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM40" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN40" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO40" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP40">
+      <c r="AN40" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP40" s="44">
         <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR40">
         <v>1</v>
       </c>
-      <c r="AS40" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV40">
-        <v>0</v>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU40">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>36</v>
       </c>
       <c r="AW40">
         <v>0</v>
       </c>
-      <c r="AX40" t="s">
-        <v>36</v>
+      <c r="AX40">
+        <v>0</v>
       </c>
       <c r="AY40" t="s">
         <v>36</v>
@@ -65313,8 +65443,8 @@
       <c r="AZ40" t="s">
         <v>36</v>
       </c>
-      <c r="BA40">
-        <v>0</v>
+      <c r="BA40" t="s">
+        <v>36</v>
       </c>
       <c r="BB40">
         <v>0</v>
@@ -65325,25 +65455,28 @@
       <c r="BD40">
         <v>0</v>
       </c>
-      <c r="BE40" t="s">
-        <v>1765</v>
+      <c r="BE40">
+        <v>0</v>
       </c>
       <c r="BF40" t="s">
-        <v>36</v>
+        <v>1760</v>
       </c>
       <c r="BG40" t="s">
-        <v>1663</v>
-      </c>
-      <c r="BH40">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH40" t="s">
+        <v>1657</v>
+      </c>
+      <c r="BI40">
+        <v>0</v>
+      </c>
+      <c r="BJ40" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:62">
       <c r="A41" s="44" t="s">
-        <v>1807</v>
+        <v>1797</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -65412,7 +65545,7 @@
         <v>3</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -65441,56 +65574,56 @@
       <c r="AG41" t="s">
         <v>36</v>
       </c>
-      <c r="AH41" s="44" t="s">
+      <c r="AH41" t="s">
+        <v>1796</v>
+      </c>
+      <c r="AI41" s="44" t="s">
         <v>1479</v>
-      </c>
-      <c r="AI41" s="44" t="s">
-        <v>1474</v>
       </c>
       <c r="AJ41" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK41" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL41" s="44" t="s">
+      <c r="AK41" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL41" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM41" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN41" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO41" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP41">
+      <c r="AN41" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP41" s="44">
         <v>0</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR41">
         <v>1</v>
       </c>
-      <c r="AS41" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV41">
-        <v>0</v>
+      <c r="AS41">
+        <v>1</v>
+      </c>
+      <c r="AT41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU41">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>36</v>
       </c>
       <c r="AW41">
         <v>0</v>
       </c>
-      <c r="AX41" t="s">
-        <v>36</v>
+      <c r="AX41">
+        <v>0</v>
       </c>
       <c r="AY41" t="s">
         <v>36</v>
@@ -65498,8 +65631,8 @@
       <c r="AZ41" t="s">
         <v>36</v>
       </c>
-      <c r="BA41">
-        <v>0</v>
+      <c r="BA41" t="s">
+        <v>36</v>
       </c>
       <c r="BB41">
         <v>0</v>
@@ -65510,28 +65643,31 @@
       <c r="BD41">
         <v>0</v>
       </c>
-      <c r="BE41" t="s">
-        <v>1765</v>
+      <c r="BE41">
+        <v>0</v>
       </c>
       <c r="BF41" t="s">
-        <v>36</v>
+        <v>1763</v>
       </c>
       <c r="BG41" t="s">
-        <v>1671</v>
-      </c>
-      <c r="BH41">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH41" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI41">
+        <v>0</v>
+      </c>
+      <c r="BJ41" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:62">
       <c r="A42" s="44" t="s">
-        <v>1868</v>
+        <v>1796</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -65597,7 +65733,7 @@
         <v>3</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -65615,67 +65751,67 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="s">
-        <v>1869</v>
-      </c>
-      <c r="AH42" s="44" t="s">
-        <v>1363</v>
+        <v>36</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>36</v>
       </c>
       <c r="AI42" s="44" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="AJ42" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK42" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL42" s="44" t="s">
+      <c r="AK42" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL42" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM42" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN42" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO42" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP42">
+      <c r="AN42" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP42" s="44">
         <v>0</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR42">
-        <v>1</v>
-      </c>
-      <c r="AS42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>1</v>
+      </c>
+      <c r="AT42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU42">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>36</v>
       </c>
       <c r="AW42">
         <v>0</v>
       </c>
-      <c r="AX42" t="s">
-        <v>36</v>
+      <c r="AX42">
+        <v>1</v>
       </c>
       <c r="AY42" t="s">
         <v>36</v>
@@ -65683,8 +65819,8 @@
       <c r="AZ42" t="s">
         <v>36</v>
       </c>
-      <c r="BA42">
-        <v>0</v>
+      <c r="BA42" t="s">
+        <v>36</v>
       </c>
       <c r="BB42">
         <v>0</v>
@@ -65695,34 +65831,37 @@
       <c r="BD42">
         <v>0</v>
       </c>
-      <c r="BE42" t="s">
-        <v>1763</v>
+      <c r="BE42">
+        <v>0</v>
       </c>
       <c r="BF42" t="s">
-        <v>36</v>
+        <v>1761</v>
       </c>
       <c r="BG42" t="s">
-        <v>1671</v>
-      </c>
-      <c r="BH42">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH42" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI42">
+        <v>0</v>
+      </c>
+      <c r="BJ42" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:62">
       <c r="A43" s="44" t="s">
-        <v>1869</v>
+        <v>1805</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -65770,7 +65909,7 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -65800,42 +65939,42 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG43" t="s">
         <v>36</v>
       </c>
-      <c r="AH43" s="44" t="s">
-        <v>1363</v>
+      <c r="AH43" t="s">
+        <v>36</v>
       </c>
       <c r="AI43" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AJ43" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AK43" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AJ43" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK43" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL43" s="44" t="s">
+      <c r="AL43" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM43" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN43" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO43" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP43">
+      <c r="AN43" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO43" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP43" s="44">
         <v>0</v>
       </c>
       <c r="AQ43">
@@ -65844,23 +65983,23 @@
       <c r="AR43">
         <v>1</v>
       </c>
-      <c r="AS43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV43">
-        <v>0</v>
+      <c r="AS43">
+        <v>1</v>
+      </c>
+      <c r="AT43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU43">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>36</v>
       </c>
       <c r="AW43">
-        <v>1</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AX43">
+        <v>0</v>
       </c>
       <c r="AY43" t="s">
         <v>36</v>
@@ -65868,8 +66007,8 @@
       <c r="AZ43" t="s">
         <v>36</v>
       </c>
-      <c r="BA43">
-        <v>0</v>
+      <c r="BA43" t="s">
+        <v>36</v>
       </c>
       <c r="BB43">
         <v>0</v>
@@ -65880,25 +66019,28 @@
       <c r="BD43">
         <v>0</v>
       </c>
-      <c r="BE43" t="s">
-        <v>1761</v>
+      <c r="BE43">
+        <v>0</v>
       </c>
       <c r="BF43" t="s">
-        <v>36</v>
+        <v>1765</v>
       </c>
       <c r="BG43" t="s">
-        <v>896</v>
-      </c>
-      <c r="BH43">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH43" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI43">
+        <v>0</v>
+      </c>
+      <c r="BJ43" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:62">
       <c r="A44" s="44" t="s">
-        <v>1870</v>
+        <v>1807</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -65967,7 +66109,7 @@
         <v>3</v>
       </c>
       <c r="X44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44">
         <v>0</v>
@@ -65994,58 +66136,58 @@
         <v>10</v>
       </c>
       <c r="AG44" t="s">
-        <v>1871</v>
-      </c>
-      <c r="AH44" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI44" s="44" t="s">
         <v>1479</v>
       </c>
-      <c r="AI44" s="44" t="s">
+      <c r="AJ44" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AK44" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AJ44" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK44" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL44" s="44" t="s">
+      <c r="AL44" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM44" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN44" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO44" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP44">
+      <c r="AN44" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO44" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP44" s="44">
         <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR44">
         <v>1</v>
       </c>
-      <c r="AS44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT44">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV44">
-        <v>0</v>
+      <c r="AS44">
+        <v>1</v>
+      </c>
+      <c r="AT44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU44">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="s">
+        <v>36</v>
       </c>
       <c r="AW44">
         <v>0</v>
       </c>
-      <c r="AX44" t="s">
-        <v>36</v>
+      <c r="AX44">
+        <v>0</v>
       </c>
       <c r="AY44" t="s">
         <v>36</v>
@@ -66053,8 +66195,8 @@
       <c r="AZ44" t="s">
         <v>36</v>
       </c>
-      <c r="BA44">
-        <v>0</v>
+      <c r="BA44" t="s">
+        <v>36</v>
       </c>
       <c r="BB44">
         <v>0</v>
@@ -66065,28 +66207,31 @@
       <c r="BD44">
         <v>0</v>
       </c>
-      <c r="BE44" t="s">
-        <v>1763</v>
+      <c r="BE44">
+        <v>0</v>
       </c>
       <c r="BF44" t="s">
-        <v>36</v>
+        <v>1765</v>
       </c>
       <c r="BG44" t="s">
-        <v>1663</v>
-      </c>
-      <c r="BH44">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH44" t="s">
+        <v>1671</v>
+      </c>
+      <c r="BI44">
+        <v>0</v>
+      </c>
+      <c r="BJ44" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:62">
       <c r="A45" s="44" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -66095,7 +66240,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -66110,7 +66255,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -66152,7 +66297,7 @@
         <v>3</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y45">
         <v>0</v>
@@ -66170,42 +66315,42 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG45" t="s">
         <v>36</v>
       </c>
-      <c r="AH45" s="44" t="s">
-        <v>1479</v>
+      <c r="AH45" t="s">
+        <v>1869</v>
       </c>
       <c r="AI45" s="44" t="s">
-        <v>1470</v>
+        <v>1363</v>
       </c>
       <c r="AJ45" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK45" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL45" s="44" t="s">
+      <c r="AK45" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL45" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM45" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN45" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO45" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP45">
+      <c r="AN45" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO45" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP45" s="44">
         <v>0</v>
       </c>
       <c r="AQ45">
@@ -66214,23 +66359,23 @@
       <c r="AR45">
         <v>1</v>
       </c>
-      <c r="AS45" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT45">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV45">
-        <v>0</v>
+      <c r="AS45">
+        <v>1</v>
+      </c>
+      <c r="AT45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU45">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>36</v>
       </c>
       <c r="AW45">
-        <v>1</v>
-      </c>
-      <c r="AX45" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="AX45">
+        <v>0</v>
       </c>
       <c r="AY45" t="s">
         <v>36</v>
@@ -66238,8 +66383,8 @@
       <c r="AZ45" t="s">
         <v>36</v>
       </c>
-      <c r="BA45">
-        <v>0</v>
+      <c r="BA45" t="s">
+        <v>36</v>
       </c>
       <c r="BB45">
         <v>0</v>
@@ -66250,34 +66395,37 @@
       <c r="BD45">
         <v>0</v>
       </c>
-      <c r="BE45" t="s">
-        <v>1761</v>
+      <c r="BE45">
+        <v>0</v>
       </c>
       <c r="BF45" t="s">
-        <v>36</v>
+        <v>1763</v>
       </c>
       <c r="BG45" t="s">
-        <v>1663</v>
-      </c>
-      <c r="BH45">
-        <v>0</v>
-      </c>
-      <c r="BI45" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH45" t="s">
+        <v>1671</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:62">
       <c r="A46" s="44" t="s">
-        <v>1883</v>
+        <v>1869</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -66286,7 +66434,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -66334,7 +66482,7 @@
         <v>0</v>
       </c>
       <c r="W46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -66355,67 +66503,67 @@
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="s">
         <v>36</v>
       </c>
-      <c r="AH46" s="44" t="s">
+      <c r="AH46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI46" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI46" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ46" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK46" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="44" t="s">
+      <c r="AK46" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL46" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM46" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN46" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO46" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP46">
+      <c r="AN46" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP46" s="44">
         <v>0</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR46">
-        <v>1</v>
-      </c>
-      <c r="AS46" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV46">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>1</v>
+      </c>
+      <c r="AT46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU46">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="s">
+        <v>36</v>
       </c>
       <c r="AW46">
         <v>0</v>
       </c>
-      <c r="AX46" t="s">
-        <v>36</v>
+      <c r="AX46">
+        <v>1</v>
       </c>
       <c r="AY46" t="s">
         <v>36</v>
@@ -66423,8 +66571,8 @@
       <c r="AZ46" t="s">
         <v>36</v>
       </c>
-      <c r="BA46">
-        <v>0</v>
+      <c r="BA46" t="s">
+        <v>36</v>
       </c>
       <c r="BB46">
         <v>0</v>
@@ -66435,25 +66583,28 @@
       <c r="BD46">
         <v>0</v>
       </c>
-      <c r="BE46" t="s">
-        <v>37</v>
+      <c r="BE46">
+        <v>0</v>
       </c>
       <c r="BF46" t="s">
-        <v>36</v>
+        <v>1761</v>
       </c>
       <c r="BG46" t="s">
-        <v>1663</v>
-      </c>
-      <c r="BH46">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH46" t="s">
+        <v>896</v>
+      </c>
+      <c r="BI46">
+        <v>0</v>
+      </c>
+      <c r="BJ46" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:62">
       <c r="A47" s="44" t="s">
-        <v>1884</v>
+        <v>1870</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -66471,7 +66622,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -66519,10 +66670,10 @@
         <v>0</v>
       </c>
       <c r="W47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y47">
         <v>0</v>
@@ -66551,56 +66702,56 @@
       <c r="AG47" t="s">
         <v>36</v>
       </c>
-      <c r="AH47" s="44" t="s">
-        <v>1363</v>
+      <c r="AH47" t="s">
+        <v>1871</v>
       </c>
       <c r="AI47" s="44" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="AJ47" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK47" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL47" s="44" t="s">
+      <c r="AK47" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL47" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM47" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN47" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO47" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP47">
+      <c r="AN47" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO47" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP47" s="44">
         <v>0</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR47">
         <v>1</v>
       </c>
-      <c r="AS47" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV47">
-        <v>0</v>
+      <c r="AS47">
+        <v>1</v>
+      </c>
+      <c r="AT47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU47">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="s">
+        <v>36</v>
       </c>
       <c r="AW47">
         <v>0</v>
       </c>
-      <c r="AX47" t="s">
-        <v>36</v>
+      <c r="AX47">
+        <v>0</v>
       </c>
       <c r="AY47" t="s">
         <v>36</v>
@@ -66608,8 +66759,8 @@
       <c r="AZ47" t="s">
         <v>36</v>
       </c>
-      <c r="BA47">
-        <v>0</v>
+      <c r="BA47" t="s">
+        <v>36</v>
       </c>
       <c r="BB47">
         <v>0</v>
@@ -66620,28 +66771,31 @@
       <c r="BD47">
         <v>0</v>
       </c>
-      <c r="BE47" t="s">
-        <v>1765</v>
+      <c r="BE47">
+        <v>0</v>
       </c>
       <c r="BF47" t="s">
-        <v>36</v>
+        <v>1763</v>
       </c>
       <c r="BG47" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH47" t="s">
         <v>1663</v>
       </c>
-      <c r="BH47">
-        <v>0</v>
-      </c>
-      <c r="BI47" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:61">
+      <c r="BI47">
+        <v>0</v>
+      </c>
+      <c r="BJ47" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:62">
       <c r="A48" s="44" t="s">
-        <v>1885</v>
+        <v>1871</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -66656,7 +66810,7 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -66665,7 +66819,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -66704,7 +66858,7 @@
         <v>0</v>
       </c>
       <c r="W48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -66725,67 +66879,67 @@
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE48">
         <v>0</v>
       </c>
       <c r="AF48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="s">
         <v>36</v>
       </c>
-      <c r="AH48" s="44" t="s">
-        <v>1363</v>
+      <c r="AH48" t="s">
+        <v>36</v>
       </c>
       <c r="AI48" s="44" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="AJ48" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK48" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL48" s="44" t="s">
+      <c r="AK48" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL48" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM48" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN48" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO48" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP48">
+      <c r="AN48" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO48" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP48" s="44">
         <v>0</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR48">
-        <v>1</v>
-      </c>
-      <c r="AS48" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV48">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>1</v>
+      </c>
+      <c r="AT48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU48">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="s">
+        <v>36</v>
       </c>
       <c r="AW48">
         <v>0</v>
       </c>
-      <c r="AX48" t="s">
-        <v>36</v>
+      <c r="AX48">
+        <v>1</v>
       </c>
       <c r="AY48" t="s">
         <v>36</v>
@@ -66793,8 +66947,8 @@
       <c r="AZ48" t="s">
         <v>36</v>
       </c>
-      <c r="BA48">
-        <v>0</v>
+      <c r="BA48" t="s">
+        <v>36</v>
       </c>
       <c r="BB48">
         <v>0</v>
@@ -66805,55 +66959,216 @@
       <c r="BD48">
         <v>0</v>
       </c>
-      <c r="BE48" t="s">
-        <v>1764</v>
+      <c r="BE48">
+        <v>0</v>
       </c>
       <c r="BF48" t="s">
-        <v>36</v>
+        <v>1761</v>
       </c>
       <c r="BG48" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH48" t="s">
         <v>1663</v>
       </c>
-      <c r="BH48">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:61" ht="14">
-      <c r="A49" s="55" t="s">
-        <v>1887</v>
-      </c>
-      <c r="B49" s="55"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="BH49">
-        <v>0</v>
-      </c>
-      <c r="BI49" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:61">
+      <c r="BI48">
+        <v>0</v>
+      </c>
+      <c r="BJ48" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:62">
+      <c r="A49" s="44" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>4</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>1</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>-1</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>10</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI49" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ49" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK49" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL49" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN49" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO49" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP49" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>1</v>
+      </c>
+      <c r="AS49">
+        <v>1</v>
+      </c>
+      <c r="AT49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU49">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW49">
+        <v>0</v>
+      </c>
+      <c r="AX49">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>0</v>
+      </c>
+      <c r="BD49">
+        <v>0</v>
+      </c>
+      <c r="BE49">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG49" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH49" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI49">
+        <v>0</v>
+      </c>
+      <c r="BJ49" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:62">
       <c r="A50" s="44" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -66871,13 +67186,13 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -66919,7 +67234,7 @@
         <v>0</v>
       </c>
       <c r="W50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -66951,31 +67266,31 @@
       <c r="AG50" t="s">
         <v>36</v>
       </c>
-      <c r="AH50" s="44" t="s">
+      <c r="AH50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI50" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI50" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ50" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK50" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL50" s="44" t="s">
+      <c r="AK50" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL50" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM50" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN50" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO50" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP50">
+      <c r="AN50" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO50" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP50" s="44">
         <v>0</v>
       </c>
       <c r="AQ50">
@@ -66984,23 +67299,23 @@
       <c r="AR50">
         <v>1</v>
       </c>
-      <c r="AS50" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV50">
-        <v>0</v>
+      <c r="AS50">
+        <v>1</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU50">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>36</v>
       </c>
       <c r="AW50">
         <v>0</v>
       </c>
-      <c r="AX50" t="s">
-        <v>36</v>
+      <c r="AX50">
+        <v>0</v>
       </c>
       <c r="AY50" t="s">
         <v>36</v>
@@ -67008,8 +67323,8 @@
       <c r="AZ50" t="s">
         <v>36</v>
       </c>
-      <c r="BA50">
-        <v>0</v>
+      <c r="BA50" t="s">
+        <v>36</v>
       </c>
       <c r="BB50">
         <v>0</v>
@@ -67018,27 +67333,30 @@
         <v>0</v>
       </c>
       <c r="BD50">
-        <v>1</v>
-      </c>
-      <c r="BE50" t="s">
-        <v>1762</v>
+        <v>0</v>
+      </c>
+      <c r="BE50">
+        <v>0</v>
       </c>
       <c r="BF50" t="s">
-        <v>36</v>
+        <v>1765</v>
       </c>
       <c r="BG50" t="s">
-        <v>1659</v>
-      </c>
-      <c r="BH50">
-        <v>10</v>
-      </c>
-      <c r="BI50" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:61">
+        <v>36</v>
+      </c>
+      <c r="BH50" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI50">
+        <v>0</v>
+      </c>
+      <c r="BJ50" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:62">
       <c r="A51" s="44" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -67056,7 +67374,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -67083,7 +67401,7 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -67104,7 +67422,7 @@
         <v>0</v>
       </c>
       <c r="W51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -67136,31 +67454,31 @@
       <c r="AG51" t="s">
         <v>36</v>
       </c>
-      <c r="AH51" s="44" t="s">
+      <c r="AH51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI51" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI51" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ51" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK51" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL51" s="44" t="s">
+      <c r="AK51" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL51" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM51" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN51" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO51" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP51">
+      <c r="AN51" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP51" s="44">
         <v>0</v>
       </c>
       <c r="AQ51">
@@ -67169,23 +67487,23 @@
       <c r="AR51">
         <v>1</v>
       </c>
-      <c r="AS51" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV51">
-        <v>0</v>
+      <c r="AS51">
+        <v>1</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU51">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>36</v>
       </c>
       <c r="AW51">
         <v>0</v>
       </c>
-      <c r="AX51" t="s">
-        <v>36</v>
+      <c r="AX51">
+        <v>0</v>
       </c>
       <c r="AY51" t="s">
         <v>36</v>
@@ -67193,8 +67511,8 @@
       <c r="AZ51" t="s">
         <v>36</v>
       </c>
-      <c r="BA51">
-        <v>0</v>
+      <c r="BA51" t="s">
+        <v>36</v>
       </c>
       <c r="BB51">
         <v>0</v>
@@ -67203,212 +67521,63 @@
         <v>0</v>
       </c>
       <c r="BD51">
-        <v>1</v>
-      </c>
-      <c r="BE51" t="s">
-        <v>1762</v>
+        <v>0</v>
+      </c>
+      <c r="BE51">
+        <v>0</v>
       </c>
       <c r="BF51" t="s">
-        <v>36</v>
+        <v>1764</v>
       </c>
       <c r="BG51" t="s">
-        <v>1659</v>
-      </c>
-      <c r="BH51">
-        <v>0</v>
-      </c>
-      <c r="BI51" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:61">
-      <c r="A52" s="44" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>3</v>
-      </c>
-      <c r="X52">
-        <v>0</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
-        <v>0</v>
-      </c>
-      <c r="AB52">
-        <v>1</v>
-      </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>-1</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>10</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="BH51" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI51">
+        <v>0</v>
+      </c>
+      <c r="BJ51" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:62" ht="14">
+      <c r="A52" s="55" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
       <c r="AG52" t="s">
         <v>36</v>
       </c>
-      <c r="AH52" s="44" t="s">
-        <v>1363</v>
-      </c>
-      <c r="AI52" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AJ52" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK52" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL52" s="44" t="s">
-        <v>1474</v>
-      </c>
-      <c r="AM52" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN52" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO52" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP52">
-        <v>0</v>
-      </c>
-      <c r="AQ52">
-        <v>0</v>
-      </c>
-      <c r="AR52">
-        <v>1</v>
-      </c>
-      <c r="AS52" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT52">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV52">
-        <v>0</v>
-      </c>
-      <c r="AW52">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="s">
-        <v>36</v>
-      </c>
-      <c r="AY52" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ52" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA52">
-        <v>0</v>
-      </c>
-      <c r="BB52">
-        <v>0</v>
-      </c>
-      <c r="BC52">
-        <v>0</v>
-      </c>
-      <c r="BD52">
-        <v>1</v>
-      </c>
-      <c r="BE52" t="s">
-        <v>1762</v>
-      </c>
-      <c r="BF52" t="s">
-        <v>36</v>
-      </c>
-      <c r="BG52" t="s">
-        <v>1659</v>
-      </c>
-      <c r="BH52">
-        <v>0</v>
-      </c>
-      <c r="BI52" s="46" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="53" spans="1:61">
+      <c r="BI52">
+        <v>0</v>
+      </c>
+      <c r="BJ52" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:62">
       <c r="A53" s="44" t="s">
-        <v>1902</v>
+        <v>1888</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -67429,10 +67598,10 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -67506,56 +67675,56 @@
       <c r="AG53" t="s">
         <v>36</v>
       </c>
-      <c r="AH53" s="44" t="s">
+      <c r="AH53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI53" s="44" t="s">
         <v>1363</v>
-      </c>
-      <c r="AI53" s="44" t="s">
-        <v>1470</v>
       </c>
       <c r="AJ53" s="44" t="s">
         <v>1470</v>
       </c>
-      <c r="AK53" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL53" s="44" t="s">
+      <c r="AK53" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL53" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="AM53" s="44">
-        <v>1</v>
-      </c>
-      <c r="AN53" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO53" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP53">
+      <c r="AN53" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP53" s="44">
         <v>0</v>
       </c>
       <c r="AQ53">
         <v>0</v>
       </c>
       <c r="AR53">
-        <v>1</v>
-      </c>
-      <c r="AS53" t="s">
-        <v>36</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV53">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>1</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU53">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>36</v>
       </c>
       <c r="AW53">
         <v>0</v>
       </c>
-      <c r="AX53" t="s">
-        <v>36</v>
+      <c r="AX53">
+        <v>0</v>
       </c>
       <c r="AY53" t="s">
         <v>36</v>
@@ -67563,8 +67732,8 @@
       <c r="AZ53" t="s">
         <v>36</v>
       </c>
-      <c r="BA53">
-        <v>0</v>
+      <c r="BA53" t="s">
+        <v>36</v>
       </c>
       <c r="BB53">
         <v>0</v>
@@ -67573,93 +67742,592 @@
         <v>0</v>
       </c>
       <c r="BD53">
-        <v>1</v>
-      </c>
-      <c r="BE53" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>1</v>
+      </c>
+      <c r="BF53" t="s">
         <v>1762</v>
       </c>
-      <c r="BF53" t="s">
-        <v>36</v>
-      </c>
       <c r="BG53" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH53" t="s">
         <v>1659</v>
       </c>
-      <c r="BH53">
-        <v>0</v>
-      </c>
-      <c r="BI53" s="46" t="s">
+      <c r="BI53">
+        <v>10</v>
+      </c>
+      <c r="BJ53" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:62">
+      <c r="A54" s="44" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>10</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>3</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>1</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>-1</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>10</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI54" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ54" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK54" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL54" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN54" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO54" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP54" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>1</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU54">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW54">
+        <v>0</v>
+      </c>
+      <c r="AX54">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ54" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA54" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>0</v>
+      </c>
+      <c r="BD54">
+        <v>0</v>
+      </c>
+      <c r="BE54">
+        <v>1</v>
+      </c>
+      <c r="BF54" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG54" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH54" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI54">
+        <v>0</v>
+      </c>
+      <c r="BJ54" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:62">
+      <c r="A55" s="44" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>3</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>1</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>-1</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>10</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI55" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ55" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK55" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL55" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN55" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO55" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP55" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>1</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU55">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW55">
+        <v>0</v>
+      </c>
+      <c r="AX55">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA55" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB55">
+        <v>0</v>
+      </c>
+      <c r="BC55">
+        <v>0</v>
+      </c>
+      <c r="BD55">
+        <v>0</v>
+      </c>
+      <c r="BE55">
+        <v>1</v>
+      </c>
+      <c r="BF55" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG55" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH55" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI55">
+        <v>0</v>
+      </c>
+      <c r="BJ55" s="46" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="56" spans="1:62">
+      <c r="A56" s="44" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>3</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>1</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>-1</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>10</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI56" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ56" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK56" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL56" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN56" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO56" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP56" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>1</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU56">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW56">
+        <v>0</v>
+      </c>
+      <c r="AX56">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA56" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB56">
+        <v>0</v>
+      </c>
+      <c r="BC56">
+        <v>0</v>
+      </c>
+      <c r="BD56">
+        <v>0</v>
+      </c>
+      <c r="BE56">
+        <v>1</v>
+      </c>
+      <c r="BF56" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG56" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH56" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI56">
+        <v>0</v>
+      </c>
+      <c r="BJ56" s="46" t="s">
         <v>1903</v>
       </c>
     </row>
-    <row r="54" spans="1:61">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="BI54" s="46"/>
-    </row>
-    <row r="55" spans="1:61">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="BI55" s="46"/>
-    </row>
-    <row r="56" spans="1:61">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="3"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="1:61">
+    <row r="57" spans="1:62">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -67680,8 +68348,9 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
-    </row>
-    <row r="58" spans="1:61">
+      <c r="BJ57" s="46"/>
+    </row>
+    <row r="58" spans="1:62">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -67702,8 +68371,9 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
-    </row>
-    <row r="59" spans="1:61">
+      <c r="BJ58" s="46"/>
+    </row>
+    <row r="59" spans="1:62">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -67725,7 +68395,7 @@
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
     </row>
-    <row r="60" spans="1:61">
+    <row r="60" spans="1:62">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -67747,7 +68417,7 @@
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
     </row>
-    <row r="61" spans="1:61">
+    <row r="61" spans="1:62">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -67769,7 +68439,7 @@
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
     </row>
-    <row r="62" spans="1:61">
+    <row r="62" spans="1:62">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -67791,7 +68461,7 @@
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
     </row>
-    <row r="63" spans="1:61">
+    <row r="63" spans="1:62">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -67813,7 +68483,7 @@
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
     </row>
-    <row r="64" spans="1:61">
+    <row r="64" spans="1:62">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -68274,6 +68944,72 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="1:20">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="1:20">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="1:20">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AABDF2-B90A-44F4-8CB4-21EFDFBBBFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D020BE0-36F8-473F-A808-CAF83C3760B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9705" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9807" uniqueCount="1924">
   <si>
     <t>NAME</t>
   </si>
@@ -5908,6 +5908,54 @@
   </si>
   <si>
     <t>do_strike</t>
+  </si>
+  <si>
+    <t>magic_arrow</t>
+  </si>
+  <si>
+    <t>light_arrow</t>
+  </si>
+  <si>
+    <t>fire_arrow,ice_arrow,earth_arrow</t>
+  </si>
+  <si>
+    <t>crit_strike,basic_buff_atk</t>
+  </si>
+  <si>
+    <t>basic_poison</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>bleed</t>
+  </si>
+  <si>
+    <t>bleed_strike</t>
+  </si>
+  <si>
+    <t>bleed,100</t>
+  </si>
+  <si>
+    <t>poison,100</t>
+  </si>
+  <si>
+    <t>taunt,100</t>
+  </si>
+  <si>
+    <t>buff_crit,100</t>
+  </si>
+  <si>
+    <t>buff_atk1,100</t>
+  </si>
+  <si>
+    <t>blind,100</t>
+  </si>
+  <si>
+    <t>buff_def1,100</t>
+  </si>
+  <si>
+    <t>basic_poison,basic_heal,blind_strike</t>
   </si>
 </sst>
 </file>
@@ -6566,7 +6614,7 @@
     <col min="27" max="27" width="8.36328125" customWidth="1"/>
     <col min="28" max="28" width="19" customWidth="1"/>
     <col min="29" max="29" width="36.08984375" customWidth="1"/>
-    <col min="30" max="30" width="22.453125" customWidth="1"/>
+    <col min="30" max="30" width="27.08984375" customWidth="1"/>
     <col min="31" max="31" width="18.26953125" customWidth="1"/>
     <col min="37" max="37" width="15" customWidth="1"/>
     <col min="40" max="40" width="8.453125" customWidth="1"/>
@@ -21363,7 +21411,7 @@
         <v>33</v>
       </c>
       <c r="AC80" s="40" t="s">
-        <v>1687</v>
+        <v>1911</v>
       </c>
       <c r="AD80" s="40" t="s">
         <v>42</v>
@@ -21551,7 +21599,7 @@
         <v>33</v>
       </c>
       <c r="AC81" s="40" t="s">
-        <v>1687</v>
+        <v>1923</v>
       </c>
       <c r="AD81" s="40" t="s">
         <v>42</v>
@@ -21739,7 +21787,7 @@
         <v>33</v>
       </c>
       <c r="AC82" s="40" t="s">
-        <v>1687</v>
+        <v>1910</v>
       </c>
       <c r="AD82" s="40" t="s">
         <v>42</v>
@@ -57892,7 +57940,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BK87"/>
+  <dimension ref="A1:BK93"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -57924,7 +57972,7 @@
     <col min="31" max="31" width="13.81640625" customWidth="1"/>
     <col min="32" max="32" width="7.1796875" customWidth="1"/>
     <col min="33" max="33" width="13.08984375" customWidth="1"/>
-    <col min="34" max="34" width="11.54296875" customWidth="1"/>
+    <col min="34" max="34" width="13.6328125" customWidth="1"/>
     <col min="35" max="35" width="13.81640625" customWidth="1"/>
     <col min="36" max="36" width="9.6328125" customWidth="1"/>
     <col min="37" max="37" width="8.08984375" customWidth="1"/>
@@ -60776,7 +60824,7 @@
     </row>
     <row r="16" spans="1:63">
       <c r="A16" s="44" t="s">
-        <v>1485</v>
+        <v>1912</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -60845,7 +60893,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -60875,7 +60923,7 @@
         <v>36</v>
       </c>
       <c r="AH16" t="s">
-        <v>1494</v>
+        <v>1917</v>
       </c>
       <c r="AI16" s="44" t="s">
         <v>1363</v>
@@ -60964,19 +61012,19 @@
     </row>
     <row r="17" spans="1:62">
       <c r="A17" s="44" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -61030,10 +61078,10 @@
         <v>0</v>
       </c>
       <c r="W17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -61063,7 +61111,7 @@
         <v>36</v>
       </c>
       <c r="AH17" t="s">
-        <v>36</v>
+        <v>1494</v>
       </c>
       <c r="AI17" s="44" t="s">
         <v>1363</v>
@@ -61084,7 +61132,7 @@
         <v>1</v>
       </c>
       <c r="AO17" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP17" s="44">
         <v>0</v>
@@ -61093,7 +61141,7 @@
         <v>0</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17">
         <v>1</v>
@@ -61123,7 +61171,7 @@
         <v>36</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC17">
         <v>0</v>
@@ -61135,13 +61183,13 @@
         <v>0</v>
       </c>
       <c r="BF17" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG17" t="s">
         <v>36</v>
       </c>
       <c r="BH17" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="BI17">
         <v>0</v>
@@ -61152,7 +61200,7 @@
     </row>
     <row r="18" spans="1:62">
       <c r="A18" s="44" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -61164,7 +61212,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -61173,10 +61221,10 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -61323,13 +61371,13 @@
         <v>0</v>
       </c>
       <c r="BF18" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BG18" t="s">
         <v>36</v>
       </c>
       <c r="BH18" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="BI18">
         <v>0</v>
@@ -61340,10 +61388,10 @@
     </row>
     <row r="19" spans="1:62">
       <c r="A19" s="44" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -61352,19 +61400,19 @@
         <v>0</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>20</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -61427,13 +61475,13 @@
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="s">
         <v>36</v>
@@ -61469,7 +61517,7 @@
         <v>0</v>
       </c>
       <c r="AR19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS19">
         <v>1</v>
@@ -61487,7 +61535,7 @@
         <v>0</v>
       </c>
       <c r="AX19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="s">
         <v>36</v>
@@ -61511,13 +61559,13 @@
         <v>0</v>
       </c>
       <c r="BF19" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BG19" t="s">
         <v>36</v>
       </c>
       <c r="BH19" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="BI19">
         <v>0</v>
@@ -61528,13 +61576,13 @@
     </row>
     <row r="20" spans="1:62">
       <c r="A20" s="44" t="s">
-        <v>1501</v>
+        <v>1915</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -61594,7 +61642,7 @@
         <v>0</v>
       </c>
       <c r="W20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -61615,19 +61663,19 @@
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="s">
         <v>36</v>
       </c>
       <c r="AH20" t="s">
-        <v>36</v>
+        <v>1916</v>
       </c>
       <c r="AI20" s="44" t="s">
         <v>1363</v>
@@ -61648,7 +61696,7 @@
         <v>1</v>
       </c>
       <c r="AO20" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP20" s="44">
         <v>0</v>
@@ -61660,7 +61708,7 @@
         <v>1</v>
       </c>
       <c r="AS20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="s">
         <v>36</v>
@@ -61699,13 +61747,13 @@
         <v>0</v>
       </c>
       <c r="BF20" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="BG20" t="s">
         <v>36</v>
       </c>
       <c r="BH20" t="s">
-        <v>1672</v>
+        <v>1657</v>
       </c>
       <c r="BI20">
         <v>0</v>
@@ -61716,10 +61764,10 @@
     </row>
     <row r="21" spans="1:62">
       <c r="A21" s="44" t="s">
-        <v>1502</v>
+        <v>1914</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -61728,7 +61776,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -61785,7 +61833,7 @@
         <v>3</v>
       </c>
       <c r="X21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y21">
         <v>0</v>
@@ -61803,19 +61851,19 @@
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="s">
         <v>36</v>
       </c>
       <c r="AH21" t="s">
-        <v>1501</v>
+        <v>36</v>
       </c>
       <c r="AI21" s="44" t="s">
         <v>1363</v>
@@ -61833,10 +61881,10 @@
         <v>1474</v>
       </c>
       <c r="AN21" s="44">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AO21" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP21" s="44">
         <v>0</v>
@@ -61848,7 +61896,7 @@
         <v>1</v>
       </c>
       <c r="AS21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT21" t="s">
         <v>36</v>
@@ -61863,7 +61911,7 @@
         <v>0</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY21" t="s">
         <v>36</v>
@@ -61887,13 +61935,13 @@
         <v>0</v>
       </c>
       <c r="BF21" t="s">
-        <v>37</v>
+        <v>1760</v>
       </c>
       <c r="BG21" t="s">
         <v>36</v>
       </c>
       <c r="BH21" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="BI21">
         <v>0</v>
@@ -61904,19 +61952,19 @@
     </row>
     <row r="22" spans="1:62">
       <c r="A22" s="44" t="s">
-        <v>1431</v>
+        <v>1913</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -61976,28 +62024,28 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC22">
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="s">
         <v>36</v>
@@ -62024,7 +62072,7 @@
         <v>1</v>
       </c>
       <c r="AO22" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP22" s="44">
         <v>0</v>
@@ -62036,7 +62084,7 @@
         <v>1</v>
       </c>
       <c r="AS22">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT22" t="s">
         <v>36</v>
@@ -62048,10 +62096,10 @@
         <v>36</v>
       </c>
       <c r="AW22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="s">
         <v>36</v>
@@ -62075,13 +62123,13 @@
         <v>0</v>
       </c>
       <c r="BF22" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG22" t="s">
         <v>36</v>
       </c>
       <c r="BH22" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="BI22">
         <v>0</v>
@@ -62092,10 +62140,10 @@
     </row>
     <row r="23" spans="1:62">
       <c r="A23" s="44" t="s">
-        <v>1551</v>
+        <v>1494</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -62104,7 +62152,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -62179,13 +62227,13 @@
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="s">
         <v>36</v>
@@ -62194,7 +62242,7 @@
         <v>36</v>
       </c>
       <c r="AI23" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ23" s="44" t="s">
         <v>1470</v>
@@ -62212,10 +62260,10 @@
         <v>1</v>
       </c>
       <c r="AO23" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP23" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
         <v>0</v>
@@ -62224,22 +62272,22 @@
         <v>1</v>
       </c>
       <c r="AS23">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT23" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AU23">
         <v>0</v>
       </c>
       <c r="AV23" t="s">
-        <v>1554</v>
+        <v>36</v>
       </c>
       <c r="AW23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="s">
         <v>36</v>
@@ -62263,13 +62311,13 @@
         <v>0</v>
       </c>
       <c r="BF23" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BG23" t="s">
         <v>36</v>
       </c>
       <c r="BH23" t="s">
-        <v>1658</v>
+        <v>1671</v>
       </c>
       <c r="BI23">
         <v>0</v>
@@ -62280,7 +62328,7 @@
     </row>
     <row r="24" spans="1:62">
       <c r="A24" s="44" t="s">
-        <v>1587</v>
+        <v>1501</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -62343,10 +62391,10 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -62367,13 +62415,13 @@
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="s">
         <v>36</v>
@@ -62382,7 +62430,7 @@
         <v>36</v>
       </c>
       <c r="AI24" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ24" s="44" t="s">
         <v>1470</v>
@@ -62400,7 +62448,7 @@
         <v>1</v>
       </c>
       <c r="AO24" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP24" s="44">
         <v>0</v>
@@ -62451,13 +62499,13 @@
         <v>0</v>
       </c>
       <c r="BF24" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="BG24" t="s">
         <v>36</v>
       </c>
       <c r="BH24" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
       <c r="BI24">
         <v>0</v>
@@ -62468,7 +62516,7 @@
     </row>
     <row r="25" spans="1:62">
       <c r="A25" s="44" t="s">
-        <v>935</v>
+        <v>1502</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -62480,7 +62528,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -62537,7 +62585,7 @@
         <v>3</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25">
         <v>0</v>
@@ -62567,10 +62615,10 @@
         <v>36</v>
       </c>
       <c r="AH25" t="s">
-        <v>36</v>
+        <v>1918</v>
       </c>
       <c r="AI25" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ25" s="44" t="s">
         <v>1470</v>
@@ -62585,13 +62633,13 @@
         <v>1474</v>
       </c>
       <c r="AN25" s="44">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AO25" s="44" t="s">
         <v>36</v>
       </c>
       <c r="AP25" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
         <v>0</v>
@@ -62600,7 +62648,7 @@
         <v>1</v>
       </c>
       <c r="AS25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="s">
         <v>36</v>
@@ -62639,13 +62687,13 @@
         <v>0</v>
       </c>
       <c r="BF25" t="s">
-        <v>1760</v>
+        <v>37</v>
       </c>
       <c r="BG25" t="s">
         <v>36</v>
       </c>
       <c r="BH25" t="s">
-        <v>1658</v>
+        <v>1673</v>
       </c>
       <c r="BI25">
         <v>0</v>
@@ -62656,13 +62704,13 @@
     </row>
     <row r="26" spans="1:62">
       <c r="A26" s="44" t="s">
-        <v>1593</v>
+        <v>1431</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -62722,22 +62770,22 @@
         <v>0</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -62749,7 +62797,7 @@
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG26" t="s">
         <v>36</v>
@@ -62758,7 +62806,7 @@
         <v>36</v>
       </c>
       <c r="AI26" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ26" s="44" t="s">
         <v>1470</v>
@@ -62779,7 +62827,7 @@
         <v>36</v>
       </c>
       <c r="AP26" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
         <v>0</v>
@@ -62788,7 +62836,7 @@
         <v>1</v>
       </c>
       <c r="AS26">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT26" t="s">
         <v>36</v>
@@ -62800,7 +62848,7 @@
         <v>36</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX26">
         <v>0</v>
@@ -62827,13 +62875,13 @@
         <v>0</v>
       </c>
       <c r="BF26" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG26" t="s">
         <v>36</v>
       </c>
       <c r="BH26" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
       <c r="BI26">
         <v>0</v>
@@ -62844,13 +62892,13 @@
     </row>
     <row r="27" spans="1:62">
       <c r="A27" s="44" t="s">
-        <v>1602</v>
+        <v>1551</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -62910,7 +62958,7 @@
         <v>0</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -62946,7 +62994,7 @@
         <v>36</v>
       </c>
       <c r="AI27" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ27" s="44" t="s">
         <v>1470</v>
@@ -62967,7 +63015,7 @@
         <v>36</v>
       </c>
       <c r="AP27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>0</v>
@@ -62976,19 +63024,19 @@
         <v>1</v>
       </c>
       <c r="AS27">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT27" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AU27">
         <v>0</v>
       </c>
       <c r="AV27" t="s">
-        <v>36</v>
+        <v>1554</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX27">
         <v>0</v>
@@ -63015,7 +63063,7 @@
         <v>0</v>
       </c>
       <c r="BF27" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG27" t="s">
         <v>36</v>
@@ -63032,7 +63080,7 @@
     </row>
     <row r="28" spans="1:62">
       <c r="A28" s="44" t="s">
-        <v>1611</v>
+        <v>1587</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -63095,10 +63143,10 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -63155,7 +63203,7 @@
         <v>36</v>
       </c>
       <c r="AP28" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
         <v>0</v>
@@ -63164,19 +63212,19 @@
         <v>1</v>
       </c>
       <c r="AS28">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT28" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AU28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="s">
         <v>36</v>
       </c>
       <c r="AW28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX28">
         <v>0</v>
@@ -63203,13 +63251,13 @@
         <v>0</v>
       </c>
       <c r="BF28" t="s">
-        <v>37</v>
+        <v>1764</v>
       </c>
       <c r="BG28" t="s">
         <v>36</v>
       </c>
       <c r="BH28" t="s">
-        <v>1559</v>
+        <v>1658</v>
       </c>
       <c r="BI28">
         <v>0</v>
@@ -63220,13 +63268,13 @@
     </row>
     <row r="29" spans="1:62">
       <c r="A29" s="44" t="s">
-        <v>1615</v>
+        <v>935</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -63286,7 +63334,7 @@
         <v>0</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X29">
         <v>0</v>
@@ -63322,7 +63370,7 @@
         <v>36</v>
       </c>
       <c r="AI29" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ29" s="44" t="s">
         <v>1470</v>
@@ -63343,7 +63391,7 @@
         <v>36</v>
       </c>
       <c r="AP29" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -63391,7 +63439,7 @@
         <v>0</v>
       </c>
       <c r="BF29" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG29" t="s">
         <v>36</v>
@@ -63408,13 +63456,13 @@
     </row>
     <row r="30" spans="1:62">
       <c r="A30" s="44" t="s">
-        <v>1616</v>
+        <v>1593</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -63474,7 +63522,7 @@
         <v>0</v>
       </c>
       <c r="W30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -63510,7 +63558,7 @@
         <v>36</v>
       </c>
       <c r="AI30" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ30" s="44" t="s">
         <v>1470</v>
@@ -63531,7 +63579,7 @@
         <v>36</v>
       </c>
       <c r="AP30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -63579,7 +63627,7 @@
         <v>0</v>
       </c>
       <c r="BF30" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="BG30" t="s">
         <v>36</v>
@@ -63596,7 +63644,7 @@
     </row>
     <row r="31" spans="1:62">
       <c r="A31" s="44" t="s">
-        <v>1620</v>
+        <v>1602</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -63662,10 +63710,10 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -63698,7 +63746,7 @@
         <v>36</v>
       </c>
       <c r="AI31" s="44" t="s">
-        <v>1621</v>
+        <v>1363</v>
       </c>
       <c r="AJ31" s="44" t="s">
         <v>1470</v>
@@ -63767,7 +63815,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="BG31" t="s">
         <v>36</v>
@@ -63784,13 +63832,13 @@
     </row>
     <row r="32" spans="1:62">
       <c r="A32" s="44" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -63886,7 +63934,7 @@
         <v>36</v>
       </c>
       <c r="AI32" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ32" s="44" t="s">
         <v>1470</v>
@@ -63907,7 +63955,7 @@
         <v>36</v>
       </c>
       <c r="AP32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>0</v>
@@ -63916,19 +63964,19 @@
         <v>1</v>
       </c>
       <c r="AS32">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT32" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="s">
         <v>36</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32">
         <v>0</v>
@@ -63940,7 +63988,7 @@
         <v>36</v>
       </c>
       <c r="BA32" t="s">
-        <v>1624</v>
+        <v>36</v>
       </c>
       <c r="BB32">
         <v>0</v>
@@ -63955,13 +64003,13 @@
         <v>0</v>
       </c>
       <c r="BF32" t="s">
-        <v>1760</v>
+        <v>37</v>
       </c>
       <c r="BG32" t="s">
         <v>36</v>
       </c>
       <c r="BH32" t="s">
-        <v>896</v>
+        <v>1559</v>
       </c>
       <c r="BI32">
         <v>0</v>
@@ -63972,13 +64020,13 @@
     </row>
     <row r="33" spans="1:62">
       <c r="A33" s="44" t="s">
-        <v>1647</v>
+        <v>1615</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -64143,13 +64191,13 @@
         <v>0</v>
       </c>
       <c r="BF33" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG33" t="s">
         <v>36</v>
       </c>
       <c r="BH33" t="s">
-        <v>896</v>
+        <v>1658</v>
       </c>
       <c r="BI33">
         <v>0</v>
@@ -64160,13 +64208,13 @@
     </row>
     <row r="34" spans="1:62">
       <c r="A34" s="44" t="s">
-        <v>1578</v>
+        <v>1616</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -64289,7 +64337,7 @@
         <v>0</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS34">
         <v>1</v>
@@ -64331,13 +64379,13 @@
         <v>0</v>
       </c>
       <c r="BF34" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG34" t="s">
         <v>36</v>
       </c>
       <c r="BH34" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="BI34">
         <v>0</v>
@@ -64348,13 +64396,13 @@
     </row>
     <row r="35" spans="1:62">
       <c r="A35" s="44" t="s">
-        <v>1686</v>
+        <v>1620</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -64414,10 +64462,10 @@
         <v>0</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y35">
         <v>0</v>
@@ -64450,7 +64498,7 @@
         <v>36</v>
       </c>
       <c r="AI35" s="44" t="s">
-        <v>1479</v>
+        <v>1621</v>
       </c>
       <c r="AJ35" s="44" t="s">
         <v>1470</v>
@@ -64471,7 +64519,7 @@
         <v>36</v>
       </c>
       <c r="AP35" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
         <v>0</v>
@@ -64519,13 +64567,13 @@
         <v>0</v>
       </c>
       <c r="BF35" t="s">
-        <v>37</v>
+        <v>1764</v>
       </c>
       <c r="BG35" t="s">
         <v>36</v>
       </c>
       <c r="BH35" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="BI35">
         <v>0</v>
@@ -64536,13 +64584,13 @@
     </row>
     <row r="36" spans="1:62">
       <c r="A36" s="44" t="s">
-        <v>1728</v>
+        <v>1624</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -64665,7 +64713,7 @@
         <v>0</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS36">
         <v>1</v>
@@ -64692,7 +64740,7 @@
         <v>36</v>
       </c>
       <c r="BA36" t="s">
-        <v>36</v>
+        <v>1624</v>
       </c>
       <c r="BB36">
         <v>0</v>
@@ -64707,7 +64755,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG36" t="s">
         <v>36</v>
@@ -64724,7 +64772,7 @@
     </row>
     <row r="37" spans="1:62">
       <c r="A37" s="44" t="s">
-        <v>1786</v>
+        <v>1647</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -64742,7 +64790,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -64790,7 +64838,7 @@
         <v>0</v>
       </c>
       <c r="W37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X37">
         <v>0</v>
@@ -64895,13 +64943,13 @@
         <v>0</v>
       </c>
       <c r="BF37" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG37" t="s">
         <v>36</v>
       </c>
       <c r="BH37" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI37">
         <v>0</v>
@@ -64912,7 +64960,7 @@
     </row>
     <row r="38" spans="1:62">
       <c r="A38" s="44" t="s">
-        <v>1905</v>
+        <v>1578</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -64981,7 +65029,7 @@
         <v>3</v>
       </c>
       <c r="X38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -65008,13 +65056,13 @@
         <v>10</v>
       </c>
       <c r="AG38" t="s">
-        <v>1907</v>
+        <v>36</v>
       </c>
       <c r="AH38" t="s">
-        <v>1906</v>
+        <v>36</v>
       </c>
       <c r="AI38" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ38" s="44" t="s">
         <v>1470</v>
@@ -65041,7 +65089,7 @@
         <v>0</v>
       </c>
       <c r="AR38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS38">
         <v>1</v>
@@ -65083,13 +65131,13 @@
         <v>0</v>
       </c>
       <c r="BF38" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BG38" t="s">
         <v>36</v>
       </c>
       <c r="BH38" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI38">
         <v>0</v>
@@ -65100,10 +65148,10 @@
     </row>
     <row r="39" spans="1:62">
       <c r="A39" s="44" t="s">
-        <v>1906</v>
+        <v>1686</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -65139,7 +65187,7 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -65166,7 +65214,7 @@
         <v>0</v>
       </c>
       <c r="W39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -65187,13 +65235,13 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG39" t="s">
         <v>36</v>
@@ -65223,13 +65271,13 @@
         <v>36</v>
       </c>
       <c r="AP39" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ39">
         <v>0</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS39">
         <v>1</v>
@@ -65247,7 +65295,7 @@
         <v>0</v>
       </c>
       <c r="AX39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="s">
         <v>36</v>
@@ -65271,13 +65319,13 @@
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>1761</v>
+        <v>37</v>
       </c>
       <c r="BG39" t="s">
         <v>36</v>
       </c>
       <c r="BH39" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI39">
         <v>0</v>
@@ -65288,13 +65336,13 @@
     </row>
     <row r="40" spans="1:62">
       <c r="A40" s="44" t="s">
-        <v>1907</v>
+        <v>1728</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -65354,7 +65402,7 @@
         <v>0</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -65417,10 +65465,10 @@
         <v>0</v>
       </c>
       <c r="AR40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT40" t="s">
         <v>36</v>
@@ -65459,13 +65507,13 @@
         <v>0</v>
       </c>
       <c r="BF40" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="BG40" t="s">
         <v>36</v>
       </c>
       <c r="BH40" t="s">
-        <v>1657</v>
+        <v>896</v>
       </c>
       <c r="BI40">
         <v>0</v>
@@ -65476,7 +65524,7 @@
     </row>
     <row r="41" spans="1:62">
       <c r="A41" s="44" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -65494,7 +65542,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -65542,10 +65590,10 @@
         <v>0</v>
       </c>
       <c r="W41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -65575,10 +65623,10 @@
         <v>36</v>
       </c>
       <c r="AH41" t="s">
-        <v>1796</v>
+        <v>36</v>
       </c>
       <c r="AI41" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ41" s="44" t="s">
         <v>1470</v>
@@ -65647,7 +65695,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BG41" t="s">
         <v>36</v>
@@ -65664,10 +65712,10 @@
     </row>
     <row r="42" spans="1:62">
       <c r="A42" s="44" t="s">
-        <v>1796</v>
+        <v>1905</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -65676,7 +65724,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -65733,7 +65781,7 @@
         <v>3</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -65751,19 +65799,19 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG42" t="s">
-        <v>36</v>
+        <v>1907</v>
       </c>
       <c r="AH42" t="s">
-        <v>36</v>
+        <v>1919</v>
       </c>
       <c r="AI42" s="44" t="s">
         <v>1479</v>
@@ -65793,7 +65841,7 @@
         <v>0</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS42">
         <v>1</v>
@@ -65811,7 +65859,7 @@
         <v>0</v>
       </c>
       <c r="AX42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="s">
         <v>36</v>
@@ -65835,7 +65883,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BG42" t="s">
         <v>36</v>
@@ -65852,10 +65900,10 @@
     </row>
     <row r="43" spans="1:62">
       <c r="A43" s="44" t="s">
-        <v>1805</v>
+        <v>1906</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -65891,7 +65939,7 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -65909,7 +65957,7 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -65939,13 +65987,13 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="s">
         <v>36</v>
@@ -65957,7 +66005,7 @@
         <v>1479</v>
       </c>
       <c r="AJ43" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK43" s="44" t="s">
         <v>1470</v>
@@ -65981,7 +66029,7 @@
         <v>0</v>
       </c>
       <c r="AR43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS43">
         <v>1</v>
@@ -65999,7 +66047,7 @@
         <v>0</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY43" t="s">
         <v>36</v>
@@ -66023,7 +66071,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG43" t="s">
         <v>36</v>
@@ -66040,13 +66088,13 @@
     </row>
     <row r="44" spans="1:62">
       <c r="A44" s="44" t="s">
-        <v>1807</v>
+        <v>1907</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -66106,7 +66154,7 @@
         <v>0</v>
       </c>
       <c r="W44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -66142,10 +66190,10 @@
         <v>36</v>
       </c>
       <c r="AI44" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ44" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK44" s="44" t="s">
         <v>1470</v>
@@ -66172,7 +66220,7 @@
         <v>1</v>
       </c>
       <c r="AS44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="s">
         <v>36</v>
@@ -66211,13 +66259,13 @@
         <v>0</v>
       </c>
       <c r="BF44" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG44" t="s">
         <v>36</v>
       </c>
       <c r="BH44" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="BI44">
         <v>0</v>
@@ -66228,7 +66276,7 @@
     </row>
     <row r="45" spans="1:62">
       <c r="A45" s="44" t="s">
-        <v>1868</v>
+        <v>1797</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -66240,7 +66288,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -66327,10 +66375,10 @@
         <v>36</v>
       </c>
       <c r="AH45" t="s">
-        <v>1869</v>
+        <v>1920</v>
       </c>
       <c r="AI45" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ45" s="44" t="s">
         <v>1470</v>
@@ -66405,7 +66453,7 @@
         <v>36</v>
       </c>
       <c r="BH45" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI45">
         <v>0</v>
@@ -66416,19 +66464,19 @@
     </row>
     <row r="46" spans="1:62">
       <c r="A46" s="44" t="s">
-        <v>1869</v>
+        <v>1796</v>
       </c>
       <c r="B46">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -66518,7 +66566,7 @@
         <v>36</v>
       </c>
       <c r="AI46" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ46" s="44" t="s">
         <v>1470</v>
@@ -66593,7 +66641,7 @@
         <v>36</v>
       </c>
       <c r="BH46" t="s">
-        <v>896</v>
+        <v>1663</v>
       </c>
       <c r="BI46">
         <v>0</v>
@@ -66604,7 +66652,7 @@
     </row>
     <row r="47" spans="1:62">
       <c r="A47" s="44" t="s">
-        <v>1870</v>
+        <v>1805</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -66661,7 +66709,7 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -66673,7 +66721,7 @@
         <v>3</v>
       </c>
       <c r="X47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y47">
         <v>0</v>
@@ -66703,13 +66751,13 @@
         <v>36</v>
       </c>
       <c r="AH47" t="s">
-        <v>1871</v>
+        <v>36</v>
       </c>
       <c r="AI47" s="44" t="s">
         <v>1479</v>
       </c>
       <c r="AJ47" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK47" s="44" t="s">
         <v>1470</v>
@@ -66775,7 +66823,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BG47" t="s">
         <v>36</v>
@@ -66792,10 +66840,10 @@
     </row>
     <row r="48" spans="1:62">
       <c r="A48" s="44" t="s">
-        <v>1871</v>
+        <v>1807</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -66819,7 +66867,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -66879,13 +66927,13 @@
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE48">
         <v>0</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG48" t="s">
         <v>36</v>
@@ -66897,7 +66945,7 @@
         <v>1479</v>
       </c>
       <c r="AJ48" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK48" s="44" t="s">
         <v>1470</v>
@@ -66921,7 +66969,7 @@
         <v>0</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS48">
         <v>1</v>
@@ -66939,7 +66987,7 @@
         <v>0</v>
       </c>
       <c r="AX48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="s">
         <v>36</v>
@@ -66963,13 +67011,13 @@
         <v>0</v>
       </c>
       <c r="BF48" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG48" t="s">
         <v>36</v>
       </c>
       <c r="BH48" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI48">
         <v>0</v>
@@ -66980,7 +67028,7 @@
     </row>
     <row r="49" spans="1:62">
       <c r="A49" s="44" t="s">
-        <v>1883</v>
+        <v>1868</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -66992,13 +67040,13 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -67046,10 +67094,10 @@
         <v>0</v>
       </c>
       <c r="W49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y49">
         <v>0</v>
@@ -67079,7 +67127,7 @@
         <v>36</v>
       </c>
       <c r="AH49" t="s">
-        <v>36</v>
+        <v>1921</v>
       </c>
       <c r="AI49" s="44" t="s">
         <v>1363</v>
@@ -67151,13 +67199,13 @@
         <v>0</v>
       </c>
       <c r="BF49" t="s">
-        <v>37</v>
+        <v>1763</v>
       </c>
       <c r="BG49" t="s">
         <v>36</v>
       </c>
       <c r="BH49" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI49">
         <v>0</v>
@@ -67168,16 +67216,16 @@
     </row>
     <row r="50" spans="1:62">
       <c r="A50" s="44" t="s">
-        <v>1884</v>
+        <v>1869</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -67186,7 +67234,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -67234,7 +67282,7 @@
         <v>0</v>
       </c>
       <c r="W50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -67255,13 +67303,13 @@
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE50">
         <v>0</v>
       </c>
       <c r="AF50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="s">
         <v>36</v>
@@ -67297,7 +67345,7 @@
         <v>0</v>
       </c>
       <c r="AR50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS50">
         <v>1</v>
@@ -67315,7 +67363,7 @@
         <v>0</v>
       </c>
       <c r="AX50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY50" t="s">
         <v>36</v>
@@ -67339,13 +67387,13 @@
         <v>0</v>
       </c>
       <c r="BF50" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG50" t="s">
         <v>36</v>
       </c>
       <c r="BH50" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI50">
         <v>0</v>
@@ -67356,7 +67404,7 @@
     </row>
     <row r="51" spans="1:62">
       <c r="A51" s="44" t="s">
-        <v>1885</v>
+        <v>1870</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -67374,7 +67422,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -67422,10 +67470,10 @@
         <v>0</v>
       </c>
       <c r="W51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y51">
         <v>0</v>
@@ -67455,10 +67503,10 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>36</v>
+        <v>1922</v>
       </c>
       <c r="AI51" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ51" s="44" t="s">
         <v>1470</v>
@@ -67527,7 +67575,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG51" t="s">
         <v>36</v>
@@ -67542,31 +67590,186 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:62" ht="14">
-      <c r="A52" s="55" t="s">
-        <v>1887</v>
-      </c>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
+    <row r="52" spans="1:62">
+      <c r="A52" s="44" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>50</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>3</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>1</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>5</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
       <c r="AG52" t="s">
         <v>36</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI52" s="44" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AJ52" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK52" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL52" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN52" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO52" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP52" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>1</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU52">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW52">
+        <v>0</v>
+      </c>
+      <c r="AX52">
+        <v>1</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
+        <v>0</v>
+      </c>
+      <c r="BD52">
+        <v>0</v>
+      </c>
+      <c r="BE52">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BG52" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH52" t="s">
+        <v>1663</v>
       </c>
       <c r="BI52">
         <v>0</v>
@@ -67577,7 +67780,7 @@
     </row>
     <row r="53" spans="1:62">
       <c r="A53" s="44" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -67595,13 +67798,13 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -67643,7 +67846,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -67706,7 +67909,7 @@
         <v>0</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS53">
         <v>1</v>
@@ -67745,19 +67948,19 @@
         <v>0</v>
       </c>
       <c r="BE53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="s">
-        <v>1762</v>
+        <v>37</v>
       </c>
       <c r="BG53" t="s">
         <v>36</v>
       </c>
       <c r="BH53" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ53" s="46" t="s">
         <v>36</v>
@@ -67765,7 +67968,7 @@
     </row>
     <row r="54" spans="1:62">
       <c r="A54" s="44" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -67783,7 +67986,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -67810,7 +68013,7 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -67831,7 +68034,7 @@
         <v>0</v>
       </c>
       <c r="W54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X54">
         <v>0</v>
@@ -67894,7 +68097,7 @@
         <v>0</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS54">
         <v>1</v>
@@ -67933,16 +68136,16 @@
         <v>0</v>
       </c>
       <c r="BE54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="BG54" t="s">
         <v>36</v>
       </c>
       <c r="BH54" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI54">
         <v>0</v>
@@ -67953,7 +68156,7 @@
     </row>
     <row r="55" spans="1:62">
       <c r="A55" s="44" t="s">
-        <v>1898</v>
+        <v>1909</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -67971,7 +68174,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -68019,7 +68222,7 @@
         <v>0</v>
       </c>
       <c r="W55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X55">
         <v>0</v>
@@ -68082,7 +68285,7 @@
         <v>0</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS55">
         <v>1</v>
@@ -68121,27 +68324,27 @@
         <v>0</v>
       </c>
       <c r="BE55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG55" t="s">
         <v>36</v>
       </c>
       <c r="BH55" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI55">
         <v>0</v>
       </c>
       <c r="BJ55" s="46" t="s">
-        <v>1901</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:62">
       <c r="A56" s="44" t="s">
-        <v>1902</v>
+        <v>1908</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -68159,7 +68362,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -68207,7 +68410,7 @@
         <v>0</v>
       </c>
       <c r="W56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X56">
         <v>0</v>
@@ -68270,7 +68473,7 @@
         <v>0</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS56">
         <v>1</v>
@@ -68309,57 +68512,224 @@
         <v>0</v>
       </c>
       <c r="BE56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG56" t="s">
         <v>36</v>
       </c>
       <c r="BH56" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI56">
         <v>0</v>
       </c>
       <c r="BJ56" s="46" t="s">
-        <v>1903</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:62">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="BJ57" s="46"/>
-    </row>
-    <row r="58" spans="1:62">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="A57" s="44" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>4</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>1</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>-1</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>10</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI57" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ57" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK57" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL57" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN57" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO57" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP57" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>1</v>
+      </c>
+      <c r="AS57">
+        <v>1</v>
+      </c>
+      <c r="AT57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU57">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW57">
+        <v>0</v>
+      </c>
+      <c r="AX57">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA57" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB57">
+        <v>0</v>
+      </c>
+      <c r="BC57">
+        <v>0</v>
+      </c>
+      <c r="BD57">
+        <v>0</v>
+      </c>
+      <c r="BE57">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BG57" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH57" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI57">
+        <v>0</v>
+      </c>
+      <c r="BJ57" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:62" ht="14">
+      <c r="A58" s="55" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B58" s="55"/>
+      <c r="C58" s="55"/>
+      <c r="D58" s="55"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
@@ -68371,95 +68741,767 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
-      <c r="BJ58" s="46"/>
+      <c r="AG58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI58">
+        <v>0</v>
+      </c>
+      <c r="BJ58" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="59" spans="1:62">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
+      <c r="A59" s="44" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>200</v>
+      </c>
+      <c r="I59">
+        <v>200</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>3</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>1</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>-1</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>10</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI59" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ59" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK59" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL59" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN59" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO59" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP59" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>1</v>
+      </c>
+      <c r="AT59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU59">
+        <v>0</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW59">
+        <v>0</v>
+      </c>
+      <c r="AX59">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ59" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA59" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB59">
+        <v>0</v>
+      </c>
+      <c r="BC59">
+        <v>0</v>
+      </c>
+      <c r="BD59">
+        <v>0</v>
+      </c>
+      <c r="BE59">
+        <v>1</v>
+      </c>
+      <c r="BF59" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG59" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH59" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI59">
+        <v>10</v>
+      </c>
+      <c r="BJ59" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="60" spans="1:62">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
+      <c r="A60" s="44" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>10</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>3</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>1</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>-1</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>10</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI60" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ60" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK60" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL60" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN60" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO60" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP60" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>1</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU60">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW60">
+        <v>0</v>
+      </c>
+      <c r="AX60">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ60" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA60" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB60">
+        <v>0</v>
+      </c>
+      <c r="BC60">
+        <v>0</v>
+      </c>
+      <c r="BD60">
+        <v>0</v>
+      </c>
+      <c r="BE60">
+        <v>1</v>
+      </c>
+      <c r="BF60" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG60" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH60" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI60">
+        <v>0</v>
+      </c>
+      <c r="BJ60" s="46" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="61" spans="1:62">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
+      <c r="A61" s="44" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>3</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>1</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>-1</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>10</v>
+      </c>
+      <c r="AG61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI61" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ61" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK61" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL61" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN61" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO61" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP61" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>1</v>
+      </c>
+      <c r="AT61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU61">
+        <v>0</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW61">
+        <v>0</v>
+      </c>
+      <c r="AX61">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ61" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA61" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB61">
+        <v>0</v>
+      </c>
+      <c r="BC61">
+        <v>0</v>
+      </c>
+      <c r="BD61">
+        <v>0</v>
+      </c>
+      <c r="BE61">
+        <v>1</v>
+      </c>
+      <c r="BF61" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG61" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH61" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI61">
+        <v>0</v>
+      </c>
+      <c r="BJ61" s="46" t="s">
+        <v>1901</v>
+      </c>
     </row>
     <row r="62" spans="1:62">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
+      <c r="A62" s="44" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>3</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>1</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>-1</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>10</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI62" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ62" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK62" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL62" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN62" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO62" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP62" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>1</v>
+      </c>
+      <c r="AT62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU62">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW62">
+        <v>0</v>
+      </c>
+      <c r="AX62">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA62" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB62">
+        <v>0</v>
+      </c>
+      <c r="BC62">
+        <v>0</v>
+      </c>
+      <c r="BD62">
+        <v>0</v>
+      </c>
+      <c r="BE62">
+        <v>1</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH62" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI62">
+        <v>0</v>
+      </c>
+      <c r="BJ62" s="46" t="s">
+        <v>1903</v>
+      </c>
     </row>
     <row r="63" spans="1:62">
       <c r="A63" s="3"/>
@@ -68482,6 +69524,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
+      <c r="BJ63" s="46"/>
     </row>
     <row r="64" spans="1:62">
       <c r="A64" s="3"/>
@@ -68504,6 +69547,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
+      <c r="BJ64" s="46"/>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" s="3"/>
@@ -69010,6 +70054,138 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="1:20">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="1:20">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+      <c r="S89" s="3"/>
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="1:20">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="1:20">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="3"/>
+      <c r="S91" s="3"/>
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="1:20">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="1:20">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+      <c r="S93" s="3"/>
+      <c r="T93" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D020BE0-36F8-473F-A808-CAF83C3760B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5312B713-55FD-4667-88D5-7D10231F588F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9807" uniqueCount="1924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10028" uniqueCount="1946">
   <si>
     <t>NAME</t>
   </si>
@@ -5956,6 +5956,72 @@
   </si>
   <si>
     <t>basic_poison,basic_heal,blind_strike</t>
+  </si>
+  <si>
+    <t>basic_buff_mag</t>
+  </si>
+  <si>
+    <t>buff_mag1</t>
+  </si>
+  <si>
+    <t>magic_shld</t>
+  </si>
+  <si>
+    <t>buff_res1</t>
+  </si>
+  <si>
+    <t>drain_strike</t>
+  </si>
+  <si>
+    <t>mute_strike</t>
+  </si>
+  <si>
+    <t>debuf_res1</t>
+  </si>
+  <si>
+    <t>basic_buff_mag,magic_shld,drain_strike,mute_strike</t>
+  </si>
+  <si>
+    <t>debuf_mag1</t>
+  </si>
+  <si>
+    <t>debuf_mag1,100</t>
+  </si>
+  <si>
+    <t>do_strike,100</t>
+  </si>
+  <si>
+    <t>nightmare</t>
+  </si>
+  <si>
+    <t>asleep</t>
+  </si>
+  <si>
+    <t>asleep,100</t>
+  </si>
+  <si>
+    <t>sleep,1</t>
+  </si>
+  <si>
+    <t>inferno</t>
+  </si>
+  <si>
+    <t>burn2,25</t>
+  </si>
+  <si>
+    <t>burn2</t>
+  </si>
+  <si>
+    <t>basic_harm,25</t>
+  </si>
+  <si>
+    <t>nightmare,inferno</t>
+  </si>
+  <si>
+    <t>mana_reduc1</t>
+  </si>
+  <si>
+    <t>mana_reduction,-10</t>
   </si>
 </sst>
 </file>
@@ -6613,7 +6679,7 @@
     <col min="26" max="26" width="9.26953125" customWidth="1"/>
     <col min="27" max="27" width="8.36328125" customWidth="1"/>
     <col min="28" max="28" width="19" customWidth="1"/>
-    <col min="29" max="29" width="36.08984375" customWidth="1"/>
+    <col min="29" max="29" width="48.453125" customWidth="1"/>
     <col min="30" max="30" width="27.08984375" customWidth="1"/>
     <col min="31" max="31" width="18.26953125" customWidth="1"/>
     <col min="37" max="37" width="15" customWidth="1"/>
@@ -21975,13 +22041,13 @@
         <v>33</v>
       </c>
       <c r="AC83" s="40" t="s">
-        <v>1687</v>
+        <v>1931</v>
       </c>
       <c r="AD83" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AE83" s="40" t="s">
-        <v>1886</v>
+      <c r="AE83" s="59" t="s">
+        <v>1902</v>
       </c>
       <c r="AF83" s="40">
         <v>40</v>
@@ -22163,7 +22229,7 @@
         <v>33</v>
       </c>
       <c r="AC84" s="40" t="s">
-        <v>1687</v>
+        <v>1943</v>
       </c>
       <c r="AD84" s="40" t="s">
         <v>42</v>
@@ -57940,7 +58006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BK93"/>
+  <dimension ref="A1:BK105"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -57972,7 +58038,7 @@
     <col min="31" max="31" width="13.81640625" customWidth="1"/>
     <col min="32" max="32" width="7.1796875" customWidth="1"/>
     <col min="33" max="33" width="13.08984375" customWidth="1"/>
-    <col min="34" max="34" width="13.6328125" customWidth="1"/>
+    <col min="34" max="34" width="15.26953125" customWidth="1"/>
     <col min="35" max="35" width="13.81640625" customWidth="1"/>
     <col min="36" max="36" width="9.6328125" customWidth="1"/>
     <col min="37" max="37" width="8.08984375" customWidth="1"/>
@@ -58380,13 +58446,13 @@
     </row>
     <row r="3" spans="1:63">
       <c r="A3" s="44" t="s">
-        <v>1900</v>
+        <v>1928</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -58425,7 +58491,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -58568,13 +58634,13 @@
     </row>
     <row r="4" spans="1:63">
       <c r="A4" s="44" t="s">
-        <v>42</v>
+        <v>1900</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -58634,7 +58700,7 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -58661,7 +58727,7 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="s">
         <v>36</v>
@@ -58739,13 +58805,13 @@
         <v>0</v>
       </c>
       <c r="BF4" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BG4" t="s">
         <v>36</v>
       </c>
       <c r="BH4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="BI4">
         <v>0</v>
@@ -58756,13 +58822,13 @@
     </row>
     <row r="5" spans="1:63">
       <c r="A5" s="44" t="s">
-        <v>1371</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -58777,10 +58843,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -58822,7 +58888,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -58849,7 +58915,7 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="s">
         <v>36</v>
@@ -58885,10 +58951,10 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="s">
         <v>36</v>
@@ -58924,16 +58990,16 @@
         <v>0</v>
       </c>
       <c r="BE5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG5" t="s">
         <v>36</v>
       </c>
       <c r="BH5" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="BI5">
         <v>0</v>
@@ -58944,7 +59010,7 @@
     </row>
     <row r="6" spans="1:63">
       <c r="A6" s="44" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -58956,19 +59022,19 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>20</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -59112,16 +59178,16 @@
         <v>0</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BG6" t="s">
         <v>36</v>
       </c>
       <c r="BH6" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="BI6">
         <v>0</v>
@@ -59132,19 +59198,19 @@
     </row>
     <row r="7" spans="1:63">
       <c r="A7" s="44" t="s">
-        <v>1890</v>
+        <v>1372</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -59234,10 +59300,10 @@
         <v>36</v>
       </c>
       <c r="AI7" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ7" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK7" s="44" t="s">
         <v>1470</v>
@@ -59261,7 +59327,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS7">
         <v>1</v>
@@ -59303,7 +59369,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BG7" t="s">
         <v>36</v>
@@ -59320,13 +59386,13 @@
     </row>
     <row r="8" spans="1:63">
       <c r="A8" s="44" t="s">
-        <v>1469</v>
+        <v>1890</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -59508,13 +59574,13 @@
     </row>
     <row r="9" spans="1:63">
       <c r="A9" s="44" t="s">
-        <v>1483</v>
+        <v>1469</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -59613,7 +59679,7 @@
         <v>1479</v>
       </c>
       <c r="AJ9" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK9" s="44" t="s">
         <v>1470</v>
@@ -59640,10 +59706,10 @@
         <v>1</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT9" t="s">
-        <v>1481</v>
+        <v>36</v>
       </c>
       <c r="AU9">
         <v>0</v>
@@ -59679,13 +59745,13 @@
         <v>0</v>
       </c>
       <c r="BF9" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BG9" t="s">
         <v>36</v>
       </c>
       <c r="BH9" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="BI9">
         <v>0</v>
@@ -59696,13 +59762,13 @@
     </row>
     <row r="10" spans="1:63">
       <c r="A10" s="44" t="s">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -59789,7 +59855,7 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="s">
         <v>36</v>
@@ -59798,7 +59864,7 @@
         <v>36</v>
       </c>
       <c r="AI10" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ10" s="44" t="s">
         <v>1470</v>
@@ -59831,7 +59897,7 @@
         <v>60</v>
       </c>
       <c r="AT10" t="s">
-        <v>36</v>
+        <v>1481</v>
       </c>
       <c r="AU10">
         <v>0</v>
@@ -59840,7 +59906,7 @@
         <v>36</v>
       </c>
       <c r="AW10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX10">
         <v>0</v>
@@ -59867,13 +59933,13 @@
         <v>0</v>
       </c>
       <c r="BF10" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG10" t="s">
         <v>36</v>
       </c>
       <c r="BH10" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="BI10">
         <v>0</v>
@@ -59884,13 +59950,13 @@
     </row>
     <row r="11" spans="1:63">
       <c r="A11" s="44" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -59953,7 +60019,7 @@
         <v>3</v>
       </c>
       <c r="X11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y11">
         <v>0</v>
@@ -59968,7 +60034,7 @@
         <v>1</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>-1</v>
@@ -60055,13 +60121,13 @@
         <v>0</v>
       </c>
       <c r="BF11" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BG11" t="s">
         <v>36</v>
       </c>
       <c r="BH11" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="BI11">
         <v>0</v>
@@ -60072,19 +60138,19 @@
     </row>
     <row r="12" spans="1:63">
       <c r="A12" s="44" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -60141,7 +60207,7 @@
         <v>3</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12">
         <v>0</v>
@@ -60156,7 +60222,7 @@
         <v>1</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12">
         <v>-1</v>
@@ -60165,7 +60231,7 @@
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="s">
         <v>36</v>
@@ -60201,10 +60267,10 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT12" t="s">
         <v>36</v>
@@ -60216,7 +60282,7 @@
         <v>36</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX12">
         <v>0</v>
@@ -60243,13 +60309,13 @@
         <v>0</v>
       </c>
       <c r="BF12" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BG12" t="s">
         <v>36</v>
       </c>
       <c r="BH12" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="BI12">
         <v>0</v>
@@ -60260,7 +60326,7 @@
     </row>
     <row r="13" spans="1:63">
       <c r="A13" s="44" t="s">
-        <v>1524</v>
+        <v>1447</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -60272,7 +60338,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -60281,10 +60347,10 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -60431,13 +60497,13 @@
         <v>0</v>
       </c>
       <c r="BF13" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG13" t="s">
         <v>36</v>
       </c>
       <c r="BH13" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="BI13">
         <v>0</v>
@@ -60448,7 +60514,7 @@
     </row>
     <row r="14" spans="1:63">
       <c r="A14" s="44" t="s">
-        <v>1448</v>
+        <v>1524</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -60469,10 +60535,10 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -60619,13 +60685,13 @@
         <v>0</v>
       </c>
       <c r="BF14" t="s">
-        <v>37</v>
+        <v>1762</v>
       </c>
       <c r="BG14" t="s">
         <v>36</v>
       </c>
       <c r="BH14" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="BI14">
         <v>0</v>
@@ -60636,7 +60702,7 @@
     </row>
     <row r="15" spans="1:63">
       <c r="A15" s="44" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -60657,13 +60723,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -60807,13 +60873,13 @@
         <v>0</v>
       </c>
       <c r="BF15" t="s">
-        <v>1765</v>
+        <v>37</v>
       </c>
       <c r="BG15" t="s">
         <v>36</v>
       </c>
       <c r="BH15" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="BI15">
         <v>0</v>
@@ -60824,13 +60890,13 @@
     </row>
     <row r="16" spans="1:63">
       <c r="A16" s="44" t="s">
-        <v>1912</v>
+        <v>1449</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -60851,7 +60917,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -60890,7 +60956,7 @@
         <v>0</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -60917,13 +60983,13 @@
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="s">
         <v>36</v>
       </c>
       <c r="AH16" t="s">
-        <v>1917</v>
+        <v>36</v>
       </c>
       <c r="AI16" s="44" t="s">
         <v>1363</v>
@@ -60953,7 +61019,7 @@
         <v>0</v>
       </c>
       <c r="AR16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS16">
         <v>1</v>
@@ -60983,7 +61049,7 @@
         <v>36</v>
       </c>
       <c r="BB16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BC16">
         <v>0</v>
@@ -60995,13 +61061,13 @@
         <v>0</v>
       </c>
       <c r="BF16" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BG16" t="s">
         <v>36</v>
       </c>
       <c r="BH16" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="BI16">
         <v>0</v>
@@ -61012,7 +61078,7 @@
     </row>
     <row r="17" spans="1:62">
       <c r="A17" s="44" t="s">
-        <v>1485</v>
+        <v>1912</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -61081,7 +61147,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -61111,7 +61177,7 @@
         <v>36</v>
       </c>
       <c r="AH17" t="s">
-        <v>1494</v>
+        <v>1917</v>
       </c>
       <c r="AI17" s="44" t="s">
         <v>1363</v>
@@ -61200,19 +61266,19 @@
     </row>
     <row r="18" spans="1:62">
       <c r="A18" s="44" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -61266,10 +61332,10 @@
         <v>0</v>
       </c>
       <c r="W18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -61299,7 +61365,7 @@
         <v>36</v>
       </c>
       <c r="AH18" t="s">
-        <v>36</v>
+        <v>1494</v>
       </c>
       <c r="AI18" s="44" t="s">
         <v>1363</v>
@@ -61320,7 +61386,7 @@
         <v>1</v>
       </c>
       <c r="AO18" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP18" s="44">
         <v>0</v>
@@ -61329,7 +61395,7 @@
         <v>0</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS18">
         <v>1</v>
@@ -61359,7 +61425,7 @@
         <v>36</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC18">
         <v>0</v>
@@ -61371,13 +61437,13 @@
         <v>0</v>
       </c>
       <c r="BF18" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG18" t="s">
         <v>36</v>
       </c>
       <c r="BH18" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="BI18">
         <v>0</v>
@@ -61388,7 +61454,7 @@
     </row>
     <row r="19" spans="1:62">
       <c r="A19" s="44" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -61400,7 +61466,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -61409,10 +61475,10 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -61559,13 +61625,13 @@
         <v>0</v>
       </c>
       <c r="BF19" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="BG19" t="s">
         <v>36</v>
       </c>
       <c r="BH19" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="BI19">
         <v>0</v>
@@ -61576,13 +61642,13 @@
     </row>
     <row r="20" spans="1:62">
       <c r="A20" s="44" t="s">
-        <v>1915</v>
+        <v>1490</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -61597,10 +61663,10 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -61642,7 +61708,7 @@
         <v>0</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -61675,7 +61741,7 @@
         <v>36</v>
       </c>
       <c r="AH20" t="s">
-        <v>1916</v>
+        <v>36</v>
       </c>
       <c r="AI20" s="44" t="s">
         <v>1363</v>
@@ -61696,7 +61762,7 @@
         <v>1</v>
       </c>
       <c r="AO20" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP20" s="44">
         <v>0</v>
@@ -61705,10 +61771,10 @@
         <v>0</v>
       </c>
       <c r="AR20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT20" t="s">
         <v>36</v>
@@ -61753,7 +61819,7 @@
         <v>36</v>
       </c>
       <c r="BH20" t="s">
-        <v>1657</v>
+        <v>1670</v>
       </c>
       <c r="BI20">
         <v>0</v>
@@ -61764,106 +61830,106 @@
     </row>
     <row r="21" spans="1:62">
       <c r="A21" s="44" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>5</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
         <v>-1</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>20</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>3</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>5</v>
-      </c>
       <c r="AE21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="s">
         <v>36</v>
       </c>
       <c r="AH21" t="s">
-        <v>36</v>
+        <v>1916</v>
       </c>
       <c r="AI21" s="44" t="s">
         <v>1363</v>
@@ -61884,7 +61950,7 @@
         <v>1</v>
       </c>
       <c r="AO21" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP21" s="44">
         <v>0</v>
@@ -61896,7 +61962,7 @@
         <v>1</v>
       </c>
       <c r="AS21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="s">
         <v>36</v>
@@ -61911,7 +61977,7 @@
         <v>0</v>
       </c>
       <c r="AX21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="s">
         <v>36</v>
@@ -61941,7 +62007,7 @@
         <v>36</v>
       </c>
       <c r="BH21" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="BI21">
         <v>0</v>
@@ -61952,7 +62018,7 @@
     </row>
     <row r="22" spans="1:62">
       <c r="A22" s="44" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B22">
         <v>-1</v>
@@ -62123,7 +62189,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BG22" t="s">
         <v>36</v>
@@ -62140,106 +62206,106 @@
     </row>
     <row r="23" spans="1:62">
       <c r="A23" s="44" t="s">
-        <v>1494</v>
+        <v>1929</v>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
         <v>-1</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>20</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>3</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>5</v>
-      </c>
       <c r="AE23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="s">
         <v>36</v>
       </c>
       <c r="AH23" t="s">
-        <v>36</v>
+        <v>1933</v>
       </c>
       <c r="AI23" s="44" t="s">
         <v>1363</v>
@@ -62260,7 +62326,7 @@
         <v>1</v>
       </c>
       <c r="AO23" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP23" s="44">
         <v>0</v>
@@ -62272,7 +62338,7 @@
         <v>1</v>
       </c>
       <c r="AS23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="s">
         <v>36</v>
@@ -62287,7 +62353,7 @@
         <v>0</v>
       </c>
       <c r="AX23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="s">
         <v>36</v>
@@ -62311,13 +62377,13 @@
         <v>0</v>
       </c>
       <c r="BF23" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG23" t="s">
         <v>36</v>
       </c>
       <c r="BH23" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="BI23">
         <v>0</v>
@@ -62328,10 +62394,10 @@
     </row>
     <row r="24" spans="1:62">
       <c r="A24" s="44" t="s">
-        <v>1501</v>
+        <v>1932</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -62340,7 +62406,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -62475,7 +62541,7 @@
         <v>0</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY24" t="s">
         <v>36</v>
@@ -62499,13 +62565,13 @@
         <v>0</v>
       </c>
       <c r="BF24" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="BG24" t="s">
         <v>36</v>
       </c>
       <c r="BH24" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="BI24">
         <v>0</v>
@@ -62516,10 +62582,10 @@
     </row>
     <row r="25" spans="1:62">
       <c r="A25" s="44" t="s">
-        <v>1502</v>
+        <v>1930</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -62528,7 +62594,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -62546,7 +62612,7 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -62585,7 +62651,7 @@
         <v>3</v>
       </c>
       <c r="X25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25">
         <v>0</v>
@@ -62603,19 +62669,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="s">
         <v>36</v>
       </c>
       <c r="AH25" t="s">
-        <v>1918</v>
+        <v>36</v>
       </c>
       <c r="AI25" s="44" t="s">
         <v>1363</v>
@@ -62633,10 +62699,10 @@
         <v>1474</v>
       </c>
       <c r="AN25" s="44">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AO25" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP25" s="44">
         <v>0</v>
@@ -62648,7 +62714,7 @@
         <v>1</v>
       </c>
       <c r="AS25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="s">
         <v>36</v>
@@ -62663,7 +62729,7 @@
         <v>0</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY25" t="s">
         <v>36</v>
@@ -62687,13 +62753,13 @@
         <v>0</v>
       </c>
       <c r="BF25" t="s">
-        <v>37</v>
+        <v>1760</v>
       </c>
       <c r="BG25" t="s">
         <v>36</v>
       </c>
       <c r="BH25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="BI25">
         <v>0</v>
@@ -62704,19 +62770,19 @@
     </row>
     <row r="26" spans="1:62">
       <c r="A26" s="44" t="s">
-        <v>1431</v>
+        <v>1913</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -62776,28 +62842,28 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC26">
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="s">
         <v>36</v>
@@ -62824,7 +62890,7 @@
         <v>1</v>
       </c>
       <c r="AO26" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP26" s="44">
         <v>0</v>
@@ -62836,7 +62902,7 @@
         <v>1</v>
       </c>
       <c r="AS26">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT26" t="s">
         <v>36</v>
@@ -62848,10 +62914,10 @@
         <v>36</v>
       </c>
       <c r="AW26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY26" t="s">
         <v>36</v>
@@ -62875,13 +62941,13 @@
         <v>0</v>
       </c>
       <c r="BF26" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG26" t="s">
         <v>36</v>
       </c>
       <c r="BH26" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="BI26">
         <v>0</v>
@@ -62892,10 +62958,10 @@
     </row>
     <row r="27" spans="1:62">
       <c r="A27" s="44" t="s">
-        <v>1551</v>
+        <v>1494</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -62904,7 +62970,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -62979,13 +63045,13 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="s">
         <v>36</v>
@@ -62994,7 +63060,7 @@
         <v>36</v>
       </c>
       <c r="AI27" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ27" s="44" t="s">
         <v>1470</v>
@@ -63012,10 +63078,10 @@
         <v>1</v>
       </c>
       <c r="AO27" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP27" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
         <v>0</v>
@@ -63024,22 +63090,22 @@
         <v>1</v>
       </c>
       <c r="AS27">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT27" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AU27">
         <v>0</v>
       </c>
       <c r="AV27" t="s">
-        <v>1554</v>
+        <v>36</v>
       </c>
       <c r="AW27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY27" t="s">
         <v>36</v>
@@ -63063,13 +63129,13 @@
         <v>0</v>
       </c>
       <c r="BF27" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="BG27" t="s">
         <v>36</v>
       </c>
       <c r="BH27" t="s">
-        <v>1658</v>
+        <v>1671</v>
       </c>
       <c r="BI27">
         <v>0</v>
@@ -63080,7 +63146,7 @@
     </row>
     <row r="28" spans="1:62">
       <c r="A28" s="44" t="s">
-        <v>1587</v>
+        <v>1501</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -63143,10 +63209,10 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -63167,13 +63233,13 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="s">
         <v>36</v>
@@ -63182,7 +63248,7 @@
         <v>36</v>
       </c>
       <c r="AI28" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ28" s="44" t="s">
         <v>1470</v>
@@ -63200,7 +63266,7 @@
         <v>1</v>
       </c>
       <c r="AO28" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP28" s="44">
         <v>0</v>
@@ -63251,13 +63317,13 @@
         <v>0</v>
       </c>
       <c r="BF28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="BG28" t="s">
         <v>36</v>
       </c>
       <c r="BH28" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
       <c r="BI28">
         <v>0</v>
@@ -63268,7 +63334,7 @@
     </row>
     <row r="29" spans="1:62">
       <c r="A29" s="44" t="s">
-        <v>935</v>
+        <v>1502</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -63280,7 +63346,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -63337,7 +63403,7 @@
         <v>3</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y29">
         <v>0</v>
@@ -63367,10 +63433,10 @@
         <v>36</v>
       </c>
       <c r="AH29" t="s">
-        <v>36</v>
+        <v>1918</v>
       </c>
       <c r="AI29" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ29" s="44" t="s">
         <v>1470</v>
@@ -63385,13 +63451,13 @@
         <v>1474</v>
       </c>
       <c r="AN29" s="44">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AO29" s="44" t="s">
         <v>36</v>
       </c>
       <c r="AP29" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -63400,7 +63466,7 @@
         <v>1</v>
       </c>
       <c r="AS29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="s">
         <v>36</v>
@@ -63439,13 +63505,13 @@
         <v>0</v>
       </c>
       <c r="BF29" t="s">
-        <v>1760</v>
+        <v>37</v>
       </c>
       <c r="BG29" t="s">
         <v>36</v>
       </c>
       <c r="BH29" t="s">
-        <v>1658</v>
+        <v>1673</v>
       </c>
       <c r="BI29">
         <v>0</v>
@@ -63456,13 +63522,13 @@
     </row>
     <row r="30" spans="1:62">
       <c r="A30" s="44" t="s">
-        <v>1593</v>
+        <v>1431</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -63522,22 +63588,22 @@
         <v>0</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X30">
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -63549,7 +63615,7 @@
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="s">
         <v>36</v>
@@ -63558,7 +63624,7 @@
         <v>36</v>
       </c>
       <c r="AI30" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ30" s="44" t="s">
         <v>1470</v>
@@ -63579,7 +63645,7 @@
         <v>36</v>
       </c>
       <c r="AP30" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -63588,7 +63654,7 @@
         <v>1</v>
       </c>
       <c r="AS30">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT30" t="s">
         <v>36</v>
@@ -63600,7 +63666,7 @@
         <v>36</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX30">
         <v>0</v>
@@ -63627,13 +63693,13 @@
         <v>0</v>
       </c>
       <c r="BF30" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG30" t="s">
         <v>36</v>
       </c>
       <c r="BH30" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
       <c r="BI30">
         <v>0</v>
@@ -63644,13 +63710,13 @@
     </row>
     <row r="31" spans="1:62">
       <c r="A31" s="44" t="s">
-        <v>1602</v>
+        <v>1551</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -63710,7 +63776,7 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X31">
         <v>0</v>
@@ -63746,7 +63812,7 @@
         <v>36</v>
       </c>
       <c r="AI31" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ31" s="44" t="s">
         <v>1470</v>
@@ -63767,7 +63833,7 @@
         <v>36</v>
       </c>
       <c r="AP31" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>0</v>
@@ -63776,19 +63842,19 @@
         <v>1</v>
       </c>
       <c r="AS31">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT31" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AU31">
         <v>0</v>
       </c>
       <c r="AV31" t="s">
-        <v>36</v>
+        <v>1554</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX31">
         <v>0</v>
@@ -63815,7 +63881,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG31" t="s">
         <v>36</v>
@@ -63832,7 +63898,7 @@
     </row>
     <row r="32" spans="1:62">
       <c r="A32" s="44" t="s">
-        <v>1611</v>
+        <v>1587</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -63895,10 +63961,10 @@
         <v>0</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -63955,7 +64021,7 @@
         <v>36</v>
       </c>
       <c r="AP32" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
         <v>0</v>
@@ -63964,19 +64030,19 @@
         <v>1</v>
       </c>
       <c r="AS32">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="AT32" t="s">
-        <v>1552</v>
+        <v>36</v>
       </c>
       <c r="AU32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="s">
         <v>36</v>
       </c>
       <c r="AW32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX32">
         <v>0</v>
@@ -64003,13 +64069,13 @@
         <v>0</v>
       </c>
       <c r="BF32" t="s">
-        <v>37</v>
+        <v>1764</v>
       </c>
       <c r="BG32" t="s">
         <v>36</v>
       </c>
       <c r="BH32" t="s">
-        <v>1559</v>
+        <v>1658</v>
       </c>
       <c r="BI32">
         <v>0</v>
@@ -64020,13 +64086,13 @@
     </row>
     <row r="33" spans="1:62">
       <c r="A33" s="44" t="s">
-        <v>1615</v>
+        <v>935</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -64086,7 +64152,7 @@
         <v>0</v>
       </c>
       <c r="W33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -64122,7 +64188,7 @@
         <v>36</v>
       </c>
       <c r="AI33" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ33" s="44" t="s">
         <v>1470</v>
@@ -64143,7 +64209,7 @@
         <v>36</v>
       </c>
       <c r="AP33" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0</v>
@@ -64191,7 +64257,7 @@
         <v>0</v>
       </c>
       <c r="BF33" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG33" t="s">
         <v>36</v>
@@ -64208,13 +64274,13 @@
     </row>
     <row r="34" spans="1:62">
       <c r="A34" s="44" t="s">
-        <v>1616</v>
+        <v>1593</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -64274,7 +64340,7 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -64310,7 +64376,7 @@
         <v>36</v>
       </c>
       <c r="AI34" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ34" s="44" t="s">
         <v>1470</v>
@@ -64331,7 +64397,7 @@
         <v>36</v>
       </c>
       <c r="AP34" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>0</v>
@@ -64379,7 +64445,7 @@
         <v>0</v>
       </c>
       <c r="BF34" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="BG34" t="s">
         <v>36</v>
@@ -64396,7 +64462,7 @@
     </row>
     <row r="35" spans="1:62">
       <c r="A35" s="44" t="s">
-        <v>1620</v>
+        <v>1602</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -64462,10 +64528,10 @@
         <v>0</v>
       </c>
       <c r="W35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35">
         <v>0</v>
@@ -64498,7 +64564,7 @@
         <v>36</v>
       </c>
       <c r="AI35" s="44" t="s">
-        <v>1621</v>
+        <v>1363</v>
       </c>
       <c r="AJ35" s="44" t="s">
         <v>1470</v>
@@ -64567,7 +64633,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="BG35" t="s">
         <v>36</v>
@@ -64584,13 +64650,13 @@
     </row>
     <row r="36" spans="1:62">
       <c r="A36" s="44" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -64686,7 +64752,7 @@
         <v>36</v>
       </c>
       <c r="AI36" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ36" s="44" t="s">
         <v>1470</v>
@@ -64707,7 +64773,7 @@
         <v>36</v>
       </c>
       <c r="AP36" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
         <v>0</v>
@@ -64716,19 +64782,19 @@
         <v>1</v>
       </c>
       <c r="AS36">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AT36" t="s">
-        <v>36</v>
+        <v>1552</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV36" t="s">
         <v>36</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX36">
         <v>0</v>
@@ -64740,7 +64806,7 @@
         <v>36</v>
       </c>
       <c r="BA36" t="s">
-        <v>1624</v>
+        <v>36</v>
       </c>
       <c r="BB36">
         <v>0</v>
@@ -64755,13 +64821,13 @@
         <v>0</v>
       </c>
       <c r="BF36" t="s">
-        <v>1760</v>
+        <v>37</v>
       </c>
       <c r="BG36" t="s">
         <v>36</v>
       </c>
       <c r="BH36" t="s">
-        <v>896</v>
+        <v>1559</v>
       </c>
       <c r="BI36">
         <v>0</v>
@@ -64772,13 +64838,13 @@
     </row>
     <row r="37" spans="1:62">
       <c r="A37" s="44" t="s">
-        <v>1647</v>
+        <v>1615</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -64943,13 +65009,13 @@
         <v>0</v>
       </c>
       <c r="BF37" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG37" t="s">
         <v>36</v>
       </c>
       <c r="BH37" t="s">
-        <v>896</v>
+        <v>1658</v>
       </c>
       <c r="BI37">
         <v>0</v>
@@ -64960,13 +65026,13 @@
     </row>
     <row r="38" spans="1:62">
       <c r="A38" s="44" t="s">
-        <v>1578</v>
+        <v>1616</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -65089,7 +65155,7 @@
         <v>0</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS38">
         <v>1</v>
@@ -65131,13 +65197,13 @@
         <v>0</v>
       </c>
       <c r="BF38" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG38" t="s">
         <v>36</v>
       </c>
       <c r="BH38" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="BI38">
         <v>0</v>
@@ -65148,13 +65214,13 @@
     </row>
     <row r="39" spans="1:62">
       <c r="A39" s="44" t="s">
-        <v>1686</v>
+        <v>1620</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -65214,10 +65280,10 @@
         <v>0</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y39">
         <v>0</v>
@@ -65250,7 +65316,7 @@
         <v>36</v>
       </c>
       <c r="AI39" s="44" t="s">
-        <v>1479</v>
+        <v>1621</v>
       </c>
       <c r="AJ39" s="44" t="s">
         <v>1470</v>
@@ -65271,7 +65337,7 @@
         <v>36</v>
       </c>
       <c r="AP39" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
         <v>0</v>
@@ -65319,13 +65385,13 @@
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>37</v>
+        <v>1764</v>
       </c>
       <c r="BG39" t="s">
         <v>36</v>
       </c>
       <c r="BH39" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="BI39">
         <v>0</v>
@@ -65336,13 +65402,13 @@
     </row>
     <row r="40" spans="1:62">
       <c r="A40" s="44" t="s">
-        <v>1728</v>
+        <v>1624</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -65465,7 +65531,7 @@
         <v>0</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS40">
         <v>1</v>
@@ -65492,7 +65558,7 @@
         <v>36</v>
       </c>
       <c r="BA40" t="s">
-        <v>36</v>
+        <v>1624</v>
       </c>
       <c r="BB40">
         <v>0</v>
@@ -65507,7 +65573,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG40" t="s">
         <v>36</v>
@@ -65524,7 +65590,7 @@
     </row>
     <row r="41" spans="1:62">
       <c r="A41" s="44" t="s">
-        <v>1786</v>
+        <v>1647</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -65542,7 +65608,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -65590,7 +65656,7 @@
         <v>0</v>
       </c>
       <c r="W41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X41">
         <v>0</v>
@@ -65695,13 +65761,13 @@
         <v>0</v>
       </c>
       <c r="BF41" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG41" t="s">
         <v>36</v>
       </c>
       <c r="BH41" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI41">
         <v>0</v>
@@ -65712,7 +65778,7 @@
     </row>
     <row r="42" spans="1:62">
       <c r="A42" s="44" t="s">
-        <v>1905</v>
+        <v>1578</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -65781,7 +65847,7 @@
         <v>3</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -65808,13 +65874,13 @@
         <v>10</v>
       </c>
       <c r="AG42" t="s">
-        <v>1907</v>
+        <v>36</v>
       </c>
       <c r="AH42" t="s">
-        <v>1919</v>
+        <v>36</v>
       </c>
       <c r="AI42" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ42" s="44" t="s">
         <v>1470</v>
@@ -65841,7 +65907,7 @@
         <v>0</v>
       </c>
       <c r="AR42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS42">
         <v>1</v>
@@ -65883,13 +65949,13 @@
         <v>0</v>
       </c>
       <c r="BF42" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BG42" t="s">
         <v>36</v>
       </c>
       <c r="BH42" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI42">
         <v>0</v>
@@ -65900,10 +65966,10 @@
     </row>
     <row r="43" spans="1:62">
       <c r="A43" s="44" t="s">
-        <v>1906</v>
+        <v>1686</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -65939,7 +66005,7 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -65966,7 +66032,7 @@
         <v>0</v>
       </c>
       <c r="W43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -65987,13 +66053,13 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG43" t="s">
         <v>36</v>
@@ -66023,13 +66089,13 @@
         <v>36</v>
       </c>
       <c r="AP43" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>0</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS43">
         <v>1</v>
@@ -66047,7 +66113,7 @@
         <v>0</v>
       </c>
       <c r="AX43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="s">
         <v>36</v>
@@ -66071,13 +66137,13 @@
         <v>0</v>
       </c>
       <c r="BF43" t="s">
-        <v>1761</v>
+        <v>37</v>
       </c>
       <c r="BG43" t="s">
         <v>36</v>
       </c>
       <c r="BH43" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI43">
         <v>0</v>
@@ -66088,13 +66154,13 @@
     </row>
     <row r="44" spans="1:62">
       <c r="A44" s="44" t="s">
-        <v>1907</v>
+        <v>1728</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -66154,7 +66220,7 @@
         <v>0</v>
       </c>
       <c r="W44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -66217,10 +66283,10 @@
         <v>0</v>
       </c>
       <c r="AR44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT44" t="s">
         <v>36</v>
@@ -66259,13 +66325,13 @@
         <v>0</v>
       </c>
       <c r="BF44" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="BG44" t="s">
         <v>36</v>
       </c>
       <c r="BH44" t="s">
-        <v>1657</v>
+        <v>896</v>
       </c>
       <c r="BI44">
         <v>0</v>
@@ -66276,7 +66342,7 @@
     </row>
     <row r="45" spans="1:62">
       <c r="A45" s="44" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -66294,7 +66360,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -66342,10 +66408,10 @@
         <v>0</v>
       </c>
       <c r="W45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45">
         <v>0</v>
@@ -66375,10 +66441,10 @@
         <v>36</v>
       </c>
       <c r="AH45" t="s">
-        <v>1920</v>
+        <v>36</v>
       </c>
       <c r="AI45" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ45" s="44" t="s">
         <v>1470</v>
@@ -66447,7 +66513,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="BG45" t="s">
         <v>36</v>
@@ -66464,10 +66530,10 @@
     </row>
     <row r="46" spans="1:62">
       <c r="A46" s="44" t="s">
-        <v>1796</v>
+        <v>1905</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -66476,7 +66542,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -66533,7 +66599,7 @@
         <v>3</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y46">
         <v>0</v>
@@ -66551,19 +66617,19 @@
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG46" t="s">
-        <v>36</v>
+        <v>1934</v>
       </c>
       <c r="AH46" t="s">
-        <v>36</v>
+        <v>1919</v>
       </c>
       <c r="AI46" s="44" t="s">
         <v>1479</v>
@@ -66593,7 +66659,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS46">
         <v>1</v>
@@ -66611,7 +66677,7 @@
         <v>0</v>
       </c>
       <c r="AX46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="s">
         <v>36</v>
@@ -66635,7 +66701,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="BG46" t="s">
         <v>36</v>
@@ -66652,10 +66718,10 @@
     </row>
     <row r="47" spans="1:62">
       <c r="A47" s="44" t="s">
-        <v>1805</v>
+        <v>1906</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -66691,7 +66757,7 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -66709,7 +66775,7 @@
         <v>0</v>
       </c>
       <c r="T47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -66739,13 +66805,13 @@
         <v>0</v>
       </c>
       <c r="AD47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="s">
         <v>36</v>
@@ -66757,7 +66823,7 @@
         <v>1479</v>
       </c>
       <c r="AJ47" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK47" s="44" t="s">
         <v>1470</v>
@@ -66781,7 +66847,7 @@
         <v>0</v>
       </c>
       <c r="AR47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS47">
         <v>1</v>
@@ -66799,7 +66865,7 @@
         <v>0</v>
       </c>
       <c r="AX47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY47" t="s">
         <v>36</v>
@@ -66823,7 +66889,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG47" t="s">
         <v>36</v>
@@ -66840,13 +66906,13 @@
     </row>
     <row r="48" spans="1:62">
       <c r="A48" s="44" t="s">
-        <v>1807</v>
+        <v>1907</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -66906,7 +66972,7 @@
         <v>0</v>
       </c>
       <c r="W48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -66942,10 +67008,10 @@
         <v>36</v>
       </c>
       <c r="AI48" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ48" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK48" s="44" t="s">
         <v>1470</v>
@@ -66972,7 +67038,7 @@
         <v>1</v>
       </c>
       <c r="AS48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="s">
         <v>36</v>
@@ -67011,13 +67077,13 @@
         <v>0</v>
       </c>
       <c r="BF48" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="BG48" t="s">
         <v>36</v>
       </c>
       <c r="BH48" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="BI48">
         <v>0</v>
@@ -67028,7 +67094,7 @@
     </row>
     <row r="49" spans="1:62">
       <c r="A49" s="44" t="s">
-        <v>1868</v>
+        <v>1924</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -67040,7 +67106,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -67127,10 +67193,10 @@
         <v>36</v>
       </c>
       <c r="AH49" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AI49" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ49" s="44" t="s">
         <v>1470</v>
@@ -67205,7 +67271,7 @@
         <v>36</v>
       </c>
       <c r="BH49" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI49">
         <v>0</v>
@@ -67216,22 +67282,22 @@
     </row>
     <row r="50" spans="1:62">
       <c r="A50" s="44" t="s">
-        <v>1869</v>
+        <v>1925</v>
       </c>
       <c r="B50">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -67318,7 +67384,7 @@
         <v>36</v>
       </c>
       <c r="AI50" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ50" s="44" t="s">
         <v>1470</v>
@@ -67393,7 +67459,7 @@
         <v>36</v>
       </c>
       <c r="BH50" t="s">
-        <v>896</v>
+        <v>1663</v>
       </c>
       <c r="BI50">
         <v>0</v>
@@ -67404,7 +67470,7 @@
     </row>
     <row r="51" spans="1:62">
       <c r="A51" s="44" t="s">
-        <v>1870</v>
+        <v>1797</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -67503,7 +67569,7 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="AI51" s="44" t="s">
         <v>1479</v>
@@ -67592,7 +67658,7 @@
     </row>
     <row r="52" spans="1:62">
       <c r="A52" s="44" t="s">
-        <v>1871</v>
+        <v>1796</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -67604,7 +67670,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -67619,7 +67685,7 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -67780,7 +67846,7 @@
     </row>
     <row r="53" spans="1:62">
       <c r="A53" s="44" t="s">
-        <v>1883</v>
+        <v>1805</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -67798,7 +67864,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -67837,7 +67903,7 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -67846,7 +67912,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -67882,10 +67948,10 @@
         <v>36</v>
       </c>
       <c r="AI53" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ53" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK53" s="44" t="s">
         <v>1470</v>
@@ -67951,7 +68017,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="s">
-        <v>37</v>
+        <v>1765</v>
       </c>
       <c r="BG53" t="s">
         <v>36</v>
@@ -67968,7 +68034,7 @@
     </row>
     <row r="54" spans="1:62">
       <c r="A54" s="44" t="s">
-        <v>1884</v>
+        <v>1807</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -67986,7 +68052,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -68034,7 +68100,7 @@
         <v>0</v>
       </c>
       <c r="W54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X54">
         <v>0</v>
@@ -68070,10 +68136,10 @@
         <v>36</v>
       </c>
       <c r="AI54" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ54" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK54" s="44" t="s">
         <v>1470</v>
@@ -68145,7 +68211,7 @@
         <v>36</v>
       </c>
       <c r="BH54" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI54">
         <v>0</v>
@@ -68156,7 +68222,7 @@
     </row>
     <row r="55" spans="1:62">
       <c r="A55" s="44" t="s">
-        <v>1909</v>
+        <v>1935</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -68168,13 +68234,13 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -68222,10 +68288,10 @@
         <v>0</v>
       </c>
       <c r="W55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y55">
         <v>0</v>
@@ -68255,7 +68321,7 @@
         <v>36</v>
       </c>
       <c r="AH55" t="s">
-        <v>36</v>
+        <v>1937</v>
       </c>
       <c r="AI55" s="44" t="s">
         <v>1363</v>
@@ -68327,13 +68393,13 @@
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="BG55" t="s">
         <v>36</v>
       </c>
       <c r="BH55" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI55">
         <v>0</v>
@@ -68344,7 +68410,7 @@
     </row>
     <row r="56" spans="1:62">
       <c r="A56" s="44" t="s">
-        <v>1908</v>
+        <v>1936</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -68362,7 +68428,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -68410,7 +68476,7 @@
         <v>0</v>
       </c>
       <c r="W56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X56">
         <v>0</v>
@@ -68431,13 +68497,13 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="s">
         <v>36</v>
@@ -68473,7 +68539,7 @@
         <v>0</v>
       </c>
       <c r="AR56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS56">
         <v>1</v>
@@ -68491,7 +68557,7 @@
         <v>0</v>
       </c>
       <c r="AX56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY56" t="s">
         <v>36</v>
@@ -68521,18 +68587,18 @@
         <v>36</v>
       </c>
       <c r="BH56" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI56">
         <v>0</v>
       </c>
       <c r="BJ56" s="46" t="s">
-        <v>36</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="57" spans="1:62">
       <c r="A57" s="44" t="s">
-        <v>1885</v>
+        <v>1868</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -68544,13 +68610,13 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -68598,10 +68664,10 @@
         <v>0</v>
       </c>
       <c r="W57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y57">
         <v>0</v>
@@ -68631,7 +68697,7 @@
         <v>36</v>
       </c>
       <c r="AH57" t="s">
-        <v>36</v>
+        <v>1921</v>
       </c>
       <c r="AI57" s="44" t="s">
         <v>1363</v>
@@ -68703,13 +68769,13 @@
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG57" t="s">
         <v>36</v>
       </c>
       <c r="BH57" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI57">
         <v>0</v>
@@ -68718,31 +68784,186 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:62" ht="14">
-      <c r="A58" s="55" t="s">
-        <v>1887</v>
-      </c>
-      <c r="B58" s="55"/>
-      <c r="C58" s="55"/>
-      <c r="D58" s="55"/>
-      <c r="E58" s="55"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="55"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="3"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
+    <row r="58" spans="1:62">
+      <c r="A58" s="44" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B58">
+        <v>-1</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>-50</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>3</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>1</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>5</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
       <c r="AG58" t="s">
         <v>36</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI58" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ58" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK58" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL58" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN58" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO58" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP58" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>1</v>
+      </c>
+      <c r="AT58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU58">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW58">
+        <v>0</v>
+      </c>
+      <c r="AX58">
+        <v>1</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB58">
+        <v>0</v>
+      </c>
+      <c r="BC58">
+        <v>0</v>
+      </c>
+      <c r="BD58">
+        <v>0</v>
+      </c>
+      <c r="BE58">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BG58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH58" t="s">
+        <v>896</v>
       </c>
       <c r="BI58">
         <v>0</v>
@@ -68753,7 +68974,7 @@
     </row>
     <row r="59" spans="1:62">
       <c r="A59" s="44" t="s">
-        <v>1888</v>
+        <v>1926</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -68774,10 +68995,10 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -68822,7 +69043,7 @@
         <v>3</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -68852,10 +69073,10 @@
         <v>36</v>
       </c>
       <c r="AH59" t="s">
-        <v>36</v>
+        <v>1922</v>
       </c>
       <c r="AI59" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ59" s="44" t="s">
         <v>1470</v>
@@ -68882,7 +69103,7 @@
         <v>0</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS59">
         <v>1</v>
@@ -68921,19 +69142,19 @@
         <v>0</v>
       </c>
       <c r="BE59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG59" t="s">
         <v>36</v>
       </c>
       <c r="BH59" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI59">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ59" s="46" t="s">
         <v>36</v>
@@ -68941,10 +69162,10 @@
     </row>
     <row r="60" spans="1:62">
       <c r="A60" s="44" t="s">
-        <v>1889</v>
+        <v>1927</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -68971,7 +69192,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -68986,7 +69207,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -69028,13 +69249,13 @@
         <v>0</v>
       </c>
       <c r="AD60">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE60">
         <v>0</v>
       </c>
       <c r="AF60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="s">
         <v>36</v>
@@ -69043,7 +69264,7 @@
         <v>36</v>
       </c>
       <c r="AI60" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ60" s="44" t="s">
         <v>1470</v>
@@ -69088,7 +69309,7 @@
         <v>0</v>
       </c>
       <c r="AX60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY60" t="s">
         <v>36</v>
@@ -69109,16 +69330,16 @@
         <v>0</v>
       </c>
       <c r="BE60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG60" t="s">
         <v>36</v>
       </c>
       <c r="BH60" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI60">
         <v>0</v>
@@ -69129,7 +69350,7 @@
     </row>
     <row r="61" spans="1:62">
       <c r="A61" s="44" t="s">
-        <v>1898</v>
+        <v>1870</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -69198,7 +69419,7 @@
         <v>3</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y61">
         <v>0</v>
@@ -69228,10 +69449,10 @@
         <v>36</v>
       </c>
       <c r="AH61" t="s">
-        <v>36</v>
+        <v>1922</v>
       </c>
       <c r="AI61" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ61" s="44" t="s">
         <v>1470</v>
@@ -69258,7 +69479,7 @@
         <v>0</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS61">
         <v>1</v>
@@ -69297,30 +69518,30 @@
         <v>0</v>
       </c>
       <c r="BE61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF61" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="BG61" t="s">
         <v>36</v>
       </c>
       <c r="BH61" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="BI61">
         <v>0</v>
       </c>
       <c r="BJ61" s="46" t="s">
-        <v>1901</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:62">
       <c r="A62" s="44" t="s">
-        <v>1902</v>
+        <v>1871</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -69344,7 +69565,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -69404,13 +69625,13 @@
         <v>0</v>
       </c>
       <c r="AD62">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="s">
         <v>36</v>
@@ -69419,7 +69640,7 @@
         <v>36</v>
       </c>
       <c r="AI62" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ62" s="44" t="s">
         <v>1470</v>
@@ -69464,7 +69685,7 @@
         <v>0</v>
       </c>
       <c r="AX62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY62" t="s">
         <v>36</v>
@@ -69485,190 +69706,1352 @@
         <v>0</v>
       </c>
       <c r="BE62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH62" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI62">
+        <v>0</v>
+      </c>
+      <c r="BJ62" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:62">
+      <c r="A63" s="44" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>4</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>1</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>-1</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>10</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI63" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ63" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK63" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL63" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN63" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO63" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP63" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>1</v>
+      </c>
+      <c r="AS63">
+        <v>1</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU63">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW63">
+        <v>0</v>
+      </c>
+      <c r="AX63">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ63" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA63" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB63">
+        <v>0</v>
+      </c>
+      <c r="BC63">
+        <v>0</v>
+      </c>
+      <c r="BD63">
+        <v>0</v>
+      </c>
+      <c r="BE63">
+        <v>0</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG63" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH63" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI63">
+        <v>0</v>
+      </c>
+      <c r="BJ63" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:62">
+      <c r="A64" s="44" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>4</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>1</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>-1</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>10</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI64" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ64" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK64" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL64" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN64" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP64" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>1</v>
+      </c>
+      <c r="AS64">
+        <v>1</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU64">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW64">
+        <v>0</v>
+      </c>
+      <c r="AX64">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA64" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB64">
+        <v>0</v>
+      </c>
+      <c r="BC64">
+        <v>0</v>
+      </c>
+      <c r="BD64">
+        <v>0</v>
+      </c>
+      <c r="BE64">
+        <v>0</v>
+      </c>
+      <c r="BF64" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BG64" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH64" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI64">
+        <v>0</v>
+      </c>
+      <c r="BJ64" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:62">
+      <c r="A65" s="44" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>4</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>1</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>-1</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>10</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI65" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ65" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK65" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL65" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN65" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO65" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP65" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>1</v>
+      </c>
+      <c r="AS65">
+        <v>1</v>
+      </c>
+      <c r="AT65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU65">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW65">
+        <v>0</v>
+      </c>
+      <c r="AX65">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ65" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA65" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB65">
+        <v>0</v>
+      </c>
+      <c r="BC65">
+        <v>0</v>
+      </c>
+      <c r="BD65">
+        <v>0</v>
+      </c>
+      <c r="BE65">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="s">
+        <v>1763</v>
+      </c>
+      <c r="BG65" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH65" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI65">
+        <v>0</v>
+      </c>
+      <c r="BJ65" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:62">
+      <c r="A66" s="44" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>4</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>1</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>-1</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>10</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI66" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ66" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK66" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL66" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN66" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO66" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP66" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>1</v>
+      </c>
+      <c r="AS66">
+        <v>1</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU66">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW66">
+        <v>0</v>
+      </c>
+      <c r="AX66">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA66" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB66">
+        <v>0</v>
+      </c>
+      <c r="BC66">
+        <v>0</v>
+      </c>
+      <c r="BD66">
+        <v>0</v>
+      </c>
+      <c r="BE66">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="s">
+        <v>1761</v>
+      </c>
+      <c r="BG66" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH66" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI66">
+        <v>0</v>
+      </c>
+      <c r="BJ66" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:62">
+      <c r="A67" s="44" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>4</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>1</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>-1</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>10</v>
+      </c>
+      <c r="AG67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI67" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ67" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK67" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL67" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN67" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO67" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP67" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>1</v>
+      </c>
+      <c r="AS67">
+        <v>1</v>
+      </c>
+      <c r="AT67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU67">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW67">
+        <v>0</v>
+      </c>
+      <c r="AX67">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA67" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB67">
+        <v>0</v>
+      </c>
+      <c r="BC67">
+        <v>0</v>
+      </c>
+      <c r="BD67">
+        <v>0</v>
+      </c>
+      <c r="BE67">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>1764</v>
+      </c>
+      <c r="BG67" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH67" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI67">
+        <v>0</v>
+      </c>
+      <c r="BJ67" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:62">
+      <c r="A68" s="44" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>4</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>1</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>-1</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>10</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>1940</v>
+      </c>
+      <c r="AI68" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ68" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK68" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL68" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN68" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO68" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP68" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>1</v>
+      </c>
+      <c r="AS68">
+        <v>1</v>
+      </c>
+      <c r="AT68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU68">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW68">
+        <v>0</v>
+      </c>
+      <c r="AX68">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ68" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA68" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB68">
+        <v>0</v>
+      </c>
+      <c r="BC68">
+        <v>0</v>
+      </c>
+      <c r="BD68">
+        <v>0</v>
+      </c>
+      <c r="BE68">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="s">
         <v>1762</v>
       </c>
-      <c r="BG62" t="s">
-        <v>36</v>
-      </c>
-      <c r="BH62" t="s">
-        <v>1659</v>
-      </c>
-      <c r="BI62">
-        <v>0</v>
-      </c>
-      <c r="BJ62" s="46" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="63" spans="1:62">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="BJ63" s="46"/>
-    </row>
-    <row r="64" spans="1:62">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="BJ64" s="46"/>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
-    </row>
-    <row r="67" spans="1:20">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-    </row>
-    <row r="69" spans="1:20">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-    </row>
-    <row r="70" spans="1:20">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="BG68" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH68" t="s">
+        <v>1663</v>
+      </c>
+      <c r="BI68">
+        <v>0</v>
+      </c>
+      <c r="BJ68" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:62">
+      <c r="A69" s="44" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B69">
+        <v>-1</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>50</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>3</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>1</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>5</v>
+      </c>
+      <c r="AE69">
+        <v>1</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI69" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ69" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK69" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL69" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN69" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO69" s="44" t="s">
+        <v>1407</v>
+      </c>
+      <c r="AP69" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>1</v>
+      </c>
+      <c r="AS69">
+        <v>1</v>
+      </c>
+      <c r="AT69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU69">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW69">
+        <v>0</v>
+      </c>
+      <c r="AX69">
+        <v>1</v>
+      </c>
+      <c r="AY69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ69" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA69" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB69">
+        <v>0</v>
+      </c>
+      <c r="BC69">
+        <v>0</v>
+      </c>
+      <c r="BD69">
+        <v>0</v>
+      </c>
+      <c r="BE69">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>1765</v>
+      </c>
+      <c r="BG69" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH69" t="s">
+        <v>1671</v>
+      </c>
+      <c r="BI69">
+        <v>0</v>
+      </c>
+      <c r="BJ69" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:62" ht="14">
+      <c r="A70" s="55" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B70" s="55"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="55"/>
+      <c r="G70" s="55"/>
+      <c r="H70" s="55"/>
+      <c r="I70" s="55"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
@@ -69680,118 +71063,957 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
-    </row>
-    <row r="71" spans="1:20">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="3"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-    </row>
-    <row r="72" spans="1:20">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="3"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
-    </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-    </row>
-    <row r="74" spans="1:20">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
-    </row>
-    <row r="75" spans="1:20">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="AG70" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI70">
+        <v>0</v>
+      </c>
+      <c r="BJ70" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:62">
+      <c r="A71" s="44" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>200</v>
+      </c>
+      <c r="I71">
+        <v>200</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>3</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>1</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>-1</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>10</v>
+      </c>
+      <c r="AG71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI71" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ71" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK71" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL71" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN71" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP71" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>1</v>
+      </c>
+      <c r="AT71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU71">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW71">
+        <v>0</v>
+      </c>
+      <c r="AX71">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ71" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA71" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB71">
+        <v>0</v>
+      </c>
+      <c r="BC71">
+        <v>0</v>
+      </c>
+      <c r="BD71">
+        <v>0</v>
+      </c>
+      <c r="BE71">
+        <v>1</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG71" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH71" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI71">
+        <v>10</v>
+      </c>
+      <c r="BJ71" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:62">
+      <c r="A72" s="44" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>10</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>3</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>1</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>-1</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>10</v>
+      </c>
+      <c r="AG72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI72" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ72" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK72" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL72" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN72" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP72" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>1</v>
+      </c>
+      <c r="AT72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU72">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW72">
+        <v>0</v>
+      </c>
+      <c r="AX72">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB72">
+        <v>0</v>
+      </c>
+      <c r="BC72">
+        <v>0</v>
+      </c>
+      <c r="BD72">
+        <v>0</v>
+      </c>
+      <c r="BE72">
+        <v>1</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH72" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI72">
+        <v>0</v>
+      </c>
+      <c r="BJ72" s="46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:62">
+      <c r="A73" s="44" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>3</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>1</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>-1</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>10</v>
+      </c>
+      <c r="AG73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI73" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ73" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK73" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL73" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN73" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO73" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP73" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>1</v>
+      </c>
+      <c r="AT73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU73">
+        <v>0</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW73">
+        <v>0</v>
+      </c>
+      <c r="AX73">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ73" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA73" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB73">
+        <v>0</v>
+      </c>
+      <c r="BC73">
+        <v>0</v>
+      </c>
+      <c r="BD73">
+        <v>0</v>
+      </c>
+      <c r="BE73">
+        <v>1</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG73" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH73" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI73">
+        <v>0</v>
+      </c>
+      <c r="BJ73" s="46" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="74" spans="1:62">
+      <c r="A74" s="44" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>3</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>1</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>-1</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>10</v>
+      </c>
+      <c r="AG74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI74" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ74" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK74" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL74" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN74" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO74" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP74" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>1</v>
+      </c>
+      <c r="AT74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU74">
+        <v>0</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW74">
+        <v>0</v>
+      </c>
+      <c r="AX74">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ74" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA74" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB74">
+        <v>0</v>
+      </c>
+      <c r="BC74">
+        <v>0</v>
+      </c>
+      <c r="BD74">
+        <v>0</v>
+      </c>
+      <c r="BE74">
+        <v>1</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG74" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH74" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI74">
+        <v>0</v>
+      </c>
+      <c r="BJ74" s="46" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="75" spans="1:62">
+      <c r="A75" s="44" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>3</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>1</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>-1</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>10</v>
+      </c>
+      <c r="AG75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI75" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ75" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK75" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL75" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN75" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO75" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP75" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>1</v>
+      </c>
+      <c r="AT75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU75">
+        <v>0</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW75">
+        <v>0</v>
+      </c>
+      <c r="AX75">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ75" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA75" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB75">
+        <v>0</v>
+      </c>
+      <c r="BC75">
+        <v>0</v>
+      </c>
+      <c r="BD75">
+        <v>0</v>
+      </c>
+      <c r="BE75">
+        <v>1</v>
+      </c>
+      <c r="BF75" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG75" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH75" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI75">
+        <v>0</v>
+      </c>
+      <c r="BJ75" s="46" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="76" spans="1:62">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -69812,8 +72034,9 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="BJ76" s="46"/>
+    </row>
+    <row r="77" spans="1:62">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -69835,7 +72058,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:62">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -69857,7 +72080,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="1:62">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -69879,7 +72102,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="1:62">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -70186,6 +72409,270 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="1:20">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="1:20">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="1:20">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+      <c r="S97" s="3"/>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+      <c r="S99" s="3"/>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3"/>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+      <c r="S101" s="3"/>
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
+    </row>
+    <row r="103" spans="1:20">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+      <c r="S103" s="3"/>
+      <c r="T103" s="3"/>
+    </row>
+    <row r="104" spans="1:20">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+    </row>
+    <row r="105" spans="1:20">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="3"/>
+      <c r="R105" s="3"/>
+      <c r="S105" s="3"/>
+      <c r="T105" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5312B713-55FD-4667-88D5-7D10231F588F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6E0498-C7F2-4E8F-A1DE-1E5069F5DDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10028" uniqueCount="1946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10028" uniqueCount="1948">
   <si>
     <t>NAME</t>
   </si>
@@ -6022,6 +6022,12 @@
   </si>
   <si>
     <t>mana_reduction,-10</t>
+  </si>
+  <si>
+    <t>mana_siphon1,mana_reduc1</t>
+  </si>
+  <si>
+    <t>burn,100</t>
   </si>
 </sst>
 </file>
@@ -6674,14 +6680,14 @@
     <col min="15" max="15" width="9.6328125" customWidth="1"/>
     <col min="22" max="22" width="10.81640625" customWidth="1"/>
     <col min="23" max="23" width="9.6328125" customWidth="1"/>
-    <col min="24" max="24" width="9.90625" customWidth="1"/>
+    <col min="24" max="24" width="15.08984375" customWidth="1"/>
     <col min="25" max="25" width="8.6328125" customWidth="1"/>
     <col min="26" max="26" width="9.26953125" customWidth="1"/>
     <col min="27" max="27" width="8.36328125" customWidth="1"/>
     <col min="28" max="28" width="19" customWidth="1"/>
     <col min="29" max="29" width="48.453125" customWidth="1"/>
     <col min="30" max="30" width="27.08984375" customWidth="1"/>
-    <col min="31" max="31" width="18.26953125" customWidth="1"/>
+    <col min="31" max="31" width="20.7265625" customWidth="1"/>
     <col min="37" max="37" width="15" customWidth="1"/>
     <col min="40" max="40" width="8.453125" customWidth="1"/>
     <col min="41" max="41" width="8.08984375" customWidth="1"/>
@@ -22235,7 +22241,7 @@
         <v>42</v>
       </c>
       <c r="AE84" s="40" t="s">
-        <v>1886</v>
+        <v>1946</v>
       </c>
       <c r="AF84" s="40">
         <v>40</v>
@@ -61365,7 +61371,7 @@
         <v>36</v>
       </c>
       <c r="AH18" t="s">
-        <v>1494</v>
+        <v>1947</v>
       </c>
       <c r="AI18" s="44" t="s">
         <v>1363</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6E0498-C7F2-4E8F-A1DE-1E5069F5DDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8C11E4-2A6B-497F-92D4-C0C664F981D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10028" uniqueCount="1948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10112" uniqueCount="1949">
   <si>
     <t>NAME</t>
   </si>
@@ -6028,6 +6028,9 @@
   </si>
   <si>
     <t>burn,100</t>
+  </si>
+  <si>
+    <t>UNLOCK_PRICE</t>
   </si>
 </sst>
 </file>
@@ -6661,7 +6664,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BJ998"/>
+  <dimension ref="A1:BK998"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.453125" customWidth="1"/>
@@ -6711,9 +6714,10 @@
     <col min="60" max="60" width="10.453125" customWidth="1"/>
     <col min="61" max="61" width="15.08984375" customWidth="1"/>
     <col min="62" max="62" width="17.1796875" customWidth="1"/>
+    <col min="63" max="63" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="15.75" customHeight="1">
+    <row r="1" spans="1:63" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6900,8 +6904,11 @@
       <c r="BJ1" s="6" t="s">
         <v>1872</v>
       </c>
-    </row>
-    <row r="2" spans="1:62" ht="12.5">
+      <c r="BK1" s="43" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63" ht="12.5">
       <c r="A2" s="47" t="s">
         <v>954</v>
       </c>
@@ -7088,8 +7095,11 @@
       <c r="BJ2" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="3" spans="1:62" ht="12.5">
+      <c r="BK2" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63" ht="12.5">
       <c r="A3" s="47" t="s">
         <v>1406</v>
       </c>
@@ -7276,8 +7286,11 @@
       <c r="BJ3" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="4" spans="1:62" ht="12.5">
+      <c r="BK3" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63" ht="12.5">
       <c r="A4" s="47" t="s">
         <v>1766</v>
       </c>
@@ -7464,8 +7477,11 @@
       <c r="BJ4" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="5" spans="1:62" ht="12.5">
+      <c r="BK4" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63" ht="12.5">
       <c r="A5" s="47" t="s">
         <v>1767</v>
       </c>
@@ -7652,8 +7668,11 @@
       <c r="BJ5" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="6" spans="1:62" ht="12.5">
+      <c r="BK5" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="6" spans="1:63" ht="12.5">
       <c r="A6" s="47" t="s">
         <v>1466</v>
       </c>
@@ -7840,8 +7859,11 @@
       <c r="BJ6" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="7" spans="1:62" ht="12.5">
+      <c r="BK6" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63" ht="12.5">
       <c r="A7" s="47" t="s">
         <v>1467</v>
       </c>
@@ -8028,8 +8050,11 @@
       <c r="BJ7" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="8" spans="1:62" ht="12.5">
+      <c r="BK7" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63" ht="12.5">
       <c r="A8" s="47" t="s">
         <v>43</v>
       </c>
@@ -8216,8 +8241,11 @@
       <c r="BJ8" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="9" spans="1:62" ht="12.5">
+      <c r="BK8" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63" ht="12.5">
       <c r="A9" s="47" t="s">
         <v>1509</v>
       </c>
@@ -8404,8 +8432,11 @@
       <c r="BJ9" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="10" spans="1:62" ht="12.5">
+      <c r="BK9" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:63" ht="12.5">
       <c r="A10" s="47" t="s">
         <v>1510</v>
       </c>
@@ -8592,8 +8623,11 @@
       <c r="BJ10" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="11" spans="1:62" ht="12.5">
+      <c r="BK10" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:63" ht="12.5">
       <c r="A11" s="47" t="s">
         <v>1521</v>
       </c>
@@ -8780,8 +8814,11 @@
       <c r="BJ11" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="12" spans="1:62" ht="12.5">
+      <c r="BK11" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:63" ht="12.5">
       <c r="A12" s="47" t="s">
         <v>1522</v>
       </c>
@@ -8968,8 +9005,11 @@
       <c r="BJ12" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="13" spans="1:62" ht="12.5">
+      <c r="BK12" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:63" ht="12.5">
       <c r="A13" s="47" t="s">
         <v>1550</v>
       </c>
@@ -9156,8 +9196,11 @@
       <c r="BJ13" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="14" spans="1:62" ht="12.5">
+      <c r="BK13" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:63" ht="12.5">
       <c r="A14" s="47" t="s">
         <v>1578</v>
       </c>
@@ -9344,8 +9387,11 @@
       <c r="BJ14" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="15" spans="1:62" ht="12.5">
+      <c r="BK14" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:63" ht="12.5">
       <c r="A15" s="47" t="s">
         <v>1601</v>
       </c>
@@ -9532,8 +9578,11 @@
       <c r="BJ15" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="16" spans="1:62" ht="12.5">
+      <c r="BK15" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:63" ht="12.5">
       <c r="A16" s="47" t="s">
         <v>34</v>
       </c>
@@ -9720,8 +9769,11 @@
       <c r="BJ16" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="17" spans="1:62" ht="12.5">
+      <c r="BK16" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="17" spans="1:63" ht="12.5">
       <c r="A17" s="47" t="s">
         <v>1370</v>
       </c>
@@ -9908,8 +9960,11 @@
       <c r="BJ17" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="18" spans="1:62" ht="12.5">
+      <c r="BK17" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:63" ht="12.5">
       <c r="A18" s="47" t="s">
         <v>1165</v>
       </c>
@@ -10096,8 +10151,11 @@
       <c r="BJ18" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="19" spans="1:62" ht="12.5">
+      <c r="BK18" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:63" ht="12.5">
       <c r="A19" s="47" t="s">
         <v>1619</v>
       </c>
@@ -10284,8 +10342,11 @@
       <c r="BJ19" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="20" spans="1:62" ht="12.5">
+      <c r="BK19" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="20" spans="1:63" ht="12.5">
       <c r="A20" s="47" t="s">
         <v>1632</v>
       </c>
@@ -10472,8 +10533,11 @@
       <c r="BJ20" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="21" spans="1:62" ht="12.5">
+      <c r="BK20" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="21" spans="1:63" ht="12.5">
       <c r="A21" s="47" t="s">
         <v>1258</v>
       </c>
@@ -10660,8 +10724,11 @@
       <c r="BJ21" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="22" spans="1:62" ht="12.5">
+      <c r="BK21" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:63" ht="12.5">
       <c r="A22" s="47" t="s">
         <v>1716</v>
       </c>
@@ -10848,8 +10915,11 @@
       <c r="BJ22" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="23" spans="1:62" ht="12.5">
+      <c r="BK22" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="23" spans="1:63" ht="12.5">
       <c r="A23" s="47" t="s">
         <v>1736</v>
       </c>
@@ -11036,8 +11106,11 @@
       <c r="BJ23" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="24" spans="1:62" ht="12.5">
+      <c r="BK23" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="24" spans="1:63" ht="12.5">
       <c r="A24" s="47" t="s">
         <v>1737</v>
       </c>
@@ -11224,8 +11297,11 @@
       <c r="BJ24" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="25" spans="1:62" ht="12.5">
+      <c r="BK24" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="25" spans="1:63" ht="12.5">
       <c r="A25" s="47" t="s">
         <v>1739</v>
       </c>
@@ -11412,8 +11488,11 @@
       <c r="BJ25" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="26" spans="1:62" ht="12.5">
+      <c r="BK25" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="26" spans="1:63" ht="12.5">
       <c r="A26" s="47" t="s">
         <v>1738</v>
       </c>
@@ -11600,8 +11679,11 @@
       <c r="BJ26" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="27" spans="1:62" ht="12.5">
+      <c r="BK26" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="27" spans="1:63" ht="12.5">
       <c r="A27" s="47" t="s">
         <v>52</v>
       </c>
@@ -11788,8 +11870,11 @@
       <c r="BJ27" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="28" spans="1:62" ht="12.5">
+      <c r="BK27" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="28" spans="1:63" ht="12.5">
       <c r="A28" s="47" t="s">
         <v>1728</v>
       </c>
@@ -11976,8 +12061,11 @@
       <c r="BJ28" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="29" spans="1:62" ht="14">
+      <c r="BK28" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="29" spans="1:63" ht="14">
       <c r="A29" s="54" t="s">
         <v>1816</v>
       </c>
@@ -12164,8 +12252,11 @@
       <c r="BJ29" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="30" spans="1:62" ht="12.5">
+      <c r="BK29" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="30" spans="1:63" ht="12.5">
       <c r="A30" s="47" t="s">
         <v>1817</v>
       </c>
@@ -12352,8 +12443,11 @@
       <c r="BJ30" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="31" spans="1:62" ht="12.5">
+      <c r="BK30" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="31" spans="1:63" ht="12.5">
       <c r="A31" s="47" t="s">
         <v>1818</v>
       </c>
@@ -12540,8 +12634,11 @@
       <c r="BJ31" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="32" spans="1:62" ht="12.5">
+      <c r="BK31" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="32" spans="1:63" ht="12.5">
       <c r="A32" s="47" t="s">
         <v>1819</v>
       </c>
@@ -12728,8 +12825,11 @@
       <c r="BJ32" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="33" spans="1:62" ht="12.5">
+      <c r="BK32" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:63" ht="12.5">
       <c r="A33" s="47" t="s">
         <v>1820</v>
       </c>
@@ -12916,8 +13016,11 @@
       <c r="BJ33" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="34" spans="1:62" ht="12.5">
+      <c r="BK33" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="34" spans="1:63" ht="12.5">
       <c r="A34" s="47" t="s">
         <v>1821</v>
       </c>
@@ -13104,8 +13207,11 @@
       <c r="BJ34" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="35" spans="1:62" ht="12.5">
+      <c r="BK34" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="35" spans="1:63" ht="12.5">
       <c r="A35" s="47" t="s">
         <v>1822</v>
       </c>
@@ -13292,8 +13398,11 @@
       <c r="BJ35" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="36" spans="1:62" ht="12.5">
+      <c r="BK35" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:63" ht="12.5">
       <c r="A36" s="47" t="s">
         <v>1823</v>
       </c>
@@ -13480,8 +13589,11 @@
       <c r="BJ36" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="37" spans="1:62" ht="12.5">
+      <c r="BK36" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:63" ht="12.5">
       <c r="A37" s="47" t="s">
         <v>1824</v>
       </c>
@@ -13668,8 +13780,11 @@
       <c r="BJ37" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="38" spans="1:62" ht="12.5">
+      <c r="BK37" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:63" ht="12.5">
       <c r="A38" s="47" t="s">
         <v>1825</v>
       </c>
@@ -13856,8 +13971,11 @@
       <c r="BJ38" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="39" spans="1:62" ht="12.5">
+      <c r="BK38" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:63" ht="12.5">
       <c r="A39" s="47" t="s">
         <v>1826</v>
       </c>
@@ -14044,8 +14162,11 @@
       <c r="BJ39" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="40" spans="1:62" ht="12.5">
+      <c r="BK39" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="40" spans="1:63" ht="12.5">
       <c r="A40" s="47" t="s">
         <v>1827</v>
       </c>
@@ -14232,8 +14353,11 @@
       <c r="BJ40" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="41" spans="1:62" ht="12.5">
+      <c r="BK40" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="41" spans="1:63" ht="12.5">
       <c r="A41" s="47" t="s">
         <v>1828</v>
       </c>
@@ -14420,8 +14544,11 @@
       <c r="BJ41" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="42" spans="1:62" ht="12.5">
+      <c r="BK41" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="42" spans="1:63" ht="12.5">
       <c r="A42" s="47" t="s">
         <v>1829</v>
       </c>
@@ -14608,8 +14735,11 @@
       <c r="BJ42" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="43" spans="1:62" ht="12.5">
+      <c r="BK42" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="43" spans="1:63" ht="12.5">
       <c r="A43" s="47" t="s">
         <v>1830</v>
       </c>
@@ -14796,8 +14926,11 @@
       <c r="BJ43" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="44" spans="1:62" ht="12.5">
+      <c r="BK43" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="44" spans="1:63" ht="12.5">
       <c r="A44" s="47" t="s">
         <v>1831</v>
       </c>
@@ -14984,8 +15117,11 @@
       <c r="BJ44" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="45" spans="1:62" ht="12.5">
+      <c r="BK44" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="45" spans="1:63" ht="12.5">
       <c r="A45" s="47" t="s">
         <v>1832</v>
       </c>
@@ -15172,8 +15308,11 @@
       <c r="BJ45" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="46" spans="1:62" ht="12.5">
+      <c r="BK45" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="46" spans="1:63" ht="12.5">
       <c r="A46" s="47" t="s">
         <v>1833</v>
       </c>
@@ -15360,8 +15499,11 @@
       <c r="BJ46" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="47" spans="1:62" ht="12.5">
+      <c r="BK46" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="47" spans="1:63" ht="12.5">
       <c r="A47" s="47" t="s">
         <v>1834</v>
       </c>
@@ -15548,8 +15690,11 @@
       <c r="BJ47" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="48" spans="1:62" ht="12.5">
+      <c r="BK47" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="48" spans="1:63" ht="12.5">
       <c r="A48" s="47" t="s">
         <v>1835</v>
       </c>
@@ -15736,8 +15881,11 @@
       <c r="BJ48" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="49" spans="1:62" ht="12.5">
+      <c r="BK48" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="49" spans="1:63" ht="12.5">
       <c r="A49" s="47" t="s">
         <v>1836</v>
       </c>
@@ -15924,8 +16072,11 @@
       <c r="BJ49" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="50" spans="1:62" ht="12.5">
+      <c r="BK49" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:63" ht="12.5">
       <c r="A50" s="47" t="s">
         <v>1837</v>
       </c>
@@ -16112,8 +16263,11 @@
       <c r="BJ50" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="51" spans="1:62" ht="12.5">
+      <c r="BK50" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="51" spans="1:63" ht="12.5">
       <c r="A51" s="47" t="s">
         <v>1838</v>
       </c>
@@ -16300,8 +16454,11 @@
       <c r="BJ51" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="52" spans="1:62" ht="12.5">
+      <c r="BK51" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="52" spans="1:63" ht="12.5">
       <c r="A52" s="47" t="s">
         <v>1839</v>
       </c>
@@ -16488,8 +16645,11 @@
       <c r="BJ52" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="53" spans="1:62" ht="12.5">
+      <c r="BK52" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="53" spans="1:63" ht="12.5">
       <c r="A53" s="47" t="s">
         <v>1840</v>
       </c>
@@ -16676,8 +16836,11 @@
       <c r="BJ53" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="54" spans="1:62" ht="12.5">
+      <c r="BK53" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="54" spans="1:63" ht="12.5">
       <c r="A54" s="47" t="s">
         <v>1841</v>
       </c>
@@ -16864,8 +17027,11 @@
       <c r="BJ54" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="55" spans="1:62" ht="12.5">
+      <c r="BK54" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="55" spans="1:63" ht="12.5">
       <c r="A55" s="47" t="s">
         <v>1842</v>
       </c>
@@ -17052,8 +17218,11 @@
       <c r="BJ55" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="56" spans="1:62" ht="12.5">
+      <c r="BK55" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="56" spans="1:63" ht="12.5">
       <c r="A56" s="47" t="s">
         <v>1843</v>
       </c>
@@ -17240,8 +17409,11 @@
       <c r="BJ56" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="57" spans="1:62" ht="12.5">
+      <c r="BK56" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="57" spans="1:63" ht="12.5">
       <c r="A57" s="47" t="s">
         <v>1844</v>
       </c>
@@ -17428,8 +17600,11 @@
       <c r="BJ57" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="58" spans="1:62" ht="12.5">
+      <c r="BK57" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:63" ht="12.5">
       <c r="A58" s="47" t="s">
         <v>1845</v>
       </c>
@@ -17616,8 +17791,11 @@
       <c r="BJ58" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="59" spans="1:62" ht="12.5">
+      <c r="BK58" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="59" spans="1:63" ht="12.5">
       <c r="A59" s="47" t="s">
         <v>1846</v>
       </c>
@@ -17804,8 +17982,11 @@
       <c r="BJ59" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="60" spans="1:62" ht="12.5">
+      <c r="BK59" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="60" spans="1:63" ht="12.5">
       <c r="A60" s="47" t="s">
         <v>1847</v>
       </c>
@@ -17992,8 +18173,11 @@
       <c r="BJ60" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="61" spans="1:62" ht="12.5">
+      <c r="BK60" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="61" spans="1:63" ht="12.5">
       <c r="A61" s="47" t="s">
         <v>1848</v>
       </c>
@@ -18180,8 +18364,11 @@
       <c r="BJ61" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="62" spans="1:62" ht="12.5">
+      <c r="BK61" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="62" spans="1:63" ht="12.5">
       <c r="A62" s="47" t="s">
         <v>1849</v>
       </c>
@@ -18368,8 +18555,11 @@
       <c r="BJ62" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="63" spans="1:62" ht="12.5">
+      <c r="BK62" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="63" spans="1:63" ht="12.5">
       <c r="A63" s="47" t="s">
         <v>1850</v>
       </c>
@@ -18556,8 +18746,11 @@
       <c r="BJ63" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="64" spans="1:62" ht="12.5">
+      <c r="BK63" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="64" spans="1:63" ht="12.5">
       <c r="A64" s="47" t="s">
         <v>1851</v>
       </c>
@@ -18744,8 +18937,11 @@
       <c r="BJ64" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="65" spans="1:62" ht="12.5">
+      <c r="BK64" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:63" ht="12.5">
       <c r="A65" s="47" t="s">
         <v>1852</v>
       </c>
@@ -18932,8 +19128,11 @@
       <c r="BJ65" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="66" spans="1:62" ht="12.5">
+      <c r="BK65" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="66" spans="1:63" ht="12.5">
       <c r="A66" s="47" t="s">
         <v>1853</v>
       </c>
@@ -19120,8 +19319,11 @@
       <c r="BJ66" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="67" spans="1:62" ht="12.5">
+      <c r="BK66" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="67" spans="1:63" ht="12.5">
       <c r="A67" s="47" t="s">
         <v>1854</v>
       </c>
@@ -19308,8 +19510,11 @@
       <c r="BJ67" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="68" spans="1:62" ht="12.5">
+      <c r="BK67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="68" spans="1:63" ht="12.5">
       <c r="A68" s="47" t="s">
         <v>1855</v>
       </c>
@@ -19496,8 +19701,11 @@
       <c r="BJ68" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="69" spans="1:62" ht="12.5">
+      <c r="BK68" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="69" spans="1:63" ht="12.5">
       <c r="A69" s="47" t="s">
         <v>1856</v>
       </c>
@@ -19684,8 +19892,11 @@
       <c r="BJ69" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="70" spans="1:62" ht="12.5">
+      <c r="BK69" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="70" spans="1:63" ht="12.5">
       <c r="A70" s="47" t="s">
         <v>1857</v>
       </c>
@@ -19872,8 +20083,11 @@
       <c r="BJ70" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="71" spans="1:62" ht="12.5">
+      <c r="BK70" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="71" spans="1:63" ht="12.5">
       <c r="A71" s="47" t="s">
         <v>1858</v>
       </c>
@@ -20060,8 +20274,11 @@
       <c r="BJ71" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="72" spans="1:62" ht="12.5">
+      <c r="BK71" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="72" spans="1:63" ht="12.5">
       <c r="A72" s="47" t="s">
         <v>1859</v>
       </c>
@@ -20248,8 +20465,11 @@
       <c r="BJ72" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="73" spans="1:62" ht="12.5">
+      <c r="BK72" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="73" spans="1:63" ht="12.5">
       <c r="A73" s="47" t="s">
         <v>1860</v>
       </c>
@@ -20436,8 +20656,11 @@
       <c r="BJ73" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="74" spans="1:62" ht="12.5">
+      <c r="BK73" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="74" spans="1:63" ht="12.5">
       <c r="A74" s="47" t="s">
         <v>1861</v>
       </c>
@@ -20624,8 +20847,11 @@
       <c r="BJ74" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="75" spans="1:62" ht="12.5">
+      <c r="BK74" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="75" spans="1:63" ht="12.5">
       <c r="A75" s="47" t="s">
         <v>1862</v>
       </c>
@@ -20812,8 +21038,11 @@
       <c r="BJ75" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="76" spans="1:62" ht="12.5">
+      <c r="BK75" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="76" spans="1:63" ht="12.5">
       <c r="A76" s="47" t="s">
         <v>1863</v>
       </c>
@@ -21000,8 +21229,11 @@
       <c r="BJ76" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="77" spans="1:62" ht="12.5">
+      <c r="BK76" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="77" spans="1:63" ht="12.5">
       <c r="A77" s="47" t="s">
         <v>1864</v>
       </c>
@@ -21188,8 +21420,11 @@
       <c r="BJ77" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="78" spans="1:62" ht="12.5">
+      <c r="BK77" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:63" ht="12.5">
       <c r="A78" s="47" t="s">
         <v>1865</v>
       </c>
@@ -21376,8 +21611,11 @@
       <c r="BJ78" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="79" spans="1:62" ht="14">
+      <c r="BK78" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="79" spans="1:63" ht="14">
       <c r="A79" s="55" t="s">
         <v>1891</v>
       </c>
@@ -21396,8 +21634,11 @@
       <c r="N79" s="57"/>
       <c r="AA79" s="41"/>
       <c r="AH79" s="41"/>
-    </row>
-    <row r="80" spans="1:62" ht="12.5">
+      <c r="BK79" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="80" spans="1:63" ht="12.5">
       <c r="A80" s="47" t="s">
         <v>1893</v>
       </c>
@@ -21584,8 +21825,11 @@
       <c r="BJ80" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="81" spans="1:62" ht="12.5">
+      <c r="BK80" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="81" spans="1:63" ht="12.5">
       <c r="A81" s="47" t="s">
         <v>1894</v>
       </c>
@@ -21772,8 +22016,11 @@
       <c r="BJ81" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="82" spans="1:62" ht="12.5">
+      <c r="BK81" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="82" spans="1:63" ht="12.5">
       <c r="A82" s="47" t="s">
         <v>1895</v>
       </c>
@@ -21960,8 +22207,11 @@
       <c r="BJ82" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="83" spans="1:62" ht="12.5">
+      <c r="BK82" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="83" spans="1:63" ht="12.5">
       <c r="A83" s="47" t="s">
         <v>1896</v>
       </c>
@@ -22148,8 +22398,11 @@
       <c r="BJ83" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="84" spans="1:62" ht="12.5">
+      <c r="BK83" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="84" spans="1:63" ht="12.5">
       <c r="A84" s="47" t="s">
         <v>1897</v>
       </c>
@@ -22336,74 +22589,77 @@
       <c r="BJ84" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="85" spans="1:62" ht="12.5">
+      <c r="BK84" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="85" spans="1:63" ht="12.5">
       <c r="J85" s="38"/>
       <c r="K85" s="38"/>
       <c r="AA85" s="41"/>
       <c r="AH85" s="41"/>
     </row>
-    <row r="86" spans="1:62" ht="12.5">
+    <row r="86" spans="1:63" ht="12.5">
       <c r="J86" s="38"/>
       <c r="K86" s="38"/>
       <c r="AA86" s="41"/>
       <c r="AH86" s="41"/>
     </row>
-    <row r="87" spans="1:62" ht="12.5">
+    <row r="87" spans="1:63" ht="12.5">
       <c r="J87" s="38"/>
       <c r="K87" s="38"/>
       <c r="AA87" s="41"/>
       <c r="AH87" s="41"/>
     </row>
-    <row r="88" spans="1:62" ht="12.5">
+    <row r="88" spans="1:63" ht="12.5">
       <c r="J88" s="38"/>
       <c r="K88" s="38"/>
       <c r="AA88" s="41"/>
       <c r="AH88" s="41"/>
     </row>
-    <row r="89" spans="1:62" ht="12.5">
+    <row r="89" spans="1:63" ht="12.5">
       <c r="J89" s="38"/>
       <c r="K89" s="38"/>
       <c r="AA89" s="41"/>
       <c r="AH89" s="41"/>
     </row>
-    <row r="90" spans="1:62" ht="12.5">
+    <row r="90" spans="1:63" ht="12.5">
       <c r="J90" s="38"/>
       <c r="K90" s="38"/>
       <c r="AA90" s="41"/>
       <c r="AH90" s="41"/>
     </row>
-    <row r="91" spans="1:62" ht="12.5">
+    <row r="91" spans="1:63" ht="12.5">
       <c r="J91" s="38"/>
       <c r="K91" s="38"/>
       <c r="AA91" s="41"/>
       <c r="AH91" s="41"/>
     </row>
-    <row r="92" spans="1:62" ht="12.5">
+    <row r="92" spans="1:63" ht="12.5">
       <c r="J92" s="38"/>
       <c r="K92" s="38"/>
       <c r="AA92" s="41"/>
       <c r="AH92" s="41"/>
     </row>
-    <row r="93" spans="1:62" ht="12.5">
+    <row r="93" spans="1:63" ht="12.5">
       <c r="J93" s="38"/>
       <c r="K93" s="38"/>
       <c r="AA93" s="41"/>
       <c r="AH93" s="41"/>
     </row>
-    <row r="94" spans="1:62" ht="12.5">
+    <row r="94" spans="1:63" ht="12.5">
       <c r="J94" s="38"/>
       <c r="K94" s="38"/>
       <c r="AA94" s="41"/>
       <c r="AH94" s="41"/>
     </row>
-    <row r="95" spans="1:62" ht="12.5">
+    <row r="95" spans="1:63" ht="12.5">
       <c r="J95" s="38"/>
       <c r="K95" s="38"/>
       <c r="AA95" s="41"/>
       <c r="AH95" s="41"/>
     </row>
-    <row r="96" spans="1:62" ht="12.5">
+    <row r="96" spans="1:63" ht="12.5">
       <c r="J96" s="38"/>
       <c r="K96" s="38"/>
       <c r="AA96" s="41"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8C11E4-2A6B-497F-92D4-C0C664F981D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE24543F-2374-4F7F-9774-5B81BAE949F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10112" uniqueCount="1949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10441" uniqueCount="2000">
   <si>
     <t>NAME</t>
   </si>
@@ -6031,6 +6031,159 @@
   </si>
   <si>
     <t>UNLOCK_PRICE</t>
+  </si>
+  <si>
+    <t>twilight_fang</t>
+  </si>
+  <si>
+    <t>oathbreaker</t>
+  </si>
+  <si>
+    <t>ash_of_dawn</t>
+  </si>
+  <si>
+    <t>abyss_whisper</t>
+  </si>
+  <si>
+    <t>final_verdict</t>
+  </si>
+  <si>
+    <t>--------------------------------------ADORNS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>--------------------------------------WEAPONS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>--------------------------------------TRINKETS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>whispering_locket</t>
+  </si>
+  <si>
+    <t>ashen_idol</t>
+  </si>
+  <si>
+    <t>moonveil_charm</t>
+  </si>
+  <si>
+    <t>witchbone_talisman</t>
+  </si>
+  <si>
+    <t>hollow_heart</t>
+  </si>
+  <si>
+    <t>--------------------------------------SHIELDS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>ashen_knight_bulwark</t>
+  </si>
+  <si>
+    <t>voidwalker_aegis</t>
+  </si>
+  <si>
+    <t>bloodmoon_guard</t>
+  </si>
+  <si>
+    <t>frostborn_bulwark</t>
+  </si>
+  <si>
+    <t>gravewarden_shield</t>
+  </si>
+  <si>
+    <t>--------------------------------------HELMETS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>ashen_knight_helm</t>
+  </si>
+  <si>
+    <t>voidwalker_crown</t>
+  </si>
+  <si>
+    <t>bloodmoon_visage</t>
+  </si>
+  <si>
+    <t>frostborn_helm</t>
+  </si>
+  <si>
+    <t>gravewarden_greathelm</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>--------------------------------------BOOTS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>ashen_knight_greaves</t>
+  </si>
+  <si>
+    <t>voidwalker_treads</t>
+  </si>
+  <si>
+    <t>bloodmoon_striders</t>
+  </si>
+  <si>
+    <t>frostborn_sabatons</t>
+  </si>
+  <si>
+    <t>gravewarden_greaves</t>
+  </si>
+  <si>
+    <t>--------------------------------------AMULET---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>ashen_knight_pendant</t>
+  </si>
+  <si>
+    <t>voidwalker_talisman</t>
+  </si>
+  <si>
+    <t>bloodmoon_amulet</t>
+  </si>
+  <si>
+    <t>frostborn_pendant</t>
+  </si>
+  <si>
+    <t>gravewarden_charm</t>
+  </si>
+  <si>
+    <t>--------------------------------------RINGS---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>boots</t>
+  </si>
+  <si>
+    <t>--------------------------------------ARMOR---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>ashen_knight_signet</t>
+  </si>
+  <si>
+    <t>voidwalker_band</t>
+  </si>
+  <si>
+    <t>bloodmoon_ring</t>
+  </si>
+  <si>
+    <t>frostborn_signet</t>
+  </si>
+  <si>
+    <t>gravewarden_seal</t>
+  </si>
+  <si>
+    <t>ashen_knight_plate</t>
+  </si>
+  <si>
+    <t>voidwalker_carapace</t>
+  </si>
+  <si>
+    <t>bloodmoon_cuirass</t>
+  </si>
+  <si>
+    <t>frostborn_plate</t>
+  </si>
+  <si>
+    <t>gravewarden_armor</t>
   </si>
 </sst>
 </file>
@@ -6307,7 +6460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6401,6 +6554,9 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -54864,10 +55020,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" customWidth="1"/>
     <col min="2" max="3" width="11.26953125" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
@@ -57905,98 +58061,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
-      <c r="A35" s="44" t="s">
-        <v>1875</v>
-      </c>
-      <c r="B35" s="44" t="s">
-        <v>1876</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="44">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>20</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>10</v>
-      </c>
-      <c r="U35" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>1</v>
-      </c>
-      <c r="X35" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z35">
-        <v>11</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC35">
-        <v>5</v>
-      </c>
+    <row r="35" spans="1:29" ht="14">
+      <c r="A35" s="55" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="U35" s="44"/>
+      <c r="X35" s="44"/>
     </row>
     <row r="36" spans="1:29">
       <c r="A36" s="44" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="B36" s="44" t="s">
         <v>1876</v>
@@ -58014,7 +58091,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -58029,7 +58106,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -58085,7 +58162,7 @@
     </row>
     <row r="37" spans="1:29">
       <c r="A37" s="44" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B37" s="44" t="s">
         <v>1876</v>
@@ -58112,13 +58189,13 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -58174,7 +58251,7 @@
     </row>
     <row r="38" spans="1:29">
       <c r="A38" s="44" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B38" s="44" t="s">
         <v>1876</v>
@@ -58195,16 +58272,16 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -58258,6 +58335,3695 @@
         <v>36</v>
       </c>
       <c r="AC38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" s="44" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B39" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="44">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>20</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>10</v>
+      </c>
+      <c r="U39" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>1</v>
+      </c>
+      <c r="X39" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z39">
+        <v>11</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" ht="14">
+      <c r="A40" s="55" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
+      <c r="A41" s="44" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="44">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>10</v>
+      </c>
+      <c r="U41" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z41">
+        <v>11</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="A42" s="44" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="44">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>10</v>
+      </c>
+      <c r="U42" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z42">
+        <v>11</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" s="44" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B43" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="44">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>10</v>
+      </c>
+      <c r="U43" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z43">
+        <v>11</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
+      <c r="A44" s="44" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" s="44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>10</v>
+      </c>
+      <c r="U44" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>1</v>
+      </c>
+      <c r="X44" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z44">
+        <v>11</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="A45" s="44" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="44">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>10</v>
+      </c>
+      <c r="U45" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>1</v>
+      </c>
+      <c r="X45" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z45">
+        <v>11</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" ht="14">
+      <c r="A46" s="55" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="A47" s="44" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B47" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="44">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>10</v>
+      </c>
+      <c r="U47" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>1</v>
+      </c>
+      <c r="X47" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z47">
+        <v>11</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="A48" s="44" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B48" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" s="44">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>10</v>
+      </c>
+      <c r="U48" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>1</v>
+      </c>
+      <c r="X48" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z48">
+        <v>11</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
+      <c r="A49" s="44" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B49" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="44">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>10</v>
+      </c>
+      <c r="U49" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>1</v>
+      </c>
+      <c r="X49" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z49">
+        <v>11</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
+      <c r="A50" s="44" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="44">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>10</v>
+      </c>
+      <c r="U50" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>1</v>
+      </c>
+      <c r="X50" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z50">
+        <v>11</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" s="44" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B51" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="44">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>10</v>
+      </c>
+      <c r="U51" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>1</v>
+      </c>
+      <c r="X51" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z51">
+        <v>11</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" ht="14">
+      <c r="A52" s="55" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="44">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>100</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>10</v>
+      </c>
+      <c r="U53" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>1</v>
+      </c>
+      <c r="X53" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z53">
+        <v>11</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="44">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>10</v>
+      </c>
+      <c r="U54" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z54">
+        <v>11</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
+      <c r="A55" s="60" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55" s="44">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>10</v>
+      </c>
+      <c r="U55" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z55">
+        <v>11</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29">
+      <c r="A56" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="44">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>100</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>10</v>
+      </c>
+      <c r="U56" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>1</v>
+      </c>
+      <c r="X56" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z56">
+        <v>11</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29">
+      <c r="A57" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B57" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="44">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>100</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>10</v>
+      </c>
+      <c r="U57" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>1</v>
+      </c>
+      <c r="X57" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z57">
+        <v>11</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" ht="14">
+      <c r="A58" s="55" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29">
+      <c r="A59" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C59" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" s="44">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>100</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>10</v>
+      </c>
+      <c r="U59" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>1</v>
+      </c>
+      <c r="X59" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z59">
+        <v>11</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29">
+      <c r="A60" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B60" s="44" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="44">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>10</v>
+      </c>
+      <c r="U60" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>1</v>
+      </c>
+      <c r="X60" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z60">
+        <v>11</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29">
+      <c r="A61" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B61" s="44" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="44">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>100</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>10</v>
+      </c>
+      <c r="U61" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z61">
+        <v>11</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29">
+      <c r="A62" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B62" s="44" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C62" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="44">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>100</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>10</v>
+      </c>
+      <c r="U62" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>1</v>
+      </c>
+      <c r="X62" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z62">
+        <v>11</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29">
+      <c r="A63" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C63" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="44">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>100</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>10</v>
+      </c>
+      <c r="U63" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>1</v>
+      </c>
+      <c r="X63" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z63">
+        <v>11</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" ht="14">
+      <c r="A64" s="55" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29">
+      <c r="A65" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B65" s="44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C65" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" s="44">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>100</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>10</v>
+      </c>
+      <c r="U65" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>1</v>
+      </c>
+      <c r="X65" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z65">
+        <v>11</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29">
+      <c r="A66" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="44">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>100</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>10</v>
+      </c>
+      <c r="U66" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>1</v>
+      </c>
+      <c r="X66" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z66">
+        <v>11</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29">
+      <c r="A67" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="44">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>100</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>10</v>
+      </c>
+      <c r="U67" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="X67" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z67">
+        <v>11</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29">
+      <c r="A68" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B68" s="44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C68" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" s="44">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>100</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>10</v>
+      </c>
+      <c r="U68" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
+      <c r="X68" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z68">
+        <v>11</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29">
+      <c r="A69" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B69" s="44" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C69" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="44">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>100</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>10</v>
+      </c>
+      <c r="U69" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>1</v>
+      </c>
+      <c r="X69" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z69">
+        <v>11</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" ht="14">
+      <c r="A70" s="55" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29">
+      <c r="A71" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B71" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="44">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>100</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>10</v>
+      </c>
+      <c r="U71" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z71">
+        <v>11</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29">
+      <c r="A72" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B72" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" s="44">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>100</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>10</v>
+      </c>
+      <c r="U72" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="X72" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z72">
+        <v>11</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29">
+      <c r="A73" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B73" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C73" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="44">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>100</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>10</v>
+      </c>
+      <c r="U73" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>1</v>
+      </c>
+      <c r="X73" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z73">
+        <v>11</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29">
+      <c r="A74" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B74" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C74" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" s="44">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>100</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>10</v>
+      </c>
+      <c r="U74" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z74">
+        <v>11</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29">
+      <c r="A75" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C75" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="44">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>100</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>10</v>
+      </c>
+      <c r="U75" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="X75" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z75">
+        <v>11</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" ht="14">
+      <c r="A76" s="55" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29">
+      <c r="A77" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B77" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="44">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>100</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>10</v>
+      </c>
+      <c r="U77" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="X77" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z77">
+        <v>11</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29">
+      <c r="A78" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="44">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>100</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>10</v>
+      </c>
+      <c r="U78" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>1</v>
+      </c>
+      <c r="X78" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z78">
+        <v>11</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29">
+      <c r="A79" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B79" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C79" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" s="44">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>100</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>10</v>
+      </c>
+      <c r="U79" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z79">
+        <v>11</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29">
+      <c r="A80" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B80" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D80" s="44">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>100</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>10</v>
+      </c>
+      <c r="U80" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="X80" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z80">
+        <v>11</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29">
+      <c r="A81" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B81" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C81" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="44">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>100</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>10</v>
+      </c>
+      <c r="U81" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z81">
+        <v>11</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" ht="14">
+      <c r="A82" s="55" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29">
+      <c r="A83" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B83" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C83" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" s="44">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>100</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>10</v>
+      </c>
+      <c r="U83" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>1</v>
+      </c>
+      <c r="X83" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z83">
+        <v>11</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29">
+      <c r="A84" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B84" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" s="44">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>100</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>10</v>
+      </c>
+      <c r="U84" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="X84" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z84">
+        <v>11</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29">
+      <c r="A85" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B85" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C85" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" s="44">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>100</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>10</v>
+      </c>
+      <c r="U85" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>1</v>
+      </c>
+      <c r="X85" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z85">
+        <v>11</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29">
+      <c r="A86" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C86" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D86" s="44">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>100</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>10</v>
+      </c>
+      <c r="U86" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>1</v>
+      </c>
+      <c r="X86" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z86">
+        <v>11</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29">
+      <c r="A87" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B87" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C87" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" s="44">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>100</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>10</v>
+      </c>
+      <c r="U87" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="X87" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z87">
+        <v>11</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC87">
         <v>5</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE24543F-2374-4F7F-9774-5B81BAE949F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D97341-9972-4050-8386-064500E38E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10441" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="2000">
   <si>
     <t>NAME</t>
   </si>
@@ -6108,9 +6108,6 @@
     <t>gravewarden_greathelm</t>
   </si>
   <si>
-    <t>helmet</t>
-  </si>
-  <si>
     <t>--------------------------------------BOOTS---------------------------------------------------</t>
   </si>
   <si>
@@ -6184,6 +6181,9 @@
   </si>
   <si>
     <t>gravewarden_armor</t>
+  </si>
+  <si>
+    <t>town_petshop1</t>
   </si>
 </sst>
 </file>
@@ -43864,7 +43864,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
@@ -44998,6 +44998,75 @@
         <v>1885</v>
       </c>
       <c r="G70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>100</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1854</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>100</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <v>100</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G74">
         <v>0</v>
       </c>
     </row>
@@ -59787,7 +59856,7 @@
         <v>1969</v>
       </c>
       <c r="B59" s="44" t="s">
-        <v>1974</v>
+        <v>846</v>
       </c>
       <c r="C59" s="44" t="s">
         <v>36</v>
@@ -59876,7 +59945,7 @@
         <v>1970</v>
       </c>
       <c r="B60" s="44" t="s">
-        <v>1974</v>
+        <v>846</v>
       </c>
       <c r="C60" s="44" t="s">
         <v>36</v>
@@ -59965,7 +60034,7 @@
         <v>1971</v>
       </c>
       <c r="B61" s="44" t="s">
-        <v>1974</v>
+        <v>846</v>
       </c>
       <c r="C61" s="44" t="s">
         <v>36</v>
@@ -60054,7 +60123,7 @@
         <v>1972</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>1974</v>
+        <v>846</v>
       </c>
       <c r="C62" s="44" t="s">
         <v>36</v>
@@ -60143,7 +60212,7 @@
         <v>1973</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>1974</v>
+        <v>846</v>
       </c>
       <c r="C63" s="44" t="s">
         <v>36</v>
@@ -60229,15 +60298,15 @@
     </row>
     <row r="64" spans="1:29" ht="14">
       <c r="A64" s="55" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="65" spans="1:29">
       <c r="A65" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C65" s="44" t="s">
         <v>36</v>
@@ -60323,10 +60392,10 @@
     </row>
     <row r="66" spans="1:29">
       <c r="A66" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C66" s="44" t="s">
         <v>36</v>
@@ -60412,10 +60481,10 @@
     </row>
     <row r="67" spans="1:29">
       <c r="A67" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B67" s="44" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C67" s="44" t="s">
         <v>36</v>
@@ -60501,10 +60570,10 @@
     </row>
     <row r="68" spans="1:29">
       <c r="A68" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B68" s="44" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C68" s="44" t="s">
         <v>36</v>
@@ -60590,10 +60659,10 @@
     </row>
     <row r="69" spans="1:29">
       <c r="A69" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B69" s="44" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C69" s="44" t="s">
         <v>36</v>
@@ -60679,12 +60748,12 @@
     </row>
     <row r="70" spans="1:29" ht="14">
       <c r="A70" s="55" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="71" spans="1:29">
       <c r="A71" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B71" s="44" t="s">
         <v>833</v>
@@ -60773,7 +60842,7 @@
     </row>
     <row r="72" spans="1:29">
       <c r="A72" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B72" s="44" t="s">
         <v>833</v>
@@ -60862,7 +60931,7 @@
     </row>
     <row r="73" spans="1:29">
       <c r="A73" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B73" s="44" t="s">
         <v>833</v>
@@ -60951,7 +61020,7 @@
     </row>
     <row r="74" spans="1:29">
       <c r="A74" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B74" s="44" t="s">
         <v>833</v>
@@ -61040,7 +61109,7 @@
     </row>
     <row r="75" spans="1:29">
       <c r="A75" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B75" s="44" t="s">
         <v>833</v>
@@ -61129,12 +61198,12 @@
     </row>
     <row r="76" spans="1:29" ht="14">
       <c r="A76" s="55" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="77" spans="1:29">
       <c r="A77" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B77" s="44" t="s">
         <v>1079</v>
@@ -61223,7 +61292,7 @@
     </row>
     <row r="78" spans="1:29">
       <c r="A78" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B78" s="44" t="s">
         <v>1079</v>
@@ -61312,7 +61381,7 @@
     </row>
     <row r="79" spans="1:29">
       <c r="A79" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B79" s="44" t="s">
         <v>1079</v>
@@ -61401,7 +61470,7 @@
     </row>
     <row r="80" spans="1:29">
       <c r="A80" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B80" s="44" t="s">
         <v>1079</v>
@@ -61490,7 +61559,7 @@
     </row>
     <row r="81" spans="1:29">
       <c r="A81" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B81" s="44" t="s">
         <v>1079</v>
@@ -61579,12 +61648,12 @@
     </row>
     <row r="82" spans="1:29" ht="14">
       <c r="A82" s="55" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="83" spans="1:29">
       <c r="A83" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B83" s="44" t="s">
         <v>821</v>
@@ -61673,7 +61742,7 @@
     </row>
     <row r="84" spans="1:29">
       <c r="A84" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B84" s="44" t="s">
         <v>821</v>
@@ -61762,7 +61831,7 @@
     </row>
     <row r="85" spans="1:29">
       <c r="A85" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B85" s="44" t="s">
         <v>821</v>
@@ -61851,7 +61920,7 @@
     </row>
     <row r="86" spans="1:29">
       <c r="A86" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B86" s="44" t="s">
         <v>821</v>
@@ -61940,7 +62009,7 @@
     </row>
     <row r="87" spans="1:29">
       <c r="A87" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B87" s="44" t="s">
         <v>821</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D97341-9972-4050-8386-064500E38E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D1C505-5136-487D-839A-E734E95D0268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="2001">
   <si>
     <t>NAME</t>
   </si>
@@ -5826,9 +5826,6 @@
     <t>adorn_magic</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1</t>
-  </si>
-  <si>
     <t>MAX_STACK</t>
   </si>
   <si>
@@ -6108,6 +6105,9 @@
     <t>gravewarden_greathelm</t>
   </si>
   <si>
+    <t>helmet</t>
+  </si>
+  <si>
     <t>--------------------------------------BOOTS---------------------------------------------------</t>
   </si>
   <si>
@@ -6184,6 +6184,9 @@
   </si>
   <si>
     <t>town_petshop1</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1</t>
   </si>
 </sst>
 </file>
@@ -6887,7 +6890,7 @@
         <v>1809</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>1811</v>
@@ -7061,7 +7064,7 @@
         <v>1872</v>
       </c>
       <c r="BK1" s="43" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="2" spans="1:63" ht="12.5">
@@ -7156,7 +7159,7 @@
         <v>42</v>
       </c>
       <c r="AE2" s="40" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="AF2" s="40">
         <v>40</v>
@@ -21773,7 +21776,7 @@
     </row>
     <row r="79" spans="1:63" ht="14">
       <c r="A79" s="55" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B79" s="56"/>
       <c r="C79" s="57"/>
@@ -21796,7 +21799,7 @@
     </row>
     <row r="80" spans="1:63" ht="12.5">
       <c r="A80" s="47" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B80" s="53">
         <v>1</v>
@@ -21880,13 +21883,13 @@
         <v>33</v>
       </c>
       <c r="AC80" s="40" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="AD80" s="40" t="s">
         <v>42</v>
       </c>
       <c r="AE80" s="59" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="AF80" s="40">
         <v>40</v>
@@ -21987,7 +21990,7 @@
     </row>
     <row r="81" spans="1:63" ht="12.5">
       <c r="A81" s="47" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B81" s="53">
         <v>1</v>
@@ -22071,13 +22074,13 @@
         <v>33</v>
       </c>
       <c r="AC81" s="40" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="AD81" s="40" t="s">
         <v>42</v>
       </c>
       <c r="AE81" s="40" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="AF81" s="40">
         <v>40</v>
@@ -22178,7 +22181,7 @@
     </row>
     <row r="82" spans="1:63" ht="12.5">
       <c r="A82" s="47" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B82" s="53">
         <v>1</v>
@@ -22262,13 +22265,13 @@
         <v>33</v>
       </c>
       <c r="AC82" s="40" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="AD82" s="40" t="s">
         <v>42</v>
       </c>
       <c r="AE82" s="59" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="AF82" s="40">
         <v>40</v>
@@ -22369,7 +22372,7 @@
     </row>
     <row r="83" spans="1:63" ht="12.5">
       <c r="A83" s="47" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B83" s="53">
         <v>1</v>
@@ -22453,13 +22456,13 @@
         <v>33</v>
       </c>
       <c r="AC83" s="40" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="AD83" s="40" t="s">
         <v>42</v>
       </c>
       <c r="AE83" s="59" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="AF83" s="40">
         <v>40</v>
@@ -22560,7 +22563,7 @@
     </row>
     <row r="84" spans="1:63" ht="12.5">
       <c r="A84" s="47" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B84" s="53">
         <v>1</v>
@@ -22644,13 +22647,13 @@
         <v>33</v>
       </c>
       <c r="AC84" s="40" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="AD84" s="40" t="s">
         <v>42</v>
       </c>
       <c r="AE84" s="40" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="AF84" s="40">
         <v>40</v>
@@ -44934,7 +44937,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -44949,7 +44952,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -44972,7 +44975,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -44995,7 +44998,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -45919,7 +45922,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1880</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -58132,7 +58135,7 @@
     </row>
     <row r="35" spans="1:29" ht="14">
       <c r="A35" s="55" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B35" s="44"/>
       <c r="C35" s="44"/>
@@ -58498,12 +58501,12 @@
     </row>
     <row r="40" spans="1:29" ht="14">
       <c r="A40" s="55" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="41" spans="1:29">
       <c r="A41" s="44" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B41" s="44" t="s">
         <v>818</v>
@@ -58592,7 +58595,7 @@
     </row>
     <row r="42" spans="1:29">
       <c r="A42" s="44" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B42" s="44" t="s">
         <v>818</v>
@@ -58681,7 +58684,7 @@
     </row>
     <row r="43" spans="1:29">
       <c r="A43" s="44" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B43" s="44" t="s">
         <v>818</v>
@@ -58770,7 +58773,7 @@
     </row>
     <row r="44" spans="1:29">
       <c r="A44" s="44" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B44" s="44" t="s">
         <v>818</v>
@@ -58859,7 +58862,7 @@
     </row>
     <row r="45" spans="1:29">
       <c r="A45" s="44" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B45" s="44" t="s">
         <v>818</v>
@@ -58948,12 +58951,12 @@
     </row>
     <row r="46" spans="1:29" ht="14">
       <c r="A46" s="55" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="47" spans="1:29">
       <c r="A47" s="44" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B47" s="44" t="s">
         <v>1802</v>
@@ -59013,7 +59016,7 @@
         <v>10</v>
       </c>
       <c r="U47" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -59042,7 +59045,7 @@
     </row>
     <row r="48" spans="1:29">
       <c r="A48" s="44" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B48" s="44" t="s">
         <v>1802</v>
@@ -59102,7 +59105,7 @@
         <v>10</v>
       </c>
       <c r="U48" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -59131,7 +59134,7 @@
     </row>
     <row r="49" spans="1:29">
       <c r="A49" s="44" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B49" s="44" t="s">
         <v>1802</v>
@@ -59191,7 +59194,7 @@
         <v>10</v>
       </c>
       <c r="U49" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -59220,7 +59223,7 @@
     </row>
     <row r="50" spans="1:29">
       <c r="A50" s="44" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B50" s="44" t="s">
         <v>1802</v>
@@ -59280,7 +59283,7 @@
         <v>10</v>
       </c>
       <c r="U50" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -59309,7 +59312,7 @@
     </row>
     <row r="51" spans="1:29">
       <c r="A51" s="44" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B51" s="44" t="s">
         <v>1802</v>
@@ -59369,7 +59372,7 @@
         <v>10</v>
       </c>
       <c r="U51" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -59398,15 +59401,15 @@
     </row>
     <row r="52" spans="1:29" ht="14">
       <c r="A52" s="55" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="53" spans="1:29">
       <c r="A53" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B53" s="44" t="s">
-        <v>238</v>
+        <v>1800</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>36</v>
@@ -59463,7 +59466,7 @@
         <v>10</v>
       </c>
       <c r="U53" s="44" t="s">
-        <v>818</v>
+        <v>1800</v>
       </c>
       <c r="V53">
         <v>0</v>
@@ -59492,10 +59495,10 @@
     </row>
     <row r="54" spans="1:29">
       <c r="A54" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B54" s="44" t="s">
-        <v>238</v>
+        <v>1800</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>36</v>
@@ -59552,7 +59555,7 @@
         <v>10</v>
       </c>
       <c r="U54" s="44" t="s">
-        <v>818</v>
+        <v>1800</v>
       </c>
       <c r="V54">
         <v>0</v>
@@ -59581,10 +59584,10 @@
     </row>
     <row r="55" spans="1:29">
       <c r="A55" s="60" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>238</v>
+        <v>1800</v>
       </c>
       <c r="C55" s="44" t="s">
         <v>36</v>
@@ -59641,7 +59644,7 @@
         <v>10</v>
       </c>
       <c r="U55" s="44" t="s">
-        <v>818</v>
+        <v>1800</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -59670,10 +59673,10 @@
     </row>
     <row r="56" spans="1:29">
       <c r="A56" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B56" s="44" t="s">
-        <v>238</v>
+        <v>1800</v>
       </c>
       <c r="C56" s="44" t="s">
         <v>36</v>
@@ -59730,7 +59733,7 @@
         <v>10</v>
       </c>
       <c r="U56" s="44" t="s">
-        <v>818</v>
+        <v>1800</v>
       </c>
       <c r="V56">
         <v>0</v>
@@ -59759,10 +59762,10 @@
     </row>
     <row r="57" spans="1:29">
       <c r="A57" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B57" s="44" t="s">
-        <v>238</v>
+        <v>1800</v>
       </c>
       <c r="C57" s="44" t="s">
         <v>36</v>
@@ -59819,7 +59822,7 @@
         <v>10</v>
       </c>
       <c r="U57" s="44" t="s">
-        <v>818</v>
+        <v>1800</v>
       </c>
       <c r="V57">
         <v>0</v>
@@ -59848,12 +59851,12 @@
     </row>
     <row r="58" spans="1:29" ht="14">
       <c r="A58" s="55" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="59" spans="1:29">
       <c r="A59" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B59" s="44" t="s">
         <v>846</v>
@@ -59913,7 +59916,7 @@
         <v>10</v>
       </c>
       <c r="U59" s="44" t="s">
-        <v>818</v>
+        <v>1973</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -59942,7 +59945,7 @@
     </row>
     <row r="60" spans="1:29">
       <c r="A60" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B60" s="44" t="s">
         <v>846</v>
@@ -60002,7 +60005,7 @@
         <v>10</v>
       </c>
       <c r="U60" s="44" t="s">
-        <v>818</v>
+        <v>1973</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -60031,7 +60034,7 @@
     </row>
     <row r="61" spans="1:29">
       <c r="A61" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B61" s="44" t="s">
         <v>846</v>
@@ -60091,7 +60094,7 @@
         <v>10</v>
       </c>
       <c r="U61" s="44" t="s">
-        <v>818</v>
+        <v>1973</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -60120,7 +60123,7 @@
     </row>
     <row r="62" spans="1:29">
       <c r="A62" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B62" s="44" t="s">
         <v>846</v>
@@ -60180,7 +60183,7 @@
         <v>10</v>
       </c>
       <c r="U62" s="44" t="s">
-        <v>818</v>
+        <v>1973</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -60209,7 +60212,7 @@
     </row>
     <row r="63" spans="1:29">
       <c r="A63" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B63" s="44" t="s">
         <v>846</v>
@@ -60269,7 +60272,7 @@
         <v>10</v>
       </c>
       <c r="U63" s="44" t="s">
-        <v>818</v>
+        <v>1973</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -60363,7 +60366,7 @@
         <v>10</v>
       </c>
       <c r="U65" s="44" t="s">
-        <v>818</v>
+        <v>1987</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -60452,7 +60455,7 @@
         <v>10</v>
       </c>
       <c r="U66" s="44" t="s">
-        <v>818</v>
+        <v>1987</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -60541,7 +60544,7 @@
         <v>10</v>
       </c>
       <c r="U67" s="44" t="s">
-        <v>818</v>
+        <v>1987</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -60630,7 +60633,7 @@
         <v>10</v>
       </c>
       <c r="U68" s="44" t="s">
-        <v>818</v>
+        <v>1987</v>
       </c>
       <c r="V68">
         <v>0</v>
@@ -60719,7 +60722,7 @@
         <v>10</v>
       </c>
       <c r="U69" s="44" t="s">
-        <v>818</v>
+        <v>1987</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -60813,7 +60816,7 @@
         <v>10</v>
       </c>
       <c r="U71" s="44" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="V71">
         <v>0</v>
@@ -60902,7 +60905,7 @@
         <v>10</v>
       </c>
       <c r="U72" s="44" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -60991,7 +60994,7 @@
         <v>10</v>
       </c>
       <c r="U73" s="44" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="V73">
         <v>0</v>
@@ -61080,7 +61083,7 @@
         <v>10</v>
       </c>
       <c r="U74" s="44" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -61169,7 +61172,7 @@
         <v>10</v>
       </c>
       <c r="U75" s="44" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -61263,7 +61266,7 @@
         <v>10</v>
       </c>
       <c r="U77" s="44" t="s">
-        <v>818</v>
+        <v>1079</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -61352,7 +61355,7 @@
         <v>10</v>
       </c>
       <c r="U78" s="44" t="s">
-        <v>818</v>
+        <v>1079</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -61441,7 +61444,7 @@
         <v>10</v>
       </c>
       <c r="U79" s="44" t="s">
-        <v>818</v>
+        <v>1079</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -61530,7 +61533,7 @@
         <v>10</v>
       </c>
       <c r="U80" s="44" t="s">
-        <v>818</v>
+        <v>1079</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -61619,7 +61622,7 @@
         <v>10</v>
       </c>
       <c r="U81" s="44" t="s">
-        <v>818</v>
+        <v>1079</v>
       </c>
       <c r="V81">
         <v>0</v>
@@ -61713,7 +61716,7 @@
         <v>10</v>
       </c>
       <c r="U83" s="44" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -61802,7 +61805,7 @@
         <v>10</v>
       </c>
       <c r="U84" s="44" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -61891,7 +61894,7 @@
         <v>10</v>
       </c>
       <c r="U85" s="44" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -61980,7 +61983,7 @@
         <v>10</v>
       </c>
       <c r="U86" s="44" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -62069,7 +62072,7 @@
         <v>10</v>
       </c>
       <c r="U87" s="44" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -62262,7 +62265,7 @@
         <v>1360</v>
       </c>
       <c r="AG1" s="43" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="AH1" s="43" t="s">
         <v>1495</v>
@@ -62346,10 +62349,10 @@
         <v>1101</v>
       </c>
       <c r="BI1" s="43" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="BJ1" s="43" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="BK1" s="43"/>
     </row>
@@ -62543,7 +62546,7 @@
     </row>
     <row r="3" spans="1:63">
       <c r="A3" s="44" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -62731,7 +62734,7 @@
     </row>
     <row r="4" spans="1:63">
       <c r="A4" s="44" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -63483,7 +63486,7 @@
     </row>
     <row r="8" spans="1:63">
       <c r="A8" s="44" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -65175,7 +65178,7 @@
     </row>
     <row r="17" spans="1:62">
       <c r="A17" s="44" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -65274,7 +65277,7 @@
         <v>36</v>
       </c>
       <c r="AH17" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="AI17" s="44" t="s">
         <v>1363</v>
@@ -65462,7 +65465,7 @@
         <v>36</v>
       </c>
       <c r="AH18" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="AI18" s="44" t="s">
         <v>1363</v>
@@ -65927,7 +65930,7 @@
     </row>
     <row r="21" spans="1:62">
       <c r="A21" s="44" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -66026,7 +66029,7 @@
         <v>36</v>
       </c>
       <c r="AH21" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="AI21" s="44" t="s">
         <v>1363</v>
@@ -66115,7 +66118,7 @@
     </row>
     <row r="22" spans="1:62">
       <c r="A22" s="44" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B22">
         <v>-1</v>
@@ -66303,7 +66306,7 @@
     </row>
     <row r="23" spans="1:62">
       <c r="A23" s="44" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -66402,7 +66405,7 @@
         <v>36</v>
       </c>
       <c r="AH23" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="AI23" s="44" t="s">
         <v>1363</v>
@@ -66491,7 +66494,7 @@
     </row>
     <row r="24" spans="1:62">
       <c r="A24" s="44" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -66679,7 +66682,7 @@
     </row>
     <row r="25" spans="1:62">
       <c r="A25" s="44" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B25">
         <v>-1</v>
@@ -66867,7 +66870,7 @@
     </row>
     <row r="26" spans="1:62">
       <c r="A26" s="44" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B26">
         <v>-1</v>
@@ -67530,7 +67533,7 @@
         <v>36</v>
       </c>
       <c r="AH29" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="AI29" s="44" t="s">
         <v>1363</v>
@@ -70627,7 +70630,7 @@
     </row>
     <row r="46" spans="1:62">
       <c r="A46" s="44" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -70723,10 +70726,10 @@
         <v>10</v>
       </c>
       <c r="AG46" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="AH46" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="AI46" s="44" t="s">
         <v>1479</v>
@@ -70815,7 +70818,7 @@
     </row>
     <row r="47" spans="1:62">
       <c r="A47" s="44" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -71003,7 +71006,7 @@
     </row>
     <row r="48" spans="1:62">
       <c r="A48" s="44" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -71191,7 +71194,7 @@
     </row>
     <row r="49" spans="1:62">
       <c r="A49" s="44" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -71290,7 +71293,7 @@
         <v>36</v>
       </c>
       <c r="AH49" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="AI49" s="44" t="s">
         <v>1479</v>
@@ -71379,7 +71382,7 @@
     </row>
     <row r="50" spans="1:62">
       <c r="A50" s="44" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -71666,7 +71669,7 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="AI51" s="44" t="s">
         <v>1479</v>
@@ -72319,7 +72322,7 @@
     </row>
     <row r="55" spans="1:62">
       <c r="A55" s="44" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -72418,7 +72421,7 @@
         <v>36</v>
       </c>
       <c r="AH55" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="AI55" s="44" t="s">
         <v>1363</v>
@@ -72507,7 +72510,7 @@
     </row>
     <row r="56" spans="1:62">
       <c r="A56" s="44" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -72690,7 +72693,7 @@
         <v>0</v>
       </c>
       <c r="BJ56" s="46" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="57" spans="1:62">
@@ -72794,7 +72797,7 @@
         <v>36</v>
       </c>
       <c r="AH57" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AI57" s="44" t="s">
         <v>1363</v>
@@ -73071,7 +73074,7 @@
     </row>
     <row r="59" spans="1:62">
       <c r="A59" s="44" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -73170,7 +73173,7 @@
         <v>36</v>
       </c>
       <c r="AH59" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AI59" s="44" t="s">
         <v>1479</v>
@@ -73259,7 +73262,7 @@
     </row>
     <row r="60" spans="1:62">
       <c r="A60" s="44" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -73546,7 +73549,7 @@
         <v>36</v>
       </c>
       <c r="AH61" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AI61" s="44" t="s">
         <v>1479</v>
@@ -73823,7 +73826,7 @@
     </row>
     <row r="63" spans="1:62">
       <c r="A63" s="44" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -74011,7 +74014,7 @@
     </row>
     <row r="64" spans="1:62">
       <c r="A64" s="44" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -74199,7 +74202,7 @@
     </row>
     <row r="65" spans="1:62">
       <c r="A65" s="44" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -74387,7 +74390,7 @@
     </row>
     <row r="66" spans="1:62">
       <c r="A66" s="44" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -74575,7 +74578,7 @@
     </row>
     <row r="67" spans="1:62">
       <c r="A67" s="44" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -74763,7 +74766,7 @@
     </row>
     <row r="68" spans="1:62">
       <c r="A68" s="44" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -74859,10 +74862,10 @@
         <v>10</v>
       </c>
       <c r="AG68" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AH68" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="AI68" s="44" t="s">
         <v>1363</v>
@@ -74951,7 +74954,7 @@
     </row>
     <row r="69" spans="1:62">
       <c r="A69" s="44" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B69">
         <v>-1</v>
@@ -75139,7 +75142,7 @@
     </row>
     <row r="70" spans="1:62" ht="14">
       <c r="A70" s="55" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B70" s="55"/>
       <c r="C70" s="55"/>
@@ -75172,7 +75175,7 @@
     </row>
     <row r="71" spans="1:62">
       <c r="A71" s="44" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -75360,7 +75363,7 @@
     </row>
     <row r="72" spans="1:62">
       <c r="A72" s="44" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -75548,7 +75551,7 @@
     </row>
     <row r="73" spans="1:62">
       <c r="A73" s="44" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -75731,12 +75734,12 @@
         <v>0</v>
       </c>
       <c r="BJ73" s="46" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="74" spans="1:62">
       <c r="A74" s="44" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -75919,12 +75922,12 @@
         <v>0</v>
       </c>
       <c r="BJ74" s="46" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="75" spans="1:62">
       <c r="A75" s="44" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -76107,7 +76110,7 @@
         <v>0</v>
       </c>
       <c r="BJ75" s="46" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="76" spans="1:62">

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D1C505-5136-487D-839A-E734E95D0268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAD4828-85CD-490E-A0F6-C0562A9C1883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -7493,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="48">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="P4" s="48">
         <v>45</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAD4828-85CD-490E-A0F6-C0562A9C1883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEC77A1-9953-4160-936D-D85566AF6310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10837" uniqueCount="2040">
   <si>
     <t>NAME</t>
   </si>
@@ -6187,6 +6187,123 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1</t>
+  </si>
+  <si>
+    <t>monthly_0</t>
+  </si>
+  <si>
+    <t>monthly_1</t>
+  </si>
+  <si>
+    <t>monthly_2</t>
+  </si>
+  <si>
+    <t>monthly_3</t>
+  </si>
+  <si>
+    <t>monthly_4</t>
+  </si>
+  <si>
+    <t>monthly_5</t>
+  </si>
+  <si>
+    <t>monthly_6</t>
+  </si>
+  <si>
+    <t>monthly_7</t>
+  </si>
+  <si>
+    <t>monthly_8</t>
+  </si>
+  <si>
+    <t>monthly_9</t>
+  </si>
+  <si>
+    <t>gold,201</t>
+  </si>
+  <si>
+    <t>gold,202</t>
+  </si>
+  <si>
+    <t>gold,203</t>
+  </si>
+  <si>
+    <t>gold,204</t>
+  </si>
+  <si>
+    <t>gold,205</t>
+  </si>
+  <si>
+    <t>gold,206</t>
+  </si>
+  <si>
+    <t>gold,207</t>
+  </si>
+  <si>
+    <t>gold,208</t>
+  </si>
+  <si>
+    <t>gold,209</t>
+  </si>
+  <si>
+    <t>monthly_10</t>
+  </si>
+  <si>
+    <t>monthly_11</t>
+  </si>
+  <si>
+    <t>monthly_12</t>
+  </si>
+  <si>
+    <t>monthly_13</t>
+  </si>
+  <si>
+    <t>monthly_14</t>
+  </si>
+  <si>
+    <t>monthly_15</t>
+  </si>
+  <si>
+    <t>monthly_16</t>
+  </si>
+  <si>
+    <t>monthly_17</t>
+  </si>
+  <si>
+    <t>monthly_18</t>
+  </si>
+  <si>
+    <t>monthly_19</t>
+  </si>
+  <si>
+    <t>monthly_20</t>
+  </si>
+  <si>
+    <t>monthly_21</t>
+  </si>
+  <si>
+    <t>monthly_22</t>
+  </si>
+  <si>
+    <t>monthly_23</t>
+  </si>
+  <si>
+    <t>monthly_24</t>
+  </si>
+  <si>
+    <t>monthly_25</t>
+  </si>
+  <si>
+    <t>monthly_26</t>
+  </si>
+  <si>
+    <t>monthly_27</t>
+  </si>
+  <si>
+    <t>monthly_28</t>
+  </si>
+  <si>
+    <t>monthly_29</t>
   </si>
 </sst>
 </file>
@@ -45172,7 +45289,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
@@ -45850,6 +45967,1416 @@
         <v>1189</v>
       </c>
       <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J23" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>36</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>36</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F25" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J25" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J27" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>36</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J28" t="s">
+        <v>36</v>
+      </c>
+      <c r="K28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J29" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>36</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>36</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K31" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J32" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>36</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J33" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J34" t="s">
+        <v>36</v>
+      </c>
+      <c r="K34" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>36</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J35" t="s">
+        <v>36</v>
+      </c>
+      <c r="K35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>36</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J36" t="s">
+        <v>36</v>
+      </c>
+      <c r="K36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>36</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F37" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J37" t="s">
+        <v>36</v>
+      </c>
+      <c r="K37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>36</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J38" t="s">
+        <v>36</v>
+      </c>
+      <c r="K38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J39" t="s">
+        <v>36</v>
+      </c>
+      <c r="K39" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>36</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J40" t="s">
+        <v>36</v>
+      </c>
+      <c r="K40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" t="s">
+        <v>36</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J41" t="s">
+        <v>36</v>
+      </c>
+      <c r="K41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>36</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F42" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J42" t="s">
+        <v>36</v>
+      </c>
+      <c r="K42" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>36</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D43" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J43" t="s">
+        <v>36</v>
+      </c>
+      <c r="K43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>36</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>36</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" t="s">
+        <v>36</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J45" t="s">
+        <v>36</v>
+      </c>
+      <c r="K45" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>36</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" t="s">
+        <v>36</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J47" t="s">
+        <v>36</v>
+      </c>
+      <c r="K47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>36</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J48" t="s">
+        <v>36</v>
+      </c>
+      <c r="K48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>36</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49" t="s">
+        <v>36</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J49" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D50" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50" t="s">
+        <v>36</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J50" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>36</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D51" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" t="s">
+        <v>36</v>
+      </c>
+      <c r="H51" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J51" t="s">
+        <v>36</v>
+      </c>
+      <c r="K51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>36</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O51">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEC77A1-9953-4160-936D-D85566AF6310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2052D51C-C2A7-4DE8-B597-2FE2929BD4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10837" uniqueCount="2040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10837" uniqueCount="2041">
   <si>
     <t>NAME</t>
   </si>
@@ -6187,6 +6187,9 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1</t>
+  </si>
+  <si>
+    <t>monthly</t>
   </si>
   <si>
     <t>monthly_0</t>
@@ -45972,10 +45975,10 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B22" t="s">
         <v>2001</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1186</v>
       </c>
       <c r="C22" t="s">
         <v>1133</v>
@@ -46019,13 +46022,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B23" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C23" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
@@ -46066,13 +46069,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B24" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C24" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D24" t="s">
         <v>36</v>
@@ -46113,13 +46116,13 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B25" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C25" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
@@ -46160,13 +46163,13 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B26" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C26" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
@@ -46207,13 +46210,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B27" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C27" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
@@ -46254,13 +46257,13 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B28" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C28" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D28" t="s">
         <v>36</v>
@@ -46301,13 +46304,13 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B29" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C29" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
@@ -46348,13 +46351,13 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B30" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C30" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D30" t="s">
         <v>36</v>
@@ -46395,13 +46398,13 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B31" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C31" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D31" t="s">
         <v>36</v>
@@ -46442,10 +46445,10 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C32" t="s">
         <v>1133</v>
@@ -46489,13 +46492,13 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B33" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C33" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
@@ -46536,13 +46539,13 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B34" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C34" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D34" t="s">
         <v>36</v>
@@ -46583,13 +46586,13 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C35" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D35" t="s">
         <v>36</v>
@@ -46630,13 +46633,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C36" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D36" t="s">
         <v>36</v>
@@ -46677,13 +46680,13 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C37" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
@@ -46724,13 +46727,13 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B38" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C38" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D38" t="s">
         <v>36</v>
@@ -46771,13 +46774,13 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B39" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C39" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D39" t="s">
         <v>36</v>
@@ -46818,13 +46821,13 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B40" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C40" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D40" t="s">
         <v>36</v>
@@ -46865,13 +46868,13 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B41" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C41" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
@@ -46912,10 +46915,10 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B42" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C42" t="s">
         <v>1133</v>
@@ -46959,13 +46962,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B43" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C43" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D43" t="s">
         <v>36</v>
@@ -47006,13 +47009,13 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B44" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C44" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D44" t="s">
         <v>36</v>
@@ -47053,13 +47056,13 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B45" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C45" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D45" t="s">
         <v>36</v>
@@ -47100,13 +47103,13 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B46" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C46" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D46" t="s">
         <v>36</v>
@@ -47147,13 +47150,13 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B47" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C47" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D47" t="s">
         <v>36</v>
@@ -47194,13 +47197,13 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B48" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C48" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D48" t="s">
         <v>36</v>
@@ -47241,13 +47244,13 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B49" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C49" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D49" t="s">
         <v>36</v>
@@ -47288,13 +47291,13 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B50" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C50" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D50" t="s">
         <v>36</v>
@@ -47335,13 +47338,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B51" t="s">
-        <v>1186</v>
+        <v>2001</v>
       </c>
       <c r="C51" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D51" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2052D51C-C2A7-4DE8-B597-2FE2929BD4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2372888-1844-4768-8241-AEB409FEAF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10837" uniqueCount="2041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11025" uniqueCount="2045">
   <si>
     <t>NAME</t>
   </si>
@@ -6307,6 +6307,18 @@
   </si>
   <si>
     <t>monthly_29</t>
+  </si>
+  <si>
+    <t>ON_ROUND_START</t>
+  </si>
+  <si>
+    <t>basic_buff_all</t>
+  </si>
+  <si>
+    <t>buff_all1</t>
+  </si>
+  <si>
+    <t>buff_all1,100</t>
   </si>
 </sst>
 </file>
@@ -56622,22 +56634,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AD87"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
-    <col min="2" max="3" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="14.26953125" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" customWidth="1"/>
-    <col min="11" max="11" width="12.90625" customWidth="1"/>
-    <col min="25" max="25" width="10.453125" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" customWidth="1"/>
+    <col min="10" max="10" width="11.26953125" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="26" max="26" width="10.453125" customWidth="1"/>
+    <col min="28" max="28" width="11.54296875" customWidth="1"/>
+    <col min="30" max="30" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="13">
+    <row r="1" spans="1:30" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -56645,88 +56659,91 @@
         <v>1799</v>
       </c>
       <c r="C1" s="43" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>1804</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>1798</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>1351</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>1867</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="H1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="43" t="s">
         <v>1787</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>1788</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="K1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>1354</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>1355</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>1356</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>1357</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>1358</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>1359</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>1360</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>815</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>1364</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1365</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Z1" s="43" t="s">
         <v>1614</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>1655</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="AB1" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="AB1" s="43" t="s">
+      <c r="AC1" s="43" t="s">
         <v>1795</v>
       </c>
-      <c r="AC1" s="43" t="s">
+      <c r="AD1" s="43" t="s">
         <v>1874</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
@@ -56736,10 +56753,10 @@
       <c r="C2" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="44">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="44">
         <v>0</v>
       </c>
       <c r="F2">
@@ -56785,37 +56802,40 @@
         <v>0</v>
       </c>
       <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <v>10</v>
       </c>
-      <c r="U2" s="44" t="s">
+      <c r="V2" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
       <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z2">
+      <c r="Z2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2">
         <v>11</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>1657</v>
       </c>
-      <c r="AB2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC2">
+      <c r="AC2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:30">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
@@ -56825,10 +56845,10 @@
       <c r="C3" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="44">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="44">
         <v>0</v>
       </c>
       <c r="F3">
@@ -56874,37 +56894,40 @@
         <v>0</v>
       </c>
       <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
         <v>10</v>
       </c>
-      <c r="U3" s="44" t="s">
+      <c r="V3" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
       <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z3">
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3">
         <v>11</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>1658</v>
       </c>
-      <c r="AB3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC3">
+      <c r="AC3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:30">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
@@ -56914,11 +56937,11 @@
       <c r="C4" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="44">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="D4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="44">
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -56933,17 +56956,17 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>50</v>
       </c>
       <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
         <v>0</v>
       </c>
@@ -56963,37 +56986,40 @@
         <v>0</v>
       </c>
       <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>10</v>
       </c>
-      <c r="U4" s="44" t="s">
+      <c r="V4" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
       <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z4">
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA4">
         <v>11</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>1659</v>
       </c>
-      <c r="AB4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC4">
+      <c r="AC4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:30">
       <c r="A5" s="44" t="s">
         <v>1776</v>
       </c>
@@ -57003,10 +57029,10 @@
       <c r="C5" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="44">
-        <v>0</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="44">
         <v>0</v>
       </c>
       <c r="F5">
@@ -57052,37 +57078,40 @@
         <v>0</v>
       </c>
       <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>10</v>
       </c>
-      <c r="U5" s="44" t="s">
+      <c r="V5" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="X5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z5">
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA5">
         <v>11</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>1660</v>
       </c>
-      <c r="AB5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC5">
+      <c r="AC5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:30">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
@@ -57092,10 +57121,10 @@
       <c r="C6" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="44">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="44">
         <v>0</v>
       </c>
       <c r="F6">
@@ -57141,37 +57170,40 @@
         <v>0</v>
       </c>
       <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
         <v>10</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="V6" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
       <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z6">
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA6">
         <v>11</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>1660</v>
       </c>
-      <c r="AB6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC6">
+      <c r="AC6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:30">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
@@ -57181,10 +57213,10 @@
       <c r="C7" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="44">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="D7" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="44">
         <v>0</v>
       </c>
       <c r="F7">
@@ -57230,37 +57262,40 @@
         <v>0</v>
       </c>
       <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <v>10</v>
       </c>
-      <c r="U7" s="44" t="s">
+      <c r="V7" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
       <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y7" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z7">
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA7">
         <v>11</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>1661</v>
       </c>
-      <c r="AB7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC7">
+      <c r="AC7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:30">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
@@ -57270,21 +57305,21 @@
       <c r="C8" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="44">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="D8" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="44">
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>100</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -57319,37 +57354,40 @@
         <v>0</v>
       </c>
       <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>10</v>
       </c>
-      <c r="U8" s="44" t="s">
+      <c r="V8" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>1615</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>11</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>1662</v>
       </c>
-      <c r="AB8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC8">
+      <c r="AC8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:30">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
@@ -57359,21 +57397,21 @@
       <c r="C9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="44">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="D9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="44">
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>100</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -57408,37 +57446,40 @@
         <v>0</v>
       </c>
       <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>10</v>
       </c>
-      <c r="U9" s="44" t="s">
+      <c r="V9" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
       <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z9">
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA9">
         <v>11</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>1663</v>
       </c>
-      <c r="AB9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC9">
+      <c r="AC9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:30">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
@@ -57448,10 +57489,10 @@
       <c r="C10" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="44">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="D10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="44">
         <v>0</v>
       </c>
       <c r="F10">
@@ -57473,11 +57514,11 @@
         <v>0</v>
       </c>
       <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>5</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
       <c r="N10">
         <v>0</v>
       </c>
@@ -57497,37 +57538,40 @@
         <v>0</v>
       </c>
       <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
         <v>10</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
       <c r="W10">
-        <v>1</v>
-      </c>
-      <c r="X10" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z10">
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA10">
         <v>11</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>1664</v>
       </c>
-      <c r="AB10" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC10">
+      <c r="AC10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:30">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
@@ -57537,10 +57581,10 @@
       <c r="C11" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="44">
-        <v>0</v>
-      </c>
-      <c r="E11">
+      <c r="D11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="44">
         <v>0</v>
       </c>
       <c r="F11">
@@ -57586,37 +57630,40 @@
         <v>0</v>
       </c>
       <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>10</v>
       </c>
-      <c r="U11" s="44" t="s">
+      <c r="V11" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
       <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y11" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z11">
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA11">
         <v>11</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>1665</v>
       </c>
-      <c r="AB11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC11">
+      <c r="AC11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:30">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
@@ -57626,10 +57673,10 @@
       <c r="C12" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="44">
-        <v>0</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="44">
         <v>0</v>
       </c>
       <c r="F12">
@@ -57675,37 +57722,40 @@
         <v>0</v>
       </c>
       <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>10</v>
       </c>
-      <c r="U12" s="44" t="s">
+      <c r="V12" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
       <c r="W12">
-        <v>1</v>
-      </c>
-      <c r="X12" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y12" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z12">
+      <c r="Z12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA12">
         <v>11</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>1666</v>
       </c>
-      <c r="AB12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC12">
+      <c r="AC12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:30">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
@@ -57715,10 +57765,10 @@
       <c r="C13" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="44">
-        <v>0</v>
-      </c>
-      <c r="E13">
+      <c r="D13" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="44">
         <v>0</v>
       </c>
       <c r="F13">
@@ -57764,37 +57814,40 @@
         <v>0</v>
       </c>
       <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>10</v>
       </c>
-      <c r="U13" s="44" t="s">
+      <c r="V13" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
       <c r="W13">
-        <v>1</v>
-      </c>
-      <c r="X13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y13" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z13">
+      <c r="Z13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA13">
         <v>11</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>1667</v>
       </c>
-      <c r="AB13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC13">
+      <c r="AC13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:30">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
@@ -57804,10 +57857,10 @@
       <c r="C14" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="44">
-        <v>0</v>
-      </c>
-      <c r="E14">
+      <c r="D14" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="44">
         <v>0</v>
       </c>
       <c r="F14">
@@ -57853,37 +57906,40 @@
         <v>0</v>
       </c>
       <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
         <v>10</v>
       </c>
-      <c r="U14" s="44" t="s">
+      <c r="V14" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
       <c r="W14">
-        <v>1</v>
-      </c>
-      <c r="X14" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y14" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14">
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA14">
         <v>11</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>1668</v>
       </c>
-      <c r="AB14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC14">
+      <c r="AC14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:30">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
@@ -57893,10 +57949,10 @@
       <c r="C15" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="44">
-        <v>0</v>
-      </c>
-      <c r="E15">
+      <c r="D15" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="44">
         <v>0</v>
       </c>
       <c r="F15">
@@ -57942,37 +57998,40 @@
         <v>0</v>
       </c>
       <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
         <v>10</v>
       </c>
-      <c r="U15" s="44" t="s">
+      <c r="V15" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
       <c r="W15">
-        <v>1</v>
-      </c>
-      <c r="X15" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y15" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z15">
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA15">
         <v>11</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>1669</v>
       </c>
-      <c r="AB15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC15">
+      <c r="AC15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:30">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
@@ -57982,10 +58041,10 @@
       <c r="C16" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="44">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="D16" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="44">
         <v>0</v>
       </c>
       <c r="F16">
@@ -58031,37 +58090,40 @@
         <v>0</v>
       </c>
       <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
         <v>10</v>
       </c>
-      <c r="U16" s="44" t="s">
+      <c r="V16" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
       <c r="W16">
-        <v>1</v>
-      </c>
-      <c r="X16" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y16" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z16">
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA16">
         <v>11</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>1670</v>
       </c>
-      <c r="AB16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC16">
+      <c r="AC16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17" spans="1:30">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
@@ -58071,21 +58133,21 @@
       <c r="C17" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="44">
-        <v>0</v>
-      </c>
-      <c r="E17">
+      <c r="D17" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="44">
         <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>50</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -58096,11 +58158,11 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>5</v>
       </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
       <c r="N17">
         <v>0</v>
       </c>
@@ -58120,37 +58182,40 @@
         <v>0</v>
       </c>
       <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
         <v>10</v>
       </c>
-      <c r="U17" s="44" t="s">
+      <c r="V17" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
       <c r="W17">
-        <v>1</v>
-      </c>
-      <c r="X17" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Z17" t="s">
         <v>1616</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>11</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>1671</v>
       </c>
-      <c r="AB17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC17">
+      <c r="AC17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD17">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:29">
+    <row r="18" spans="1:30">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
@@ -58160,10 +58225,10 @@
       <c r="C18" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="44">
-        <v>0</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="44">
         <v>0</v>
       </c>
       <c r="F18">
@@ -58209,37 +58274,40 @@
         <v>0</v>
       </c>
       <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
         <v>10</v>
       </c>
-      <c r="U18" s="44" t="s">
+      <c r="V18" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
       <c r="W18">
-        <v>1</v>
-      </c>
-      <c r="X18" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y18" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z18">
+      <c r="Z18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA18">
         <v>11</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>1672</v>
       </c>
-      <c r="AB18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC18">
+      <c r="AC18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD18">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19" spans="1:30">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
@@ -58249,10 +58317,10 @@
       <c r="C19" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="44">
-        <v>0</v>
-      </c>
-      <c r="E19">
+      <c r="D19" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="44">
         <v>0</v>
       </c>
       <c r="F19">
@@ -58298,37 +58366,40 @@
         <v>0</v>
       </c>
       <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
         <v>10</v>
       </c>
-      <c r="U19" s="44" t="s">
+      <c r="V19" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
       <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y19" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z19">
+      <c r="Z19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA19">
         <v>11</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>1673</v>
       </c>
-      <c r="AB19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC19">
+      <c r="AC19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD19">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20" spans="1:30">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
@@ -58338,10 +58409,10 @@
       <c r="C20" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="44">
-        <v>0</v>
-      </c>
-      <c r="E20">
+      <c r="D20" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="44">
         <v>0</v>
       </c>
       <c r="F20">
@@ -58387,37 +58458,40 @@
         <v>0</v>
       </c>
       <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
         <v>10</v>
       </c>
-      <c r="U20" s="44" t="s">
+      <c r="V20" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
       <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="X20" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y20" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z20">
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA20">
         <v>11</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>1674</v>
       </c>
-      <c r="AB20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC20">
+      <c r="AC20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD20">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:30">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
@@ -58427,10 +58501,10 @@
       <c r="C21" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="44">
-        <v>0</v>
-      </c>
-      <c r="E21">
+      <c r="D21" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="44">
         <v>0</v>
       </c>
       <c r="F21">
@@ -58476,37 +58550,40 @@
         <v>0</v>
       </c>
       <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
         <v>10</v>
       </c>
-      <c r="U21" s="44" t="s">
+      <c r="V21" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
       <c r="W21">
-        <v>1</v>
-      </c>
-      <c r="X21" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y21" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z21">
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA21">
         <v>11</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>1658</v>
       </c>
-      <c r="AB21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC21">
+      <c r="AC21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:30">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
@@ -58516,10 +58593,10 @@
       <c r="C22" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="44">
-        <v>0</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="44">
         <v>0</v>
       </c>
       <c r="F22">
@@ -58565,37 +58642,40 @@
         <v>0</v>
       </c>
       <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
         <v>10</v>
       </c>
-      <c r="U22" s="44" t="s">
+      <c r="V22" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
       <c r="W22">
-        <v>1</v>
-      </c>
-      <c r="X22" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y22" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z22">
+      <c r="Z22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA22">
         <v>11</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>1658</v>
       </c>
-      <c r="AB22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC22">
+      <c r="AC22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:30">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
@@ -58605,10 +58685,10 @@
       <c r="C23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="44">
-        <v>0</v>
-      </c>
-      <c r="E23">
+      <c r="D23" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="44">
         <v>0</v>
       </c>
       <c r="F23">
@@ -58654,37 +58734,40 @@
         <v>0</v>
       </c>
       <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
         <v>10</v>
       </c>
-      <c r="U23" s="44" t="s">
+      <c r="V23" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
       <c r="W23">
-        <v>1</v>
-      </c>
-      <c r="X23" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y23" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z23">
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA23">
         <v>11</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>1658</v>
       </c>
-      <c r="AB23" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC23">
+      <c r="AC23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD23">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:30">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
@@ -58694,10 +58777,10 @@
       <c r="C24" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="44">
-        <v>0</v>
-      </c>
-      <c r="E24">
+      <c r="D24" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="44">
         <v>0</v>
       </c>
       <c r="F24">
@@ -58743,37 +58826,40 @@
         <v>0</v>
       </c>
       <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
         <v>10</v>
       </c>
-      <c r="U24" s="44" t="s">
+      <c r="V24" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
       <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y24" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z24">
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA24">
         <v>11</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>1658</v>
       </c>
-      <c r="AB24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC24">
+      <c r="AC24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD24">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25" spans="1:30">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
@@ -58783,10 +58869,10 @@
       <c r="C25" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="44">
-        <v>0</v>
-      </c>
-      <c r="E25">
+      <c r="D25" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="44">
         <v>0</v>
       </c>
       <c r="F25">
@@ -58832,37 +58918,40 @@
         <v>0</v>
       </c>
       <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
         <v>10</v>
       </c>
-      <c r="U25" s="44" t="s">
+      <c r="V25" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
       <c r="W25">
-        <v>1</v>
-      </c>
-      <c r="X25" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y25" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z25">
+      <c r="Z25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA25">
         <v>11</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>1658</v>
       </c>
-      <c r="AB25" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC25">
+      <c r="AC25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD25">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26" spans="1:30">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
@@ -58872,10 +58961,10 @@
       <c r="C26" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="44">
-        <v>0</v>
-      </c>
-      <c r="E26">
+      <c r="D26" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="44">
         <v>0</v>
       </c>
       <c r="F26">
@@ -58921,37 +59010,40 @@
         <v>0</v>
       </c>
       <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
         <v>10</v>
       </c>
-      <c r="U26" s="44" t="s">
+      <c r="V26" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
       <c r="W26">
-        <v>1</v>
-      </c>
-      <c r="X26" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y26" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z26">
+      <c r="Z26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA26">
         <v>11</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>1559</v>
       </c>
-      <c r="AB26" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC26">
+      <c r="AC26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD26">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:30">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
@@ -58961,10 +59053,10 @@
       <c r="C27" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="44">
-        <v>0</v>
-      </c>
-      <c r="E27">
+      <c r="D27" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="44">
         <v>0</v>
       </c>
       <c r="F27">
@@ -59010,37 +59102,40 @@
         <v>0</v>
       </c>
       <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
         <v>10</v>
       </c>
-      <c r="U27" s="44" t="s">
+      <c r="V27" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
       <c r="W27">
-        <v>1</v>
-      </c>
-      <c r="X27" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z27">
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA27">
         <v>11</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>1658</v>
       </c>
-      <c r="AB27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC27">
+      <c r="AC27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD27">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:29">
+    <row r="28" spans="1:30">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
@@ -59050,10 +59145,10 @@
       <c r="C28" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="44">
-        <v>0</v>
-      </c>
-      <c r="E28">
+      <c r="D28" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="44">
         <v>0</v>
       </c>
       <c r="F28">
@@ -59099,37 +59194,40 @@
         <v>0</v>
       </c>
       <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
         <v>10</v>
       </c>
-      <c r="U28" s="44" t="s">
+      <c r="V28" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
       <c r="W28">
-        <v>1</v>
-      </c>
-      <c r="X28" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y28" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z28">
+      <c r="Z28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28">
         <v>11</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>1658</v>
       </c>
-      <c r="AB28" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC28">
+      <c r="AC28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:29">
+    <row r="29" spans="1:30">
       <c r="A29" s="44" t="s">
         <v>1747</v>
       </c>
@@ -59139,10 +59237,10 @@
       <c r="C29" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="44">
-        <v>0</v>
-      </c>
-      <c r="E29">
+      <c r="D29" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="44">
         <v>0</v>
       </c>
       <c r="F29">
@@ -59188,37 +59286,40 @@
         <v>0</v>
       </c>
       <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
         <v>10</v>
       </c>
-      <c r="U29" s="44" t="s">
+      <c r="V29" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
       <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y29" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z29">
+      <c r="Z29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA29">
         <v>11</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>1658</v>
       </c>
-      <c r="AB29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC29">
+      <c r="AC29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD29">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30" spans="1:30">
       <c r="A30" s="44" t="s">
         <v>1777</v>
       </c>
@@ -59226,12 +59327,12 @@
         <v>1803</v>
       </c>
       <c r="C30" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="44" t="s">
         <v>1469</v>
       </c>
-      <c r="D30" s="44">
-        <v>0</v>
-      </c>
-      <c r="E30">
+      <c r="E30" s="44">
         <v>0</v>
       </c>
       <c r="F30">
@@ -59277,37 +59378,40 @@
         <v>0</v>
       </c>
       <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
         <v>10</v>
       </c>
-      <c r="U30" s="44" t="s">
+      <c r="V30" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
       <c r="W30">
-        <v>1</v>
-      </c>
-      <c r="X30" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y30" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z30">
+      <c r="Z30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA30">
         <v>11</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>896</v>
       </c>
-      <c r="AB30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC30">
+      <c r="AC30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD30">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31" spans="1:30">
       <c r="A31" s="44" t="s">
         <v>1778</v>
       </c>
@@ -59315,12 +59419,12 @@
         <v>1803</v>
       </c>
       <c r="C31" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="44" t="s">
         <v>1805</v>
       </c>
-      <c r="D31" s="44">
-        <v>0</v>
-      </c>
-      <c r="E31">
+      <c r="E31" s="44">
         <v>0</v>
       </c>
       <c r="F31">
@@ -59366,37 +59470,40 @@
         <v>0</v>
       </c>
       <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
         <v>10</v>
       </c>
-      <c r="U31" s="44" t="s">
+      <c r="V31" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
       <c r="W31">
-        <v>1</v>
-      </c>
-      <c r="X31" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y31" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z31">
+      <c r="Z31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA31">
         <v>11</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>896</v>
       </c>
-      <c r="AB31" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC31">
+      <c r="AC31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD31">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:29">
+    <row r="32" spans="1:30">
       <c r="A32" s="44" t="s">
         <v>238</v>
       </c>
@@ -59406,10 +59513,10 @@
       <c r="C32" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="44">
-        <v>0</v>
-      </c>
-      <c r="E32">
+      <c r="D32" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="44">
         <v>0</v>
       </c>
       <c r="F32">
@@ -59431,11 +59538,11 @@
         <v>0</v>
       </c>
       <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>50</v>
       </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
       <c r="N32">
         <v>0</v>
       </c>
@@ -59455,37 +59562,40 @@
         <v>0</v>
       </c>
       <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
         <v>10</v>
       </c>
-      <c r="U32" s="44" t="s">
+      <c r="V32" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
       <c r="W32">
-        <v>1</v>
-      </c>
-      <c r="X32" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y32" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z32">
+      <c r="Z32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA32">
         <v>11</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>1671</v>
       </c>
-      <c r="AB32" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC32">
+      <c r="AC32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD32">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:30">
       <c r="A33" s="44" t="s">
         <v>1801</v>
       </c>
@@ -59495,30 +59605,30 @@
       <c r="C33" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="44">
-        <v>0</v>
-      </c>
-      <c r="E33">
+      <c r="D33" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="44">
         <v>0</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>50</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>-50</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
       <c r="L33">
         <v>0</v>
       </c>
@@ -59544,37 +59654,40 @@
         <v>0</v>
       </c>
       <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
         <v>10</v>
       </c>
-      <c r="U33" s="44" t="s">
+      <c r="V33" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
       <c r="W33">
-        <v>1</v>
-      </c>
-      <c r="X33" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z33">
+      <c r="Z33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA33">
         <v>11</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>1671</v>
       </c>
-      <c r="AB33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC33">
+      <c r="AC33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD33">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:30">
       <c r="A34" s="44" t="s">
         <v>1808</v>
       </c>
@@ -59582,12 +59695,12 @@
         <v>1803</v>
       </c>
       <c r="C34" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="44" t="s">
         <v>1807</v>
       </c>
-      <c r="D34" s="44">
-        <v>0</v>
-      </c>
-      <c r="E34">
+      <c r="E34" s="44">
         <v>0</v>
       </c>
       <c r="F34">
@@ -59633,47 +59746,51 @@
         <v>0</v>
       </c>
       <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
         <v>10</v>
       </c>
-      <c r="U34" s="44" t="s">
+      <c r="V34" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
       <c r="W34">
-        <v>1</v>
-      </c>
-      <c r="X34" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y34" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z34">
+      <c r="Z34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA34">
         <v>11</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>896</v>
       </c>
-      <c r="AB34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC34">
+      <c r="AC34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD34">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="14">
+    <row r="35" spans="1:30" ht="14">
       <c r="A35" s="55" t="s">
         <v>1953</v>
       </c>
       <c r="B35" s="44"/>
       <c r="C35" s="44"/>
       <c r="D35" s="44"/>
-      <c r="U35" s="44"/>
-      <c r="X35" s="44"/>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="E35" s="44"/>
+      <c r="V35" s="44"/>
+      <c r="Y35" s="44"/>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36" s="44" t="s">
         <v>1875</v>
       </c>
@@ -59683,21 +59800,21 @@
       <c r="C36" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="44">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
+      <c r="D36" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="44">
+        <v>1</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>20</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -59732,37 +59849,40 @@
         <v>0</v>
       </c>
       <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
         <v>10</v>
       </c>
-      <c r="U36" s="44" t="s">
+      <c r="V36" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
       <c r="W36">
-        <v>1</v>
-      </c>
-      <c r="X36" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y36" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z36">
+      <c r="Z36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA36">
         <v>11</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>1663</v>
       </c>
-      <c r="AB36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC36">
+      <c r="AC36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD36">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:30">
       <c r="A37" s="44" t="s">
         <v>1877</v>
       </c>
@@ -59772,11 +59892,11 @@
       <c r="C37" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="44">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
+      <c r="D37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="44">
+        <v>1</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -59797,11 +59917,11 @@
         <v>0</v>
       </c>
       <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>50</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
       <c r="N37">
         <v>0</v>
       </c>
@@ -59821,37 +59941,40 @@
         <v>0</v>
       </c>
       <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
         <v>10</v>
       </c>
-      <c r="U37" s="44" t="s">
+      <c r="V37" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
       <c r="W37">
-        <v>1</v>
-      </c>
-      <c r="X37" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y37" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z37">
+      <c r="Z37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA37">
         <v>11</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>1663</v>
       </c>
-      <c r="AB37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC37">
+      <c r="AC37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD37">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:30">
       <c r="A38" s="44" t="s">
         <v>1878</v>
       </c>
@@ -59861,11 +59984,11 @@
       <c r="C38" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="44">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
+      <c r="D38" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="44">
+        <v>1</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -59880,13 +60003,13 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -59910,37 +60033,40 @@
         <v>0</v>
       </c>
       <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
         <v>10</v>
       </c>
-      <c r="U38" s="44" t="s">
+      <c r="V38" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
       <c r="W38">
-        <v>1</v>
-      </c>
-      <c r="X38" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y38" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z38">
+      <c r="Z38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA38">
         <v>11</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>1663</v>
       </c>
-      <c r="AB38" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC38">
+      <c r="AC38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD38">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39" spans="1:30">
       <c r="A39" s="44" t="s">
         <v>1879</v>
       </c>
@@ -59950,11 +60076,11 @@
       <c r="C39" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="44">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
+      <c r="D39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="44">
+        <v>1</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -59963,11 +60089,11 @@
         <v>0</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>20</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
         <v>0</v>
       </c>
@@ -59999,42 +60125,45 @@
         <v>0</v>
       </c>
       <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
         <v>10</v>
       </c>
-      <c r="U39" s="44" t="s">
+      <c r="V39" s="44" t="s">
         <v>1368</v>
       </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
       <c r="W39">
-        <v>1</v>
-      </c>
-      <c r="X39" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y39" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z39">
+      <c r="Z39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA39">
         <v>11</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>1663</v>
       </c>
-      <c r="AB39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC39">
+      <c r="AC39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD39">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="14">
+    <row r="40" spans="1:30" ht="14">
       <c r="A40" s="55" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
+    <row r="41" spans="1:30">
       <c r="A41" s="44" t="s">
         <v>1948</v>
       </c>
@@ -60044,21 +60173,21 @@
       <c r="C41" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="44">
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
+      <c r="D41" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="44">
+        <v>1</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>100</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -60093,37 +60222,40 @@
         <v>0</v>
       </c>
       <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
         <v>10</v>
       </c>
-      <c r="U41" s="44" t="s">
+      <c r="V41" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
       <c r="W41">
-        <v>1</v>
-      </c>
-      <c r="X41" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y41" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z41">
+      <c r="Z41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA41">
         <v>11</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>1663</v>
       </c>
-      <c r="AB41" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC41">
+      <c r="AC41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD41">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:29">
+    <row r="42" spans="1:30">
       <c r="A42" s="44" t="s">
         <v>1949</v>
       </c>
@@ -60133,21 +60265,21 @@
       <c r="C42" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="44">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
+      <c r="D42" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="44">
+        <v>1</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>100</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
@@ -60182,37 +60314,40 @@
         <v>0</v>
       </c>
       <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
         <v>10</v>
       </c>
-      <c r="U42" s="44" t="s">
+      <c r="V42" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
       <c r="W42">
-        <v>1</v>
-      </c>
-      <c r="X42" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y42" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z42">
+      <c r="Z42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA42">
         <v>11</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AB42" t="s">
         <v>1663</v>
       </c>
-      <c r="AB42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC42">
+      <c r="AC42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD42">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:29">
+    <row r="43" spans="1:30">
       <c r="A43" s="44" t="s">
         <v>1950</v>
       </c>
@@ -60222,21 +60357,21 @@
       <c r="C43" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="44">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
+      <c r="D43" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="44">
+        <v>1</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>100</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -60271,37 +60406,40 @@
         <v>0</v>
       </c>
       <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
         <v>10</v>
       </c>
-      <c r="U43" s="44" t="s">
+      <c r="V43" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
       <c r="W43">
-        <v>1</v>
-      </c>
-      <c r="X43" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y43" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z43">
+      <c r="Z43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA43">
         <v>11</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>1663</v>
       </c>
-      <c r="AB43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC43">
+      <c r="AC43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD43">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
+    <row r="44" spans="1:30">
       <c r="A44" s="44" t="s">
         <v>1951</v>
       </c>
@@ -60311,21 +60449,21 @@
       <c r="C44" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
+      <c r="D44" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="44">
+        <v>1</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>100</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
@@ -60360,37 +60498,40 @@
         <v>0</v>
       </c>
       <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
         <v>10</v>
       </c>
-      <c r="U44" s="44" t="s">
+      <c r="V44" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
       <c r="W44">
-        <v>1</v>
-      </c>
-      <c r="X44" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y44" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z44">
+      <c r="Z44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA44">
         <v>11</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AB44" t="s">
         <v>1663</v>
       </c>
-      <c r="AB44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC44">
+      <c r="AC44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD44">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:29">
+    <row r="45" spans="1:30">
       <c r="A45" s="44" t="s">
         <v>1952</v>
       </c>
@@ -60400,21 +60541,21 @@
       <c r="C45" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="44">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
+      <c r="D45" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="44">
+        <v>1</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>100</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
       <c r="I45">
         <v>0</v>
       </c>
@@ -60449,42 +60590,45 @@
         <v>0</v>
       </c>
       <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
         <v>10</v>
       </c>
-      <c r="U45" s="44" t="s">
+      <c r="V45" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
       <c r="W45">
-        <v>1</v>
-      </c>
-      <c r="X45" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y45" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z45">
+      <c r="Z45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA45">
         <v>11</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AB45" t="s">
         <v>1663</v>
       </c>
-      <c r="AB45" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC45">
+      <c r="AC45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD45">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="14">
+    <row r="46" spans="1:30" ht="14">
       <c r="A46" s="55" t="s">
         <v>1955</v>
       </c>
     </row>
-    <row r="47" spans="1:29">
+    <row r="47" spans="1:30">
       <c r="A47" s="44" t="s">
         <v>1956</v>
       </c>
@@ -60494,21 +60638,21 @@
       <c r="C47" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="44">
-        <v>1</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
+      <c r="D47" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="44">
+        <v>1</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>100</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
@@ -60543,37 +60687,40 @@
         <v>0</v>
       </c>
       <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
         <v>10</v>
       </c>
-      <c r="U47" s="44" t="s">
+      <c r="V47" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
       <c r="W47">
-        <v>1</v>
-      </c>
-      <c r="X47" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y47" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z47">
+      <c r="Z47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA47">
         <v>11</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AB47" t="s">
         <v>1663</v>
       </c>
-      <c r="AB47" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC47">
+      <c r="AC47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD47">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:29">
+    <row r="48" spans="1:30">
       <c r="A48" s="44" t="s">
         <v>1957</v>
       </c>
@@ -60583,21 +60730,21 @@
       <c r="C48" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D48" s="44">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
+      <c r="D48" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="44">
+        <v>1</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>100</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -60632,37 +60779,40 @@
         <v>0</v>
       </c>
       <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
         <v>10</v>
       </c>
-      <c r="U48" s="44" t="s">
+      <c r="V48" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
       <c r="W48">
-        <v>1</v>
-      </c>
-      <c r="X48" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y48" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z48">
+      <c r="Z48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA48">
         <v>11</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AB48" t="s">
         <v>1663</v>
       </c>
-      <c r="AB48" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC48">
+      <c r="AC48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD48">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49" spans="1:30">
       <c r="A49" s="44" t="s">
         <v>1958</v>
       </c>
@@ -60672,21 +60822,21 @@
       <c r="C49" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="44">
-        <v>1</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
+      <c r="D49" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="44">
+        <v>1</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
         <v>100</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -60721,37 +60871,40 @@
         <v>0</v>
       </c>
       <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
         <v>10</v>
       </c>
-      <c r="U49" s="44" t="s">
+      <c r="V49" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
       <c r="W49">
-        <v>1</v>
-      </c>
-      <c r="X49" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y49" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z49">
+      <c r="Z49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA49">
         <v>11</v>
       </c>
-      <c r="AA49" t="s">
+      <c r="AB49" t="s">
         <v>1663</v>
       </c>
-      <c r="AB49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC49">
+      <c r="AC49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD49">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50" spans="1:30">
       <c r="A50" s="44" t="s">
         <v>1959</v>
       </c>
@@ -60761,21 +60914,21 @@
       <c r="C50" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="44">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
+      <c r="D50" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="44">
+        <v>1</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
         <v>100</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
@@ -60810,37 +60963,40 @@
         <v>0</v>
       </c>
       <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
         <v>10</v>
       </c>
-      <c r="U50" s="44" t="s">
+      <c r="V50" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
       <c r="W50">
-        <v>1</v>
-      </c>
-      <c r="X50" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y50" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z50">
+      <c r="Z50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA50">
         <v>11</v>
       </c>
-      <c r="AA50" t="s">
+      <c r="AB50" t="s">
         <v>1663</v>
       </c>
-      <c r="AB50" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC50">
+      <c r="AC50" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD50">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51" spans="1:30">
       <c r="A51" s="44" t="s">
         <v>1960</v>
       </c>
@@ -60850,21 +61006,21 @@
       <c r="C51" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="44">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
+      <c r="D51" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="44">
+        <v>1</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>100</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
       <c r="I51">
         <v>0</v>
       </c>
@@ -60899,42 +61055,45 @@
         <v>0</v>
       </c>
       <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
         <v>10</v>
       </c>
-      <c r="U51" s="44" t="s">
+      <c r="V51" s="44" t="s">
         <v>1802</v>
       </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
       <c r="W51">
-        <v>1</v>
-      </c>
-      <c r="X51" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y51" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z51">
+      <c r="Z51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA51">
         <v>11</v>
       </c>
-      <c r="AA51" t="s">
+      <c r="AB51" t="s">
         <v>1663</v>
       </c>
-      <c r="AB51" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC51">
+      <c r="AC51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD51">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="14">
+    <row r="52" spans="1:30" ht="14">
       <c r="A52" s="55" t="s">
         <v>1961</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53" spans="1:30">
       <c r="A53" t="s">
         <v>1962</v>
       </c>
@@ -60944,21 +61103,21 @@
       <c r="C53" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="44">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
+      <c r="D53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="44">
+        <v>1</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>100</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
@@ -60993,37 +61152,40 @@
         <v>0</v>
       </c>
       <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
         <v>10</v>
       </c>
-      <c r="U53" s="44" t="s">
+      <c r="V53" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
       <c r="W53">
-        <v>1</v>
-      </c>
-      <c r="X53" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y53" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z53">
+      <c r="Z53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA53">
         <v>11</v>
       </c>
-      <c r="AA53" t="s">
+      <c r="AB53" t="s">
         <v>1663</v>
       </c>
-      <c r="AB53" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC53">
+      <c r="AC53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54" spans="1:30">
       <c r="A54" t="s">
         <v>1963</v>
       </c>
@@ -61033,21 +61195,21 @@
       <c r="C54" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="44">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
+      <c r="D54" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="44">
+        <v>1</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>100</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
       <c r="I54">
         <v>0</v>
       </c>
@@ -61082,37 +61244,40 @@
         <v>0</v>
       </c>
       <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
         <v>10</v>
       </c>
-      <c r="U54" s="44" t="s">
+      <c r="V54" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
       <c r="W54">
-        <v>1</v>
-      </c>
-      <c r="X54" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y54" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z54">
+      <c r="Z54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA54">
         <v>11</v>
       </c>
-      <c r="AA54" t="s">
+      <c r="AB54" t="s">
         <v>1663</v>
       </c>
-      <c r="AB54" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC54">
+      <c r="AC54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD54">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55" spans="1:30">
       <c r="A55" s="60" t="s">
         <v>1964</v>
       </c>
@@ -61122,21 +61287,21 @@
       <c r="C55" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D55" s="44">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
+      <c r="D55" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E55" s="44">
+        <v>1</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>100</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -61171,37 +61336,40 @@
         <v>0</v>
       </c>
       <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
         <v>10</v>
       </c>
-      <c r="U55" s="44" t="s">
+      <c r="V55" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
       <c r="W55">
-        <v>1</v>
-      </c>
-      <c r="X55" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y55" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z55">
+      <c r="Z55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA55">
         <v>11</v>
       </c>
-      <c r="AA55" t="s">
+      <c r="AB55" t="s">
         <v>1663</v>
       </c>
-      <c r="AB55" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC55">
+      <c r="AC55" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD55">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:29">
+    <row r="56" spans="1:30">
       <c r="A56" t="s">
         <v>1965</v>
       </c>
@@ -61211,21 +61379,21 @@
       <c r="C56" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D56" s="44">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
+      <c r="D56" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" s="44">
+        <v>1</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
         <v>100</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
       <c r="I56">
         <v>0</v>
       </c>
@@ -61260,37 +61428,40 @@
         <v>0</v>
       </c>
       <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
         <v>10</v>
       </c>
-      <c r="U56" s="44" t="s">
+      <c r="V56" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
       <c r="W56">
-        <v>1</v>
-      </c>
-      <c r="X56" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y56" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z56">
+      <c r="Z56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA56">
         <v>11</v>
       </c>
-      <c r="AA56" t="s">
+      <c r="AB56" t="s">
         <v>1663</v>
       </c>
-      <c r="AB56" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC56">
+      <c r="AC56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD56">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57" spans="1:30">
       <c r="A57" t="s">
         <v>1966</v>
       </c>
@@ -61300,21 +61471,21 @@
       <c r="C57" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="44">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
+      <c r="D57" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E57" s="44">
+        <v>1</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
         <v>100</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -61349,42 +61520,45 @@
         <v>0</v>
       </c>
       <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
         <v>10</v>
       </c>
-      <c r="U57" s="44" t="s">
+      <c r="V57" s="44" t="s">
         <v>1800</v>
       </c>
-      <c r="V57">
-        <v>0</v>
-      </c>
       <c r="W57">
-        <v>1</v>
-      </c>
-      <c r="X57" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y57" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z57">
+      <c r="Z57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA57">
         <v>11</v>
       </c>
-      <c r="AA57" t="s">
+      <c r="AB57" t="s">
         <v>1663</v>
       </c>
-      <c r="AB57" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC57">
+      <c r="AC57" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD57">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="14">
+    <row r="58" spans="1:30" ht="14">
       <c r="A58" s="55" t="s">
         <v>1967</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59" spans="1:30">
       <c r="A59" t="s">
         <v>1968</v>
       </c>
@@ -61394,21 +61568,21 @@
       <c r="C59" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D59" s="44">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
+      <c r="D59" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E59" s="44">
+        <v>1</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
         <v>100</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
       <c r="I59">
         <v>0</v>
       </c>
@@ -61443,37 +61617,40 @@
         <v>0</v>
       </c>
       <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
         <v>10</v>
       </c>
-      <c r="U59" s="44" t="s">
+      <c r="V59" s="44" t="s">
         <v>1973</v>
       </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
       <c r="W59">
-        <v>1</v>
-      </c>
-      <c r="X59" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y59" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z59">
+      <c r="Z59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA59">
         <v>11</v>
       </c>
-      <c r="AA59" t="s">
+      <c r="AB59" t="s">
         <v>1663</v>
       </c>
-      <c r="AB59" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC59">
+      <c r="AC59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD59">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60" spans="1:30">
       <c r="A60" t="s">
         <v>1969</v>
       </c>
@@ -61483,21 +61660,21 @@
       <c r="C60" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="44">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
+      <c r="D60" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E60" s="44">
+        <v>1</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>100</v>
       </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
@@ -61532,37 +61709,40 @@
         <v>0</v>
       </c>
       <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
         <v>10</v>
       </c>
-      <c r="U60" s="44" t="s">
+      <c r="V60" s="44" t="s">
         <v>1973</v>
       </c>
-      <c r="V60">
-        <v>0</v>
-      </c>
       <c r="W60">
-        <v>1</v>
-      </c>
-      <c r="X60" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y60" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z60">
+      <c r="Z60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA60">
         <v>11</v>
       </c>
-      <c r="AA60" t="s">
+      <c r="AB60" t="s">
         <v>1663</v>
       </c>
-      <c r="AB60" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC60">
+      <c r="AC60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD60">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61" spans="1:30">
       <c r="A61" t="s">
         <v>1970</v>
       </c>
@@ -61572,21 +61752,21 @@
       <c r="C61" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D61" s="44">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
+      <c r="D61" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E61" s="44">
+        <v>1</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>100</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -61621,37 +61801,40 @@
         <v>0</v>
       </c>
       <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
         <v>10</v>
       </c>
-      <c r="U61" s="44" t="s">
+      <c r="V61" s="44" t="s">
         <v>1973</v>
       </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
       <c r="W61">
-        <v>1</v>
-      </c>
-      <c r="X61" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y61" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z61">
+      <c r="Z61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA61">
         <v>11</v>
       </c>
-      <c r="AA61" t="s">
+      <c r="AB61" t="s">
         <v>1663</v>
       </c>
-      <c r="AB61" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC61">
+      <c r="AC61" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD61">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62" spans="1:30">
       <c r="A62" t="s">
         <v>1971</v>
       </c>
@@ -61661,21 +61844,21 @@
       <c r="C62" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="44">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
+      <c r="D62" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E62" s="44">
+        <v>1</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
         <v>100</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
       <c r="I62">
         <v>0</v>
       </c>
@@ -61710,37 +61893,40 @@
         <v>0</v>
       </c>
       <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
         <v>10</v>
       </c>
-      <c r="U62" s="44" t="s">
+      <c r="V62" s="44" t="s">
         <v>1973</v>
       </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
       <c r="W62">
-        <v>1</v>
-      </c>
-      <c r="X62" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y62" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z62">
+      <c r="Z62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA62">
         <v>11</v>
       </c>
-      <c r="AA62" t="s">
+      <c r="AB62" t="s">
         <v>1663</v>
       </c>
-      <c r="AB62" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC62">
+      <c r="AC62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD62">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:30">
       <c r="A63" t="s">
         <v>1972</v>
       </c>
@@ -61750,21 +61936,21 @@
       <c r="C63" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="44">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
+      <c r="D63" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" s="44">
+        <v>1</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
         <v>100</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -61799,42 +61985,45 @@
         <v>0</v>
       </c>
       <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
         <v>10</v>
       </c>
-      <c r="U63" s="44" t="s">
+      <c r="V63" s="44" t="s">
         <v>1973</v>
       </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
       <c r="W63">
-        <v>1</v>
-      </c>
-      <c r="X63" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y63" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z63">
+      <c r="Z63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA63">
         <v>11</v>
       </c>
-      <c r="AA63" t="s">
+      <c r="AB63" t="s">
         <v>1663</v>
       </c>
-      <c r="AB63" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC63">
+      <c r="AC63" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD63">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="14">
+    <row r="64" spans="1:30" ht="14">
       <c r="A64" s="55" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="65" spans="1:29">
+    <row r="65" spans="1:30">
       <c r="A65" t="s">
         <v>1975</v>
       </c>
@@ -61844,21 +62033,21 @@
       <c r="C65" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="44">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
+      <c r="D65" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" s="44">
+        <v>1</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
         <v>100</v>
       </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
       <c r="I65">
         <v>0</v>
       </c>
@@ -61893,37 +62082,40 @@
         <v>0</v>
       </c>
       <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
         <v>10</v>
       </c>
-      <c r="U65" s="44" t="s">
+      <c r="V65" s="44" t="s">
         <v>1987</v>
       </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
       <c r="W65">
-        <v>1</v>
-      </c>
-      <c r="X65" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y65" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z65">
+      <c r="Z65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA65">
         <v>11</v>
       </c>
-      <c r="AA65" t="s">
+      <c r="AB65" t="s">
         <v>1663</v>
       </c>
-      <c r="AB65" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC65">
+      <c r="AC65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD65">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66" spans="1:30">
       <c r="A66" t="s">
         <v>1976</v>
       </c>
@@ -61933,21 +62125,21 @@
       <c r="C66" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D66" s="44">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
+      <c r="D66" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E66" s="44">
+        <v>1</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>100</v>
       </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
       <c r="I66">
         <v>0</v>
       </c>
@@ -61982,37 +62174,40 @@
         <v>0</v>
       </c>
       <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
         <v>10</v>
       </c>
-      <c r="U66" s="44" t="s">
+      <c r="V66" s="44" t="s">
         <v>1987</v>
       </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
       <c r="W66">
-        <v>1</v>
-      </c>
-      <c r="X66" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y66" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z66">
+      <c r="Z66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA66">
         <v>11</v>
       </c>
-      <c r="AA66" t="s">
+      <c r="AB66" t="s">
         <v>1663</v>
       </c>
-      <c r="AB66" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC66">
+      <c r="AC66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD66">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:29">
+    <row r="67" spans="1:30">
       <c r="A67" t="s">
         <v>1977</v>
       </c>
@@ -62022,21 +62217,21 @@
       <c r="C67" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D67" s="44">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
+      <c r="D67" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E67" s="44">
+        <v>1</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
         <v>100</v>
       </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -62071,37 +62266,40 @@
         <v>0</v>
       </c>
       <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
         <v>10</v>
       </c>
-      <c r="U67" s="44" t="s">
+      <c r="V67" s="44" t="s">
         <v>1987</v>
       </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
       <c r="W67">
-        <v>1</v>
-      </c>
-      <c r="X67" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z67">
+      <c r="Z67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA67">
         <v>11</v>
       </c>
-      <c r="AA67" t="s">
+      <c r="AB67" t="s">
         <v>1663</v>
       </c>
-      <c r="AB67" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC67">
+      <c r="AC67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:29">
+    <row r="68" spans="1:30">
       <c r="A68" t="s">
         <v>1978</v>
       </c>
@@ -62111,21 +62309,21 @@
       <c r="C68" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D68" s="44">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
+      <c r="D68" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" s="44">
+        <v>1</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
         <v>100</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
       <c r="I68">
         <v>0</v>
       </c>
@@ -62160,37 +62358,40 @@
         <v>0</v>
       </c>
       <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
         <v>10</v>
       </c>
-      <c r="U68" s="44" t="s">
+      <c r="V68" s="44" t="s">
         <v>1987</v>
       </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
       <c r="W68">
-        <v>1</v>
-      </c>
-      <c r="X68" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y68" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z68">
+      <c r="Z68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA68">
         <v>11</v>
       </c>
-      <c r="AA68" t="s">
+      <c r="AB68" t="s">
         <v>1663</v>
       </c>
-      <c r="AB68" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC68">
+      <c r="AC68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD68">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:29">
+    <row r="69" spans="1:30">
       <c r="A69" t="s">
         <v>1979</v>
       </c>
@@ -62200,21 +62401,21 @@
       <c r="C69" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D69" s="44">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
+      <c r="D69" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" s="44">
+        <v>1</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
         <v>100</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
       <c r="I69">
         <v>0</v>
       </c>
@@ -62249,42 +62450,45 @@
         <v>0</v>
       </c>
       <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
         <v>10</v>
       </c>
-      <c r="U69" s="44" t="s">
+      <c r="V69" s="44" t="s">
         <v>1987</v>
       </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
       <c r="W69">
-        <v>1</v>
-      </c>
-      <c r="X69" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y69" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z69">
+      <c r="Z69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA69">
         <v>11</v>
       </c>
-      <c r="AA69" t="s">
+      <c r="AB69" t="s">
         <v>1663</v>
       </c>
-      <c r="AB69" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC69">
+      <c r="AC69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD69">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="14">
+    <row r="70" spans="1:30" ht="14">
       <c r="A70" s="55" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="71" spans="1:29">
+    <row r="71" spans="1:30">
       <c r="A71" t="s">
         <v>1981</v>
       </c>
@@ -62294,21 +62498,21 @@
       <c r="C71" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D71" s="44">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
+      <c r="D71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" s="44">
+        <v>1</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
         <v>100</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
       <c r="I71">
         <v>0</v>
       </c>
@@ -62343,37 +62547,40 @@
         <v>0</v>
       </c>
       <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
         <v>10</v>
       </c>
-      <c r="U71" s="44" t="s">
+      <c r="V71" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
       <c r="W71">
-        <v>1</v>
-      </c>
-      <c r="X71" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>1</v>
+      </c>
+      <c r="Y71" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y71" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z71">
+      <c r="Z71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA71">
         <v>11</v>
       </c>
-      <c r="AA71" t="s">
+      <c r="AB71" t="s">
         <v>1663</v>
       </c>
-      <c r="AB71" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC71">
+      <c r="AC71" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD71">
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:29">
+    <row r="72" spans="1:30">
       <c r="A72" t="s">
         <v>1982</v>
       </c>
@@ -62383,21 +62590,21 @@
       <c r="C72" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D72" s="44">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
+      <c r="D72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" s="44">
+        <v>1</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
         <v>100</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
       <c r="I72">
         <v>0</v>
       </c>
@@ -62432,37 +62639,40 @@
         <v>0</v>
       </c>
       <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
         <v>10</v>
       </c>
-      <c r="U72" s="44" t="s">
+      <c r="V72" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
       <c r="W72">
-        <v>1</v>
-      </c>
-      <c r="X72" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>1</v>
+      </c>
+      <c r="Y72" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y72" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z72">
+      <c r="Z72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA72">
         <v>11</v>
       </c>
-      <c r="AA72" t="s">
+      <c r="AB72" t="s">
         <v>1663</v>
       </c>
-      <c r="AB72" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC72">
+      <c r="AC72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD72">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:29">
+    <row r="73" spans="1:30">
       <c r="A73" t="s">
         <v>1983</v>
       </c>
@@ -62472,21 +62682,21 @@
       <c r="C73" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D73" s="44">
-        <v>1</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
+      <c r="D73" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E73" s="44">
+        <v>1</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
         <v>100</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
       <c r="I73">
         <v>0</v>
       </c>
@@ -62521,37 +62731,40 @@
         <v>0</v>
       </c>
       <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
         <v>10</v>
       </c>
-      <c r="U73" s="44" t="s">
+      <c r="V73" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
       <c r="W73">
-        <v>1</v>
-      </c>
-      <c r="X73" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y73" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z73">
+      <c r="Z73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA73">
         <v>11</v>
       </c>
-      <c r="AA73" t="s">
+      <c r="AB73" t="s">
         <v>1663</v>
       </c>
-      <c r="AB73" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC73">
+      <c r="AC73" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:29">
+    <row r="74" spans="1:30">
       <c r="A74" t="s">
         <v>1984</v>
       </c>
@@ -62561,21 +62774,21 @@
       <c r="C74" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D74" s="44">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
+      <c r="D74" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E74" s="44">
+        <v>1</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>100</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
       <c r="I74">
         <v>0</v>
       </c>
@@ -62610,37 +62823,40 @@
         <v>0</v>
       </c>
       <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
         <v>10</v>
       </c>
-      <c r="U74" s="44" t="s">
+      <c r="V74" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
       <c r="W74">
-        <v>1</v>
-      </c>
-      <c r="X74" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Y74" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y74" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z74">
+      <c r="Z74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA74">
         <v>11</v>
       </c>
-      <c r="AA74" t="s">
+      <c r="AB74" t="s">
         <v>1663</v>
       </c>
-      <c r="AB74" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC74">
+      <c r="AC74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD74">
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:29">
+    <row r="75" spans="1:30">
       <c r="A75" t="s">
         <v>1985</v>
       </c>
@@ -62650,21 +62866,21 @@
       <c r="C75" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D75" s="44">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
+      <c r="D75" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75" s="44">
+        <v>1</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
         <v>100</v>
       </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
       <c r="I75">
         <v>0</v>
       </c>
@@ -62699,42 +62915,45 @@
         <v>0</v>
       </c>
       <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
         <v>10</v>
       </c>
-      <c r="U75" s="44" t="s">
+      <c r="V75" s="44" t="s">
         <v>833</v>
       </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
       <c r="W75">
-        <v>1</v>
-      </c>
-      <c r="X75" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y75" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z75">
+      <c r="Z75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA75">
         <v>11</v>
       </c>
-      <c r="AA75" t="s">
+      <c r="AB75" t="s">
         <v>1663</v>
       </c>
-      <c r="AB75" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC75">
+      <c r="AC75" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD75">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="14">
+    <row r="76" spans="1:30" ht="14">
       <c r="A76" s="55" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="77" spans="1:29">
+    <row r="77" spans="1:30">
       <c r="A77" t="s">
         <v>1989</v>
       </c>
@@ -62744,21 +62963,21 @@
       <c r="C77" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D77" s="44">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
+      <c r="D77" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="44">
+        <v>1</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
         <v>100</v>
       </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
       <c r="I77">
         <v>0</v>
       </c>
@@ -62793,37 +63012,40 @@
         <v>0</v>
       </c>
       <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
         <v>10</v>
       </c>
-      <c r="U77" s="44" t="s">
+      <c r="V77" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
       <c r="W77">
-        <v>1</v>
-      </c>
-      <c r="X77" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y77" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z77">
+      <c r="Z77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA77">
         <v>11</v>
       </c>
-      <c r="AA77" t="s">
+      <c r="AB77" t="s">
         <v>1663</v>
       </c>
-      <c r="AB77" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC77">
+      <c r="AC77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD77">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:29">
+    <row r="78" spans="1:30">
       <c r="A78" t="s">
         <v>1990</v>
       </c>
@@ -62833,21 +63055,21 @@
       <c r="C78" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D78" s="44">
-        <v>1</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
+      <c r="D78" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E78" s="44">
+        <v>1</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
         <v>100</v>
       </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
       <c r="I78">
         <v>0</v>
       </c>
@@ -62882,37 +63104,40 @@
         <v>0</v>
       </c>
       <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
         <v>10</v>
       </c>
-      <c r="U78" s="44" t="s">
+      <c r="V78" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
       <c r="W78">
-        <v>1</v>
-      </c>
-      <c r="X78" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="Y78" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y78" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z78">
+      <c r="Z78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA78">
         <v>11</v>
       </c>
-      <c r="AA78" t="s">
+      <c r="AB78" t="s">
         <v>1663</v>
       </c>
-      <c r="AB78" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC78">
+      <c r="AC78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD78">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:29">
+    <row r="79" spans="1:30">
       <c r="A79" t="s">
         <v>1991</v>
       </c>
@@ -62922,21 +63147,21 @@
       <c r="C79" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D79" s="44">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
+      <c r="D79" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79" s="44">
+        <v>1</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
         <v>100</v>
       </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
       <c r="I79">
         <v>0</v>
       </c>
@@ -62971,37 +63196,40 @@
         <v>0</v>
       </c>
       <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
         <v>10</v>
       </c>
-      <c r="U79" s="44" t="s">
+      <c r="V79" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
       <c r="W79">
-        <v>1</v>
-      </c>
-      <c r="X79" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y79" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z79">
+      <c r="Z79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA79">
         <v>11</v>
       </c>
-      <c r="AA79" t="s">
+      <c r="AB79" t="s">
         <v>1663</v>
       </c>
-      <c r="AB79" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC79">
+      <c r="AC79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD79">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:29">
+    <row r="80" spans="1:30">
       <c r="A80" t="s">
         <v>1992</v>
       </c>
@@ -63011,21 +63239,21 @@
       <c r="C80" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="44">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
+      <c r="D80" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="44">
+        <v>1</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
         <v>100</v>
       </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
       <c r="I80">
         <v>0</v>
       </c>
@@ -63060,37 +63288,40 @@
         <v>0</v>
       </c>
       <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
         <v>10</v>
       </c>
-      <c r="U80" s="44" t="s">
+      <c r="V80" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
       <c r="W80">
-        <v>1</v>
-      </c>
-      <c r="X80" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y80" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z80">
+      <c r="Z80" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA80">
         <v>11</v>
       </c>
-      <c r="AA80" t="s">
+      <c r="AB80" t="s">
         <v>1663</v>
       </c>
-      <c r="AB80" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC80">
+      <c r="AC80" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD80">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81" spans="1:30">
       <c r="A81" t="s">
         <v>1993</v>
       </c>
@@ -63100,21 +63331,21 @@
       <c r="C81" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D81" s="44">
-        <v>1</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
+      <c r="D81" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81" s="44">
+        <v>1</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
         <v>100</v>
       </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
       <c r="I81">
         <v>0</v>
       </c>
@@ -63149,42 +63380,45 @@
         <v>0</v>
       </c>
       <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
         <v>10</v>
       </c>
-      <c r="U81" s="44" t="s">
+      <c r="V81" s="44" t="s">
         <v>1079</v>
       </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
       <c r="W81">
-        <v>1</v>
-      </c>
-      <c r="X81" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y81" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z81">
+      <c r="Z81" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA81">
         <v>11</v>
       </c>
-      <c r="AA81" t="s">
+      <c r="AB81" t="s">
         <v>1663</v>
       </c>
-      <c r="AB81" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC81">
+      <c r="AC81" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD81">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="14">
+    <row r="82" spans="1:30" ht="14">
       <c r="A82" s="55" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83" spans="1:30">
       <c r="A83" t="s">
         <v>1994</v>
       </c>
@@ -63192,23 +63426,23 @@
         <v>821</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D83" s="44">
-        <v>1</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
+        <v>2042</v>
+      </c>
+      <c r="D83" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="44">
+        <v>1</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
         <v>100</v>
       </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
       <c r="I83">
         <v>0</v>
       </c>
@@ -63243,37 +63477,40 @@
         <v>0</v>
       </c>
       <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
         <v>10</v>
       </c>
-      <c r="U83" s="44" t="s">
+      <c r="V83" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
       <c r="W83">
-        <v>1</v>
-      </c>
-      <c r="X83" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+      <c r="Y83" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y83" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z83">
+      <c r="Z83" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA83">
         <v>11</v>
       </c>
-      <c r="AA83" t="s">
+      <c r="AB83" t="s">
         <v>1663</v>
       </c>
-      <c r="AB83" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC83">
+      <c r="AC83" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD83">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84" spans="1:30">
       <c r="A84" t="s">
         <v>1995</v>
       </c>
@@ -63283,21 +63520,21 @@
       <c r="C84" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D84" s="44">
-        <v>1</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
+      <c r="D84" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" s="44">
+        <v>1</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
         <v>100</v>
       </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
       <c r="I84">
         <v>0</v>
       </c>
@@ -63332,37 +63569,40 @@
         <v>0</v>
       </c>
       <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
         <v>10</v>
       </c>
-      <c r="U84" s="44" t="s">
+      <c r="V84" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
       <c r="W84">
-        <v>1</v>
-      </c>
-      <c r="X84" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>1</v>
+      </c>
+      <c r="Y84" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y84" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z84">
+      <c r="Z84" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA84">
         <v>11</v>
       </c>
-      <c r="AA84" t="s">
+      <c r="AB84" t="s">
         <v>1663</v>
       </c>
-      <c r="AB84" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC84">
+      <c r="AC84" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD84">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85" spans="1:30">
       <c r="A85" t="s">
         <v>1996</v>
       </c>
@@ -63372,21 +63612,21 @@
       <c r="C85" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D85" s="44">
-        <v>1</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
+      <c r="D85" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" s="44">
+        <v>1</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
         <v>100</v>
       </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
       <c r="I85">
         <v>0</v>
       </c>
@@ -63421,37 +63661,40 @@
         <v>0</v>
       </c>
       <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
         <v>10</v>
       </c>
-      <c r="U85" s="44" t="s">
+      <c r="V85" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
       <c r="W85">
-        <v>1</v>
-      </c>
-      <c r="X85" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y85" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z85">
+      <c r="Z85" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA85">
         <v>11</v>
       </c>
-      <c r="AA85" t="s">
+      <c r="AB85" t="s">
         <v>1663</v>
       </c>
-      <c r="AB85" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC85">
+      <c r="AC85" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD85">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86" spans="1:30">
       <c r="A86" t="s">
         <v>1997</v>
       </c>
@@ -63461,21 +63704,21 @@
       <c r="C86" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D86" s="44">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
+      <c r="D86" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E86" s="44">
+        <v>1</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
         <v>100</v>
       </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
       <c r="I86">
         <v>0</v>
       </c>
@@ -63510,37 +63753,40 @@
         <v>0</v>
       </c>
       <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
         <v>10</v>
       </c>
-      <c r="U86" s="44" t="s">
+      <c r="V86" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
       <c r="W86">
-        <v>1</v>
-      </c>
-      <c r="X86" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y86" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z86">
+      <c r="Z86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA86">
         <v>11</v>
       </c>
-      <c r="AA86" t="s">
+      <c r="AB86" t="s">
         <v>1663</v>
       </c>
-      <c r="AB86" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC86">
+      <c r="AC86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD86">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87" spans="1:30">
       <c r="A87" t="s">
         <v>1998</v>
       </c>
@@ -63550,21 +63796,21 @@
       <c r="C87" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D87" s="44">
-        <v>1</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
+      <c r="D87" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87" s="44">
+        <v>1</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
         <v>100</v>
       </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
       <c r="I87">
         <v>0</v>
       </c>
@@ -63599,33 +63845,36 @@
         <v>0</v>
       </c>
       <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87">
         <v>10</v>
       </c>
-      <c r="U87" s="44" t="s">
+      <c r="V87" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
       <c r="W87">
-        <v>1</v>
-      </c>
-      <c r="X87" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="44" t="s">
         <v>1182</v>
       </c>
-      <c r="Y87" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z87">
+      <c r="Z87" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA87">
         <v>11</v>
       </c>
-      <c r="AA87" t="s">
+      <c r="AB87" t="s">
         <v>1663</v>
       </c>
-      <c r="AB87" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC87">
+      <c r="AC87" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD87">
         <v>5</v>
       </c>
     </row>
@@ -63636,7 +63885,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BK105"/>
+  <dimension ref="A1:BL107"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -63693,11 +63942,12 @@
     <col min="59" max="59" width="10" customWidth="1"/>
     <col min="60" max="60" width="11.54296875" customWidth="1"/>
     <col min="61" max="61" width="13.26953125" customWidth="1"/>
-    <col min="62" max="62" width="26.26953125" customWidth="1"/>
-    <col min="63" max="63" width="10" customWidth="1"/>
+    <col min="62" max="62" width="14.1796875" customWidth="1"/>
+    <col min="63" max="63" width="18.81640625" customWidth="1"/>
+    <col min="64" max="64" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="13">
+    <row r="1" spans="1:64" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -63884,9 +64134,12 @@
       <c r="BJ1" s="43" t="s">
         <v>1898</v>
       </c>
-      <c r="BK1" s="43"/>
-    </row>
-    <row r="2" spans="1:63">
+      <c r="BK1" s="43" t="s">
+        <v>2041</v>
+      </c>
+      <c r="BL1" s="43"/>
+    </row>
+    <row r="2" spans="1:64">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
@@ -64073,8 +64326,11 @@
       <c r="BJ2" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:63">
+      <c r="BK2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64">
       <c r="A3" s="44" t="s">
         <v>1927</v>
       </c>
@@ -64261,8 +64517,11 @@
       <c r="BJ3" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:63">
+      <c r="BK3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64">
       <c r="A4" s="44" t="s">
         <v>1899</v>
       </c>
@@ -64449,8 +64708,11 @@
       <c r="BJ4" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:63">
+      <c r="BK4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64">
       <c r="A5" s="44" t="s">
         <v>42</v>
       </c>
@@ -64637,8 +64899,11 @@
       <c r="BJ5" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:63">
+      <c r="BK5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64">
       <c r="A6" s="44" t="s">
         <v>1371</v>
       </c>
@@ -64825,8 +65090,11 @@
       <c r="BJ6" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:63">
+      <c r="BK6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64">
       <c r="A7" s="44" t="s">
         <v>1372</v>
       </c>
@@ -65013,8 +65281,11 @@
       <c r="BJ7" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:63">
+      <c r="BK7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64">
       <c r="A8" s="44" t="s">
         <v>1889</v>
       </c>
@@ -65201,8 +65472,11 @@
       <c r="BJ8" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:63">
+      <c r="BK8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64">
       <c r="A9" s="44" t="s">
         <v>1469</v>
       </c>
@@ -65389,8 +65663,11 @@
       <c r="BJ9" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:63">
+      <c r="BK9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:64">
       <c r="A10" s="44" t="s">
         <v>1483</v>
       </c>
@@ -65577,8 +65854,11 @@
       <c r="BJ10" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:63">
+      <c r="BK10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:64">
       <c r="A11" s="44" t="s">
         <v>1430</v>
       </c>
@@ -65765,8 +66045,11 @@
       <c r="BJ11" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:63">
+      <c r="BK11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:64">
       <c r="A12" s="44" t="s">
         <v>1433</v>
       </c>
@@ -65953,8 +66236,11 @@
       <c r="BJ12" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:63">
+      <c r="BK12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:64">
       <c r="A13" s="44" t="s">
         <v>1447</v>
       </c>
@@ -66141,8 +66427,11 @@
       <c r="BJ13" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:63">
+      <c r="BK13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:64">
       <c r="A14" s="44" t="s">
         <v>1524</v>
       </c>
@@ -66329,8 +66618,11 @@
       <c r="BJ14" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:63">
+      <c r="BK14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:64">
       <c r="A15" s="44" t="s">
         <v>1448</v>
       </c>
@@ -66517,8 +66809,11 @@
       <c r="BJ15" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:63">
+      <c r="BK15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:64">
       <c r="A16" s="44" t="s">
         <v>1449</v>
       </c>
@@ -66705,8 +67000,11 @@
       <c r="BJ16" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:62">
+      <c r="BK16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:63">
       <c r="A17" s="44" t="s">
         <v>1911</v>
       </c>
@@ -66893,8 +67191,11 @@
       <c r="BJ17" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:62">
+      <c r="BK17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:63">
       <c r="A18" s="44" t="s">
         <v>1485</v>
       </c>
@@ -67081,8 +67382,11 @@
       <c r="BJ18" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:62">
+      <c r="BK18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:63">
       <c r="A19" s="44" t="s">
         <v>1489</v>
       </c>
@@ -67269,8 +67573,11 @@
       <c r="BJ19" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:62">
+      <c r="BK19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:63">
       <c r="A20" s="44" t="s">
         <v>1490</v>
       </c>
@@ -67457,8 +67764,11 @@
       <c r="BJ20" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:62">
+      <c r="BK20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:63">
       <c r="A21" s="44" t="s">
         <v>1914</v>
       </c>
@@ -67645,8 +67955,11 @@
       <c r="BJ21" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:62">
+      <c r="BK21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:63">
       <c r="A22" s="44" t="s">
         <v>1913</v>
       </c>
@@ -67833,8 +68146,11 @@
       <c r="BJ22" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:62">
+      <c r="BK22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:63">
       <c r="A23" s="44" t="s">
         <v>1928</v>
       </c>
@@ -68021,8 +68337,11 @@
       <c r="BJ23" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:62">
+      <c r="BK23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:63">
       <c r="A24" s="44" t="s">
         <v>1931</v>
       </c>
@@ -68209,8 +68528,11 @@
       <c r="BJ24" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:62">
+      <c r="BK24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:63">
       <c r="A25" s="44" t="s">
         <v>1929</v>
       </c>
@@ -68397,8 +68719,11 @@
       <c r="BJ25" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:62">
+      <c r="BK25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:63">
       <c r="A26" s="44" t="s">
         <v>1912</v>
       </c>
@@ -68585,8 +68910,11 @@
       <c r="BJ26" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:62">
+      <c r="BK26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:63">
       <c r="A27" s="44" t="s">
         <v>1494</v>
       </c>
@@ -68773,8 +69101,11 @@
       <c r="BJ27" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:62">
+      <c r="BK27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:63">
       <c r="A28" s="44" t="s">
         <v>1501</v>
       </c>
@@ -68961,8 +69292,11 @@
       <c r="BJ28" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:62">
+      <c r="BK28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:63">
       <c r="A29" s="44" t="s">
         <v>1502</v>
       </c>
@@ -69149,8 +69483,11 @@
       <c r="BJ29" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:62">
+      <c r="BK29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:63">
       <c r="A30" s="44" t="s">
         <v>1431</v>
       </c>
@@ -69337,8 +69674,11 @@
       <c r="BJ30" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:62">
+      <c r="BK30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:63">
       <c r="A31" s="44" t="s">
         <v>1551</v>
       </c>
@@ -69525,8 +69865,11 @@
       <c r="BJ31" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:62">
+      <c r="BK31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:63">
       <c r="A32" s="44" t="s">
         <v>1587</v>
       </c>
@@ -69713,8 +70056,11 @@
       <c r="BJ32" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:62">
+      <c r="BK32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:63">
       <c r="A33" s="44" t="s">
         <v>935</v>
       </c>
@@ -69901,8 +70247,11 @@
       <c r="BJ33" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:62">
+      <c r="BK33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:63">
       <c r="A34" s="44" t="s">
         <v>1593</v>
       </c>
@@ -70089,8 +70438,11 @@
       <c r="BJ34" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:62">
+      <c r="BK34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:63">
       <c r="A35" s="44" t="s">
         <v>1602</v>
       </c>
@@ -70277,8 +70629,11 @@
       <c r="BJ35" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:62">
+      <c r="BK35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:63">
       <c r="A36" s="44" t="s">
         <v>1611</v>
       </c>
@@ -70465,8 +70820,11 @@
       <c r="BJ36" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:62">
+      <c r="BK36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:63">
       <c r="A37" s="44" t="s">
         <v>1615</v>
       </c>
@@ -70653,8 +71011,11 @@
       <c r="BJ37" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:62">
+      <c r="BK37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:63">
       <c r="A38" s="44" t="s">
         <v>1616</v>
       </c>
@@ -70841,8 +71202,11 @@
       <c r="BJ38" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:62">
+      <c r="BK38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:63">
       <c r="A39" s="44" t="s">
         <v>1620</v>
       </c>
@@ -71029,8 +71393,11 @@
       <c r="BJ39" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:62">
+      <c r="BK39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:63">
       <c r="A40" s="44" t="s">
         <v>1624</v>
       </c>
@@ -71217,8 +71584,11 @@
       <c r="BJ40" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:62">
+      <c r="BK40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:63">
       <c r="A41" s="44" t="s">
         <v>1647</v>
       </c>
@@ -71405,8 +71775,11 @@
       <c r="BJ41" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:62">
+      <c r="BK41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:63">
       <c r="A42" s="44" t="s">
         <v>1578</v>
       </c>
@@ -71593,8 +71966,11 @@
       <c r="BJ42" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:62">
+      <c r="BK42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:63">
       <c r="A43" s="44" t="s">
         <v>1686</v>
       </c>
@@ -71781,8 +72157,11 @@
       <c r="BJ43" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="1:62">
+      <c r="BK43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:63">
       <c r="A44" s="44" t="s">
         <v>1728</v>
       </c>
@@ -71969,8 +72348,11 @@
       <c r="BJ44" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="45" spans="1:62">
+      <c r="BK44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:63">
       <c r="A45" s="44" t="s">
         <v>1786</v>
       </c>
@@ -72157,8 +72539,11 @@
       <c r="BJ45" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="46" spans="1:62">
+      <c r="BK45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:63">
       <c r="A46" s="44" t="s">
         <v>1904</v>
       </c>
@@ -72345,8 +72730,11 @@
       <c r="BJ46" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="47" spans="1:62">
+      <c r="BK46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:63">
       <c r="A47" s="44" t="s">
         <v>1905</v>
       </c>
@@ -72533,8 +72921,11 @@
       <c r="BJ47" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="48" spans="1:62">
+      <c r="BK47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:63">
       <c r="A48" s="44" t="s">
         <v>1906</v>
       </c>
@@ -72721,8 +73112,11 @@
       <c r="BJ48" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="49" spans="1:62">
+      <c r="BK48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:63">
       <c r="A49" s="44" t="s">
         <v>1923</v>
       </c>
@@ -72909,8 +73303,11 @@
       <c r="BJ49" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:62">
+      <c r="BK49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:63">
       <c r="A50" s="44" t="s">
         <v>1924</v>
       </c>
@@ -73097,10 +73494,13 @@
       <c r="BJ50" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="51" spans="1:62">
+      <c r="BK50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:63">
       <c r="A51" s="44" t="s">
-        <v>1797</v>
+        <v>2042</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -73199,7 +73599,7 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>1919</v>
+        <v>2044</v>
       </c>
       <c r="AI51" s="44" t="s">
         <v>1479</v>
@@ -73285,10 +73685,13 @@
       <c r="BJ51" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="52" spans="1:62">
+      <c r="BK51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:63">
       <c r="A52" s="44" t="s">
-        <v>1796</v>
+        <v>2043</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -73300,10 +73703,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -73315,10 +73718,10 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -73473,10 +73876,13 @@
       <c r="BJ52" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="53" spans="1:62">
+      <c r="BK52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:63">
       <c r="A53" s="44" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -73533,7 +73939,7 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -73545,7 +73951,7 @@
         <v>3</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y53">
         <v>0</v>
@@ -73575,13 +73981,13 @@
         <v>36</v>
       </c>
       <c r="AH53" t="s">
-        <v>36</v>
+        <v>1919</v>
       </c>
       <c r="AI53" s="44" t="s">
         <v>1479</v>
       </c>
       <c r="AJ53" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK53" s="44" t="s">
         <v>1470</v>
@@ -73647,7 +74053,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="BG53" t="s">
         <v>36</v>
@@ -73661,13 +74067,16 @@
       <c r="BJ53" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="1:62">
+      <c r="BK53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:63">
       <c r="A54" s="44" t="s">
-        <v>1807</v>
+        <v>1796</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -73676,7 +74085,7 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -73751,13 +74160,13 @@
         <v>0</v>
       </c>
       <c r="AD54">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE54">
         <v>0</v>
       </c>
       <c r="AF54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="s">
         <v>36</v>
@@ -73769,7 +74178,7 @@
         <v>1479</v>
       </c>
       <c r="AJ54" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK54" s="44" t="s">
         <v>1470</v>
@@ -73793,7 +74202,7 @@
         <v>0</v>
       </c>
       <c r="AR54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS54">
         <v>1</v>
@@ -73811,7 +74220,7 @@
         <v>0</v>
       </c>
       <c r="AX54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="s">
         <v>36</v>
@@ -73835,13 +74244,13 @@
         <v>0</v>
       </c>
       <c r="BF54" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG54" t="s">
         <v>36</v>
       </c>
       <c r="BH54" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI54">
         <v>0</v>
@@ -73849,10 +74258,13 @@
       <c r="BJ54" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="55" spans="1:62">
+      <c r="BK54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:63">
       <c r="A55" s="44" t="s">
-        <v>1934</v>
+        <v>1805</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -73864,52 +74276,52 @@
         <v>0</v>
       </c>
       <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
         <v>50</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -73921,7 +74333,7 @@
         <v>3</v>
       </c>
       <c r="X55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y55">
         <v>0</v>
@@ -73951,13 +74363,13 @@
         <v>36</v>
       </c>
       <c r="AH55" t="s">
-        <v>1936</v>
+        <v>36</v>
       </c>
       <c r="AI55" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ55" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK55" s="44" t="s">
         <v>1470</v>
@@ -74023,13 +74435,13 @@
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="BG55" t="s">
         <v>36</v>
       </c>
       <c r="BH55" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI55">
         <v>0</v>
@@ -74037,10 +74449,13 @@
       <c r="BJ55" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="1:62">
+      <c r="BK55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:63">
       <c r="A56" s="44" t="s">
-        <v>1935</v>
+        <v>1807</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -74127,13 +74542,13 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG56" t="s">
         <v>36</v>
@@ -74142,10 +74557,10 @@
         <v>36</v>
       </c>
       <c r="AI56" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ56" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK56" s="44" t="s">
         <v>1470</v>
@@ -74169,7 +74584,7 @@
         <v>0</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS56">
         <v>1</v>
@@ -74187,7 +74602,7 @@
         <v>0</v>
       </c>
       <c r="AX56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="s">
         <v>36</v>
@@ -74211,24 +74626,27 @@
         <v>0</v>
       </c>
       <c r="BF56" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG56" t="s">
         <v>36</v>
       </c>
       <c r="BH56" t="s">
-        <v>896</v>
+        <v>1671</v>
       </c>
       <c r="BI56">
         <v>0</v>
       </c>
       <c r="BJ56" s="46" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="57" spans="1:62">
+        <v>36</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:63">
       <c r="A57" s="44" t="s">
-        <v>1868</v>
+        <v>1934</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -74327,7 +74745,7 @@
         <v>36</v>
       </c>
       <c r="AH57" t="s">
-        <v>1920</v>
+        <v>1936</v>
       </c>
       <c r="AI57" s="44" t="s">
         <v>1363</v>
@@ -74399,7 +74817,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="BG57" t="s">
         <v>36</v>
@@ -74413,19 +74831,22 @@
       <c r="BJ57" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="58" spans="1:62">
+      <c r="BK57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:63">
       <c r="A58" s="44" t="s">
-        <v>1869</v>
+        <v>1935</v>
       </c>
       <c r="B58">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -74599,12 +75020,15 @@
         <v>0</v>
       </c>
       <c r="BJ58" s="46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:62">
+        <v>1937</v>
+      </c>
+      <c r="BK58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:63">
       <c r="A59" s="44" t="s">
-        <v>1925</v>
+        <v>1868</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -74616,7 +75040,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -74703,10 +75127,10 @@
         <v>36</v>
       </c>
       <c r="AH59" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AI59" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ59" s="44" t="s">
         <v>1470</v>
@@ -74781,7 +75205,7 @@
         <v>36</v>
       </c>
       <c r="BH59" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI59">
         <v>0</v>
@@ -74789,19 +75213,22 @@
       <c r="BJ59" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" spans="1:62">
+      <c r="BK59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:63">
       <c r="A60" s="44" t="s">
-        <v>1926</v>
+        <v>1869</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -74822,7 +75249,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -74894,7 +75321,7 @@
         <v>36</v>
       </c>
       <c r="AI60" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ60" s="44" t="s">
         <v>1470</v>
@@ -74969,7 +75396,7 @@
         <v>36</v>
       </c>
       <c r="BH60" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI60">
         <v>0</v>
@@ -74977,10 +75404,13 @@
       <c r="BJ60" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="61" spans="1:62">
+      <c r="BK60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:63">
       <c r="A61" s="44" t="s">
-        <v>1870</v>
+        <v>1925</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -75165,10 +75595,13 @@
       <c r="BJ61" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="62" spans="1:62">
+      <c r="BK61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:63">
       <c r="A62" s="44" t="s">
-        <v>1871</v>
+        <v>1926</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -75195,10 +75628,10 @@
         <v>0</v>
       </c>
       <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
         <v>50</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -75353,10 +75786,13 @@
       <c r="BJ62" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="63" spans="1:62">
+      <c r="BK62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:63">
       <c r="A63" s="44" t="s">
-        <v>1882</v>
+        <v>1870</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -75374,7 +75810,7 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -75422,10 +75858,10 @@
         <v>0</v>
       </c>
       <c r="W63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y63">
         <v>0</v>
@@ -75455,10 +75891,10 @@
         <v>36</v>
       </c>
       <c r="AH63" t="s">
-        <v>36</v>
+        <v>1921</v>
       </c>
       <c r="AI63" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ63" s="44" t="s">
         <v>1470</v>
@@ -75527,7 +75963,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="s">
-        <v>37</v>
+        <v>1763</v>
       </c>
       <c r="BG63" t="s">
         <v>36</v>
@@ -75541,13 +75977,16 @@
       <c r="BJ63" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="64" spans="1:62">
+      <c r="BK63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:63">
       <c r="A64" s="44" t="s">
-        <v>1883</v>
+        <v>1871</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -75562,7 +76001,7 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -75571,7 +76010,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -75610,7 +76049,7 @@
         <v>0</v>
       </c>
       <c r="W64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -75631,13 +76070,13 @@
         <v>0</v>
       </c>
       <c r="AD64">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE64">
         <v>0</v>
       </c>
       <c r="AF64">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="s">
         <v>36</v>
@@ -75646,7 +76085,7 @@
         <v>36</v>
       </c>
       <c r="AI64" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ64" s="44" t="s">
         <v>1470</v>
@@ -75673,7 +76112,7 @@
         <v>0</v>
       </c>
       <c r="AR64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS64">
         <v>1</v>
@@ -75691,7 +76130,7 @@
         <v>0</v>
       </c>
       <c r="AX64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY64" t="s">
         <v>36</v>
@@ -75715,7 +76154,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG64" t="s">
         <v>36</v>
@@ -75729,10 +76168,13 @@
       <c r="BJ64" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="65" spans="1:62">
+      <c r="BK64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:63">
       <c r="A65" s="44" t="s">
-        <v>1908</v>
+        <v>1882</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -75903,7 +76345,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="s">
-        <v>1763</v>
+        <v>37</v>
       </c>
       <c r="BG65" t="s">
         <v>36</v>
@@ -75917,10 +76359,13 @@
       <c r="BJ65" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="66" spans="1:62">
+      <c r="BK65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:63">
       <c r="A66" s="44" t="s">
-        <v>1907</v>
+        <v>1883</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -76091,7 +76536,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG66" t="s">
         <v>36</v>
@@ -76105,10 +76550,13 @@
       <c r="BJ66" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="67" spans="1:62">
+      <c r="BK66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:63">
       <c r="A67" s="44" t="s">
-        <v>1884</v>
+        <v>1908</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -76279,7 +76727,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG67" t="s">
         <v>36</v>
@@ -76293,10 +76741,13 @@
       <c r="BJ67" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="68" spans="1:62">
+      <c r="BK67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:63">
       <c r="A68" s="44" t="s">
-        <v>1938</v>
+        <v>1907</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -76314,7 +76765,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -76392,10 +76843,10 @@
         <v>10</v>
       </c>
       <c r="AG68" t="s">
-        <v>1941</v>
+        <v>36</v>
       </c>
       <c r="AH68" t="s">
-        <v>1939</v>
+        <v>36</v>
       </c>
       <c r="AI68" s="44" t="s">
         <v>1363</v>
@@ -76467,7 +76918,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG68" t="s">
         <v>36</v>
@@ -76481,103 +76932,106 @@
       <c r="BJ68" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="69" spans="1:62">
+      <c r="BK68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:63">
       <c r="A69" s="44" t="s">
-        <v>1940</v>
+        <v>1884</v>
       </c>
       <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>4</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>1</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
         <v>-1</v>
       </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <v>50</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>3</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>1</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>5</v>
-      </c>
       <c r="AE69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG69" t="s">
         <v>36</v>
@@ -76604,7 +77058,7 @@
         <v>1</v>
       </c>
       <c r="AO69" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP69" s="44">
         <v>0</v>
@@ -76631,7 +77085,7 @@
         <v>0</v>
       </c>
       <c r="AX69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY69" t="s">
         <v>36</v>
@@ -76655,13 +77109,13 @@
         <v>0</v>
       </c>
       <c r="BF69" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BG69" t="s">
         <v>36</v>
       </c>
       <c r="BH69" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI69">
         <v>0</v>
@@ -76669,32 +77123,190 @@
       <c r="BJ69" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="70" spans="1:62" ht="14">
-      <c r="A70" s="55" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B70" s="55"/>
-      <c r="C70" s="55"/>
-      <c r="D70" s="55"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="55"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="55"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
+      <c r="BK69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:63">
+      <c r="A70" s="44" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>4</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>1</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>-1</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>10</v>
+      </c>
       <c r="AG70" t="s">
-        <v>36</v>
+        <v>1941</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>1939</v>
+      </c>
+      <c r="AI70" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ70" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK70" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL70" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN70" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO70" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP70" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>1</v>
+      </c>
+      <c r="AS70">
+        <v>1</v>
+      </c>
+      <c r="AT70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU70">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW70">
+        <v>0</v>
+      </c>
+      <c r="AX70">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ70" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA70" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB70">
+        <v>0</v>
+      </c>
+      <c r="BC70">
+        <v>0</v>
+      </c>
+      <c r="BD70">
+        <v>0</v>
+      </c>
+      <c r="BE70">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG70" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH70" t="s">
+        <v>1663</v>
       </c>
       <c r="BI70">
         <v>0</v>
@@ -76702,13 +77314,16 @@
       <c r="BJ70" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="71" spans="1:62">
+      <c r="BK70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:63">
       <c r="A71" s="44" t="s">
-        <v>1887</v>
+        <v>1940</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -76717,7 +77332,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -76726,10 +77341,10 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -76792,13 +77407,13 @@
         <v>0</v>
       </c>
       <c r="AD71">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="s">
         <v>36</v>
@@ -76825,7 +77440,7 @@
         <v>1</v>
       </c>
       <c r="AO71" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP71" s="44">
         <v>0</v>
@@ -76834,7 +77449,7 @@
         <v>0</v>
       </c>
       <c r="AR71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS71">
         <v>1</v>
@@ -76852,7 +77467,7 @@
         <v>0</v>
       </c>
       <c r="AX71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY71" t="s">
         <v>36</v>
@@ -76873,205 +77488,53 @@
         <v>0</v>
       </c>
       <c r="BE71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF71" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="BG71" t="s">
         <v>36</v>
       </c>
       <c r="BH71" t="s">
-        <v>1659</v>
+        <v>1671</v>
       </c>
       <c r="BI71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ71" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="1:62">
-      <c r="A72" s="44" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>10</v>
-      </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>3</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>1</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>-1</v>
-      </c>
-      <c r="AE72">
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <v>10</v>
-      </c>
+      <c r="BK71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:63" ht="14">
+      <c r="A72" s="55" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
       <c r="AG72" t="s">
         <v>36</v>
       </c>
-      <c r="AH72" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI72" s="44" t="s">
-        <v>1363</v>
-      </c>
-      <c r="AJ72" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK72" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AL72" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM72" s="44" t="s">
-        <v>1474</v>
-      </c>
-      <c r="AN72" s="44">
-        <v>1</v>
-      </c>
-      <c r="AO72" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP72" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>1</v>
-      </c>
-      <c r="AT72" t="s">
-        <v>36</v>
-      </c>
-      <c r="AU72">
-        <v>0</v>
-      </c>
-      <c r="AV72" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW72">
-        <v>0</v>
-      </c>
-      <c r="AX72">
-        <v>0</v>
-      </c>
-      <c r="AY72" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ72" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA72" t="s">
-        <v>36</v>
-      </c>
-      <c r="BB72">
-        <v>0</v>
-      </c>
-      <c r="BC72">
-        <v>0</v>
-      </c>
-      <c r="BD72">
-        <v>0</v>
-      </c>
-      <c r="BE72">
-        <v>1</v>
-      </c>
-      <c r="BF72" t="s">
-        <v>1762</v>
-      </c>
-      <c r="BG72" t="s">
-        <v>36</v>
-      </c>
-      <c r="BH72" t="s">
-        <v>1659</v>
-      </c>
       <c r="BI72">
         <v>0</v>
       </c>
@@ -77079,9 +77542,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:62">
+    <row r="73" spans="1:63">
       <c r="A73" s="44" t="s">
-        <v>1897</v>
+        <v>1887</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -77102,10 +77565,10 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -77261,15 +77724,18 @@
         <v>1659</v>
       </c>
       <c r="BI73">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ73" s="46" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="74" spans="1:62">
+        <v>36</v>
+      </c>
+      <c r="BK73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:63">
       <c r="A74" s="44" t="s">
-        <v>1901</v>
+        <v>1888</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -77314,7 +77780,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -77452,12 +77918,15 @@
         <v>0</v>
       </c>
       <c r="BJ74" s="46" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="75" spans="1:62">
+        <v>36</v>
+      </c>
+      <c r="BK74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:63">
       <c r="A75" s="44" t="s">
-        <v>1943</v>
+        <v>1897</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -77640,55 +78109,395 @@
         <v>0</v>
       </c>
       <c r="BJ75" s="46" t="s">
+        <v>1900</v>
+      </c>
+      <c r="BK75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:63">
+      <c r="A76" s="44" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>3</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>1</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>-1</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>10</v>
+      </c>
+      <c r="AG76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI76" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ76" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK76" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL76" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN76" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO76" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP76" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76">
+        <v>0</v>
+      </c>
+      <c r="AS76">
+        <v>1</v>
+      </c>
+      <c r="AT76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU76">
+        <v>0</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW76">
+        <v>0</v>
+      </c>
+      <c r="AX76">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ76" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA76" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB76">
+        <v>0</v>
+      </c>
+      <c r="BC76">
+        <v>0</v>
+      </c>
+      <c r="BD76">
+        <v>0</v>
+      </c>
+      <c r="BE76">
+        <v>1</v>
+      </c>
+      <c r="BF76" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG76" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH76" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI76">
+        <v>0</v>
+      </c>
+      <c r="BJ76" s="46" t="s">
+        <v>1902</v>
+      </c>
+      <c r="BK76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:63">
+      <c r="A77" s="44" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>3</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>1</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>-1</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>10</v>
+      </c>
+      <c r="AG77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI77" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ77" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK77" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL77" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN77" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO77" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP77" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77">
+        <v>0</v>
+      </c>
+      <c r="AS77">
+        <v>1</v>
+      </c>
+      <c r="AT77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU77">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW77">
+        <v>0</v>
+      </c>
+      <c r="AX77">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ77" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA77" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB77">
+        <v>0</v>
+      </c>
+      <c r="BC77">
+        <v>0</v>
+      </c>
+      <c r="BD77">
+        <v>0</v>
+      </c>
+      <c r="BE77">
+        <v>1</v>
+      </c>
+      <c r="BF77" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG77" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH77" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI77">
+        <v>0</v>
+      </c>
+      <c r="BJ77" s="46" t="s">
         <v>1944</v>
       </c>
-    </row>
-    <row r="76" spans="1:62">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="3"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
-      <c r="BJ76" s="46"/>
-    </row>
-    <row r="77" spans="1:62">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-    </row>
-    <row r="78" spans="1:62">
+      <c r="BK77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:63">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -77709,8 +78518,9 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
-    </row>
-    <row r="79" spans="1:62">
+      <c r="BJ78" s="46"/>
+    </row>
+    <row r="79" spans="1:63">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -77732,7 +78542,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
     </row>
-    <row r="80" spans="1:62">
+    <row r="80" spans="1:63">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -78303,6 +79113,50 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
+    </row>
+    <row r="106" spans="1:20">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3"/>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+    </row>
+    <row r="107" spans="1:20">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="3"/>
+      <c r="R107" s="3"/>
+      <c r="S107" s="3"/>
+      <c r="T107" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2372888-1844-4768-8241-AEB409FEAF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFB1DEA-62E5-4025-8A91-D7A78E9228C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="6" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11025" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11025" uniqueCount="2049">
   <si>
     <t>NAME</t>
   </si>
@@ -6231,9 +6231,6 @@
     <t>gold,203</t>
   </si>
   <si>
-    <t>gold,204</t>
-  </si>
-  <si>
     <t>gold,205</t>
   </si>
   <si>
@@ -6319,6 +6316,21 @@
   </si>
   <si>
     <t>buff_all1,100</t>
+  </si>
+  <si>
+    <t>bear_white,1</t>
+  </si>
+  <si>
+    <t>oathbreaker,1</t>
+  </si>
+  <si>
+    <t>ashen_idol,1</t>
+  </si>
+  <si>
+    <t>bloodmoon_guard,1</t>
+  </si>
+  <si>
+    <t>frostborn_helm,1</t>
   </si>
 </sst>
 </file>
@@ -46181,7 +46193,7 @@
         <v>2001</v>
       </c>
       <c r="C26" t="s">
-        <v>2015</v>
+        <v>2044</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
@@ -46228,7 +46240,7 @@
         <v>2001</v>
       </c>
       <c r="C27" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
@@ -46275,7 +46287,7 @@
         <v>2001</v>
       </c>
       <c r="C28" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D28" t="s">
         <v>36</v>
@@ -46322,7 +46334,7 @@
         <v>2001</v>
       </c>
       <c r="C29" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
@@ -46369,7 +46381,7 @@
         <v>2001</v>
       </c>
       <c r="C30" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D30" t="s">
         <v>36</v>
@@ -46416,7 +46428,7 @@
         <v>2001</v>
       </c>
       <c r="C31" t="s">
-        <v>2020</v>
+        <v>2045</v>
       </c>
       <c r="D31" t="s">
         <v>36</v>
@@ -46457,7 +46469,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B32" t="s">
         <v>2001</v>
@@ -46504,7 +46516,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B33" t="s">
         <v>2001</v>
@@ -46551,7 +46563,7 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B34" t="s">
         <v>2001</v>
@@ -46598,7 +46610,7 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B35" t="s">
         <v>2001</v>
@@ -46645,13 +46657,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="s">
         <v>2001</v>
       </c>
       <c r="C36" t="s">
-        <v>2015</v>
+        <v>2046</v>
       </c>
       <c r="D36" t="s">
         <v>36</v>
@@ -46692,13 +46704,13 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B37" t="s">
         <v>2001</v>
       </c>
       <c r="C37" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
@@ -46739,13 +46751,13 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="s">
         <v>2001</v>
       </c>
       <c r="C38" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D38" t="s">
         <v>36</v>
@@ -46786,13 +46798,13 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B39" t="s">
         <v>2001</v>
       </c>
       <c r="C39" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D39" t="s">
         <v>36</v>
@@ -46833,13 +46845,13 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B40" t="s">
         <v>2001</v>
       </c>
       <c r="C40" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D40" t="s">
         <v>36</v>
@@ -46880,13 +46892,13 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B41" t="s">
         <v>2001</v>
       </c>
       <c r="C41" t="s">
-        <v>2020</v>
+        <v>2047</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
@@ -46927,7 +46939,7 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B42" t="s">
         <v>2001</v>
@@ -46974,7 +46986,7 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B43" t="s">
         <v>2001</v>
@@ -47021,7 +47033,7 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B44" t="s">
         <v>2001</v>
@@ -47068,7 +47080,7 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B45" t="s">
         <v>2001</v>
@@ -47115,13 +47127,13 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B46" t="s">
         <v>2001</v>
       </c>
       <c r="C46" t="s">
-        <v>2015</v>
+        <v>2048</v>
       </c>
       <c r="D46" t="s">
         <v>36</v>
@@ -47162,13 +47174,13 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B47" t="s">
         <v>2001</v>
       </c>
       <c r="C47" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D47" t="s">
         <v>36</v>
@@ -47209,13 +47221,13 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B48" t="s">
         <v>2001</v>
       </c>
       <c r="C48" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D48" t="s">
         <v>36</v>
@@ -47256,13 +47268,13 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B49" t="s">
         <v>2001</v>
       </c>
       <c r="C49" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D49" t="s">
         <v>36</v>
@@ -47303,13 +47315,13 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B50" t="s">
         <v>2001</v>
       </c>
       <c r="C50" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D50" t="s">
         <v>36</v>
@@ -47350,13 +47362,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B51" t="s">
         <v>2001</v>
       </c>
       <c r="C51" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D51" t="s">
         <v>36</v>
@@ -56659,7 +56671,7 @@
         <v>1799</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>1804</v>
@@ -63426,7 +63438,7 @@
         <v>821</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D83" s="44" t="s">
         <v>36</v>
@@ -64135,7 +64147,7 @@
         <v>1898</v>
       </c>
       <c r="BK1" s="43" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="BL1" s="43"/>
     </row>
@@ -73500,7 +73512,7 @@
     </row>
     <row r="51" spans="1:63">
       <c r="A51" s="44" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -73599,7 +73611,7 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="AI51" s="44" t="s">
         <v>1479</v>
@@ -73691,7 +73703,7 @@
     </row>
     <row r="52" spans="1:63">
       <c r="A52" s="44" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B52">
         <v>1</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFB1DEA-62E5-4025-8A91-D7A78E9228C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B603E3-97C4-4AB2-80F8-FA477C24C95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="6" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11025" uniqueCount="2049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11054" uniqueCount="2052">
   <si>
     <t>NAME</t>
   </si>
@@ -6186,9 +6186,6 @@
     <t>town_petshop1</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1</t>
-  </si>
-  <si>
     <t>monthly</t>
   </si>
   <si>
@@ -6331,6 +6328,18 @@
   </si>
   <si>
     <t>frostborn_helm,1</t>
+  </si>
+  <si>
+    <t>adorn_res</t>
+  </si>
+  <si>
+    <t>adorn_crit</t>
+  </si>
+  <si>
+    <t>adorn_critdmg</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1#adorn_crit,1#adorn_critdmg,1</t>
   </si>
 </sst>
 </file>
@@ -45999,10 +46008,10 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B22" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C22" t="s">
         <v>1133</v>
@@ -46046,13 +46055,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B23" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C23" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
@@ -46093,13 +46102,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B24" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C24" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D24" t="s">
         <v>36</v>
@@ -46140,13 +46149,13 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B25" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C25" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
@@ -46187,13 +46196,13 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B26" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C26" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
@@ -46234,13 +46243,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B27" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C27" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
@@ -46281,13 +46290,13 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B28" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C28" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D28" t="s">
         <v>36</v>
@@ -46328,13 +46337,13 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B29" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C29" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D29" t="s">
         <v>36</v>
@@ -46375,13 +46384,13 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B30" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C30" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D30" t="s">
         <v>36</v>
@@ -46422,13 +46431,13 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B31" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C31" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D31" t="s">
         <v>36</v>
@@ -46469,10 +46478,10 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B32" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C32" t="s">
         <v>1133</v>
@@ -46516,13 +46525,13 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B33" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C33" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
@@ -46563,13 +46572,13 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C34" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D34" t="s">
         <v>36</v>
@@ -46610,13 +46619,13 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B35" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C35" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D35" t="s">
         <v>36</v>
@@ -46657,13 +46666,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B36" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C36" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D36" t="s">
         <v>36</v>
@@ -46704,13 +46713,13 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C37" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
@@ -46751,13 +46760,13 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B38" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C38" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D38" t="s">
         <v>36</v>
@@ -46798,13 +46807,13 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C39" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D39" t="s">
         <v>36</v>
@@ -46845,13 +46854,13 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B40" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C40" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D40" t="s">
         <v>36</v>
@@ -46892,13 +46901,13 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B41" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C41" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
@@ -46939,10 +46948,10 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B42" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C42" t="s">
         <v>1133</v>
@@ -46986,13 +46995,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B43" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C43" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D43" t="s">
         <v>36</v>
@@ -47033,13 +47042,13 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B44" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C44" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D44" t="s">
         <v>36</v>
@@ -47080,13 +47089,13 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B45" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C45" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D45" t="s">
         <v>36</v>
@@ -47127,13 +47136,13 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B46" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C46" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="D46" t="s">
         <v>36</v>
@@ -47174,13 +47183,13 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B47" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C47" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D47" t="s">
         <v>36</v>
@@ -47221,13 +47230,13 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B48" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C48" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D48" t="s">
         <v>36</v>
@@ -47268,13 +47277,13 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B49" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C49" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D49" t="s">
         <v>36</v>
@@ -47315,13 +47324,13 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B50" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C50" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D50" t="s">
         <v>36</v>
@@ -47362,13 +47371,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B51" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C51" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D51" t="s">
         <v>36</v>
@@ -47476,7 +47485,7 @@
         <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>2000</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -56646,7 +56655,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AD87"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -56661,9 +56670,11 @@
     <col min="26" max="26" width="10.453125" customWidth="1"/>
     <col min="28" max="28" width="11.54296875" customWidth="1"/>
     <col min="30" max="30" width="12.26953125" customWidth="1"/>
+    <col min="31" max="31" width="7.6328125" customWidth="1"/>
+    <col min="32" max="32" width="7.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="13">
+    <row r="1" spans="1:32" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -56671,7 +56682,7 @@
         <v>1799</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>1804</v>
@@ -56754,8 +56765,14 @@
       <c r="AD1" s="43" t="s">
         <v>1874</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="43" t="s">
+        <v>1528</v>
+      </c>
+      <c r="AF1" s="43" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
@@ -56846,8 +56863,14 @@
       <c r="AD2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:30">
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
@@ -56938,8 +56961,14 @@
       <c r="AD3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:30">
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
@@ -57030,8 +57059,14 @@
       <c r="AD4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:30">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5" s="44" t="s">
         <v>1776</v>
       </c>
@@ -57122,8 +57157,14 @@
       <c r="AD5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:30">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
@@ -57214,8 +57255,14 @@
       <c r="AD6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:30">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
@@ -57306,8 +57353,14 @@
       <c r="AD7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:30">
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
@@ -57398,8 +57451,14 @@
       <c r="AD8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:30">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
@@ -57490,8 +57549,14 @@
       <c r="AD9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30">
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
@@ -57582,8 +57647,14 @@
       <c r="AD10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11" s="44" t="s">
         <v>1142</v>
       </c>
@@ -57674,8 +57745,14 @@
       <c r="AD11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:30">
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" s="44" t="s">
         <v>1143</v>
       </c>
@@ -57766,8 +57843,14 @@
       <c r="AD12">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30">
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13" s="44" t="s">
         <v>1458</v>
       </c>
@@ -57858,8 +57941,14 @@
       <c r="AD13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:30">
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" s="44" t="s">
         <v>1459</v>
       </c>
@@ -57950,8 +58039,14 @@
       <c r="AD14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:30">
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15" s="44" t="s">
         <v>1507</v>
       </c>
@@ -58042,8 +58137,14 @@
       <c r="AD15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:30">
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16" s="44" t="s">
         <v>1508</v>
       </c>
@@ -58134,8 +58235,14 @@
       <c r="AD16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:30">
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" s="44" t="s">
         <v>1617</v>
       </c>
@@ -58226,8 +58333,14 @@
       <c r="AD17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:30">
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18" s="44" t="s">
         <v>1625</v>
       </c>
@@ -58318,8 +58431,14 @@
       <c r="AD18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:30">
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19" s="44" t="s">
         <v>1626</v>
       </c>
@@ -58410,8 +58529,14 @@
       <c r="AD19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:30">
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20" s="44" t="s">
         <v>1627</v>
       </c>
@@ -58502,8 +58627,14 @@
       <c r="AD20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:30">
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21" s="44" t="s">
         <v>1146</v>
       </c>
@@ -58594,8 +58725,14 @@
       <c r="AD21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:30">
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22" s="44" t="s">
         <v>1719</v>
       </c>
@@ -58686,8 +58823,14 @@
       <c r="AD22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:30">
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="44" t="s">
         <v>1720</v>
       </c>
@@ -58778,8 +58921,14 @@
       <c r="AD23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:30">
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24" s="44" t="s">
         <v>1721</v>
       </c>
@@ -58870,8 +59019,14 @@
       <c r="AD24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:30">
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25" s="44" t="s">
         <v>1728</v>
       </c>
@@ -58962,8 +59117,14 @@
       <c r="AD25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:30">
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26" s="44" t="s">
         <v>1729</v>
       </c>
@@ -59054,8 +59215,14 @@
       <c r="AD26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:30">
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
       <c r="A27" s="44" t="s">
         <v>1740</v>
       </c>
@@ -59146,8 +59313,14 @@
       <c r="AD27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:30">
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28" s="44" t="s">
         <v>959</v>
       </c>
@@ -59238,8 +59411,14 @@
       <c r="AD28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:30">
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29" s="44" t="s">
         <v>1747</v>
       </c>
@@ -59330,8 +59509,14 @@
       <c r="AD29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:30">
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30" s="44" t="s">
         <v>1777</v>
       </c>
@@ -59422,8 +59607,14 @@
       <c r="AD30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:30">
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31" s="44" t="s">
         <v>1778</v>
       </c>
@@ -59514,8 +59705,14 @@
       <c r="AD31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:30">
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32" s="44" t="s">
         <v>238</v>
       </c>
@@ -59606,8 +59803,14 @@
       <c r="AD32">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:30">
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33" s="44" t="s">
         <v>1801</v>
       </c>
@@ -59698,8 +59901,14 @@
       <c r="AD33">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:30">
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
       <c r="A34" s="44" t="s">
         <v>1808</v>
       </c>
@@ -59790,8 +59999,14 @@
       <c r="AD34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" ht="14">
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" ht="14">
       <c r="A35" s="55" t="s">
         <v>1953</v>
       </c>
@@ -59801,8 +60016,14 @@
       <c r="E35" s="44"/>
       <c r="V35" s="44"/>
       <c r="Y35" s="44"/>
-    </row>
-    <row r="36" spans="1:30">
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32">
       <c r="A36" s="44" t="s">
         <v>1875</v>
       </c>
@@ -59893,8 +60114,14 @@
       <c r="AD36">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:30">
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32">
       <c r="A37" s="44" t="s">
         <v>1877</v>
       </c>
@@ -59985,8 +60212,14 @@
       <c r="AD37">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:30">
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38" s="44" t="s">
         <v>1878</v>
       </c>
@@ -60077,10 +60310,16 @@
       <c r="AD38">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:30">
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39" s="44" t="s">
-        <v>1879</v>
+        <v>2050</v>
       </c>
       <c r="B39" s="44" t="s">
         <v>1876</v>
@@ -60104,7 +60343,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -60169,18 +60408,117 @@
       <c r="AD39">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" ht="14">
-      <c r="A40" s="55" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30">
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32">
+      <c r="A40" s="44" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="44">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>10</v>
+      </c>
+      <c r="V40" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA40">
+        <v>11</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD40">
+        <v>5</v>
+      </c>
+      <c r="AE40">
+        <v>5</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41" s="44" t="s">
-        <v>1948</v>
+        <v>2048</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>818</v>
+        <v>1876</v>
       </c>
       <c r="C41" s="44" t="s">
         <v>36</v>
@@ -60198,7 +60536,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -60216,7 +60554,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -60240,7 +60578,7 @@
         <v>10</v>
       </c>
       <c r="V41" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -60266,13 +60604,19 @@
       <c r="AD41">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:30">
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42" s="44" t="s">
-        <v>1949</v>
+        <v>1879</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>818</v>
+        <v>1876</v>
       </c>
       <c r="C42" s="44" t="s">
         <v>36</v>
@@ -60290,10 +60634,10 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -60332,7 +60676,7 @@
         <v>10</v>
       </c>
       <c r="V42" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -60358,102 +60702,27 @@
       <c r="AD42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:30">
-      <c r="A43" s="44" t="s">
-        <v>1950</v>
-      </c>
-      <c r="B43" s="44" t="s">
-        <v>818</v>
-      </c>
-      <c r="C43" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" s="44">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>100</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>10</v>
-      </c>
-      <c r="V43" s="44" t="s">
-        <v>818</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA43">
-        <v>11</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30">
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" ht="14">
+      <c r="A43" s="55" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32">
       <c r="A44" s="44" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="B44" s="44" t="s">
         <v>818</v>
@@ -60542,10 +60811,16 @@
       <c r="AD44">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:30">
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
       <c r="A45" s="44" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="B45" s="44" t="s">
         <v>818</v>
@@ -60634,18 +60909,117 @@
       <c r="AD45">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:30" ht="14">
-      <c r="A46" s="55" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30">
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32">
+      <c r="A46" s="44" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="44">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>10</v>
+      </c>
+      <c r="V46" s="44" t="s">
+        <v>818</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA46">
+        <v>11</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD46">
+        <v>5</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47" s="44" t="s">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>1802</v>
+        <v>818</v>
       </c>
       <c r="C47" s="44" t="s">
         <v>36</v>
@@ -60705,7 +61079,7 @@
         <v>10</v>
       </c>
       <c r="V47" s="44" t="s">
-        <v>1802</v>
+        <v>818</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -60731,13 +61105,19 @@
       <c r="AD47">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:30">
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48" s="44" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="B48" s="44" t="s">
-        <v>1802</v>
+        <v>818</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>36</v>
@@ -60797,7 +61177,7 @@
         <v>10</v>
       </c>
       <c r="V48" s="44" t="s">
-        <v>1802</v>
+        <v>818</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -60823,102 +61203,27 @@
       <c r="AD48">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:30">
-      <c r="A49" s="44" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B49" s="44" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C49" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" s="44">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>100</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>10</v>
-      </c>
-      <c r="V49" s="44" t="s">
-        <v>1802</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA49">
-        <v>11</v>
-      </c>
-      <c r="AB49" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC49" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30">
+      <c r="AE48">
+        <v>25</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" ht="14">
+      <c r="A49" s="55" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50" s="44" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="B50" s="44" t="s">
         <v>1802</v>
@@ -61007,10 +61312,16 @@
       <c r="AD50">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:30">
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51" s="44" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="B51" s="44" t="s">
         <v>1802</v>
@@ -61099,18 +61410,117 @@
       <c r="AD51">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:30" ht="14">
-      <c r="A52" s="55" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30">
-      <c r="A53" t="s">
-        <v>1962</v>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32">
+      <c r="A52" s="44" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B52" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="44">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>100</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>10</v>
+      </c>
+      <c r="V52" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA52">
+        <v>11</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD52">
+        <v>5</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
+      <c r="A53" s="44" t="s">
+        <v>1959</v>
       </c>
       <c r="B53" s="44" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>36</v>
@@ -61170,7 +61580,7 @@
         <v>10</v>
       </c>
       <c r="V53" s="44" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -61196,13 +61606,19 @@
       <c r="AD53">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:30">
-      <c r="A54" t="s">
-        <v>1963</v>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32">
+      <c r="A54" s="44" t="s">
+        <v>1960</v>
       </c>
       <c r="B54" s="44" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>36</v>
@@ -61262,7 +61678,7 @@
         <v>10</v>
       </c>
       <c r="V54" s="44" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -61288,102 +61704,27 @@
       <c r="AD54">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:30">
-      <c r="A55" s="60" t="s">
-        <v>1964</v>
-      </c>
-      <c r="B55" s="44" t="s">
-        <v>1800</v>
-      </c>
-      <c r="C55" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E55" s="44">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>100</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55">
-        <v>10</v>
-      </c>
-      <c r="V55" s="44" t="s">
-        <v>1800</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-      <c r="X55">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA55">
-        <v>11</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD55">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30">
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32" ht="14">
+      <c r="A55" s="55" t="s">
+        <v>1961</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="B56" s="44" t="s">
         <v>1800</v>
@@ -61472,10 +61813,16 @@
       <c r="AD56">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:30">
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B57" s="44" t="s">
         <v>1800</v>
@@ -61564,18 +61911,117 @@
       <c r="AD57">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:30" ht="14">
-      <c r="A58" s="55" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30">
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32">
+      <c r="A58" s="60" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B58" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C58" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="44">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>100</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>10</v>
+      </c>
+      <c r="V58" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA58">
+        <v>11</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD58">
+        <v>5</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="B59" s="44" t="s">
-        <v>846</v>
+        <v>1800</v>
       </c>
       <c r="C59" s="44" t="s">
         <v>36</v>
@@ -61635,7 +62081,7 @@
         <v>10</v>
       </c>
       <c r="V59" s="44" t="s">
-        <v>1973</v>
+        <v>1800</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -61661,13 +62107,19 @@
       <c r="AD59">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:30">
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="B60" s="44" t="s">
-        <v>846</v>
+        <v>1800</v>
       </c>
       <c r="C60" s="44" t="s">
         <v>36</v>
@@ -61727,7 +62179,7 @@
         <v>10</v>
       </c>
       <c r="V60" s="44" t="s">
-        <v>1973</v>
+        <v>1800</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -61753,102 +62205,27 @@
       <c r="AD60">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:30">
-      <c r="A61" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B61" s="44" t="s">
-        <v>846</v>
-      </c>
-      <c r="C61" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D61" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E61" s="44">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>100</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>10</v>
-      </c>
-      <c r="V61" s="44" t="s">
-        <v>1973</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA61">
-        <v>11</v>
-      </c>
-      <c r="AB61" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC61" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD61">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30">
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32" ht="14">
+      <c r="A61" s="55" t="s">
+        <v>1967</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B62" s="44" t="s">
         <v>846</v>
@@ -61937,10 +62314,16 @@
       <c r="AD62">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:30">
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B63" s="44" t="s">
         <v>846</v>
@@ -62029,18 +62412,117 @@
       <c r="AD63">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:30" ht="14">
-      <c r="A64" s="55" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="65" spans="1:30">
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32">
+      <c r="A64" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B64" s="44" t="s">
+        <v>846</v>
+      </c>
+      <c r="C64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E64" s="44">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>100</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>10</v>
+      </c>
+      <c r="V64" s="44" t="s">
+        <v>1973</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA64">
+        <v>11</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD64">
+        <v>5</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>1987</v>
+        <v>846</v>
       </c>
       <c r="C65" s="44" t="s">
         <v>36</v>
@@ -62100,7 +62582,7 @@
         <v>10</v>
       </c>
       <c r="V65" s="44" t="s">
-        <v>1987</v>
+        <v>1973</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -62126,13 +62608,19 @@
       <c r="AD65">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:30">
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>1987</v>
+        <v>846</v>
       </c>
       <c r="C66" s="44" t="s">
         <v>36</v>
@@ -62192,7 +62680,7 @@
         <v>10</v>
       </c>
       <c r="V66" s="44" t="s">
-        <v>1987</v>
+        <v>1973</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -62218,102 +62706,27 @@
       <c r="AD66">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:30">
-      <c r="A67" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B67" s="44" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C67" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E67" s="44">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>100</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>10</v>
-      </c>
-      <c r="V67" s="44" t="s">
-        <v>1987</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA67">
-        <v>11</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC67" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD67">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:30">
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" ht="14">
+      <c r="A67" s="55" t="s">
+        <v>1974</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="B68" s="44" t="s">
         <v>1987</v>
@@ -62402,10 +62815,16 @@
       <c r="AD68">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:30">
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="B69" s="44" t="s">
         <v>1987</v>
@@ -62494,18 +62913,117 @@
       <c r="AD69">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:30" ht="14">
-      <c r="A70" s="55" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="71" spans="1:30">
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:32">
+      <c r="A70" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B70" s="44" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C70" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E70" s="44">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>100</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>10</v>
+      </c>
+      <c r="V70" s="44" t="s">
+        <v>1987</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA70">
+        <v>11</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD70">
+        <v>5</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="B71" s="44" t="s">
-        <v>833</v>
+        <v>1987</v>
       </c>
       <c r="C71" s="44" t="s">
         <v>36</v>
@@ -62565,7 +63083,7 @@
         <v>10</v>
       </c>
       <c r="V71" s="44" t="s">
-        <v>833</v>
+        <v>1987</v>
       </c>
       <c r="W71">
         <v>0</v>
@@ -62591,13 +63109,19 @@
       <c r="AD71">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:30">
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="B72" s="44" t="s">
-        <v>833</v>
+        <v>1987</v>
       </c>
       <c r="C72" s="44" t="s">
         <v>36</v>
@@ -62657,7 +63181,7 @@
         <v>10</v>
       </c>
       <c r="V72" s="44" t="s">
-        <v>833</v>
+        <v>1987</v>
       </c>
       <c r="W72">
         <v>0</v>
@@ -62683,102 +63207,23 @@
       <c r="AD72">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:30">
-      <c r="A73" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B73" s="44" t="s">
-        <v>833</v>
-      </c>
-      <c r="C73" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E73" s="44">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>100</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73">
-        <v>0</v>
-      </c>
-      <c r="U73">
-        <v>10</v>
-      </c>
-      <c r="V73" s="44" t="s">
-        <v>833</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>1</v>
-      </c>
-      <c r="Y73" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA73">
-        <v>11</v>
-      </c>
-      <c r="AB73" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC73" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD73">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:30">
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" ht="14">
+      <c r="A73" s="55" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AE73" s="3"/>
+      <c r="AF73" s="3"/>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="B74" s="44" t="s">
         <v>833</v>
@@ -62867,10 +63312,16 @@
       <c r="AD74">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:30">
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="B75" s="44" t="s">
         <v>833</v>
@@ -62959,18 +63410,117 @@
       <c r="AD75">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:30" ht="14">
-      <c r="A76" s="55" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="77" spans="1:30">
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32">
+      <c r="A76" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B76" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="C76" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" s="44">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>100</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>10</v>
+      </c>
+      <c r="V76" s="44" t="s">
+        <v>833</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA76">
+        <v>11</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD76">
+        <v>5</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="B77" s="44" t="s">
-        <v>1079</v>
+        <v>833</v>
       </c>
       <c r="C77" s="44" t="s">
         <v>36</v>
@@ -63030,7 +63580,7 @@
         <v>10</v>
       </c>
       <c r="V77" s="44" t="s">
-        <v>1079</v>
+        <v>833</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -63056,13 +63606,19 @@
       <c r="AD77">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:30">
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="B78" s="44" t="s">
-        <v>1079</v>
+        <v>833</v>
       </c>
       <c r="C78" s="44" t="s">
         <v>36</v>
@@ -63122,7 +63678,7 @@
         <v>10</v>
       </c>
       <c r="V78" s="44" t="s">
-        <v>1079</v>
+        <v>833</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -63148,102 +63704,23 @@
       <c r="AD78">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:30">
-      <c r="A79" t="s">
-        <v>1991</v>
-      </c>
-      <c r="B79" s="44" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C79" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D79" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E79" s="44">
-        <v>1</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79">
-        <v>100</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>10</v>
-      </c>
-      <c r="V79" s="44" t="s">
-        <v>1079</v>
-      </c>
-      <c r="W79">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA79">
-        <v>11</v>
-      </c>
-      <c r="AB79" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC79" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD79">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:30">
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32" ht="14">
+      <c r="A79" s="55" t="s">
+        <v>1986</v>
+      </c>
+      <c r="AE79" s="3"/>
+      <c r="AF79" s="3"/>
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="B80" s="44" t="s">
         <v>1079</v>
@@ -63332,10 +63809,12 @@
       <c r="AD80">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:30">
+      <c r="AE80" s="3"/>
+      <c r="AF80" s="3"/>
+    </row>
+    <row r="81" spans="1:32">
       <c r="A81" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="B81" s="44" t="s">
         <v>1079</v>
@@ -63424,21 +63903,112 @@
       <c r="AD81">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:30" ht="14">
-      <c r="A82" s="55" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="83" spans="1:30">
+      <c r="AE81" s="3"/>
+      <c r="AF81" s="3"/>
+    </row>
+    <row r="82" spans="1:32">
+      <c r="A82" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C82" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E82" s="44">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>100</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>10</v>
+      </c>
+      <c r="V82" s="44" t="s">
+        <v>1079</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA82">
+        <v>11</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD82">
+        <v>5</v>
+      </c>
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="1:32">
       <c r="A83" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B83" s="44" t="s">
-        <v>821</v>
+        <v>1079</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>2041</v>
+        <v>36</v>
       </c>
       <c r="D83" s="44" t="s">
         <v>36</v>
@@ -63495,7 +64065,7 @@
         <v>10</v>
       </c>
       <c r="V83" s="44" t="s">
-        <v>821</v>
+        <v>1079</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -63521,13 +64091,15 @@
       <c r="AD83">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:30">
+      <c r="AE83" s="3"/>
+      <c r="AF83" s="3"/>
+    </row>
+    <row r="84" spans="1:32">
       <c r="A84" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B84" s="44" t="s">
-        <v>821</v>
+        <v>1079</v>
       </c>
       <c r="C84" s="44" t="s">
         <v>36</v>
@@ -63587,7 +64159,7 @@
         <v>10</v>
       </c>
       <c r="V84" s="44" t="s">
-        <v>821</v>
+        <v>1079</v>
       </c>
       <c r="W84">
         <v>0</v>
@@ -63613,108 +64185,25 @@
       <c r="AD84">
         <v>5</v>
       </c>
-    </row>
-    <row r="85" spans="1:30">
-      <c r="A85" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B85" s="44" t="s">
-        <v>821</v>
-      </c>
-      <c r="C85" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D85" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E85" s="44">
-        <v>1</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>100</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-      <c r="S85">
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>10</v>
-      </c>
-      <c r="V85" s="44" t="s">
-        <v>821</v>
-      </c>
-      <c r="W85">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="Y85" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA85">
-        <v>11</v>
-      </c>
-      <c r="AB85" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AC85" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD85">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:30">
+      <c r="AE84" s="3"/>
+      <c r="AF84" s="3"/>
+    </row>
+    <row r="85" spans="1:32" ht="14">
+      <c r="A85" s="55" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AE85" s="3"/>
+      <c r="AF85" s="3"/>
+    </row>
+    <row r="86" spans="1:32">
       <c r="A86" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="B86" s="44" t="s">
         <v>821</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>36</v>
+        <v>2040</v>
       </c>
       <c r="D86" s="44" t="s">
         <v>36</v>
@@ -63797,10 +64286,12 @@
       <c r="AD86">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:30">
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+    </row>
+    <row r="87" spans="1:32">
       <c r="A87" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="B87" s="44" t="s">
         <v>821</v>
@@ -63889,6 +64380,362 @@
       <c r="AD87">
         <v>5</v>
       </c>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+    </row>
+    <row r="88" spans="1:32">
+      <c r="A88" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B88" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E88" s="44">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>100</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88">
+        <v>10</v>
+      </c>
+      <c r="V88" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA88">
+        <v>11</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD88">
+        <v>5</v>
+      </c>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
+    </row>
+    <row r="89" spans="1:32">
+      <c r="A89" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" s="44">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>100</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>10</v>
+      </c>
+      <c r="V89" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA89">
+        <v>11</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD89">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
+    </row>
+    <row r="90" spans="1:32">
+      <c r="A90" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B90" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="C90" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="44">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>100</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>10</v>
+      </c>
+      <c r="V90" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA90">
+        <v>11</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD90">
+        <v>5</v>
+      </c>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="1:32">
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
+    </row>
+    <row r="92" spans="1:32">
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
+    </row>
+    <row r="93" spans="1:32">
+      <c r="AE93" s="3"/>
+      <c r="AF93" s="3"/>
+    </row>
+    <row r="94" spans="1:32">
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
+    </row>
+    <row r="95" spans="1:32">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="1:32">
+      <c r="AE96" s="3"/>
+      <c r="AF96" s="3"/>
+    </row>
+    <row r="97" spans="31:32">
+      <c r="AE97" s="3"/>
+      <c r="AF97" s="3"/>
+    </row>
+    <row r="98" spans="31:32">
+      <c r="AE98" s="3"/>
+      <c r="AF98" s="3"/>
+    </row>
+    <row r="99" spans="31:32">
+      <c r="AE99" s="3"/>
+      <c r="AF99" s="3"/>
+    </row>
+    <row r="100" spans="31:32">
+      <c r="AE100" s="3"/>
+      <c r="AF100" s="3"/>
+    </row>
+    <row r="101" spans="31:32">
+      <c r="AE101" s="3"/>
+      <c r="AF101" s="3"/>
+    </row>
+    <row r="102" spans="31:32">
+      <c r="AE102" s="3"/>
+      <c r="AF102" s="3"/>
+    </row>
+    <row r="103" spans="31:32">
+      <c r="AE103" s="3"/>
+      <c r="AF103" s="3"/>
+    </row>
+    <row r="104" spans="31:32">
+      <c r="AE104" s="3"/>
+      <c r="AF104" s="3"/>
+    </row>
+    <row r="105" spans="31:32">
+      <c r="AE105" s="3"/>
+      <c r="AF105" s="3"/>
+    </row>
+    <row r="106" spans="31:32">
+      <c r="AE106" s="3"/>
+      <c r="AF106" s="3"/>
+    </row>
+    <row r="107" spans="31:32">
+      <c r="AE107" s="3"/>
+      <c r="AF107" s="3"/>
+    </row>
+    <row r="108" spans="31:32">
+      <c r="AE108" s="3"/>
+      <c r="AF108" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -64147,7 +64994,7 @@
         <v>1898</v>
       </c>
       <c r="BK1" s="43" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="BL1" s="43"/>
     </row>
@@ -73512,7 +74359,7 @@
     </row>
     <row r="51" spans="1:63">
       <c r="A51" s="44" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -73611,7 +74458,7 @@
         <v>36</v>
       </c>
       <c r="AH51" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="AI51" s="44" t="s">
         <v>1479</v>
@@ -73703,7 +74550,7 @@
     </row>
     <row r="52" spans="1:63">
       <c r="A52" s="44" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B52">
         <v>1</v>
